--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1614</v>
+        <v>1389</v>
       </c>
       <c r="D2" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E2" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1610</v>
+        <v>1386</v>
       </c>
       <c r="D3" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="E3" t="n">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
       <c r="F3" t="n">
         <v>47.5</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -570,23 +570,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1552</v>
+        <v>1387</v>
       </c>
       <c r="D4" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="E4" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1614</v>
+        <v>1391</v>
       </c>
       <c r="D5" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
       <c r="E5" t="n">
-        <v>52.4</v>
+        <v>53.3</v>
       </c>
       <c r="F5" t="n">
-        <v>53.8</v>
+        <v>53.1</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1612</v>
+        <v>1332</v>
       </c>
       <c r="D6" t="n">
-        <v>48.8</v>
+        <v>49.9</v>
       </c>
       <c r="E6" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="F6" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1585</v>
+        <v>1364</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="F7" t="n">
-        <v>54.6</v>
+        <v>54</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1600</v>
+        <v>1375</v>
       </c>
       <c r="D8" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E8" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F8" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1611</v>
+        <v>1390</v>
       </c>
       <c r="D9" t="n">
-        <v>48.5</v>
+        <v>47.9</v>
       </c>
       <c r="E9" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="F9" t="n">
-        <v>56.7</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1585</v>
+        <v>1361</v>
       </c>
       <c r="D10" t="n">
         <v>51.7</v>
@@ -817,10 +817,10 @@
         <v>48.3</v>
       </c>
       <c r="F10" t="n">
-        <v>41.8</v>
+        <v>43.1</v>
       </c>
       <c r="G10" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1581</v>
+        <v>1359</v>
       </c>
       <c r="D11" t="n">
         <v>51.4</v>
@@ -856,10 +856,10 @@
         <v>48.6</v>
       </c>
       <c r="F11" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="G11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1587</v>
+        <v>1362</v>
       </c>
       <c r="D12" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="E12" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="F12" t="n">
-        <v>39.7</v>
+        <v>40.1</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1612</v>
+        <v>1388</v>
       </c>
       <c r="D13" t="n">
         <v>49.7</v>
@@ -934,10 +934,10 @@
         <v>50.3</v>
       </c>
       <c r="F13" t="n">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="G13" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -960,23 +960,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1595</v>
+        <v>1371</v>
       </c>
       <c r="D14" t="n">
-        <v>50.9</v>
+        <v>49.2</v>
       </c>
       <c r="E14" t="n">
-        <v>49.1</v>
+        <v>50.8</v>
       </c>
       <c r="F14" t="n">
-        <v>35.8</v>
+        <v>63.7</v>
       </c>
       <c r="G14" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15">
@@ -999,23 +999,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1592</v>
+        <v>1375</v>
       </c>
       <c r="D15" t="n">
-        <v>49.9</v>
+        <v>51.7</v>
       </c>
       <c r="E15" t="n">
-        <v>50.1</v>
+        <v>48.3</v>
       </c>
       <c r="F15" t="n">
-        <v>64.8</v>
+        <v>36.2</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8</v>
+        <v>13.8</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>87</v>
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1589</v>
+        <v>1365</v>
       </c>
       <c r="D16" t="n">
-        <v>48.6</v>
+        <v>47.3</v>
       </c>
       <c r="E16" t="n">
-        <v>51.4</v>
+        <v>52.7</v>
       </c>
       <c r="F16" t="n">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G16" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1077,23 +1077,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1568</v>
+        <v>1352</v>
       </c>
       <c r="D17" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
       <c r="E17" t="n">
-        <v>50.2</v>
+        <v>48.7</v>
       </c>
       <c r="F17" t="n">
-        <v>49.9</v>
+        <v>50.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1116,23 +1116,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1617</v>
+        <v>1348</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>49.3</v>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>50.7</v>
       </c>
       <c r="F18" t="n">
-        <v>50.3</v>
+        <v>51.1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>EURNOK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1569</v>
+        <v>1271</v>
       </c>
       <c r="D19" t="n">
-        <v>50.5</v>
+        <v>48.8</v>
       </c>
       <c r="E19" t="n">
-        <v>49.5</v>
+        <v>51.2</v>
       </c>
       <c r="F19" t="n">
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EURNOK</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1505</v>
+        <v>1393</v>
       </c>
       <c r="D20" t="n">
-        <v>49.4</v>
+        <v>47.1</v>
       </c>
       <c r="E20" t="n">
-        <v>50.6</v>
+        <v>52.9</v>
       </c>
       <c r="F20" t="n">
-        <v>48.2</v>
+        <v>51.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>462</v>
+        <v>382</v>
       </c>
       <c r="D21" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>51.9</v>
+        <v>52.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1589</v>
+        <v>1375</v>
       </c>
       <c r="D22" t="n">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="E22" t="n">
-        <v>48.7</v>
+        <v>50.4</v>
       </c>
       <c r="F22" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1311,23 +1311,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1608</v>
+        <v>1361</v>
       </c>
       <c r="D23" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
-        <v>49.5</v>
+        <v>54</v>
       </c>
       <c r="F23" t="n">
-        <v>54.4</v>
+        <v>54.1</v>
       </c>
       <c r="G23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1350,23 +1350,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1599</v>
+        <v>1383</v>
       </c>
       <c r="D24" t="n">
-        <v>49.3</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
-        <v>50.7</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>45.4</v>
+        <v>54.4</v>
       </c>
       <c r="G24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25">
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1580</v>
+        <v>1382</v>
       </c>
       <c r="D25" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E25" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F25" t="n">
-        <v>54.8</v>
+        <v>44.9</v>
       </c>
       <c r="G25" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1609</v>
+        <v>1368</v>
       </c>
       <c r="D26" t="n">
-        <v>51.2</v>
+        <v>52.1</v>
       </c>
       <c r="E26" t="n">
-        <v>48.8</v>
+        <v>47.9</v>
       </c>
       <c r="F26" t="n">
-        <v>45.1</v>
+        <v>44.4</v>
       </c>
       <c r="G26" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1467,23 +1467,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1581</v>
+        <v>1355</v>
       </c>
       <c r="D27" t="n">
-        <v>46.3</v>
+        <v>52.3</v>
       </c>
       <c r="E27" t="n">
-        <v>53.7</v>
+        <v>47.7</v>
       </c>
       <c r="F27" t="n">
-        <v>55.3</v>
+        <v>55.7</v>
       </c>
       <c r="G27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1618</v>
+        <v>1393</v>
       </c>
       <c r="D28" t="n">
-        <v>48.2</v>
+        <v>47.7</v>
       </c>
       <c r="E28" t="n">
-        <v>51.8</v>
+        <v>52.3</v>
       </c>
       <c r="F28" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -1545,23 +1545,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1611</v>
+        <v>1376</v>
       </c>
       <c r="D29" t="n">
-        <v>47.1</v>
+        <v>48</v>
       </c>
       <c r="E29" t="n">
-        <v>52.9</v>
+        <v>52</v>
       </c>
       <c r="F29" t="n">
-        <v>43.9</v>
+        <v>56.6</v>
       </c>
       <c r="G29" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1607</v>
+        <v>1386</v>
       </c>
       <c r="D30" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="E30" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
       <c r="F30" t="n">
-        <v>56.3</v>
+        <v>56.6</v>
       </c>
       <c r="G30" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1606</v>
+        <v>1386</v>
       </c>
       <c r="D31" t="n">
-        <v>49.3</v>
+        <v>47.4</v>
       </c>
       <c r="E31" t="n">
-        <v>50.7</v>
+        <v>52.6</v>
       </c>
       <c r="F31" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="G31" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -1662,23 +1662,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1598</v>
+        <v>1273</v>
       </c>
       <c r="D32" t="n">
-        <v>48</v>
+        <v>49.3</v>
       </c>
       <c r="E32" t="n">
-        <v>52</v>
+        <v>50.7</v>
       </c>
       <c r="F32" t="n">
-        <v>57.1</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -1701,23 +1701,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1507</v>
+        <v>1384</v>
       </c>
       <c r="D33" t="n">
-        <v>48.9</v>
+        <v>49.6</v>
       </c>
       <c r="E33" t="n">
-        <v>51.1</v>
+        <v>50.4</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>39</v>
@@ -1740,17 +1740,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1456</v>
+        <v>1382</v>
       </c>
       <c r="D34" t="n">
-        <v>48.1</v>
+        <v>45.4</v>
       </c>
       <c r="E34" t="n">
-        <v>51.9</v>
+        <v>54.6</v>
       </c>
       <c r="F34" t="n">
         <v>58.9</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35">
@@ -1779,23 +1779,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1602</v>
+        <v>1263</v>
       </c>
       <c r="D35" t="n">
-        <v>46.4</v>
+        <v>47.4</v>
       </c>
       <c r="E35" t="n">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
       <c r="F35" t="n">
-        <v>59.2</v>
+        <v>58.9</v>
       </c>
       <c r="G35" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36">
@@ -1818,23 +1818,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EURAUD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1602</v>
+        <v>1369</v>
       </c>
       <c r="D36" t="n">
-        <v>48.3</v>
+        <v>49.6</v>
       </c>
       <c r="E36" t="n">
-        <v>51.7</v>
+        <v>50.4</v>
       </c>
       <c r="F36" t="n">
-        <v>40.6</v>
+        <v>59.5</v>
       </c>
       <c r="G36" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>EURAUD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1610</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="n">
-        <v>48.2</v>
+        <v>47</v>
       </c>
       <c r="E37" t="n">
-        <v>51.8</v>
+        <v>53</v>
       </c>
       <c r="F37" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="G37" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1589</v>
+        <v>1370</v>
       </c>
       <c r="D38" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E38" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F38" t="n">
         <v>59.8</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39">
@@ -1935,23 +1935,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUDCAD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1594</v>
+        <v>1383</v>
       </c>
       <c r="D39" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E39" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F39" t="n">
-        <v>60.7</v>
+        <v>39.6</v>
       </c>
       <c r="G39" t="n">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1617</v>
+        <v>1391</v>
       </c>
       <c r="D40" t="n">
-        <v>49.6</v>
+        <v>49.9</v>
       </c>
       <c r="E40" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
       <c r="F40" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="G40" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1623</v>
+        <v>1397</v>
       </c>
       <c r="D41" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E41" t="n">
         <v>49.9</v>
       </c>
-      <c r="E41" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F41" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="G41" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="42">
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1580</v>
+        <v>1378</v>
       </c>
       <c r="D42" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="E42" t="n">
-        <v>49.5</v>
+        <v>52</v>
       </c>
       <c r="F42" t="n">
-        <v>62.1</v>
+        <v>38.1</v>
       </c>
       <c r="G42" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>71</v>
@@ -2091,23 +2091,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1636</v>
+        <v>1360</v>
       </c>
       <c r="D43" t="n">
-        <v>47.9</v>
+        <v>51.2</v>
       </c>
       <c r="E43" t="n">
-        <v>52.1</v>
+        <v>48.8</v>
       </c>
       <c r="F43" t="n">
-        <v>37.5</v>
+        <v>62.1</v>
       </c>
       <c r="G43" t="n">
-        <v>12.5</v>
+        <v>12.1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44">
@@ -2130,23 +2130,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1622</v>
+        <v>1391</v>
       </c>
       <c r="D44" t="n">
-        <v>51.2</v>
+        <v>49.8</v>
       </c>
       <c r="E44" t="n">
-        <v>48.8</v>
+        <v>50.2</v>
       </c>
       <c r="F44" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="G44" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="45">
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1617</v>
+        <v>1269</v>
       </c>
       <c r="D45" t="n">
-        <v>49.4</v>
+        <v>51.1</v>
       </c>
       <c r="E45" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
       </c>
       <c r="F45" t="n">
         <v>37.2</v>
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1647</v>
+        <v>1387</v>
       </c>
       <c r="D46" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E46" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>36.5</v>
+        <v>37.1</v>
       </c>
       <c r="G46" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="47">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1620</v>
+        <v>1397</v>
       </c>
       <c r="D47" t="n">
-        <v>50.4</v>
+        <v>51.5</v>
       </c>
       <c r="E47" t="n">
-        <v>49.6</v>
+        <v>48.5</v>
       </c>
       <c r="F47" t="n">
-        <v>36.3</v>
+        <v>36.9</v>
       </c>
       <c r="G47" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="J47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
@@ -2286,23 +2286,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1501</v>
+        <v>1395</v>
       </c>
       <c r="D48" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="E48" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="F48" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="G48" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1583</v>
+        <v>1394</v>
       </c>
       <c r="D49" t="n">
-        <v>48.1</v>
+        <v>49.1</v>
       </c>
       <c r="E49" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="F49" t="n">
-        <v>34.6</v>
+        <v>35.4</v>
       </c>
       <c r="G49" t="n">
-        <v>15.4</v>
+        <v>14.6</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1621</v>
+        <v>1361</v>
       </c>
       <c r="D50" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E50" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F50" t="n">
-        <v>34.4</v>
+        <v>35.3</v>
       </c>
       <c r="G50" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1591</v>
+        <v>1371</v>
       </c>
       <c r="D51" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E51" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F51" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
       <c r="G51" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="52">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1594</v>
+        <v>1371</v>
       </c>
       <c r="D52" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="E52" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="F52" t="n">
-        <v>67.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G52" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1622</v>
+        <v>1396</v>
       </c>
       <c r="D53" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E53" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F53" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="G53" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1513</v>
+        <v>1300</v>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F54" t="n">
-        <v>30.6</v>
+        <v>31.5</v>
       </c>
       <c r="G54" t="n">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1613</v>
+        <v>1386</v>
       </c>
       <c r="D55" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>70.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1600</v>
+        <v>1376</v>
       </c>
       <c r="D56" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
-        <v>75.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="G56" t="n">
-        <v>25.6</v>
+        <v>24.8</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1617</v>
+        <v>1392</v>
       </c>
       <c r="D57" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E57" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F57" t="n">
-        <v>82</v>
+        <v>82.3</v>
       </c>
       <c r="G57" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1617</v>
+        <v>1394</v>
       </c>
       <c r="D58" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E58" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F58" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="G58" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1619</v>
+        <v>1394</v>
       </c>
       <c r="D59" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="E59" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="F59" t="n">
-        <v>93.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>43.9</v>
+        <v>44.4</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1611</v>
+        <v>1298</v>
       </c>
       <c r="D60" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="E60" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
       <c r="F60" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="G60" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1526</v>
+        <v>1431</v>
       </c>
       <c r="D61" t="n">
-        <v>51.4</v>
+        <v>50.2</v>
       </c>
       <c r="E61" t="n">
-        <v>48.6</v>
+        <v>49.8</v>
       </c>
       <c r="F61" t="n">
-        <v>42.3</v>
+        <v>42.8</v>
       </c>
       <c r="G61" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
@@ -2832,23 +2832,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1003</v>
+        <v>863</v>
       </c>
       <c r="D62" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
       <c r="E62" t="n">
-        <v>50.9</v>
+        <v>51.9</v>
       </c>
       <c r="F62" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="G62" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63">
@@ -2871,23 +2871,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1018</v>
+        <v>874</v>
       </c>
       <c r="D63" t="n">
-        <v>52.6</v>
+        <v>49.4</v>
       </c>
       <c r="E63" t="n">
-        <v>47.4</v>
+        <v>50.6</v>
       </c>
       <c r="F63" t="n">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="G63" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64">
@@ -2910,23 +2910,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>998</v>
+        <v>886</v>
       </c>
       <c r="D64" t="n">
-        <v>50.4</v>
+        <v>53.3</v>
       </c>
       <c r="E64" t="n">
-        <v>49.6</v>
+        <v>46.7</v>
       </c>
       <c r="F64" t="n">
-        <v>58.5</v>
+        <v>59.1</v>
       </c>
       <c r="G64" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65">
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>997</v>
+        <v>868</v>
       </c>
       <c r="D65" t="n">
-        <v>47.5</v>
+        <v>52</v>
       </c>
       <c r="E65" t="n">
-        <v>52.5</v>
+        <v>48</v>
       </c>
       <c r="F65" t="n">
-        <v>58.6</v>
+        <v>59.3</v>
       </c>
       <c r="G65" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66">
@@ -2992,19 +2992,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1502</v>
+        <v>1245</v>
       </c>
       <c r="D66" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="E66" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="F66" t="n">
-        <v>59.5</v>
+        <v>59.3</v>
       </c>
       <c r="G66" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67">
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1619</v>
+        <v>1360</v>
       </c>
       <c r="D67" t="n">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
       <c r="E67" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="F67" t="n">
         <v>61.5</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="68">
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1646</v>
+        <v>1389</v>
       </c>
       <c r="D68" t="n">
-        <v>49.8</v>
+        <v>50.8</v>
       </c>
       <c r="E68" t="n">
-        <v>50.2</v>
+        <v>49.2</v>
       </c>
       <c r="F68" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
       <c r="G68" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1437</v>
+        <v>1007</v>
       </c>
       <c r="D69" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="E69" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="F69" t="n">
-        <v>62.1</v>
+        <v>62.4</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70">
@@ -3144,23 +3144,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1594</v>
+        <v>1211</v>
       </c>
       <c r="D70" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="E70" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="F70" t="n">
-        <v>62.4</v>
+        <v>62.8</v>
       </c>
       <c r="G70" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1619</v>
+        <v>1371</v>
       </c>
       <c r="D71" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="E71" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="F71" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="G71" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="72">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1169</v>
+        <v>1434</v>
       </c>
       <c r="D72" t="n">
-        <v>49</v>
+        <v>49.9</v>
       </c>
       <c r="E72" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
       <c r="F72" t="n">
-        <v>63.1</v>
+        <v>63.7</v>
       </c>
       <c r="G72" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1441</v>
+        <v>1207</v>
       </c>
       <c r="D73" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="E73" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="F73" t="n">
-        <v>66.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G73" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -3300,17 +3300,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="D74" t="n">
-        <v>49.5</v>
+        <v>50.2</v>
       </c>
       <c r="E74" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
       <c r="F74" t="n">
         <v>53.1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>633</v>
+        <v>526</v>
       </c>
       <c r="D75" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="E75" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="F75" t="n">
-        <v>53.2</v>
+        <v>54.4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
@@ -3378,23 +3378,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>638</v>
+        <v>520</v>
       </c>
       <c r="D76" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E76" t="n">
         <v>49.8</v>
       </c>
-      <c r="E76" t="n">
-        <v>50.2</v>
-      </c>
       <c r="F76" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="G76" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1219</v>
+        <v>1022</v>
       </c>
       <c r="D77" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="E77" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="F77" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G77" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1545</v>
+        <v>1301</v>
       </c>
       <c r="D78" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="E78" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
       <c r="F78" t="n">
-        <v>71.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="G78" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>615</v>
+        <v>510</v>
       </c>
       <c r="D79" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="E79" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
       <c r="F79" t="n">
-        <v>58.7</v>
+        <v>57.6</v>
       </c>
       <c r="G79" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1251</v>
+        <v>1069</v>
       </c>
       <c r="D80" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="F80" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
       <c r="G80" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1201</v>
+        <v>1001</v>
       </c>
       <c r="D81" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="F81" t="n">
-        <v>63.5</v>
+        <v>63</v>
       </c>
       <c r="G81" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>437</v>
+        <v>360</v>
       </c>
       <c r="D82" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E82" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="F82" t="n">
-        <v>50.8</v>
+        <v>49.4</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3655,19 +3655,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>441</v>
+        <v>368</v>
       </c>
       <c r="D83" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="E83" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="F83" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>417</v>
+        <v>368</v>
       </c>
       <c r="D84" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>51.9</v>
       </c>
       <c r="F84" t="n">
-        <v>48.9</v>
+        <v>51.1</v>
       </c>
       <c r="G84" t="n">
         <v>1.1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
@@ -3729,23 +3729,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>434</v>
+        <v>382</v>
       </c>
       <c r="D85" t="n">
-        <v>50.5</v>
+        <v>47.1</v>
       </c>
       <c r="E85" t="n">
-        <v>49.5</v>
+        <v>52.9</v>
       </c>
       <c r="F85" t="n">
-        <v>54.1</v>
+        <v>55.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
@@ -3768,23 +3768,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>435</v>
+        <v>364</v>
       </c>
       <c r="D86" t="n">
-        <v>48.3</v>
+        <v>52.2</v>
       </c>
       <c r="E86" t="n">
-        <v>51.7</v>
+        <v>47.8</v>
       </c>
       <c r="F86" t="n">
-        <v>54.7</v>
+        <v>56.3</v>
       </c>
       <c r="G86" t="n">
-        <v>4.7</v>
+        <v>6.3</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87">
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="D87" t="n">
-        <v>48.5</v>
+        <v>46.8</v>
       </c>
       <c r="E87" t="n">
-        <v>51.5</v>
+        <v>53.2</v>
       </c>
       <c r="F87" t="n">
-        <v>56.5</v>
+        <v>57.3</v>
       </c>
       <c r="G87" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="88">
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>433</v>
+        <v>380</v>
       </c>
       <c r="D88" t="n">
         <v>50.3</v>
@@ -3859,10 +3859,10 @@
         <v>49.7</v>
       </c>
       <c r="F88" t="n">
-        <v>60.3</v>
+        <v>60.5</v>
       </c>
       <c r="G88" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89">
@@ -3885,23 +3885,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="D89" t="n">
-        <v>47.2</v>
+        <v>50.6</v>
       </c>
       <c r="E89" t="n">
-        <v>52.8</v>
+        <v>49.4</v>
       </c>
       <c r="F89" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="G89" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="90">
@@ -3924,23 +3924,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>463</v>
+        <v>384</v>
       </c>
       <c r="D90" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
       <c r="E90" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="F90" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
       <c r="G90" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>431</v>
+        <v>390</v>
       </c>
       <c r="D91" t="n">
-        <v>49.4</v>
+        <v>51.8</v>
       </c>
       <c r="E91" t="n">
-        <v>50.6</v>
+        <v>48.2</v>
       </c>
       <c r="F91" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="G91" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="92">
@@ -4002,11 +4002,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>468</v>
+        <v>378</v>
       </c>
       <c r="D92" t="n">
         <v>51.1</v>
@@ -4015,10 +4015,10 @@
         <v>48.9</v>
       </c>
       <c r="F92" t="n">
-        <v>62.8</v>
+        <v>62.4</v>
       </c>
       <c r="G92" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>406</v>
+        <v>353</v>
       </c>
       <c r="D93" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="E93" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="F93" t="n">
-        <v>71.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4080,23 +4080,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1620</v>
+        <v>1237</v>
       </c>
       <c r="D94" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="G94" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95">
@@ -4119,23 +4119,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1568</v>
+        <v>1396</v>
       </c>
       <c r="D95" t="n">
-        <v>51.3</v>
+        <v>49.3</v>
       </c>
       <c r="E95" t="n">
-        <v>48.7</v>
+        <v>50.7</v>
       </c>
       <c r="F95" t="n">
-        <v>58.1</v>
+        <v>58.6</v>
       </c>
       <c r="G95" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1417</v>
+        <v>1356</v>
       </c>
       <c r="D96" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E96" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F96" t="n">
-        <v>58.2</v>
+        <v>58.9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1623</v>
+        <v>1397</v>
       </c>
       <c r="D97" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E97" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F97" t="n">
-        <v>58.9</v>
+        <v>59.6</v>
       </c>
       <c r="G97" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1622</v>
+        <v>1397</v>
       </c>
       <c r="D98" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="E98" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="F98" t="n">
-        <v>59.2</v>
+        <v>59.7</v>
       </c>
       <c r="G98" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="99">
@@ -4275,23 +4275,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1623</v>
+        <v>1347</v>
       </c>
       <c r="D99" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E99" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F99" t="n">
-        <v>59.2</v>
+        <v>60.4</v>
       </c>
       <c r="G99" t="n">
-        <v>9.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="100">
@@ -4314,23 +4314,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1558</v>
+        <v>1381</v>
       </c>
       <c r="D100" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="E100" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="F100" t="n">
-        <v>59.3</v>
+        <v>60.4</v>
       </c>
       <c r="G100" t="n">
-        <v>9.300000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
@@ -4353,23 +4353,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1602</v>
+        <v>1390</v>
       </c>
       <c r="D101" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E101" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>59.6</v>
+        <v>60.6</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102">
@@ -4392,23 +4392,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1615</v>
+        <v>1396</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="F102" t="n">
-        <v>60.3</v>
+        <v>60.7</v>
       </c>
       <c r="G102" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1602</v>
+        <v>1376</v>
       </c>
       <c r="D103" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="E103" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="F103" t="n">
-        <v>60.5</v>
+        <v>61.6</v>
       </c>
       <c r="G103" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37573</v>
+        <v>37609</v>
       </c>
       <c r="D2" t="n">
         <v>49.9</v>
@@ -4554,10 +4554,10 @@
         <v>50.1</v>
       </c>
       <c r="F2" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -4580,23 +4580,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37118</v>
+        <v>37326</v>
       </c>
       <c r="D3" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F3" t="n">
         <v>49</v>
       </c>
-      <c r="E3" t="n">
-        <v>51</v>
-      </c>
-      <c r="F3" t="n">
-        <v>49.1</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -4619,17 +4619,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURCHF</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37288</v>
+        <v>37155</v>
       </c>
       <c r="D4" t="n">
-        <v>49.9</v>
+        <v>49</v>
       </c>
       <c r="E4" t="n">
-        <v>50.1</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
         <v>49</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37846</v>
+        <v>37884</v>
       </c>
       <c r="D5" t="n">
         <v>51</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37899</v>
+        <v>37937</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37763</v>
+        <v>37799</v>
       </c>
       <c r="D7" t="n">
         <v>50.6</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37912</v>
+        <v>37950</v>
       </c>
       <c r="D8" t="n">
         <v>51.3</v>
@@ -4788,10 +4788,10 @@
         <v>48.7</v>
       </c>
       <c r="F8" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37303</v>
+        <v>37340</v>
       </c>
       <c r="D9" t="n">
         <v>49.5</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37739</v>
+        <v>37777</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37797</v>
+        <v>37835</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4905,10 +4905,10 @@
         <v>49.9</v>
       </c>
       <c r="F11" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="G11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37823</v>
+        <v>37861</v>
       </c>
       <c r="D12" t="n">
         <v>51.1</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37624</v>
+        <v>37661</v>
       </c>
       <c r="D13" t="n">
         <v>50.2</v>
@@ -4983,10 +4983,10 @@
         <v>49.8</v>
       </c>
       <c r="F13" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -5000,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37578</v>
+        <v>37616</v>
       </c>
       <c r="D14" t="n">
         <v>50</v>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37703</v>
+        <v>37742</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5061,10 +5061,10 @@
         <v>50.5</v>
       </c>
       <c r="F15" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="G15" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37719</v>
+        <v>37757</v>
       </c>
       <c r="D16" t="n">
         <v>49.7</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37850</v>
+        <v>37888</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8371</v>
+        <v>8374</v>
       </c>
       <c r="D18" t="n">
         <v>51</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37519</v>
+        <v>37557</v>
       </c>
       <c r="D19" t="n">
         <v>49.9</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37052</v>
+        <v>37088</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37684</v>
+        <v>37721</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34758</v>
+        <v>34764</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37848</v>
+        <v>37885</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37587</v>
+        <v>37624</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37615</v>
+        <v>37653</v>
       </c>
       <c r="D25" t="n">
         <v>48.9</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37859</v>
+        <v>37897</v>
       </c>
       <c r="D26" t="n">
         <v>49.1</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37541</v>
+        <v>37579</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37204</v>
+        <v>37241</v>
       </c>
       <c r="D28" t="n">
         <v>49.3</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37351</v>
+        <v>37388</v>
       </c>
       <c r="D29" t="n">
         <v>49.9</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37905</v>
+        <v>37943</v>
       </c>
       <c r="D30" t="n">
         <v>49.5</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="31">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37719</v>
+        <v>37757</v>
       </c>
       <c r="D31" t="n">
         <v>50.5</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37765</v>
+        <v>37803</v>
       </c>
       <c r="D32" t="n">
         <v>50.9</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37879</v>
+        <v>37915</v>
       </c>
       <c r="D33" t="n">
         <v>49.3</v>
@@ -5763,10 +5763,10 @@
         <v>50.7</v>
       </c>
       <c r="F33" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="G33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37881</v>
+        <v>37919</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37844</v>
+        <v>37881</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38128</v>
+        <v>38166</v>
       </c>
       <c r="D36" t="n">
         <v>48.9</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38118</v>
+        <v>38156</v>
       </c>
       <c r="D37" t="n">
         <v>49</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35190</v>
+        <v>35227</v>
       </c>
       <c r="D38" t="n">
         <v>50.2</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34872</v>
+        <v>34878</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37603</v>
+        <v>37641</v>
       </c>
       <c r="D40" t="n">
         <v>49.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37472</v>
+        <v>37509</v>
       </c>
       <c r="D41" t="n">
         <v>50.3</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37647</v>
+        <v>37684</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38040</v>
+        <v>38078</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38093</v>
+        <v>38130</v>
       </c>
       <c r="D44" t="n">
         <v>49.1</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38087</v>
+        <v>38125</v>
       </c>
       <c r="D45" t="n">
         <v>49.3</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37939</v>
+        <v>37944</v>
       </c>
       <c r="D46" t="n">
         <v>49.5</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37898</v>
+        <v>37899</v>
       </c>
       <c r="D47" t="n">
         <v>49.4</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38035</v>
+        <v>38073</v>
       </c>
       <c r="D48" t="n">
         <v>49.8</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34704</v>
+        <v>34710</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37518</v>
+        <v>37555</v>
       </c>
       <c r="D50" t="n">
         <v>49.5</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37559</v>
+        <v>37597</v>
       </c>
       <c r="D51" t="n">
         <v>49.9</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37511</v>
+        <v>37549</v>
       </c>
       <c r="D52" t="n">
         <v>50.2</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37985</v>
+        <v>38023</v>
       </c>
       <c r="D53" t="n">
         <v>49</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36021</v>
+        <v>36058</v>
       </c>
       <c r="D54" t="n">
         <v>48.9</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37737</v>
+        <v>37774</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37448</v>
+        <v>37485</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37802</v>
+        <v>37840</v>
       </c>
       <c r="D57" t="n">
         <v>50.9</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37875</v>
+        <v>37913</v>
       </c>
       <c r="D58" t="n">
         <v>51.4</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38077</v>
+        <v>38115</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36438</v>
+        <v>36513</v>
       </c>
       <c r="D60" t="n">
         <v>50.3</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34936</v>
+        <v>34945</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36937</v>
+        <v>36938</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23320</v>
+        <v>23353</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23746</v>
+        <v>23778</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -6989,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23691</v>
+        <v>23720</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37816</v>
+        <v>37822</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21064</v>
+        <v>21098</v>
       </c>
       <c r="D67" t="n">
         <v>51.9</v>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37288</v>
+        <v>37326</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>35676</v>
+        <v>35677</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30386</v>
+        <v>30393</v>
       </c>
       <c r="D70" t="n">
         <v>50.9</v>
@@ -7236,19 +7236,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36954</v>
+        <v>37028</v>
       </c>
       <c r="D71" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E71" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F71" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="G71" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33027</v>
+        <v>33028</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25889</v>
+        <v>25919</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14204</v>
+        <v>14211</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14009</v>
+        <v>14011</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15065</v>
+        <v>15074</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -7470,19 +7470,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26507</v>
+        <v>26513</v>
       </c>
       <c r="D77" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E77" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F77" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="G77" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35348</v>
+        <v>35349</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28543</v>
+        <v>28551</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15685</v>
+        <v>15689</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10376</v>
+        <v>10401</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10672</v>
+        <v>10697</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10179</v>
+        <v>10180</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10626</v>
+        <v>10650</v>
       </c>
       <c r="D87" t="n">
         <v>50.8</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10733</v>
+        <v>10758</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10895</v>
+        <v>10912</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10796</v>
+        <v>10821</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10219</v>
+        <v>10261</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8064,10 +8064,10 @@
         <v>49.3</v>
       </c>
       <c r="F92" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="G92" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93">
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10149</v>
+        <v>10172</v>
       </c>
       <c r="D93" t="n">
         <v>51.3</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37322</v>
+        <v>37359</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37920</v>
+        <v>37958</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35558</v>
+        <v>35594</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38037</v>
+        <v>38075</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37256</v>
+        <v>37293</v>
       </c>
       <c r="D98" t="n">
         <v>49.2</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37830</v>
+        <v>37868</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37434</v>
+        <v>37472</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38114</v>
+        <v>38152</v>
       </c>
       <c r="D101" t="n">
         <v>50</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37694</v>
+        <v>37731</v>
       </c>
       <c r="D102" t="n">
         <v>49.7</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38134</v>
+        <v>38172</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1595</v>
+        <v>1375</v>
       </c>
       <c r="D2" t="n">
-        <v>50.9</v>
+        <v>51.7</v>
       </c>
       <c r="E2" t="n">
-        <v>49.1</v>
+        <v>48.3</v>
       </c>
       <c r="F2" t="n">
-        <v>35.8</v>
+        <v>36.2</v>
       </c>
       <c r="G2" t="n">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8633,7 +8633,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1612</v>
+        <v>1388</v>
       </c>
       <c r="D3" t="n">
         <v>49.7</v>
@@ -8642,10 +8642,10 @@
         <v>50.3</v>
       </c>
       <c r="F3" t="n">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="G3" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8659,7 +8659,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1587</v>
+        <v>1362</v>
       </c>
       <c r="D4" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="E4" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="F4" t="n">
-        <v>39.7</v>
+        <v>40.1</v>
       </c>
       <c r="G4" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1581</v>
+        <v>1359</v>
       </c>
       <c r="D5" t="n">
         <v>51.4</v>
@@ -8720,10 +8720,10 @@
         <v>48.6</v>
       </c>
       <c r="F5" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1585</v>
+        <v>1361</v>
       </c>
       <c r="D6" t="n">
         <v>51.7</v>
@@ -8759,10 +8759,10 @@
         <v>48.3</v>
       </c>
       <c r="F6" t="n">
-        <v>41.8</v>
+        <v>43.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1600</v>
+        <v>1375</v>
       </c>
       <c r="D7" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E7" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F7" t="n">
-        <v>45.4</v>
+        <v>45.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -8824,23 +8824,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1612</v>
+        <v>1332</v>
       </c>
       <c r="D8" t="n">
-        <v>48.8</v>
+        <v>49.9</v>
       </c>
       <c r="E8" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="F8" t="n">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -8863,23 +8863,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1552</v>
+        <v>1387</v>
       </c>
       <c r="D9" t="n">
-        <v>51</v>
+        <v>48.4</v>
       </c>
       <c r="E9" t="n">
-        <v>49</v>
+        <v>51.6</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>47.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,13 +8906,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1610</v>
+        <v>1386</v>
       </c>
       <c r="D10" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="E10" t="n">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
       <c r="F10" t="n">
         <v>47.5</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1614</v>
+        <v>1389</v>
       </c>
       <c r="D11" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E11" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1614</v>
+        <v>1391</v>
       </c>
       <c r="D12" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
       <c r="E12" t="n">
-        <v>52.4</v>
+        <v>53.3</v>
       </c>
       <c r="F12" t="n">
-        <v>53.8</v>
+        <v>53.1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1585</v>
+        <v>1364</v>
       </c>
       <c r="D13" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="E13" t="n">
-        <v>51</v>
+        <v>51.5</v>
       </c>
       <c r="F13" t="n">
-        <v>54.6</v>
+        <v>54</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1611</v>
+        <v>1390</v>
       </c>
       <c r="D14" t="n">
-        <v>48.5</v>
+        <v>47.9</v>
       </c>
       <c r="E14" t="n">
-        <v>51.5</v>
+        <v>52.1</v>
       </c>
       <c r="F14" t="n">
-        <v>56.7</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1592</v>
+        <v>1371</v>
       </c>
       <c r="D15" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="E15" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="F15" t="n">
-        <v>64.8</v>
+        <v>63.7</v>
       </c>
       <c r="G15" t="n">
-        <v>14.8</v>
+        <v>13.7</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1589</v>
+        <v>1365</v>
       </c>
       <c r="D16" t="n">
-        <v>48.6</v>
+        <v>47.3</v>
       </c>
       <c r="E16" t="n">
-        <v>51.4</v>
+        <v>52.7</v>
       </c>
       <c r="F16" t="n">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G16" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1513</v>
+        <v>1300</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F17" t="n">
-        <v>30.6</v>
+        <v>31.5</v>
       </c>
       <c r="G17" t="n">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1622</v>
+        <v>1396</v>
       </c>
       <c r="D18" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E18" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F18" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="G18" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9253,23 +9253,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1621</v>
+        <v>1361</v>
       </c>
       <c r="D19" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E19" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F19" t="n">
-        <v>34.4</v>
+        <v>35.3</v>
       </c>
       <c r="G19" t="n">
-        <v>15.6</v>
+        <v>14.7</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9292,23 +9292,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1583</v>
+        <v>1394</v>
       </c>
       <c r="D20" t="n">
-        <v>48.1</v>
+        <v>49.1</v>
       </c>
       <c r="E20" t="n">
-        <v>51.9</v>
+        <v>50.9</v>
       </c>
       <c r="F20" t="n">
-        <v>34.6</v>
+        <v>35.4</v>
       </c>
       <c r="G20" t="n">
-        <v>15.4</v>
+        <v>14.6</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9331,23 +9331,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1501</v>
+        <v>1395</v>
       </c>
       <c r="D21" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="E21" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="F21" t="n">
-        <v>36.2</v>
+        <v>36.7</v>
       </c>
       <c r="G21" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9370,23 +9370,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1620</v>
+        <v>1397</v>
       </c>
       <c r="D22" t="n">
-        <v>50.4</v>
+        <v>51.5</v>
       </c>
       <c r="E22" t="n">
-        <v>49.6</v>
+        <v>48.5</v>
       </c>
       <c r="F22" t="n">
-        <v>36.3</v>
+        <v>36.9</v>
       </c>
       <c r="G22" t="n">
-        <v>13.7</v>
+        <v>13.1</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>7</v>
@@ -9413,19 +9413,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1647</v>
+        <v>1387</v>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>36.5</v>
+        <v>37.1</v>
       </c>
       <c r="G23" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9448,17 +9448,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1617</v>
+        <v>1269</v>
       </c>
       <c r="D24" t="n">
-        <v>49.4</v>
+        <v>51.1</v>
       </c>
       <c r="E24" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
       </c>
       <c r="F24" t="n">
         <v>37.2</v>
@@ -9478,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -9487,23 +9487,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1622</v>
+        <v>1391</v>
       </c>
       <c r="D25" t="n">
-        <v>51.2</v>
+        <v>49.8</v>
       </c>
       <c r="E25" t="n">
-        <v>48.8</v>
+        <v>50.2</v>
       </c>
       <c r="F25" t="n">
-        <v>37.3</v>
+        <v>37.7</v>
       </c>
       <c r="G25" t="n">
-        <v>12.7</v>
+        <v>12.3</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9530,19 +9530,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1636</v>
+        <v>1378</v>
       </c>
       <c r="D26" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="F26" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
       <c r="G26" t="n">
-        <v>12.5</v>
+        <v>11.9</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9556,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1623</v>
+        <v>1397</v>
       </c>
       <c r="D27" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E27" t="n">
         <v>49.9</v>
       </c>
-      <c r="E27" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F27" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="G27" t="n">
-        <v>11.4</v>
+        <v>11.6</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9595,7 +9595,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1617</v>
+        <v>1391</v>
       </c>
       <c r="D28" t="n">
-        <v>49.6</v>
+        <v>49.9</v>
       </c>
       <c r="E28" t="n">
-        <v>50.4</v>
+        <v>50.1</v>
       </c>
       <c r="F28" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="G28" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1610</v>
+        <v>1383</v>
       </c>
       <c r="D29" t="n">
         <v>48.2</v>
@@ -9656,10 +9656,10 @@
         <v>51.8</v>
       </c>
       <c r="F29" t="n">
-        <v>40.5</v>
+        <v>39.6</v>
       </c>
       <c r="G29" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1602</v>
+        <v>1380</v>
       </c>
       <c r="D30" t="n">
-        <v>48.3</v>
+        <v>47</v>
       </c>
       <c r="E30" t="n">
-        <v>51.7</v>
+        <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="G30" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9721,23 +9721,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1507</v>
+        <v>1384</v>
       </c>
       <c r="D31" t="n">
-        <v>48.9</v>
+        <v>49.6</v>
       </c>
       <c r="E31" t="n">
-        <v>51.1</v>
+        <v>50.4</v>
       </c>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -9760,11 +9760,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1606</v>
+        <v>1273</v>
       </c>
       <c r="D32" t="n">
         <v>49.3</v>
@@ -9773,10 +9773,10 @@
         <v>50.7</v>
       </c>
       <c r="F32" t="n">
-        <v>43.5</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1611</v>
+        <v>1386</v>
       </c>
       <c r="D33" t="n">
-        <v>47.1</v>
+        <v>47.4</v>
       </c>
       <c r="E33" t="n">
-        <v>52.9</v>
+        <v>52.6</v>
       </c>
       <c r="F33" t="n">
-        <v>43.9</v>
+        <v>43.2</v>
       </c>
       <c r="G33" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1618</v>
+        <v>1393</v>
       </c>
       <c r="D34" t="n">
-        <v>48.2</v>
+        <v>47.7</v>
       </c>
       <c r="E34" t="n">
-        <v>51.8</v>
+        <v>52.3</v>
       </c>
       <c r="F34" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="G34" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9877,23 +9877,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1609</v>
+        <v>1368</v>
       </c>
       <c r="D35" t="n">
-        <v>51.2</v>
+        <v>52.1</v>
       </c>
       <c r="E35" t="n">
-        <v>48.8</v>
+        <v>47.9</v>
       </c>
       <c r="F35" t="n">
-        <v>45.1</v>
+        <v>44.4</v>
       </c>
       <c r="G35" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9916,23 +9916,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1599</v>
+        <v>1382</v>
       </c>
       <c r="D36" t="n">
-        <v>49.3</v>
+        <v>51.2</v>
       </c>
       <c r="E36" t="n">
-        <v>50.7</v>
+        <v>48.8</v>
       </c>
       <c r="F36" t="n">
-        <v>45.4</v>
+        <v>44.9</v>
       </c>
       <c r="G36" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
@@ -9955,23 +9955,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1589</v>
+        <v>1375</v>
       </c>
       <c r="D37" t="n">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="E37" t="n">
-        <v>48.7</v>
+        <v>50.4</v>
       </c>
       <c r="F37" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1505</v>
+        <v>1271</v>
       </c>
       <c r="D38" t="n">
-        <v>49.4</v>
+        <v>48.8</v>
       </c>
       <c r="E38" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="F38" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="G38" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10033,23 +10033,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1568</v>
+        <v>1352</v>
       </c>
       <c r="D39" t="n">
-        <v>49.8</v>
+        <v>51.3</v>
       </c>
       <c r="E39" t="n">
-        <v>50.2</v>
+        <v>48.7</v>
       </c>
       <c r="F39" t="n">
-        <v>49.9</v>
+        <v>50.9</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -10072,23 +10072,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1617</v>
+        <v>1348</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>49.3</v>
       </c>
       <c r="E40" t="n">
-        <v>53</v>
+        <v>50.7</v>
       </c>
       <c r="F40" t="n">
-        <v>50.3</v>
+        <v>51.1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10111,23 +10111,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1569</v>
+        <v>1393</v>
       </c>
       <c r="D41" t="n">
-        <v>50.5</v>
+        <v>47.1</v>
       </c>
       <c r="E41" t="n">
-        <v>49.5</v>
+        <v>52.9</v>
       </c>
       <c r="F41" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>462</v>
+        <v>382</v>
       </c>
       <c r="D42" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="E42" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>51.9</v>
+        <v>52.6</v>
       </c>
       <c r="G42" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10189,23 +10189,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1608</v>
+        <v>1361</v>
       </c>
       <c r="D43" t="n">
-        <v>50.5</v>
+        <v>46</v>
       </c>
       <c r="E43" t="n">
-        <v>49.5</v>
+        <v>54</v>
       </c>
       <c r="F43" t="n">
-        <v>54.4</v>
+        <v>54.1</v>
       </c>
       <c r="G43" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -10228,23 +10228,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1580</v>
+        <v>1383</v>
       </c>
       <c r="D44" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E44" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>54.8</v>
+        <v>54.4</v>
       </c>
       <c r="G44" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10258,7 +10258,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45">
@@ -10267,23 +10267,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1581</v>
+        <v>1355</v>
       </c>
       <c r="D45" t="n">
-        <v>46.3</v>
+        <v>52.3</v>
       </c>
       <c r="E45" t="n">
-        <v>53.7</v>
+        <v>47.7</v>
       </c>
       <c r="F45" t="n">
-        <v>55.3</v>
+        <v>55.7</v>
       </c>
       <c r="G45" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -10306,23 +10306,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1607</v>
+        <v>1376</v>
       </c>
       <c r="D46" t="n">
-        <v>49.9</v>
+        <v>48</v>
       </c>
       <c r="E46" t="n">
-        <v>50.1</v>
+        <v>52</v>
       </c>
       <c r="F46" t="n">
-        <v>56.3</v>
+        <v>56.6</v>
       </c>
       <c r="G46" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47">
@@ -10345,23 +10345,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1598</v>
+        <v>1386</v>
       </c>
       <c r="D47" t="n">
-        <v>48</v>
+        <v>49.3</v>
       </c>
       <c r="E47" t="n">
-        <v>52</v>
+        <v>50.7</v>
       </c>
       <c r="F47" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="G47" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
@@ -10384,17 +10384,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1456</v>
+        <v>1382</v>
       </c>
       <c r="D48" t="n">
-        <v>48.1</v>
+        <v>45.4</v>
       </c>
       <c r="E48" t="n">
-        <v>51.9</v>
+        <v>54.6</v>
       </c>
       <c r="F48" t="n">
         <v>58.9</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49">
@@ -10423,23 +10423,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1602</v>
+        <v>1263</v>
       </c>
       <c r="D49" t="n">
-        <v>46.4</v>
+        <v>47.4</v>
       </c>
       <c r="E49" t="n">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
       <c r="F49" t="n">
-        <v>59.2</v>
+        <v>58.9</v>
       </c>
       <c r="G49" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="50">
@@ -10466,19 +10466,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1589</v>
+        <v>1369</v>
       </c>
       <c r="D50" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E50" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F50" t="n">
-        <v>59.8</v>
+        <v>59.5</v>
       </c>
       <c r="G50" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1594</v>
+        <v>1370</v>
       </c>
       <c r="D51" t="n">
-        <v>48.3</v>
+        <v>49.3</v>
       </c>
       <c r="E51" t="n">
-        <v>51.7</v>
+        <v>50.7</v>
       </c>
       <c r="F51" t="n">
-        <v>60.7</v>
+        <v>59.8</v>
       </c>
       <c r="G51" t="n">
-        <v>10.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52">
@@ -10544,13 +10544,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1580</v>
+        <v>1360</v>
       </c>
       <c r="D52" t="n">
-        <v>50.5</v>
+        <v>51.2</v>
       </c>
       <c r="E52" t="n">
-        <v>49.5</v>
+        <v>48.8</v>
       </c>
       <c r="F52" t="n">
         <v>62.1</v>
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1591</v>
+        <v>1371</v>
       </c>
       <c r="D53" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E53" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F53" t="n">
-        <v>66.5</v>
+        <v>66.2</v>
       </c>
       <c r="G53" t="n">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="54">
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1594</v>
+        <v>1371</v>
       </c>
       <c r="D54" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="E54" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="F54" t="n">
-        <v>67.09999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="G54" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1613</v>
+        <v>1386</v>
       </c>
       <c r="D55" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="F55" t="n">
-        <v>70.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>20.6</v>
+        <v>19.1</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,19 +10700,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1600</v>
+        <v>1376</v>
       </c>
       <c r="D56" t="n">
-        <v>48.5</v>
+        <v>48</v>
       </c>
       <c r="E56" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="F56" t="n">
-        <v>75.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="G56" t="n">
-        <v>25.6</v>
+        <v>24.8</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1617</v>
+        <v>1392</v>
       </c>
       <c r="D57" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E57" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F57" t="n">
-        <v>82</v>
+        <v>82.3</v>
       </c>
       <c r="G57" t="n">
-        <v>32</v>
+        <v>32.3</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1617</v>
+        <v>1394</v>
       </c>
       <c r="D58" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E58" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F58" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="G58" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1619</v>
+        <v>1394</v>
       </c>
       <c r="D59" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="E59" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="F59" t="n">
-        <v>93.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>43.9</v>
+        <v>44.4</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10856,19 +10856,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1526</v>
+        <v>1298</v>
       </c>
       <c r="D60" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E60" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F60" t="n">
-        <v>42.3</v>
+        <v>42.8</v>
       </c>
       <c r="G60" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -10895,19 +10895,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1611</v>
+        <v>1431</v>
       </c>
       <c r="D61" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="E61" t="n">
-        <v>49.1</v>
+        <v>49.8</v>
       </c>
       <c r="F61" t="n">
-        <v>42.5</v>
+        <v>42.8</v>
       </c>
       <c r="G61" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
@@ -10930,23 +10930,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1003</v>
+        <v>863</v>
       </c>
       <c r="D62" t="n">
-        <v>49.1</v>
+        <v>48.1</v>
       </c>
       <c r="E62" t="n">
-        <v>50.9</v>
+        <v>51.9</v>
       </c>
       <c r="F62" t="n">
-        <v>57</v>
+        <v>57.8</v>
       </c>
       <c r="G62" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63">
@@ -10969,23 +10969,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1018</v>
+        <v>874</v>
       </c>
       <c r="D63" t="n">
-        <v>52.6</v>
+        <v>49.4</v>
       </c>
       <c r="E63" t="n">
-        <v>47.4</v>
+        <v>50.6</v>
       </c>
       <c r="F63" t="n">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="G63" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -11008,23 +11008,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>998</v>
+        <v>886</v>
       </c>
       <c r="D64" t="n">
-        <v>50.4</v>
+        <v>53.3</v>
       </c>
       <c r="E64" t="n">
-        <v>49.6</v>
+        <v>46.7</v>
       </c>
       <c r="F64" t="n">
-        <v>58.5</v>
+        <v>59.1</v>
       </c>
       <c r="G64" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>997</v>
+        <v>868</v>
       </c>
       <c r="D65" t="n">
-        <v>47.5</v>
+        <v>52</v>
       </c>
       <c r="E65" t="n">
-        <v>52.5</v>
+        <v>48</v>
       </c>
       <c r="F65" t="n">
-        <v>58.6</v>
+        <v>59.3</v>
       </c>
       <c r="G65" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="66">
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1502</v>
+        <v>1245</v>
       </c>
       <c r="D66" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="E66" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="F66" t="n">
-        <v>59.5</v>
+        <v>59.3</v>
       </c>
       <c r="G66" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67">
@@ -11129,13 +11129,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1619</v>
+        <v>1360</v>
       </c>
       <c r="D67" t="n">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
       <c r="E67" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="F67" t="n">
         <v>61.5</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68">
@@ -11168,19 +11168,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1646</v>
+        <v>1389</v>
       </c>
       <c r="D68" t="n">
-        <v>49.8</v>
+        <v>50.8</v>
       </c>
       <c r="E68" t="n">
-        <v>50.2</v>
+        <v>49.2</v>
       </c>
       <c r="F68" t="n">
-        <v>61.9</v>
+        <v>61.7</v>
       </c>
       <c r="G68" t="n">
-        <v>11.9</v>
+        <v>11.7</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69">
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1437</v>
+        <v>1007</v>
       </c>
       <c r="D69" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="E69" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="F69" t="n">
-        <v>62.1</v>
+        <v>62.4</v>
       </c>
       <c r="G69" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70">
@@ -11242,23 +11242,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1594</v>
+        <v>1211</v>
       </c>
       <c r="D70" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="E70" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="F70" t="n">
-        <v>62.4</v>
+        <v>62.8</v>
       </c>
       <c r="G70" t="n">
-        <v>12.4</v>
+        <v>12.8</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71">
@@ -11281,23 +11281,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1619</v>
+        <v>1371</v>
       </c>
       <c r="D71" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="E71" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="F71" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="G71" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72">
@@ -11320,23 +11320,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1169</v>
+        <v>1434</v>
       </c>
       <c r="D72" t="n">
-        <v>49</v>
+        <v>49.9</v>
       </c>
       <c r="E72" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
       <c r="F72" t="n">
-        <v>63.1</v>
+        <v>63.7</v>
       </c>
       <c r="G72" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73">
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1441</v>
+        <v>1207</v>
       </c>
       <c r="D73" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="E73" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="F73" t="n">
-        <v>66.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="G73" t="n">
-        <v>16.1</v>
+        <v>16.8</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11389,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
@@ -11398,17 +11398,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="D74" t="n">
-        <v>49.5</v>
+        <v>50.2</v>
       </c>
       <c r="E74" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
       <c r="F74" t="n">
         <v>53.1</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>633</v>
+        <v>526</v>
       </c>
       <c r="D75" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="E75" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="F75" t="n">
-        <v>53.2</v>
+        <v>54.4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76">
@@ -11476,23 +11476,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>638</v>
+        <v>520</v>
       </c>
       <c r="D76" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E76" t="n">
         <v>49.8</v>
       </c>
-      <c r="E76" t="n">
-        <v>50.2</v>
-      </c>
       <c r="F76" t="n">
-        <v>53.8</v>
+        <v>54.6</v>
       </c>
       <c r="G76" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1219</v>
+        <v>1022</v>
       </c>
       <c r="D77" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="E77" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="F77" t="n">
-        <v>55.8</v>
+        <v>56.5</v>
       </c>
       <c r="G77" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78">
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1545</v>
+        <v>1301</v>
       </c>
       <c r="D78" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="E78" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
       <c r="F78" t="n">
-        <v>71.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="G78" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>615</v>
+        <v>510</v>
       </c>
       <c r="D79" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="E79" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
       <c r="F79" t="n">
-        <v>58.7</v>
+        <v>57.6</v>
       </c>
       <c r="G79" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1251</v>
+        <v>1069</v>
       </c>
       <c r="D80" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>53.1</v>
       </c>
       <c r="F80" t="n">
-        <v>60.4</v>
+        <v>60</v>
       </c>
       <c r="G80" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="81">
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1201</v>
+        <v>1001</v>
       </c>
       <c r="D81" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="E81" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="F81" t="n">
-        <v>63.5</v>
+        <v>63</v>
       </c>
       <c r="G81" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="82">
@@ -11710,17 +11710,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>417</v>
+        <v>368</v>
       </c>
       <c r="D82" t="n">
-        <v>47</v>
+        <v>50.5</v>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>49.5</v>
       </c>
       <c r="F82" t="n">
         <v>48.9</v>
@@ -11749,23 +11749,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>441</v>
+        <v>360</v>
       </c>
       <c r="D83" t="n">
-        <v>50.3</v>
+        <v>48.3</v>
       </c>
       <c r="E83" t="n">
-        <v>49.7</v>
+        <v>51.7</v>
       </c>
       <c r="F83" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11788,23 +11788,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>437</v>
+        <v>368</v>
       </c>
       <c r="D84" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="E84" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="F84" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85">
@@ -11827,23 +11827,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>434</v>
+        <v>382</v>
       </c>
       <c r="D85" t="n">
-        <v>50.5</v>
+        <v>47.1</v>
       </c>
       <c r="E85" t="n">
-        <v>49.5</v>
+        <v>52.9</v>
       </c>
       <c r="F85" t="n">
-        <v>54.1</v>
+        <v>55.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="86">
@@ -11866,23 +11866,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>435</v>
+        <v>364</v>
       </c>
       <c r="D86" t="n">
-        <v>48.3</v>
+        <v>52.2</v>
       </c>
       <c r="E86" t="n">
-        <v>51.7</v>
+        <v>47.8</v>
       </c>
       <c r="F86" t="n">
-        <v>54.7</v>
+        <v>56.3</v>
       </c>
       <c r="G86" t="n">
-        <v>4.7</v>
+        <v>6.3</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="87">
@@ -11909,19 +11909,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="D87" t="n">
-        <v>48.5</v>
+        <v>46.8</v>
       </c>
       <c r="E87" t="n">
-        <v>51.5</v>
+        <v>53.2</v>
       </c>
       <c r="F87" t="n">
-        <v>56.5</v>
+        <v>57.3</v>
       </c>
       <c r="G87" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="88">
@@ -11948,7 +11948,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>433</v>
+        <v>380</v>
       </c>
       <c r="D88" t="n">
         <v>50.3</v>
@@ -11957,10 +11957,10 @@
         <v>49.7</v>
       </c>
       <c r="F88" t="n">
-        <v>60.3</v>
+        <v>60.5</v>
       </c>
       <c r="G88" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="89">
@@ -11983,23 +11983,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="D89" t="n">
-        <v>47.2</v>
+        <v>50.6</v>
       </c>
       <c r="E89" t="n">
-        <v>52.8</v>
+        <v>49.4</v>
       </c>
       <c r="F89" t="n">
-        <v>61.7</v>
+        <v>61.8</v>
       </c>
       <c r="G89" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="90">
@@ -12022,23 +12022,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>463</v>
+        <v>384</v>
       </c>
       <c r="D90" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
       <c r="E90" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="F90" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
       <c r="G90" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>431</v>
+        <v>390</v>
       </c>
       <c r="D91" t="n">
-        <v>49.4</v>
+        <v>51.8</v>
       </c>
       <c r="E91" t="n">
-        <v>50.6</v>
+        <v>48.2</v>
       </c>
       <c r="F91" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="G91" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92">
@@ -12100,11 +12100,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>468</v>
+        <v>378</v>
       </c>
       <c r="D92" t="n">
         <v>51.1</v>
@@ -12113,10 +12113,10 @@
         <v>48.9</v>
       </c>
       <c r="F92" t="n">
-        <v>62.8</v>
+        <v>62.4</v>
       </c>
       <c r="G92" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>406</v>
+        <v>353</v>
       </c>
       <c r="D93" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="E93" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="F93" t="n">
-        <v>71.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G93" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12178,23 +12178,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1620</v>
+        <v>1237</v>
       </c>
       <c r="D94" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="G94" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="95">
@@ -12217,23 +12217,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1568</v>
+        <v>1396</v>
       </c>
       <c r="D95" t="n">
-        <v>51.3</v>
+        <v>49.3</v>
       </c>
       <c r="E95" t="n">
-        <v>48.7</v>
+        <v>50.7</v>
       </c>
       <c r="F95" t="n">
-        <v>58.1</v>
+        <v>58.6</v>
       </c>
       <c r="G95" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96">
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1417</v>
+        <v>1356</v>
       </c>
       <c r="D96" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E96" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F96" t="n">
-        <v>58.2</v>
+        <v>58.9</v>
       </c>
       <c r="G96" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97">
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1623</v>
+        <v>1397</v>
       </c>
       <c r="D97" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E97" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F97" t="n">
-        <v>58.9</v>
+        <v>59.6</v>
       </c>
       <c r="G97" t="n">
-        <v>8.9</v>
+        <v>9.6</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1622</v>
+        <v>1397</v>
       </c>
       <c r="D98" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="E98" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="F98" t="n">
-        <v>59.2</v>
+        <v>59.7</v>
       </c>
       <c r="G98" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99">
@@ -12373,23 +12373,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1623</v>
+        <v>1347</v>
       </c>
       <c r="D99" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E99" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F99" t="n">
-        <v>59.2</v>
+        <v>60.4</v>
       </c>
       <c r="G99" t="n">
-        <v>9.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="100">
@@ -12412,23 +12412,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1558</v>
+        <v>1381</v>
       </c>
       <c r="D100" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="E100" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="F100" t="n">
-        <v>59.3</v>
+        <v>60.4</v>
       </c>
       <c r="G100" t="n">
-        <v>9.300000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101">
@@ -12451,23 +12451,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1602</v>
+        <v>1390</v>
       </c>
       <c r="D101" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E101" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F101" t="n">
-        <v>59.6</v>
+        <v>60.6</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102">
@@ -12490,23 +12490,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1615</v>
+        <v>1396</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="F102" t="n">
-        <v>60.3</v>
+        <v>60.7</v>
       </c>
       <c r="G102" t="n">
-        <v>10.3</v>
+        <v>10.7</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1602</v>
+        <v>1376</v>
       </c>
       <c r="D103" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="E103" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="F103" t="n">
-        <v>60.5</v>
+        <v>61.6</v>
       </c>
       <c r="G103" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37578</v>
+        <v>37616</v>
       </c>
       <c r="D2" t="n">
         <v>50</v>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37624</v>
+        <v>37661</v>
       </c>
       <c r="D3" t="n">
         <v>50.2</v>
@@ -12691,10 +12691,10 @@
         <v>49.8</v>
       </c>
       <c r="F3" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="G3" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37823</v>
+        <v>37861</v>
       </c>
       <c r="D4" t="n">
         <v>51.1</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37303</v>
+        <v>37340</v>
       </c>
       <c r="D5" t="n">
         <v>49.5</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37763</v>
+        <v>37799</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37288</v>
+        <v>37326</v>
       </c>
       <c r="D7" t="n">
         <v>49.9</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37118</v>
+        <v>37155</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12886,10 +12886,10 @@
         <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37573</v>
+        <v>37609</v>
       </c>
       <c r="D9" t="n">
         <v>49.9</v>
@@ -12925,10 +12925,10 @@
         <v>50.1</v>
       </c>
       <c r="F9" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37846</v>
+        <v>37884</v>
       </c>
       <c r="D10" t="n">
         <v>51</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37899</v>
+        <v>37937</v>
       </c>
       <c r="D11" t="n">
         <v>50.6</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37912</v>
+        <v>37950</v>
       </c>
       <c r="D12" t="n">
         <v>51.3</v>
@@ -13042,10 +13042,10 @@
         <v>48.7</v>
       </c>
       <c r="F12" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37739</v>
+        <v>37777</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37797</v>
+        <v>37835</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13120,10 +13120,10 @@
         <v>49.9</v>
       </c>
       <c r="F14" t="n">
-        <v>55.2</v>
+        <v>55.1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -13137,7 +13137,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37703</v>
+        <v>37742</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13159,10 +13159,10 @@
         <v>50.5</v>
       </c>
       <c r="F15" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="G15" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37719</v>
+        <v>37757</v>
       </c>
       <c r="D16" t="n">
         <v>49.7</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36021</v>
+        <v>36058</v>
       </c>
       <c r="D17" t="n">
         <v>48.9</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>37985</v>
+        <v>38023</v>
       </c>
       <c r="D18" t="n">
         <v>49</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37511</v>
+        <v>37549</v>
       </c>
       <c r="D19" t="n">
         <v>50.2</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34704</v>
+        <v>34710</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38035</v>
+        <v>38073</v>
       </c>
       <c r="D21" t="n">
         <v>49.8</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37898</v>
+        <v>37899</v>
       </c>
       <c r="D22" t="n">
         <v>49.4</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37939</v>
+        <v>37944</v>
       </c>
       <c r="D23" t="n">
         <v>49.5</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38087</v>
+        <v>38125</v>
       </c>
       <c r="D24" t="n">
         <v>49.3</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38093</v>
+        <v>38130</v>
       </c>
       <c r="D25" t="n">
         <v>49.1</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38040</v>
+        <v>38078</v>
       </c>
       <c r="D26" t="n">
         <v>49.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34872</v>
+        <v>34878</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38118</v>
+        <v>38156</v>
       </c>
       <c r="D28" t="n">
         <v>49</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38128</v>
+        <v>38166</v>
       </c>
       <c r="D29" t="n">
         <v>48.9</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37844</v>
+        <v>37881</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13770,17 +13770,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37881</v>
+        <v>37915</v>
       </c>
       <c r="D31" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E31" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F31" t="n">
         <v>44.5</v>
@@ -13809,23 +13809,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37879</v>
+        <v>37919</v>
       </c>
       <c r="D32" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E32" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F32" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="G32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37905</v>
+        <v>37943</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37859</v>
+        <v>37897</v>
       </c>
       <c r="D34" t="n">
         <v>49.1</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37848</v>
+        <v>37885</v>
       </c>
       <c r="D35" t="n">
         <v>49.6</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34758</v>
+        <v>34764</v>
       </c>
       <c r="D36" t="n">
         <v>49.8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37684</v>
+        <v>37721</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37052</v>
+        <v>37088</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37850</v>
+        <v>37888</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8371</v>
+        <v>8374</v>
       </c>
       <c r="D40" t="n">
         <v>51</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37519</v>
+        <v>37557</v>
       </c>
       <c r="D41" t="n">
         <v>49.9</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37587</v>
+        <v>37624</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37615</v>
+        <v>37653</v>
       </c>
       <c r="D43" t="n">
         <v>48.9</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37541</v>
+        <v>37579</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37204</v>
+        <v>37241</v>
       </c>
       <c r="D45" t="n">
         <v>49.3</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37351</v>
+        <v>37388</v>
       </c>
       <c r="D46" t="n">
         <v>49.9</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37719</v>
+        <v>37757</v>
       </c>
       <c r="D47" t="n">
         <v>50.5</v>
@@ -14424,7 +14424,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48">
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37765</v>
+        <v>37803</v>
       </c>
       <c r="D48" t="n">
         <v>50.9</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35190</v>
+        <v>35227</v>
       </c>
       <c r="D49" t="n">
         <v>50.2</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37603</v>
+        <v>37641</v>
       </c>
       <c r="D50" t="n">
         <v>49.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37472</v>
+        <v>37509</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37647</v>
+        <v>37684</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37518</v>
+        <v>37555</v>
       </c>
       <c r="D53" t="n">
         <v>49.5</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37559</v>
+        <v>37597</v>
       </c>
       <c r="D54" t="n">
         <v>49.9</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37737</v>
+        <v>37774</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37448</v>
+        <v>37485</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37802</v>
+        <v>37840</v>
       </c>
       <c r="D57" t="n">
         <v>50.9</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37875</v>
+        <v>37913</v>
       </c>
       <c r="D58" t="n">
         <v>51.4</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38077</v>
+        <v>38115</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>34936</v>
+        <v>34945</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36438</v>
+        <v>36513</v>
       </c>
       <c r="D61" t="n">
         <v>50.3</v>
@@ -14970,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62">
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36937</v>
+        <v>36938</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23320</v>
+        <v>23353</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23746</v>
+        <v>23778</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23691</v>
+        <v>23720</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37816</v>
+        <v>37822</v>
       </c>
       <c r="D66" t="n">
         <v>51.1</v>
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21064</v>
+        <v>21098</v>
       </c>
       <c r="D67" t="n">
         <v>51.9</v>
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37288</v>
+        <v>37326</v>
       </c>
       <c r="D68" t="n">
         <v>50.5</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>35676</v>
+        <v>35677</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30386</v>
+        <v>30393</v>
       </c>
       <c r="D70" t="n">
         <v>50.9</v>
@@ -15334,19 +15334,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>36954</v>
+        <v>37028</v>
       </c>
       <c r="D71" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E71" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F71" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="G71" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33027</v>
+        <v>33028</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25889</v>
+        <v>25919</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14204</v>
+        <v>14211</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14009</v>
+        <v>14011</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15065</v>
+        <v>15074</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -15568,19 +15568,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26507</v>
+        <v>26513</v>
       </c>
       <c r="D77" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E77" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F77" t="n">
-        <v>53.1</v>
+        <v>53.2</v>
       </c>
       <c r="G77" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35348</v>
+        <v>35349</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28543</v>
+        <v>28551</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15685</v>
+        <v>15689</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10376</v>
+        <v>10401</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10672</v>
+        <v>10697</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10179</v>
+        <v>10180</v>
       </c>
       <c r="D86" t="n">
         <v>51.3</v>
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10626</v>
+        <v>10650</v>
       </c>
       <c r="D87" t="n">
         <v>50.8</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10733</v>
+        <v>10758</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10895</v>
+        <v>10912</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10796</v>
+        <v>10821</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10219</v>
+        <v>10261</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16162,10 +16162,10 @@
         <v>49.3</v>
       </c>
       <c r="F92" t="n">
-        <v>59.7</v>
+        <v>59.8</v>
       </c>
       <c r="G92" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10149</v>
+        <v>10172</v>
       </c>
       <c r="D93" t="n">
         <v>51.3</v>
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37322</v>
+        <v>37359</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37920</v>
+        <v>37958</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35558</v>
+        <v>35594</v>
       </c>
       <c r="D96" t="n">
         <v>48.8</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38037</v>
+        <v>38075</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37256</v>
+        <v>37293</v>
       </c>
       <c r="D98" t="n">
         <v>49.2</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37830</v>
+        <v>37868</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37434</v>
+        <v>37472</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38114</v>
+        <v>38152</v>
       </c>
       <c r="D101" t="n">
         <v>50</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37694</v>
+        <v>37731</v>
       </c>
       <c r="D102" t="n">
         <v>49.7</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38134</v>
+        <v>38172</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1389</v>
+        <v>1491</v>
       </c>
       <c r="D2" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="F2" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1386</v>
+        <v>1490</v>
       </c>
       <c r="D3" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="E3" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
       <c r="F3" t="n">
         <v>47.5</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -570,20 +570,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1387</v>
+        <v>1494</v>
       </c>
       <c r="D4" t="n">
-        <v>48.4</v>
+        <v>47.2</v>
       </c>
       <c r="E4" t="n">
-        <v>51.6</v>
+        <v>52.8</v>
       </c>
       <c r="F4" t="n">
-        <v>47.2</v>
+        <v>52.8</v>
       </c>
       <c r="G4" t="n">
         <v>2.8</v>
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHFJPY</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1391</v>
+        <v>1490</v>
       </c>
       <c r="D5" t="n">
-        <v>46.7</v>
+        <v>49.1</v>
       </c>
       <c r="E5" t="n">
-        <v>53.3</v>
+        <v>50.9</v>
       </c>
       <c r="F5" t="n">
-        <v>53.1</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1332</v>
+        <v>1434</v>
       </c>
       <c r="D6" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="E6" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="F6" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1364</v>
+        <v>1467</v>
       </c>
       <c r="D7" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="E7" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1375</v>
+        <v>1477</v>
       </c>
       <c r="D8" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="E8" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="F8" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1390</v>
+        <v>1494</v>
       </c>
       <c r="D9" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="E9" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>55.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1361</v>
+        <v>1464</v>
       </c>
       <c r="D10" t="n">
-        <v>51.7</v>
+        <v>52.4</v>
       </c>
       <c r="E10" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="F10" t="n">
-        <v>43.1</v>
+        <v>43.6</v>
       </c>
       <c r="G10" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1359</v>
+        <v>1460</v>
       </c>
       <c r="D11" t="n">
         <v>51.4</v>
@@ -856,10 +856,10 @@
         <v>48.6</v>
       </c>
       <c r="F11" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1362</v>
+        <v>1466</v>
       </c>
       <c r="D12" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="E12" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="F12" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="G12" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1388</v>
+        <v>1490</v>
       </c>
       <c r="D13" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="E13" t="n">
         <v>49.7</v>
       </c>
-      <c r="E13" t="n">
-        <v>50.3</v>
-      </c>
       <c r="F13" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="G13" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1371</v>
+        <v>1472</v>
       </c>
       <c r="D14" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E14" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F14" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="G14" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1375</v>
+        <v>1474</v>
       </c>
       <c r="D15" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1365</v>
+        <v>1468</v>
       </c>
       <c r="D16" t="n">
-        <v>47.3</v>
+        <v>47.6</v>
       </c>
       <c r="E16" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
       <c r="F16" t="n">
-        <v>64.5</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1077,23 +1077,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1352</v>
+        <v>1445</v>
       </c>
       <c r="D17" t="n">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="E17" t="n">
-        <v>48.7</v>
+        <v>50.4</v>
       </c>
       <c r="F17" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1116,23 +1116,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>EURNOK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="D18" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="E18" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="F18" t="n">
-        <v>51.1</v>
+        <v>48.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EURNOK</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1271</v>
+        <v>1455</v>
       </c>
       <c r="D19" t="n">
-        <v>48.8</v>
+        <v>51.3</v>
       </c>
       <c r="E19" t="n">
-        <v>51.2</v>
+        <v>48.7</v>
       </c>
       <c r="F19" t="n">
-        <v>48.8</v>
+        <v>51.4</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1393</v>
+        <v>1496</v>
       </c>
       <c r="D20" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="E20" t="n">
-        <v>52.9</v>
+        <v>53.1</v>
       </c>
       <c r="F20" t="n">
         <v>51.5</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="F21" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1375</v>
+        <v>1476</v>
       </c>
       <c r="D22" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F22" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1311,23 +1311,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1361</v>
+        <v>1482</v>
       </c>
       <c r="D23" t="n">
-        <v>46</v>
+        <v>51.6</v>
       </c>
       <c r="E23" t="n">
-        <v>54</v>
+        <v>48.4</v>
       </c>
       <c r="F23" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="G23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1350,17 +1350,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1383</v>
+        <v>1462</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>46.4</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>53.6</v>
       </c>
       <c r="F24" t="n">
         <v>54.4</v>
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1382</v>
+        <v>1486</v>
       </c>
       <c r="D25" t="n">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1368</v>
+        <v>1471</v>
       </c>
       <c r="D26" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="E26" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="F26" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="G26" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1355</v>
+        <v>1459</v>
       </c>
       <c r="D27" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="E27" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="F27" t="n">
-        <v>55.7</v>
+        <v>56.2</v>
       </c>
       <c r="G27" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -1506,23 +1506,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1393</v>
+        <v>1480</v>
       </c>
       <c r="D28" t="n">
-        <v>47.7</v>
+        <v>48.8</v>
       </c>
       <c r="E28" t="n">
-        <v>52.3</v>
+        <v>51.2</v>
       </c>
       <c r="F28" t="n">
-        <v>43.9</v>
+        <v>56.4</v>
       </c>
       <c r="G28" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -1545,23 +1545,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1376</v>
+        <v>1495</v>
       </c>
       <c r="D29" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
       <c r="E29" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="F29" t="n">
-        <v>56.6</v>
+        <v>43.5</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1386</v>
+        <v>1489</v>
       </c>
       <c r="D30" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="E30" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F30" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1627,19 +1627,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1386</v>
+        <v>1486</v>
       </c>
       <c r="D31" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="F31" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1273</v>
+        <v>1347</v>
       </c>
       <c r="D32" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E32" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F32" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1384</v>
+        <v>1488</v>
       </c>
       <c r="D33" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="E33" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="F33" t="n">
-        <v>42.3</v>
+        <v>41.9</v>
       </c>
       <c r="G33" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="34">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1382</v>
+        <v>1484</v>
       </c>
       <c r="D34" t="n">
-        <v>45.4</v>
+        <v>46</v>
       </c>
       <c r="E34" t="n">
-        <v>54.6</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>58.9</v>
+        <v>58.5</v>
       </c>
       <c r="G34" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1263</v>
+        <v>1360</v>
       </c>
       <c r="D35" t="n">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
       <c r="E35" t="n">
-        <v>52.6</v>
+        <v>52.1</v>
       </c>
       <c r="F35" t="n">
-        <v>58.9</v>
+        <v>59.1</v>
       </c>
       <c r="G35" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1369</v>
+        <v>1470</v>
       </c>
       <c r="D36" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E36" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F36" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="G36" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1380</v>
+        <v>1483</v>
       </c>
       <c r="D37" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="E37" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="F37" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="G37" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1900,19 +1900,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1370</v>
+        <v>1473</v>
       </c>
       <c r="D38" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E38" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F38" t="n">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="G38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1383</v>
+        <v>1487</v>
       </c>
       <c r="D39" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="E39" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="F39" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="G39" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40">
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1391</v>
+        <v>1494</v>
       </c>
       <c r="D40" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="E40" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="F40" t="n">
         <v>38.6</v>
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1397</v>
+        <v>1501</v>
       </c>
       <c r="D41" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="E41" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="F41" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="G41" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42">
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1378</v>
+        <v>1462</v>
       </c>
       <c r="D42" t="n">
-        <v>48</v>
+        <v>51.2</v>
       </c>
       <c r="E42" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="F42" t="n">
-        <v>38.1</v>
+        <v>62.2</v>
       </c>
       <c r="G42" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="43">
@@ -2091,23 +2091,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1360</v>
+        <v>1481</v>
       </c>
       <c r="D43" t="n">
-        <v>51.2</v>
+        <v>48.5</v>
       </c>
       <c r="E43" t="n">
-        <v>48.8</v>
+        <v>51.5</v>
       </c>
       <c r="F43" t="n">
-        <v>62.1</v>
+        <v>37.7</v>
       </c>
       <c r="G43" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44">
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1391</v>
+        <v>1495</v>
       </c>
       <c r="D44" t="n">
-        <v>49.8</v>
+        <v>50.6</v>
       </c>
       <c r="E44" t="n">
-        <v>50.2</v>
+        <v>49.4</v>
       </c>
       <c r="F44" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="G44" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1269</v>
+        <v>1490</v>
       </c>
       <c r="D45" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="E45" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="F45" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="G45" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46">
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1387</v>
+        <v>1343</v>
       </c>
       <c r="D46" t="n">
-        <v>51</v>
+        <v>51.6</v>
       </c>
       <c r="E46" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="F46" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="G46" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1397</v>
+        <v>1499</v>
       </c>
       <c r="D47" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E47" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F47" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="G47" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="J47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>82</v>
@@ -2286,23 +2286,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1395</v>
+        <v>1501</v>
       </c>
       <c r="D48" t="n">
-        <v>50.5</v>
+        <v>52</v>
       </c>
       <c r="E48" t="n">
-        <v>49.5</v>
+        <v>48</v>
       </c>
       <c r="F48" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G48" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="J48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="D49" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="E49" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="F49" t="n">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="G49" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2364,17 +2364,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1361</v>
+        <v>1498</v>
       </c>
       <c r="D50" t="n">
-        <v>48.7</v>
+        <v>49.9</v>
       </c>
       <c r="E50" t="n">
-        <v>51.3</v>
+        <v>50.1</v>
       </c>
       <c r="F50" t="n">
         <v>35.3</v>
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1371</v>
+        <v>1471</v>
       </c>
       <c r="D51" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E51" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F51" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1371</v>
+        <v>1473</v>
       </c>
       <c r="D52" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="E52" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="F52" t="n">
-        <v>67.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1396</v>
+        <v>1500</v>
       </c>
       <c r="D53" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E53" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F53" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="G53" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1300</v>
+        <v>1397</v>
       </c>
       <c r="D54" t="n">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="E54" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="F54" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="G54" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1386</v>
+        <v>1490</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="E55" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="F55" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="G55" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1376</v>
+        <v>1480</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="F56" t="n">
         <v>74.8</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1392</v>
+        <v>1495</v>
       </c>
       <c r="D57" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E57" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F57" t="n">
-        <v>82.3</v>
+        <v>82.7</v>
       </c>
       <c r="G57" t="n">
-        <v>32.3</v>
+        <v>32.7</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1394</v>
+        <v>1498</v>
       </c>
       <c r="D58" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E58" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F58" t="n">
-        <v>83.2</v>
+        <v>83.5</v>
       </c>
       <c r="G58" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1394</v>
+        <v>1498</v>
       </c>
       <c r="D59" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E59" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F59" t="n">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="G59" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,17 +2754,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1298</v>
+        <v>1457</v>
       </c>
       <c r="D60" t="n">
-        <v>51.5</v>
+        <v>50.2</v>
       </c>
       <c r="E60" t="n">
-        <v>48.5</v>
+        <v>49.8</v>
       </c>
       <c r="F60" t="n">
         <v>42.8</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1431</v>
+        <v>1372</v>
       </c>
       <c r="D61" t="n">
-        <v>50.2</v>
+        <v>51.4</v>
       </c>
       <c r="E61" t="n">
-        <v>49.8</v>
+        <v>48.6</v>
       </c>
       <c r="F61" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="G61" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="62">
@@ -2832,23 +2832,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>863</v>
+        <v>929</v>
       </c>
       <c r="D62" t="n">
-        <v>48.1</v>
+        <v>49.6</v>
       </c>
       <c r="E62" t="n">
-        <v>51.9</v>
+        <v>50.4</v>
       </c>
       <c r="F62" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="G62" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="63">
@@ -2871,23 +2871,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>874</v>
+        <v>919</v>
       </c>
       <c r="D63" t="n">
-        <v>49.4</v>
+        <v>47.9</v>
       </c>
       <c r="E63" t="n">
-        <v>50.6</v>
+        <v>52.1</v>
       </c>
       <c r="F63" t="n">
-        <v>58</v>
+        <v>58.1</v>
       </c>
       <c r="G63" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>886</v>
+        <v>942</v>
       </c>
       <c r="D64" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="E64" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="F64" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="G64" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>868</v>
+        <v>1338</v>
       </c>
       <c r="D65" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="E65" t="n">
-        <v>48</v>
+        <v>51.2</v>
       </c>
       <c r="F65" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G65" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1245</v>
+        <v>922</v>
       </c>
       <c r="D66" t="n">
-        <v>48.5</v>
+        <v>51.7</v>
       </c>
       <c r="E66" t="n">
-        <v>51.5</v>
+        <v>48.3</v>
       </c>
       <c r="F66" t="n">
-        <v>59.3</v>
+        <v>59.9</v>
       </c>
       <c r="G66" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67">
@@ -3031,19 +3031,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1360</v>
+        <v>1463</v>
       </c>
       <c r="D67" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E67" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F67" t="n">
-        <v>61.5</v>
+        <v>62.3</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68">
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1389</v>
+        <v>1492</v>
       </c>
       <c r="D68" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E68" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F68" t="n">
-        <v>61.7</v>
+        <v>62.3</v>
       </c>
       <c r="G68" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69">
@@ -3109,19 +3109,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1007</v>
+        <v>1069</v>
       </c>
       <c r="D69" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E69" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F69" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G69" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1211</v>
+        <v>1280</v>
       </c>
       <c r="D70" t="n">
         <v>48.6</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71">
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1371</v>
+        <v>1475</v>
       </c>
       <c r="D71" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E71" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F71" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
       <c r="G71" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="D72" t="n">
         <v>49.9</v>
@@ -3235,10 +3235,10 @@
         <v>50.1</v>
       </c>
       <c r="F72" t="n">
-        <v>63.7</v>
+        <v>63.8</v>
       </c>
       <c r="G72" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="73">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1207</v>
+        <v>1282</v>
       </c>
       <c r="D73" t="n">
         <v>48.4</v>
@@ -3274,10 +3274,10 @@
         <v>51.6</v>
       </c>
       <c r="F73" t="n">
-        <v>66.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="D74" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E74" t="n">
         <v>50.2</v>
       </c>
-      <c r="E74" t="n">
-        <v>49.8</v>
-      </c>
       <c r="F74" t="n">
-        <v>53.1</v>
+        <v>53.5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
@@ -3339,23 +3339,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="D75" t="n">
-        <v>52.7</v>
+        <v>50.5</v>
       </c>
       <c r="E75" t="n">
-        <v>47.3</v>
+        <v>49.5</v>
       </c>
       <c r="F75" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3378,17 +3378,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="D76" t="n">
-        <v>50.2</v>
+        <v>52.7</v>
       </c>
       <c r="E76" t="n">
-        <v>49.8</v>
+        <v>47.3</v>
       </c>
       <c r="F76" t="n">
         <v>54.6</v>
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1022</v>
+        <v>1085</v>
       </c>
       <c r="D77" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E77" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F77" t="n">
-        <v>56.5</v>
+        <v>56.1</v>
       </c>
       <c r="G77" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1301</v>
+        <v>1396</v>
       </c>
       <c r="D78" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="E78" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
       <c r="F78" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="G78" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="D79" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E79" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="F79" t="n">
-        <v>57.6</v>
+        <v>58.1</v>
       </c>
       <c r="G79" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1069</v>
+        <v>1134</v>
       </c>
       <c r="D80" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="E80" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="F80" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81">
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1001</v>
+        <v>1088</v>
       </c>
       <c r="D81" t="n">
         <v>46.5</v>
@@ -3612,23 +3612,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>360</v>
+        <v>392</v>
       </c>
       <c r="D82" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="E82" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="F82" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="G82" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3655,19 +3655,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="D83" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="E83" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="F83" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="G83" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -3690,23 +3690,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D84" t="n">
-        <v>48.1</v>
+        <v>47.4</v>
       </c>
       <c r="E84" t="n">
-        <v>51.9</v>
+        <v>52.6</v>
       </c>
       <c r="F84" t="n">
-        <v>51.1</v>
+        <v>49.2</v>
       </c>
       <c r="G84" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="D85" t="n">
-        <v>47.1</v>
+        <v>47.5</v>
       </c>
       <c r="E85" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="F85" t="n">
-        <v>55.5</v>
+        <v>54.7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -3772,19 +3772,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="D86" t="n">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="E86" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="F86" t="n">
-        <v>56.3</v>
+        <v>56.7</v>
       </c>
       <c r="G86" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="D87" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="E87" t="n">
-        <v>53.2</v>
+        <v>53.8</v>
       </c>
       <c r="F87" t="n">
-        <v>57.3</v>
+        <v>56.8</v>
       </c>
       <c r="G87" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="D88" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E88" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F88" t="n">
-        <v>60.5</v>
+        <v>61.1</v>
       </c>
       <c r="G88" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="89">
@@ -3885,23 +3885,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D89" t="n">
-        <v>50.6</v>
+        <v>49.2</v>
       </c>
       <c r="E89" t="n">
-        <v>49.4</v>
+        <v>50.8</v>
       </c>
       <c r="F89" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="G89" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90">
@@ -3924,23 +3924,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E90" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F90" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="G90" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D91" t="n">
-        <v>51.8</v>
+        <v>50.2</v>
       </c>
       <c r="E91" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
       <c r="F91" t="n">
-        <v>62.1</v>
+        <v>62.6</v>
       </c>
       <c r="G91" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="92">
@@ -4002,23 +4002,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="D92" t="n">
-        <v>51.1</v>
+        <v>51.9</v>
       </c>
       <c r="E92" t="n">
-        <v>48.9</v>
+        <v>48.1</v>
       </c>
       <c r="F92" t="n">
-        <v>62.4</v>
+        <v>62.7</v>
       </c>
       <c r="G92" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="D93" t="n">
-        <v>48.2</v>
+        <v>47.9</v>
       </c>
       <c r="E93" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
       <c r="F93" t="n">
-        <v>71.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="G93" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4080,23 +4080,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1237</v>
+        <v>1500</v>
       </c>
       <c r="D94" t="n">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="F94" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="G94" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95">
@@ -4119,17 +4119,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1396</v>
+        <v>1458</v>
       </c>
       <c r="D95" t="n">
-        <v>49.3</v>
+        <v>51.2</v>
       </c>
       <c r="E95" t="n">
-        <v>50.7</v>
+        <v>48.8</v>
       </c>
       <c r="F95" t="n">
         <v>58.6</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1356</v>
+        <v>1336</v>
       </c>
       <c r="D96" t="n">
-        <v>51.3</v>
+        <v>50</v>
       </c>
       <c r="E96" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="G96" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1397</v>
+        <v>1501</v>
       </c>
       <c r="D97" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E97" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F97" t="n">
         <v>59.6</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1397</v>
+        <v>1501</v>
       </c>
       <c r="D98" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E98" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F98" t="n">
-        <v>59.7</v>
+        <v>60</v>
       </c>
       <c r="G98" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="99">
@@ -4275,23 +4275,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1347</v>
+        <v>1484</v>
       </c>
       <c r="D99" t="n">
-        <v>49.6</v>
+        <v>48.9</v>
       </c>
       <c r="E99" t="n">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="F99" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="G99" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100">
@@ -4314,23 +4314,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1381</v>
+        <v>1494</v>
       </c>
       <c r="D100" t="n">
-        <v>48.5</v>
+        <v>49.9</v>
       </c>
       <c r="E100" t="n">
-        <v>51.5</v>
+        <v>50.1</v>
       </c>
       <c r="F100" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G100" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4353,17 +4353,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1390</v>
+        <v>1446</v>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F101" t="n">
         <v>60.6</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102">
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1396</v>
+        <v>1500</v>
       </c>
       <c r="D102" t="n">
         <v>49.5</v>
@@ -4405,10 +4405,10 @@
         <v>50.5</v>
       </c>
       <c r="F102" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
       <c r="G102" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1376</v>
+        <v>1480</v>
       </c>
       <c r="D103" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E103" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F103" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="G103" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37609</v>
+        <v>38044</v>
       </c>
       <c r="D2" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
         <v>49.8</v>
@@ -4580,23 +4580,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EURCHF</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37326</v>
+        <v>37593</v>
       </c>
       <c r="D3" t="n">
-        <v>49.9</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>50.1</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -4619,17 +4619,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37155</v>
+        <v>37760</v>
       </c>
       <c r="D4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
         <v>49</v>
@@ -4662,13 +4662,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37884</v>
+        <v>38326</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E5" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F5" t="n">
         <v>51.4</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37937</v>
+        <v>38377</v>
       </c>
       <c r="D6" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E6" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F6" t="n">
         <v>51.8</v>
@@ -4740,13 +4740,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37799</v>
+        <v>38240</v>
       </c>
       <c r="D7" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E7" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F7" t="n">
         <v>48.1</v>
@@ -4779,13 +4779,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37950</v>
+        <v>38390</v>
       </c>
       <c r="D8" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E8" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F8" t="n">
         <v>51.9</v>
@@ -4818,13 +4818,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37340</v>
+        <v>37775</v>
       </c>
       <c r="D9" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E9" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F9" t="n">
         <v>45.8</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37777</v>
+        <v>38214</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37835</v>
+        <v>38273</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,19 +4935,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37861</v>
+        <v>38298</v>
       </c>
       <c r="D12" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E12" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F12" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="G12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37661</v>
+        <v>38099</v>
       </c>
       <c r="D13" t="n">
         <v>50.2</v>
@@ -5013,13 +5013,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37616</v>
+        <v>38048</v>
       </c>
       <c r="D14" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F14" t="n">
         <v>40.2</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37742</v>
+        <v>38177</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,19 +5091,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37757</v>
+        <v>38193</v>
       </c>
       <c r="D16" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E16" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F16" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="G16" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>37888</v>
+        <v>38315</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5139,10 +5139,10 @@
         <v>52.8</v>
       </c>
       <c r="F17" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -5169,19 +5169,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8374</v>
+        <v>8080</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F18" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -5208,19 +5208,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37557</v>
+        <v>37996</v>
       </c>
       <c r="D19" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37088</v>
+        <v>37504</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>37721</v>
+        <v>38159</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5295,10 +5295,10 @@
         <v>48.3</v>
       </c>
       <c r="F21" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -5312,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34764</v>
+        <v>34794</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -5364,13 +5364,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37885</v>
+        <v>38321</v>
       </c>
       <c r="D23" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E23" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F23" t="n">
         <v>46.4</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>37624</v>
+        <v>38058</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5412,10 +5412,10 @@
         <v>50.2</v>
       </c>
       <c r="F24" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37653</v>
+        <v>38091</v>
       </c>
       <c r="D25" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E25" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
         <v>53.9</v>
@@ -5481,19 +5481,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>37897</v>
+        <v>38319</v>
       </c>
       <c r="D26" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E26" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F26" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="G26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>37579</v>
+        <v>38017</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5529,10 +5529,10 @@
         <v>49.6</v>
       </c>
       <c r="F27" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="G27" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -5559,13 +5559,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37241</v>
+        <v>37674</v>
       </c>
       <c r="D28" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E28" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F28" t="n">
         <v>54.5</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37388</v>
+        <v>37824</v>
       </c>
       <c r="D29" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E29" t="n">
         <v>49.9</v>
-      </c>
-      <c r="E29" t="n">
-        <v>50.1</v>
       </c>
       <c r="F29" t="n">
         <v>54.7</v>
@@ -5633,20 +5633,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37943</v>
+        <v>38197</v>
       </c>
       <c r="D30" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
       <c r="E30" t="n">
-        <v>50.5</v>
+        <v>49.4</v>
       </c>
       <c r="F30" t="n">
-        <v>44.9</v>
+        <v>55.1</v>
       </c>
       <c r="G30" t="n">
         <v>5.1</v>
@@ -5672,23 +5672,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37757</v>
+        <v>38382</v>
       </c>
       <c r="D31" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="E31" t="n">
-        <v>49.5</v>
+        <v>50.4</v>
       </c>
       <c r="F31" t="n">
-        <v>55.1</v>
+        <v>44.8</v>
       </c>
       <c r="G31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -5715,19 +5715,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37803</v>
+        <v>38240</v>
       </c>
       <c r="D32" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E32" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F32" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="G32" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -5754,13 +5754,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37915</v>
+        <v>38356</v>
       </c>
       <c r="D33" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E33" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F33" t="n">
         <v>44.5</v>
@@ -5780,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34">
@@ -5793,13 +5793,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37919</v>
+        <v>38359</v>
       </c>
       <c r="D34" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E34" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F34" t="n">
         <v>44.5</v>
@@ -5819,7 +5819,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37881</v>
+        <v>38323</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,13 +5871,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38166</v>
+        <v>38606</v>
       </c>
       <c r="D36" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E36" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F36" t="n">
         <v>43.3</v>
@@ -5910,19 +5910,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38156</v>
+        <v>38598</v>
       </c>
       <c r="D37" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E37" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F37" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="G37" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -5949,13 +5949,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35227</v>
+        <v>35638</v>
       </c>
       <c r="D38" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E38" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F38" t="n">
         <v>57.3</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34878</v>
+        <v>34908</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,13 +6027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37641</v>
+        <v>38078</v>
       </c>
       <c r="D40" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E40" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F40" t="n">
         <v>58.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37509</v>
+        <v>37943</v>
       </c>
       <c r="D41" t="n">
         <v>50.3</v>
@@ -6092,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="42">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37684</v>
+        <v>38122</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38078</v>
+        <v>38516</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,19 +6183,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38130</v>
+        <v>38573</v>
       </c>
       <c r="D44" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E44" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F44" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="G44" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -6222,19 +6222,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38125</v>
+        <v>38562</v>
       </c>
       <c r="D45" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E45" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F45" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="G45" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -6261,19 +6261,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37944</v>
+        <v>38382</v>
       </c>
       <c r="D46" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E46" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F46" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="G46" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -6300,19 +6300,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37899</v>
+        <v>38332</v>
       </c>
       <c r="D47" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E47" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F47" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="G47" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -6326,7 +6326,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48">
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38073</v>
+        <v>38516</v>
       </c>
       <c r="D48" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E48" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F48" t="n">
         <v>39.8</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34710</v>
+        <v>34740</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,13 +6417,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37555</v>
+        <v>37993</v>
       </c>
       <c r="D50" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E50" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F50" t="n">
         <v>61.5</v>
@@ -6452,23 +6452,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37597</v>
+        <v>37985</v>
       </c>
       <c r="D51" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="E51" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="F51" t="n">
-        <v>62.1</v>
+        <v>38</v>
       </c>
       <c r="G51" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>92</v>
@@ -6491,20 +6491,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37549</v>
+        <v>38031</v>
       </c>
       <c r="D52" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>37.9</v>
+        <v>62.1</v>
       </c>
       <c r="G52" t="n">
         <v>12.1</v>
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="J52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>93</v>
@@ -6534,19 +6534,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38023</v>
+        <v>38444</v>
       </c>
       <c r="D53" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E53" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F53" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="G53" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -6573,19 +6573,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36058</v>
+        <v>36467</v>
       </c>
       <c r="D54" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E54" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F54" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="G54" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37774</v>
+        <v>38211</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37485</v>
+        <v>37915</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,19 +6690,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37840</v>
+        <v>38276</v>
       </c>
       <c r="D57" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="E57" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="F57" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="G57" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -6729,19 +6729,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37913</v>
+        <v>38356</v>
       </c>
       <c r="D58" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E58" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F58" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38115</v>
+        <v>38558</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,13 +6807,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36513</v>
+        <v>36867</v>
       </c>
       <c r="D60" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="E60" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="F60" t="n">
         <v>49.8</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34945</v>
+        <v>34991</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36938</v>
+        <v>37374</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23353</v>
+        <v>23329</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23778</v>
+        <v>23752</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -6972,10 +6972,10 @@
         <v>49.2</v>
       </c>
       <c r="F64" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="G64" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -6989,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65">
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23720</v>
+        <v>23776</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37822</v>
+        <v>38261</v>
       </c>
       <c r="D66" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
         <v>55.9</v>
@@ -7076,23 +7076,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21098</v>
+        <v>37766</v>
       </c>
       <c r="D67" t="n">
-        <v>51.9</v>
+        <v>50.6</v>
       </c>
       <c r="E67" t="n">
-        <v>48.1</v>
+        <v>49.4</v>
       </c>
       <c r="F67" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="G67" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37326</v>
+        <v>21154</v>
       </c>
       <c r="D68" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="E68" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="F68" t="n">
         <v>56.1</v>
@@ -7158,13 +7158,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>35677</v>
+        <v>36035</v>
       </c>
       <c r="D69" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E69" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30393</v>
+        <v>30447</v>
       </c>
       <c r="D70" t="n">
         <v>50.9</v>
@@ -7236,13 +7236,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37028</v>
+        <v>37386</v>
       </c>
       <c r="D71" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E71" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F71" t="n">
         <v>56.8</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33028</v>
+        <v>32913</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7284,10 +7284,10 @@
         <v>49.8</v>
       </c>
       <c r="F72" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="G72" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25919</v>
+        <v>25954</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14211</v>
+        <v>14168</v>
       </c>
       <c r="D74" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E74" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F74" t="n">
         <v>51</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14011</v>
+        <v>14045</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7401,10 +7401,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15074</v>
+        <v>15100</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26513</v>
+        <v>26548</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7479,10 +7479,10 @@
         <v>50.1</v>
       </c>
       <c r="F77" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="G77" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35349</v>
+        <v>35759</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28551</v>
+        <v>28528</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15689</v>
+        <v>15722</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27418</v>
+        <v>27768</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7665,19 +7665,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10399</v>
+        <v>10396</v>
       </c>
       <c r="D82" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E82" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F82" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10401</v>
+        <v>10397</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7713,10 +7713,10 @@
         <v>49.4</v>
       </c>
       <c r="F83" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="G83" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -7730,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10697</v>
+        <v>10695</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7791,10 +7791,10 @@
         <v>49.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="G85" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10180</v>
+        <v>10181</v>
       </c>
       <c r="D86" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E86" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F86" t="n">
         <v>56</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10650</v>
+        <v>10648</v>
       </c>
       <c r="D87" t="n">
         <v>50.8</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10758</v>
+        <v>10756</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -7908,10 +7908,10 @@
         <v>48.4</v>
       </c>
       <c r="F88" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="G88" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10893</v>
+        <v>10892</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -7947,10 +7947,10 @@
         <v>48.5</v>
       </c>
       <c r="F89" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G89" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="90">
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10912</v>
+        <v>10893</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -8016,13 +8016,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10821</v>
+        <v>10819</v>
       </c>
       <c r="D91" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="E91" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="F91" t="n">
         <v>59.4</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10261</v>
+        <v>10242</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="93">
@@ -8097,16 +8097,16 @@
         <v>10172</v>
       </c>
       <c r="D93" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E93" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G93" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -8133,19 +8133,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37359</v>
+        <v>37796</v>
       </c>
       <c r="D94" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="G94" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37958</v>
+        <v>38401</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8181,10 +8181,10 @@
         <v>50.7</v>
       </c>
       <c r="F95" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G95" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35594</v>
+        <v>36020</v>
       </c>
       <c r="D96" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E96" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F96" t="n">
         <v>53.8</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38075</v>
+        <v>38517</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,13 +8289,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37293</v>
+        <v>37726</v>
       </c>
       <c r="D98" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E98" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F98" t="n">
         <v>54</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37868</v>
+        <v>38310</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37472</v>
+        <v>37911</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8393,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="101">
@@ -8406,13 +8406,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38152</v>
+        <v>38594</v>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F101" t="n">
         <v>54.5</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37731</v>
+        <v>38172</v>
       </c>
       <c r="D102" t="n">
         <v>49.7</v>
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38172</v>
+        <v>38615</v>
       </c>
       <c r="D103" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E103" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F103" t="n">
         <v>54.9</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1375</v>
+        <v>1474</v>
       </c>
       <c r="D2" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="E2" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>36.2</v>
+        <v>36.6</v>
       </c>
       <c r="G2" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1388</v>
+        <v>1490</v>
       </c>
       <c r="D3" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="E3" t="n">
         <v>49.7</v>
       </c>
-      <c r="E3" t="n">
-        <v>50.3</v>
-      </c>
       <c r="F3" t="n">
-        <v>38.8</v>
+        <v>39.1</v>
       </c>
       <c r="G3" t="n">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1362</v>
+        <v>1466</v>
       </c>
       <c r="D4" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="E4" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="F4" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="G4" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1359</v>
+        <v>1460</v>
       </c>
       <c r="D5" t="n">
         <v>51.4</v>
@@ -8720,10 +8720,10 @@
         <v>48.6</v>
       </c>
       <c r="F5" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8737,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1361</v>
+        <v>1464</v>
       </c>
       <c r="D6" t="n">
-        <v>51.7</v>
+        <v>52.4</v>
       </c>
       <c r="E6" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="F6" t="n">
-        <v>43.1</v>
+        <v>43.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1375</v>
+        <v>1477</v>
       </c>
       <c r="D7" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="E7" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="F7" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8828,19 +8828,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1332</v>
+        <v>1434</v>
       </c>
       <c r="D8" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="E8" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="F8" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8867,19 +8867,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1387</v>
+        <v>1490</v>
       </c>
       <c r="D9" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="E9" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="F9" t="n">
-        <v>47.2</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,13 +8906,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1386</v>
+        <v>1490</v>
       </c>
       <c r="D10" t="n">
-        <v>48.1</v>
+        <v>48.6</v>
       </c>
       <c r="E10" t="n">
-        <v>51.9</v>
+        <v>51.4</v>
       </c>
       <c r="F10" t="n">
         <v>47.5</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1389</v>
+        <v>1491</v>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="F11" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1391</v>
+        <v>1494</v>
       </c>
       <c r="D12" t="n">
-        <v>46.7</v>
+        <v>47.2</v>
       </c>
       <c r="E12" t="n">
-        <v>53.3</v>
+        <v>52.8</v>
       </c>
       <c r="F12" t="n">
-        <v>53.1</v>
+        <v>52.8</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1364</v>
+        <v>1467</v>
       </c>
       <c r="D13" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="E13" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="F13" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1390</v>
+        <v>1494</v>
       </c>
       <c r="D14" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="E14" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>55.6</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1371</v>
+        <v>1472</v>
       </c>
       <c r="D15" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E15" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F15" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="G15" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1365</v>
+        <v>1468</v>
       </c>
       <c r="D16" t="n">
-        <v>47.3</v>
+        <v>47.6</v>
       </c>
       <c r="E16" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
       <c r="F16" t="n">
-        <v>64.5</v>
+        <v>64</v>
       </c>
       <c r="G16" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1300</v>
+        <v>1397</v>
       </c>
       <c r="D17" t="n">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="E17" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="F17" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="G17" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1396</v>
+        <v>1500</v>
       </c>
       <c r="D18" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E18" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F18" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="G18" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9253,17 +9253,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1361</v>
+        <v>1498</v>
       </c>
       <c r="D19" t="n">
-        <v>48.7</v>
+        <v>49.9</v>
       </c>
       <c r="E19" t="n">
-        <v>51.3</v>
+        <v>50.1</v>
       </c>
       <c r="F19" t="n">
         <v>35.3</v>
@@ -9292,23 +9292,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1394</v>
+        <v>1462</v>
       </c>
       <c r="D20" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="E20" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="F20" t="n">
-        <v>35.4</v>
+        <v>35.8</v>
       </c>
       <c r="G20" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9331,23 +9331,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1395</v>
+        <v>1501</v>
       </c>
       <c r="D21" t="n">
-        <v>50.5</v>
+        <v>52</v>
       </c>
       <c r="E21" t="n">
-        <v>49.5</v>
+        <v>48</v>
       </c>
       <c r="F21" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="G21" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
@@ -9370,23 +9370,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1397</v>
+        <v>1499</v>
       </c>
       <c r="D22" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E22" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F22" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="G22" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>7</v>
@@ -9409,23 +9409,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1387</v>
+        <v>1343</v>
       </c>
       <c r="D23" t="n">
-        <v>51</v>
+        <v>51.6</v>
       </c>
       <c r="E23" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="F23" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="G23" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9448,23 +9448,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1269</v>
+        <v>1490</v>
       </c>
       <c r="D24" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="E24" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="F24" t="n">
-        <v>37.2</v>
+        <v>37.4</v>
       </c>
       <c r="G24" t="n">
-        <v>12.8</v>
+        <v>12.6</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9491,19 +9491,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1391</v>
+        <v>1495</v>
       </c>
       <c r="D25" t="n">
-        <v>49.8</v>
+        <v>50.6</v>
       </c>
       <c r="E25" t="n">
-        <v>50.2</v>
+        <v>49.4</v>
       </c>
       <c r="F25" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="G25" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9530,19 +9530,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1378</v>
+        <v>1481</v>
       </c>
       <c r="D26" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="E26" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="F26" t="n">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9</v>
+        <v>12.3</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1397</v>
+        <v>1501</v>
       </c>
       <c r="D27" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="E27" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="F27" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="G27" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,13 +9608,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1391</v>
+        <v>1494</v>
       </c>
       <c r="D28" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="E28" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="F28" t="n">
         <v>38.6</v>
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1383</v>
+        <v>1487</v>
       </c>
       <c r="D29" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="E29" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="F29" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="G29" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1380</v>
+        <v>1483</v>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>52.5</v>
       </c>
       <c r="F30" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="G30" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1384</v>
+        <v>1488</v>
       </c>
       <c r="D31" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="E31" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="F31" t="n">
-        <v>42.3</v>
+        <v>41.9</v>
       </c>
       <c r="G31" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32">
@@ -9764,19 +9764,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1273</v>
+        <v>1347</v>
       </c>
       <c r="D32" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E32" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F32" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9790,7 +9790,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1386</v>
+        <v>1486</v>
       </c>
       <c r="D33" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="E33" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="F33" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9829,7 +9829,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1393</v>
+        <v>1495</v>
       </c>
       <c r="D34" t="n">
-        <v>47.7</v>
+        <v>48.4</v>
       </c>
       <c r="E34" t="n">
-        <v>52.3</v>
+        <v>51.6</v>
       </c>
       <c r="F34" t="n">
-        <v>43.9</v>
+        <v>43.5</v>
       </c>
       <c r="G34" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1368</v>
+        <v>1471</v>
       </c>
       <c r="D35" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="E35" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="F35" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="G35" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1382</v>
+        <v>1486</v>
       </c>
       <c r="D36" t="n">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="E36" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="F36" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="G36" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1375</v>
+        <v>1476</v>
       </c>
       <c r="D37" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1271</v>
+        <v>1345</v>
       </c>
       <c r="D38" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="E38" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="F38" t="n">
         <v>48.8</v>
@@ -10033,23 +10033,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1352</v>
+        <v>1445</v>
       </c>
       <c r="D39" t="n">
-        <v>51.3</v>
+        <v>49.6</v>
       </c>
       <c r="E39" t="n">
-        <v>48.7</v>
+        <v>50.4</v>
       </c>
       <c r="F39" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -10072,23 +10072,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1348</v>
+        <v>1455</v>
       </c>
       <c r="D40" t="n">
-        <v>49.3</v>
+        <v>51.3</v>
       </c>
       <c r="E40" t="n">
-        <v>50.7</v>
+        <v>48.7</v>
       </c>
       <c r="F40" t="n">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
       <c r="G40" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -10115,13 +10115,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1393</v>
+        <v>1496</v>
       </c>
       <c r="D41" t="n">
-        <v>47.1</v>
+        <v>46.9</v>
       </c>
       <c r="E41" t="n">
-        <v>52.9</v>
+        <v>53.1</v>
       </c>
       <c r="F41" t="n">
         <v>51.5</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="D42" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="F42" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="G42" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10189,23 +10189,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1361</v>
+        <v>1482</v>
       </c>
       <c r="D43" t="n">
-        <v>46</v>
+        <v>51.6</v>
       </c>
       <c r="E43" t="n">
-        <v>54</v>
+        <v>48.4</v>
       </c>
       <c r="F43" t="n">
-        <v>54.1</v>
+        <v>54.2</v>
       </c>
       <c r="G43" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10228,17 +10228,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1383</v>
+        <v>1462</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>46.4</v>
       </c>
       <c r="E44" t="n">
-        <v>49</v>
+        <v>53.6</v>
       </c>
       <c r="F44" t="n">
         <v>54.4</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1355</v>
+        <v>1459</v>
       </c>
       <c r="D45" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="E45" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="F45" t="n">
-        <v>55.7</v>
+        <v>56.2</v>
       </c>
       <c r="G45" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46">
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1376</v>
+        <v>1480</v>
       </c>
       <c r="D46" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="E46" t="n">
-        <v>52</v>
+        <v>51.2</v>
       </c>
       <c r="F46" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="G46" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="47">
@@ -10349,19 +10349,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1386</v>
+        <v>1489</v>
       </c>
       <c r="D47" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="E47" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F47" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="G47" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
@@ -10388,19 +10388,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1382</v>
+        <v>1484</v>
       </c>
       <c r="D48" t="n">
-        <v>45.4</v>
+        <v>46</v>
       </c>
       <c r="E48" t="n">
-        <v>54.6</v>
+        <v>54</v>
       </c>
       <c r="F48" t="n">
-        <v>58.9</v>
+        <v>58.5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="49">
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1263</v>
+        <v>1360</v>
       </c>
       <c r="D49" t="n">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
       <c r="E49" t="n">
-        <v>52.6</v>
+        <v>52.1</v>
       </c>
       <c r="F49" t="n">
-        <v>58.9</v>
+        <v>59.1</v>
       </c>
       <c r="G49" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50">
@@ -10466,19 +10466,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1369</v>
+        <v>1470</v>
       </c>
       <c r="D50" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E50" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F50" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="G50" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1370</v>
+        <v>1473</v>
       </c>
       <c r="D51" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E51" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F51" t="n">
-        <v>59.8</v>
+        <v>60</v>
       </c>
       <c r="G51" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52">
@@ -10544,7 +10544,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1360</v>
+        <v>1462</v>
       </c>
       <c r="D52" t="n">
         <v>51.2</v>
@@ -10553,10 +10553,10 @@
         <v>48.8</v>
       </c>
       <c r="F52" t="n">
-        <v>62.1</v>
+        <v>62.2</v>
       </c>
       <c r="G52" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="53">
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1371</v>
+        <v>1471</v>
       </c>
       <c r="D53" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E53" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F53" t="n">
-        <v>66.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1371</v>
+        <v>1473</v>
       </c>
       <c r="D54" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="E54" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="F54" t="n">
-        <v>67.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1386</v>
+        <v>1490</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="E55" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="F55" t="n">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="G55" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1376</v>
+        <v>1480</v>
       </c>
       <c r="D56" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="E56" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="F56" t="n">
         <v>74.8</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1392</v>
+        <v>1495</v>
       </c>
       <c r="D57" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E57" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F57" t="n">
-        <v>82.3</v>
+        <v>82.7</v>
       </c>
       <c r="G57" t="n">
-        <v>32.3</v>
+        <v>32.7</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1394</v>
+        <v>1498</v>
       </c>
       <c r="D58" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E58" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F58" t="n">
-        <v>83.2</v>
+        <v>83.5</v>
       </c>
       <c r="G58" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1394</v>
+        <v>1498</v>
       </c>
       <c r="D59" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E59" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F59" t="n">
-        <v>94.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="G59" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10856,19 +10856,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1298</v>
+        <v>1372</v>
       </c>
       <c r="D60" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E60" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F60" t="n">
-        <v>42.8</v>
+        <v>42.5</v>
       </c>
       <c r="G60" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1431</v>
+        <v>1457</v>
       </c>
       <c r="D61" t="n">
         <v>50.2</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -10930,23 +10930,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>863</v>
+        <v>929</v>
       </c>
       <c r="D62" t="n">
-        <v>48.1</v>
+        <v>49.6</v>
       </c>
       <c r="E62" t="n">
-        <v>51.9</v>
+        <v>50.4</v>
       </c>
       <c r="F62" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="G62" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63">
@@ -10969,37 +10969,37 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>874</v>
+        <v>919</v>
       </c>
       <c r="D63" t="n">
-        <v>49.4</v>
+        <v>47.9</v>
       </c>
       <c r="E63" t="n">
-        <v>50.6</v>
+        <v>52.1</v>
       </c>
       <c r="F63" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="G63" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Indices</t>
+        </is>
+      </c>
+      <c r="J63" t="b">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
         <v>58</v>
-      </c>
-      <c r="G63" t="n">
-        <v>8</v>
-      </c>
-      <c r="H63" t="b">
-        <v>1</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>Indices</t>
-        </is>
-      </c>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>59</v>
       </c>
     </row>
     <row r="64">
@@ -11012,19 +11012,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>886</v>
+        <v>942</v>
       </c>
       <c r="D64" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="E64" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="F64" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="G64" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>868</v>
+        <v>1338</v>
       </c>
       <c r="D65" t="n">
-        <v>52</v>
+        <v>48.8</v>
       </c>
       <c r="E65" t="n">
-        <v>48</v>
+        <v>51.2</v>
       </c>
       <c r="F65" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G65" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11086,23 +11086,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1245</v>
+        <v>922</v>
       </c>
       <c r="D66" t="n">
-        <v>48.5</v>
+        <v>51.7</v>
       </c>
       <c r="E66" t="n">
-        <v>51.5</v>
+        <v>48.3</v>
       </c>
       <c r="F66" t="n">
-        <v>59.3</v>
+        <v>59.9</v>
       </c>
       <c r="G66" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67">
@@ -11129,19 +11129,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1360</v>
+        <v>1463</v>
       </c>
       <c r="D67" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E67" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F67" t="n">
-        <v>61.5</v>
+        <v>62.3</v>
       </c>
       <c r="G67" t="n">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
@@ -11168,19 +11168,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1389</v>
+        <v>1492</v>
       </c>
       <c r="D68" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E68" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F68" t="n">
-        <v>61.7</v>
+        <v>62.3</v>
       </c>
       <c r="G68" t="n">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69">
@@ -11207,19 +11207,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1007</v>
+        <v>1069</v>
       </c>
       <c r="D69" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E69" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F69" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G69" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70">
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1211</v>
+        <v>1280</v>
       </c>
       <c r="D70" t="n">
         <v>48.6</v>
@@ -11285,19 +11285,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1371</v>
+        <v>1475</v>
       </c>
       <c r="D71" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E71" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F71" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
       <c r="G71" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72">
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1434</v>
+        <v>1460</v>
       </c>
       <c r="D72" t="n">
         <v>49.9</v>
@@ -11333,10 +11333,10 @@
         <v>50.1</v>
       </c>
       <c r="F72" t="n">
-        <v>63.7</v>
+        <v>63.8</v>
       </c>
       <c r="G72" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11363,7 +11363,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1207</v>
+        <v>1282</v>
       </c>
       <c r="D73" t="n">
         <v>48.4</v>
@@ -11372,10 +11372,10 @@
         <v>51.6</v>
       </c>
       <c r="F73" t="n">
-        <v>66.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>540</v>
+        <v>566</v>
       </c>
       <c r="D74" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="E74" t="n">
         <v>50.2</v>
       </c>
-      <c r="E74" t="n">
-        <v>49.8</v>
-      </c>
       <c r="F74" t="n">
-        <v>53.1</v>
+        <v>53.5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11437,23 +11437,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>526</v>
+        <v>545</v>
       </c>
       <c r="D75" t="n">
-        <v>52.7</v>
+        <v>50.5</v>
       </c>
       <c r="E75" t="n">
-        <v>47.3</v>
+        <v>49.5</v>
       </c>
       <c r="F75" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11476,17 +11476,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>520</v>
+        <v>560</v>
       </c>
       <c r="D76" t="n">
-        <v>50.2</v>
+        <v>52.7</v>
       </c>
       <c r="E76" t="n">
-        <v>49.8</v>
+        <v>47.3</v>
       </c>
       <c r="F76" t="n">
         <v>54.6</v>
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1022</v>
+        <v>1085</v>
       </c>
       <c r="D77" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E77" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F77" t="n">
-        <v>56.5</v>
+        <v>56.1</v>
       </c>
       <c r="G77" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78">
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1301</v>
+        <v>1396</v>
       </c>
       <c r="D78" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="E78" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
       <c r="F78" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="G78" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="D79" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E79" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="F79" t="n">
-        <v>57.6</v>
+        <v>58.1</v>
       </c>
       <c r="G79" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1069</v>
+        <v>1134</v>
       </c>
       <c r="D80" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="E80" t="n">
-        <v>53.1</v>
+        <v>53.4</v>
       </c>
       <c r="F80" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1001</v>
+        <v>1088</v>
       </c>
       <c r="D81" t="n">
         <v>46.5</v>
@@ -11710,23 +11710,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D82" t="n">
-        <v>50.5</v>
+        <v>47.4</v>
       </c>
       <c r="E82" t="n">
-        <v>49.5</v>
+        <v>52.6</v>
       </c>
       <c r="F82" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="G82" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11749,17 +11749,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>360</v>
+        <v>393</v>
       </c>
       <c r="D83" t="n">
-        <v>48.3</v>
+        <v>49.9</v>
       </c>
       <c r="E83" t="n">
-        <v>51.7</v>
+        <v>50.1</v>
       </c>
       <c r="F83" t="n">
         <v>49.4</v>
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="D84" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E84" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F84" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="G84" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85">
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="D85" t="n">
-        <v>47.1</v>
+        <v>47.5</v>
       </c>
       <c r="E85" t="n">
-        <v>52.9</v>
+        <v>52.5</v>
       </c>
       <c r="F85" t="n">
-        <v>55.5</v>
+        <v>54.7</v>
       </c>
       <c r="G85" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11870,19 +11870,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="D86" t="n">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="E86" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="F86" t="n">
-        <v>56.3</v>
+        <v>56.7</v>
       </c>
       <c r="G86" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87">
@@ -11909,19 +11909,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="D87" t="n">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="E87" t="n">
-        <v>53.2</v>
+        <v>53.8</v>
       </c>
       <c r="F87" t="n">
-        <v>57.3</v>
+        <v>56.8</v>
       </c>
       <c r="G87" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="D88" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E88" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F88" t="n">
-        <v>60.5</v>
+        <v>61.1</v>
       </c>
       <c r="G88" t="n">
-        <v>10.5</v>
+        <v>11.1</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89">
@@ -11983,23 +11983,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="D89" t="n">
-        <v>50.6</v>
+        <v>49.2</v>
       </c>
       <c r="E89" t="n">
-        <v>49.4</v>
+        <v>50.8</v>
       </c>
       <c r="F89" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
       <c r="G89" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90">
@@ -12022,23 +12022,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>384</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E90" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F90" t="n">
-        <v>62</v>
+        <v>61.9</v>
       </c>
       <c r="G90" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D91" t="n">
-        <v>51.8</v>
+        <v>50.2</v>
       </c>
       <c r="E91" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
       <c r="F91" t="n">
-        <v>62.1</v>
+        <v>62.6</v>
       </c>
       <c r="G91" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92">
@@ -12100,23 +12100,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="D92" t="n">
-        <v>51.1</v>
+        <v>51.9</v>
       </c>
       <c r="E92" t="n">
-        <v>48.9</v>
+        <v>48.1</v>
       </c>
       <c r="F92" t="n">
-        <v>62.4</v>
+        <v>62.7</v>
       </c>
       <c r="G92" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>353</v>
+        <v>378</v>
       </c>
       <c r="D93" t="n">
-        <v>48.2</v>
+        <v>47.9</v>
       </c>
       <c r="E93" t="n">
-        <v>51.8</v>
+        <v>52.1</v>
       </c>
       <c r="F93" t="n">
-        <v>71.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="G93" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12178,23 +12178,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1237</v>
+        <v>1500</v>
       </c>
       <c r="D94" t="n">
-        <v>50</v>
+        <v>49.1</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>50.9</v>
       </c>
       <c r="F94" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="G94" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="95">
@@ -12217,17 +12217,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1396</v>
+        <v>1458</v>
       </c>
       <c r="D95" t="n">
-        <v>49.3</v>
+        <v>51.2</v>
       </c>
       <c r="E95" t="n">
-        <v>50.7</v>
+        <v>48.8</v>
       </c>
       <c r="F95" t="n">
         <v>58.6</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96">
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1356</v>
+        <v>1336</v>
       </c>
       <c r="D96" t="n">
-        <v>51.3</v>
+        <v>50</v>
       </c>
       <c r="E96" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="G96" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="97">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1397</v>
+        <v>1501</v>
       </c>
       <c r="D97" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E97" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F97" t="n">
         <v>59.6</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1397</v>
+        <v>1501</v>
       </c>
       <c r="D98" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E98" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F98" t="n">
-        <v>59.7</v>
+        <v>60</v>
       </c>
       <c r="G98" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="99">
@@ -12373,23 +12373,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1347</v>
+        <v>1484</v>
       </c>
       <c r="D99" t="n">
-        <v>49.6</v>
+        <v>48.9</v>
       </c>
       <c r="E99" t="n">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="F99" t="n">
-        <v>60.4</v>
+        <v>60.1</v>
       </c>
       <c r="G99" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100">
@@ -12412,23 +12412,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1381</v>
+        <v>1494</v>
       </c>
       <c r="D100" t="n">
-        <v>48.5</v>
+        <v>49.9</v>
       </c>
       <c r="E100" t="n">
-        <v>51.5</v>
+        <v>50.1</v>
       </c>
       <c r="F100" t="n">
-        <v>60.4</v>
+        <v>60.5</v>
       </c>
       <c r="G100" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12451,17 +12451,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1390</v>
+        <v>1446</v>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F101" t="n">
         <v>60.6</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102">
@@ -12494,7 +12494,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1396</v>
+        <v>1500</v>
       </c>
       <c r="D102" t="n">
         <v>49.5</v>
@@ -12503,10 +12503,10 @@
         <v>50.5</v>
       </c>
       <c r="F102" t="n">
-        <v>60.7</v>
+        <v>60.6</v>
       </c>
       <c r="G102" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1376</v>
+        <v>1480</v>
       </c>
       <c r="D103" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E103" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F103" t="n">
-        <v>61.6</v>
+        <v>61.8</v>
       </c>
       <c r="G103" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12643,13 +12643,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>37616</v>
+        <v>38048</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F2" t="n">
         <v>40.2</v>
@@ -12669,7 +12669,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37661</v>
+        <v>38099</v>
       </c>
       <c r="D3" t="n">
         <v>50.2</v>
@@ -12721,19 +12721,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37861</v>
+        <v>38298</v>
       </c>
       <c r="D4" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E4" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F4" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="G4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -12760,13 +12760,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37340</v>
+        <v>37775</v>
       </c>
       <c r="D5" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E5" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F5" t="n">
         <v>45.8</v>
@@ -12786,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -12799,13 +12799,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>37799</v>
+        <v>38240</v>
       </c>
       <c r="D6" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E6" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F6" t="n">
         <v>48.1</v>
@@ -12838,13 +12838,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37326</v>
+        <v>37760</v>
       </c>
       <c r="D7" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
         <v>49</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37155</v>
+        <v>37593</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12886,10 +12886,10 @@
         <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37609</v>
+        <v>38044</v>
       </c>
       <c r="D9" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
         <v>49.8</v>
@@ -12955,13 +12955,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37884</v>
+        <v>38326</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E10" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F10" t="n">
         <v>51.4</v>
@@ -12994,13 +12994,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>37937</v>
+        <v>38377</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E11" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F11" t="n">
         <v>51.8</v>
@@ -13033,13 +13033,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>37950</v>
+        <v>38390</v>
       </c>
       <c r="D12" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E12" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F12" t="n">
         <v>51.9</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37777</v>
+        <v>38214</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37835</v>
+        <v>38273</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>37742</v>
+        <v>38177</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,19 +13189,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>37757</v>
+        <v>38193</v>
       </c>
       <c r="D16" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E16" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F16" t="n">
-        <v>60.9</v>
+        <v>60.8</v>
       </c>
       <c r="G16" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -13228,19 +13228,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36058</v>
+        <v>36467</v>
       </c>
       <c r="D17" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E17" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F17" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="G17" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -13267,19 +13267,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38023</v>
+        <v>38444</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F18" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="G18" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -13306,19 +13306,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37549</v>
+        <v>37985</v>
       </c>
       <c r="D19" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E19" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F19" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34710</v>
+        <v>34740</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,13 +13384,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38073</v>
+        <v>38516</v>
       </c>
       <c r="D21" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E21" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F21" t="n">
         <v>39.8</v>
@@ -13423,19 +13423,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37899</v>
+        <v>38332</v>
       </c>
       <c r="D22" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E22" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F22" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="G22" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -13449,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -13462,19 +13462,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37944</v>
+        <v>38382</v>
       </c>
       <c r="D23" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E23" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F23" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="G23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -13501,19 +13501,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38125</v>
+        <v>38562</v>
       </c>
       <c r="D24" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E24" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F24" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="G24" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -13536,23 +13536,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38130</v>
+        <v>38516</v>
       </c>
       <c r="D25" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="E25" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="F25" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="G25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -13575,17 +13575,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38078</v>
+        <v>38573</v>
       </c>
       <c r="D26" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="E26" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="F26" t="n">
         <v>40.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34878</v>
+        <v>34908</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,19 +13657,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38156</v>
+        <v>38598</v>
       </c>
       <c r="D28" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E28" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F28" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -13696,13 +13696,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38166</v>
+        <v>38606</v>
       </c>
       <c r="D29" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E29" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F29" t="n">
         <v>43.3</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37881</v>
+        <v>38323</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,13 +13774,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>37915</v>
+        <v>38356</v>
       </c>
       <c r="D31" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E31" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F31" t="n">
         <v>44.5</v>
@@ -13813,13 +13813,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>37919</v>
+        <v>38359</v>
       </c>
       <c r="D32" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E32" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F32" t="n">
         <v>44.5</v>
@@ -13852,19 +13852,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37943</v>
+        <v>38382</v>
       </c>
       <c r="D33" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E33" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F33" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="G33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -13891,19 +13891,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>37897</v>
+        <v>38319</v>
       </c>
       <c r="D34" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E34" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F34" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="G34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -13917,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -13930,13 +13930,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>37885</v>
+        <v>38321</v>
       </c>
       <c r="D35" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E35" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F35" t="n">
         <v>46.4</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34764</v>
+        <v>34794</v>
       </c>
       <c r="D36" t="n">
         <v>49.8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>37721</v>
+        <v>38159</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14017,10 +14017,10 @@
         <v>48.3</v>
       </c>
       <c r="F37" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="G37" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37088</v>
+        <v>37504</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>37888</v>
+        <v>38315</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14095,10 +14095,10 @@
         <v>52.8</v>
       </c>
       <c r="F39" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -14112,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -14125,19 +14125,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8374</v>
+        <v>8080</v>
       </c>
       <c r="D40" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E40" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F40" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -14164,19 +14164,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37557</v>
+        <v>37996</v>
       </c>
       <c r="D41" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="G41" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>37624</v>
+        <v>38058</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14212,10 +14212,10 @@
         <v>50.2</v>
       </c>
       <c r="F42" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -14242,13 +14242,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37653</v>
+        <v>38091</v>
       </c>
       <c r="D43" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E43" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F43" t="n">
         <v>53.9</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>37579</v>
+        <v>38017</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14290,10 +14290,10 @@
         <v>49.6</v>
       </c>
       <c r="F44" t="n">
-        <v>54.5</v>
+        <v>54.4</v>
       </c>
       <c r="G44" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -14307,7 +14307,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="45">
@@ -14320,13 +14320,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37241</v>
+        <v>37674</v>
       </c>
       <c r="D45" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E45" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F45" t="n">
         <v>54.5</v>
@@ -14359,13 +14359,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37388</v>
+        <v>37824</v>
       </c>
       <c r="D46" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E46" t="n">
         <v>49.9</v>
-      </c>
-      <c r="E46" t="n">
-        <v>50.1</v>
       </c>
       <c r="F46" t="n">
         <v>54.7</v>
@@ -14398,13 +14398,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>37757</v>
+        <v>38197</v>
       </c>
       <c r="D47" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E47" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F47" t="n">
         <v>55.1</v>
@@ -14437,19 +14437,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>37803</v>
+        <v>38240</v>
       </c>
       <c r="D48" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E48" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F48" t="n">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="G48" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35227</v>
+        <v>35638</v>
       </c>
       <c r="D49" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E49" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F49" t="n">
         <v>57.3</v>
@@ -14515,13 +14515,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37641</v>
+        <v>38078</v>
       </c>
       <c r="D50" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E50" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F50" t="n">
         <v>58.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37509</v>
+        <v>37943</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -14580,7 +14580,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52">
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>37684</v>
+        <v>38122</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37555</v>
+        <v>37993</v>
       </c>
       <c r="D53" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E53" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F53" t="n">
         <v>61.5</v>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37597</v>
+        <v>38031</v>
       </c>
       <c r="D54" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E54" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F54" t="n">
         <v>62.1</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>37774</v>
+        <v>38211</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37485</v>
+        <v>37915</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,19 +14788,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>37840</v>
+        <v>38276</v>
       </c>
       <c r="D57" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="E57" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="F57" t="n">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="G57" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -14827,19 +14827,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>37913</v>
+        <v>38356</v>
       </c>
       <c r="D58" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E58" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F58" t="n">
-        <v>76.3</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G58" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38115</v>
+        <v>38558</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>34945</v>
+        <v>34991</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14931,7 +14931,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
@@ -14944,13 +14944,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36513</v>
+        <v>36867</v>
       </c>
       <c r="D61" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="E61" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="F61" t="n">
         <v>49.8</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>36938</v>
+        <v>37374</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23353</v>
+        <v>23329</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23778</v>
+        <v>23752</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15070,10 +15070,10 @@
         <v>49.2</v>
       </c>
       <c r="F64" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="G64" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23720</v>
+        <v>23776</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -15139,13 +15139,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>37822</v>
+        <v>38261</v>
       </c>
       <c r="D66" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
         <v>55.9</v>
@@ -15174,23 +15174,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21098</v>
+        <v>37766</v>
       </c>
       <c r="D67" t="n">
-        <v>51.9</v>
+        <v>50.6</v>
       </c>
       <c r="E67" t="n">
-        <v>48.1</v>
+        <v>49.4</v>
       </c>
       <c r="F67" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="G67" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
@@ -15213,17 +15213,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37326</v>
+        <v>21154</v>
       </c>
       <c r="D68" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="E68" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="F68" t="n">
         <v>56.1</v>
@@ -15256,13 +15256,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>35677</v>
+        <v>36035</v>
       </c>
       <c r="D69" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E69" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30393</v>
+        <v>30447</v>
       </c>
       <c r="D70" t="n">
         <v>50.9</v>
@@ -15334,13 +15334,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37028</v>
+        <v>37386</v>
       </c>
       <c r="D71" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E71" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F71" t="n">
         <v>56.8</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33028</v>
+        <v>32913</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15382,10 +15382,10 @@
         <v>49.8</v>
       </c>
       <c r="F72" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="G72" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25919</v>
+        <v>25954</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15451,13 +15451,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14211</v>
+        <v>14168</v>
       </c>
       <c r="D74" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E74" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F74" t="n">
         <v>51</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14011</v>
+        <v>14045</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15499,10 +15499,10 @@
         <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15074</v>
+        <v>15100</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26513</v>
+        <v>26548</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15577,10 +15577,10 @@
         <v>50.1</v>
       </c>
       <c r="F77" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="G77" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35349</v>
+        <v>35759</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28551</v>
+        <v>28528</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15689</v>
+        <v>15722</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27418</v>
+        <v>27768</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,19 +15763,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10399</v>
+        <v>10396</v>
       </c>
       <c r="D82" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E82" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F82" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10401</v>
+        <v>10397</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15811,10 +15811,10 @@
         <v>49.4</v>
       </c>
       <c r="F83" t="n">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="G83" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10697</v>
+        <v>10695</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15889,10 +15889,10 @@
         <v>49.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="G85" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -15919,13 +15919,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10180</v>
+        <v>10181</v>
       </c>
       <c r="D86" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E86" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F86" t="n">
         <v>56</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87">
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10650</v>
+        <v>10648</v>
       </c>
       <c r="D87" t="n">
         <v>50.8</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10758</v>
+        <v>10756</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -16006,10 +16006,10 @@
         <v>48.4</v>
       </c>
       <c r="F88" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="G88" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10893</v>
+        <v>10892</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -16045,10 +16045,10 @@
         <v>48.5</v>
       </c>
       <c r="F89" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G89" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -16062,7 +16062,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90">
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10912</v>
+        <v>10893</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -16114,13 +16114,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10821</v>
+        <v>10819</v>
       </c>
       <c r="D91" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="E91" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="F91" t="n">
         <v>59.4</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10261</v>
+        <v>10242</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16195,16 +16195,16 @@
         <v>10172</v>
       </c>
       <c r="D93" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E93" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="G93" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94">
@@ -16231,19 +16231,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37359</v>
+        <v>37796</v>
       </c>
       <c r="D94" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="G94" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>37958</v>
+        <v>38401</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16279,10 +16279,10 @@
         <v>50.7</v>
       </c>
       <c r="F95" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G95" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -16309,13 +16309,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>35594</v>
+        <v>36020</v>
       </c>
       <c r="D96" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E96" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F96" t="n">
         <v>53.8</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38075</v>
+        <v>38517</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,13 +16387,13 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37293</v>
+        <v>37726</v>
       </c>
       <c r="D98" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E98" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F98" t="n">
         <v>54</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>37868</v>
+        <v>38310</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37472</v>
+        <v>37911</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16491,7 +16491,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101">
@@ -16504,13 +16504,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38152</v>
+        <v>38594</v>
       </c>
       <c r="D101" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F101" t="n">
         <v>54.5</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>37731</v>
+        <v>38172</v>
       </c>
       <c r="D102" t="n">
         <v>49.7</v>
@@ -16582,13 +16582,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38172</v>
+        <v>38615</v>
       </c>
       <c r="D103" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E103" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F103" t="n">
         <v>54.9</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1491</v>
+        <v>1435</v>
       </c>
       <c r="D2" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E2" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F2" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1490</v>
+        <v>1434</v>
       </c>
       <c r="D3" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
       <c r="E3" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="F3" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -570,23 +570,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHFJPY</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1494</v>
+        <v>1435</v>
       </c>
       <c r="D4" t="n">
-        <v>47.2</v>
+        <v>49.3</v>
       </c>
       <c r="E4" t="n">
-        <v>52.8</v>
+        <v>50.7</v>
       </c>
       <c r="F4" t="n">
-        <v>52.8</v>
+        <v>48.1</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1490</v>
+        <v>1423</v>
       </c>
       <c r="D5" t="n">
-        <v>49.1</v>
+        <v>50.2</v>
       </c>
       <c r="E5" t="n">
-        <v>50.9</v>
+        <v>49.8</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1434</v>
+        <v>1438</v>
       </c>
       <c r="D6" t="n">
-        <v>49.4</v>
+        <v>47.4</v>
       </c>
       <c r="E6" t="n">
-        <v>50.6</v>
+        <v>52.6</v>
       </c>
       <c r="F6" t="n">
-        <v>46.5</v>
+        <v>53.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -687,23 +687,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EURCAD</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1467</v>
+        <v>1382</v>
       </c>
       <c r="D7" t="n">
-        <v>48.6</v>
+        <v>50.4</v>
       </c>
       <c r="E7" t="n">
-        <v>51.4</v>
+        <v>49.6</v>
       </c>
       <c r="F7" t="n">
-        <v>53.9</v>
+        <v>46.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -726,23 +726,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURCAD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1477</v>
+        <v>1411</v>
       </c>
       <c r="D8" t="n">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="E8" t="n">
-        <v>49.6</v>
+        <v>51.5</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>53.6</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1494</v>
+        <v>1438</v>
       </c>
       <c r="D9" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E9" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F9" t="n">
-        <v>55.6</v>
+        <v>55.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1464</v>
+        <v>1407</v>
       </c>
       <c r="D10" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="E10" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="F10" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1460</v>
+        <v>1407</v>
       </c>
       <c r="D11" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E11" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -882,11 +882,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1466</v>
+        <v>1434</v>
       </c>
       <c r="D12" t="n">
         <v>50.8</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -921,23 +921,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1490</v>
+        <v>1413</v>
       </c>
       <c r="D13" t="n">
-        <v>50.3</v>
+        <v>51.5</v>
       </c>
       <c r="E13" t="n">
-        <v>49.7</v>
+        <v>48.5</v>
       </c>
       <c r="F13" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="G13" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -960,23 +960,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1472</v>
+        <v>1416</v>
       </c>
       <c r="D14" t="n">
-        <v>49.1</v>
+        <v>52.2</v>
       </c>
       <c r="E14" t="n">
-        <v>50.9</v>
+        <v>47.8</v>
       </c>
       <c r="F14" t="n">
-        <v>63.3</v>
+        <v>36.9</v>
       </c>
       <c r="G14" t="n">
-        <v>13.3</v>
+        <v>13.1</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -999,23 +999,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1474</v>
+        <v>1416</v>
       </c>
       <c r="D15" t="n">
-        <v>52</v>
+        <v>48.6</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>51.4</v>
       </c>
       <c r="F15" t="n">
-        <v>36.6</v>
+        <v>63.3</v>
       </c>
       <c r="G15" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1468</v>
+        <v>1413</v>
       </c>
       <c r="D16" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
       <c r="E16" t="n">
-        <v>52.4</v>
+        <v>53.3</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>63.8</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1077,23 +1077,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>EURNOK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1445</v>
+        <v>1289</v>
       </c>
       <c r="D17" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E17" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F17" t="n">
-        <v>50.8</v>
+        <v>49.3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1104,7 +1104,7 @@
         </is>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
@@ -1116,20 +1116,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EURNOK</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1345</v>
+        <v>1389</v>
       </c>
       <c r="D18" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
       <c r="E18" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="F18" t="n">
-        <v>48.8</v>
+        <v>51.2</v>
       </c>
       <c r="G18" t="n">
         <v>1.2</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1455</v>
+        <v>1440</v>
       </c>
       <c r="D19" t="n">
-        <v>51.3</v>
+        <v>46.7</v>
       </c>
       <c r="E19" t="n">
-        <v>48.7</v>
+        <v>53.3</v>
       </c>
       <c r="F19" t="n">
         <v>51.4</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1496</v>
+        <v>1399</v>
       </c>
       <c r="D20" t="n">
-        <v>46.9</v>
+        <v>50.7</v>
       </c>
       <c r="E20" t="n">
-        <v>53.1</v>
+        <v>49.3</v>
       </c>
       <c r="F20" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>389</v>
+        <v>1420</v>
       </c>
       <c r="D21" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>52.2</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22">
@@ -1272,11 +1272,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1476</v>
+        <v>362</v>
       </c>
       <c r="D22" t="n">
         <v>50</v>
@@ -1285,10 +1285,10 @@
         <v>50</v>
       </c>
       <c r="F22" t="n">
-        <v>46.1</v>
+        <v>53</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1311,23 +1311,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1482</v>
+        <v>1408</v>
       </c>
       <c r="D23" t="n">
-        <v>51.6</v>
+        <v>47.1</v>
       </c>
       <c r="E23" t="n">
-        <v>48.4</v>
+        <v>52.9</v>
       </c>
       <c r="F23" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="G23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1350,23 +1350,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1462</v>
+        <v>1430</v>
       </c>
       <c r="D24" t="n">
-        <v>46.4</v>
+        <v>51.3</v>
       </c>
       <c r="E24" t="n">
-        <v>53.6</v>
+        <v>48.7</v>
       </c>
       <c r="F24" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="G24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1486</v>
+        <v>1429</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="F25" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="G25" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1471</v>
+        <v>1420</v>
       </c>
       <c r="D26" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="E26" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="F26" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="G26" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27">
@@ -1467,23 +1467,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1459</v>
+        <v>1425</v>
       </c>
       <c r="D27" t="n">
-        <v>52.1</v>
+        <v>49.1</v>
       </c>
       <c r="E27" t="n">
-        <v>47.9</v>
+        <v>50.9</v>
       </c>
       <c r="F27" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="G27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28">
@@ -1506,23 +1506,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1480</v>
+        <v>1403</v>
       </c>
       <c r="D28" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="E28" t="n">
         <v>48.8</v>
       </c>
-      <c r="E28" t="n">
-        <v>51.2</v>
-      </c>
       <c r="F28" t="n">
-        <v>56.4</v>
+        <v>56.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1545,17 +1545,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1495</v>
+        <v>1291</v>
       </c>
       <c r="D29" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
       <c r="E29" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="F29" t="n">
         <v>43.5</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="J29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1489</v>
+        <v>1430</v>
       </c>
       <c r="D30" t="n">
-        <v>49.6</v>
+        <v>48.8</v>
       </c>
       <c r="E30" t="n">
-        <v>50.4</v>
+        <v>51.2</v>
       </c>
       <c r="F30" t="n">
-        <v>56.7</v>
+        <v>43.4</v>
       </c>
       <c r="G30" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31">
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1486</v>
+        <v>1439</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="E31" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="F31" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1347</v>
+        <v>1433</v>
       </c>
       <c r="D32" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="E32" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="F32" t="n">
-        <v>42.8</v>
+        <v>57.4</v>
       </c>
       <c r="G32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>35</v>
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1488</v>
+        <v>1434</v>
       </c>
       <c r="D33" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="E33" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="F33" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="G33" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1484</v>
+        <v>1429</v>
       </c>
       <c r="D34" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="E34" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="F34" t="n">
-        <v>58.5</v>
+        <v>58.1</v>
       </c>
       <c r="G34" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1360</v>
+        <v>1310</v>
       </c>
       <c r="D35" t="n">
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
       <c r="E35" t="n">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
       <c r="F35" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="G35" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1470</v>
+        <v>1415</v>
       </c>
       <c r="D36" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E36" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F36" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="G36" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1483</v>
+        <v>1428</v>
       </c>
       <c r="D37" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="E37" t="n">
-        <v>52.5</v>
+        <v>51.6</v>
       </c>
       <c r="F37" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="G37" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38">
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1473</v>
+        <v>1418</v>
       </c>
       <c r="D38" t="n">
-        <v>49.4</v>
+        <v>48.9</v>
       </c>
       <c r="E38" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
       <c r="F38" t="n">
         <v>60</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1487</v>
+        <v>1430</v>
       </c>
       <c r="D39" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="E39" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="F39" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="G39" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1494</v>
+        <v>1439</v>
       </c>
       <c r="D40" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="E40" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="F40" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="G40" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41">
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="D41" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="E41" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="F41" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="G41" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1462</v>
+        <v>1410</v>
       </c>
       <c r="D42" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="E42" t="n">
-        <v>48.8</v>
+        <v>49.6</v>
       </c>
       <c r="F42" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="G42" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="43">
@@ -2091,23 +2091,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1481</v>
+        <v>1433</v>
       </c>
       <c r="D43" t="n">
-        <v>48.5</v>
+        <v>52.3</v>
       </c>
       <c r="E43" t="n">
-        <v>51.5</v>
+        <v>47.7</v>
       </c>
       <c r="F43" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="G43" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
@@ -2130,23 +2130,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1495</v>
+        <v>1424</v>
       </c>
       <c r="D44" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
       </c>
       <c r="E44" t="n">
-        <v>49.4</v>
+        <v>51.1</v>
       </c>
       <c r="F44" t="n">
-        <v>37.5</v>
+        <v>37.7</v>
       </c>
       <c r="G44" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1490</v>
+        <v>1438</v>
       </c>
       <c r="D45" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E45" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F45" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="G45" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1343</v>
+        <v>1287</v>
       </c>
       <c r="D46" t="n">
-        <v>51.6</v>
+        <v>52.3</v>
       </c>
       <c r="E46" t="n">
-        <v>48.4</v>
+        <v>47.7</v>
       </c>
       <c r="F46" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="G46" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47">
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1499</v>
+        <v>1443</v>
       </c>
       <c r="D47" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="E47" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="F47" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="G47" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="48">
@@ -2290,19 +2290,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="D48" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="E48" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="F48" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="G48" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49">
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1462</v>
+        <v>1409</v>
       </c>
       <c r="D49" t="n">
-        <v>49.4</v>
+        <v>50.2</v>
       </c>
       <c r="E49" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="F49" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="G49" t="n">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50">
@@ -2368,19 +2368,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1498</v>
+        <v>1442</v>
       </c>
       <c r="D50" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
       <c r="E50" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="F50" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="G50" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1471</v>
+        <v>1421</v>
       </c>
       <c r="D51" t="n">
-        <v>49.6</v>
+        <v>48.6</v>
       </c>
       <c r="E51" t="n">
-        <v>50.4</v>
+        <v>51.4</v>
       </c>
       <c r="F51" t="n">
         <v>66.09999999999999</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1473</v>
+        <v>1420</v>
       </c>
       <c r="D52" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="E52" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F52" t="n">
-        <v>67.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2472,7 +2472,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1500</v>
+        <v>1444</v>
       </c>
       <c r="D53" t="n">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="E53" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="F53" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="G53" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1397</v>
+        <v>1343</v>
       </c>
       <c r="D54" t="n">
-        <v>50.6</v>
+        <v>51.7</v>
       </c>
       <c r="E54" t="n">
-        <v>49.4</v>
+        <v>48.3</v>
       </c>
       <c r="F54" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="G54" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1490</v>
+        <v>1434</v>
       </c>
       <c r="D55" t="n">
-        <v>49.3</v>
+        <v>48.7</v>
       </c>
       <c r="E55" t="n">
-        <v>50.7</v>
+        <v>51.3</v>
       </c>
       <c r="F55" t="n">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
       <c r="G55" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1480</v>
+        <v>1426</v>
       </c>
       <c r="D56" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E56" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F56" t="n">
-        <v>74.8</v>
+        <v>75</v>
       </c>
       <c r="G56" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1495</v>
+        <v>1439</v>
       </c>
       <c r="D57" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E57" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F57" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="G57" t="n">
-        <v>32.7</v>
+        <v>32.3</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1498</v>
+        <v>1442</v>
       </c>
       <c r="D58" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="E58" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="F58" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="G58" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1498</v>
+        <v>1442</v>
       </c>
       <c r="D59" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="E59" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="F59" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1457</v>
+        <v>1321</v>
       </c>
       <c r="D60" t="n">
-        <v>50.2</v>
+        <v>51.6</v>
       </c>
       <c r="E60" t="n">
-        <v>49.8</v>
+        <v>48.4</v>
       </c>
       <c r="F60" t="n">
-        <v>42.8</v>
+        <v>42</v>
       </c>
       <c r="G60" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1372</v>
+        <v>1450</v>
       </c>
       <c r="D61" t="n">
-        <v>51.4</v>
+        <v>50.6</v>
       </c>
       <c r="E61" t="n">
-        <v>48.6</v>
+        <v>49.4</v>
       </c>
       <c r="F61" t="n">
-        <v>42.5</v>
+        <v>41.9</v>
       </c>
       <c r="G61" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="62">
@@ -2836,13 +2836,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>929</v>
+        <v>878</v>
       </c>
       <c r="D62" t="n">
-        <v>49.6</v>
+        <v>48.7</v>
       </c>
       <c r="E62" t="n">
-        <v>50.4</v>
+        <v>51.3</v>
       </c>
       <c r="F62" t="n">
         <v>58</v>
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>919</v>
+        <v>869</v>
       </c>
       <c r="D63" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
       <c r="E63" t="n">
-        <v>52.1</v>
+        <v>52.8</v>
       </c>
       <c r="F63" t="n">
-        <v>58.1</v>
+        <v>58.9</v>
       </c>
       <c r="G63" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
@@ -2910,23 +2910,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>942</v>
+        <v>1284</v>
       </c>
       <c r="D64" t="n">
-        <v>52.9</v>
+        <v>48.5</v>
       </c>
       <c r="E64" t="n">
-        <v>47.1</v>
+        <v>51.5</v>
       </c>
       <c r="F64" t="n">
-        <v>59.2</v>
+        <v>60</v>
       </c>
       <c r="G64" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65">
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1338</v>
+        <v>870</v>
       </c>
       <c r="D65" t="n">
-        <v>48.8</v>
+        <v>51.4</v>
       </c>
       <c r="E65" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="F65" t="n">
-        <v>59.4</v>
+        <v>60.5</v>
       </c>
       <c r="G65" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66">
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="D66" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="E66" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="F66" t="n">
-        <v>59.9</v>
+        <v>60.5</v>
       </c>
       <c r="G66" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67">
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1463</v>
+        <v>1025</v>
       </c>
       <c r="D67" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="E67" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G67" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1492</v>
+        <v>1406</v>
       </c>
       <c r="D68" t="n">
-        <v>50.9</v>
+        <v>48.5</v>
       </c>
       <c r="E68" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
       <c r="F68" t="n">
-        <v>62.3</v>
+        <v>63</v>
       </c>
       <c r="G68" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1069</v>
+        <v>1436</v>
       </c>
       <c r="D69" t="n">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="E69" t="n">
-        <v>51.1</v>
+        <v>49.4</v>
       </c>
       <c r="F69" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="G69" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70">
@@ -3148,19 +3148,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1280</v>
+        <v>1229</v>
       </c>
       <c r="D70" t="n">
-        <v>48.6</v>
+        <v>47.8</v>
       </c>
       <c r="E70" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
       <c r="F70" t="n">
-        <v>62.8</v>
+        <v>63.5</v>
       </c>
       <c r="G70" t="n">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71">
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1475</v>
+        <v>1419</v>
       </c>
       <c r="D71" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="E71" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F71" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="G71" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72">
@@ -3226,19 +3226,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1460</v>
+        <v>1451</v>
       </c>
       <c r="D72" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="E72" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="F72" t="n">
-        <v>63.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73">
@@ -3265,13 +3265,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1282</v>
+        <v>1235</v>
       </c>
       <c r="D73" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
       <c r="E73" t="n">
-        <v>51.6</v>
+        <v>52.1</v>
       </c>
       <c r="F73" t="n">
         <v>66.59999999999999</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="74">
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>566</v>
+        <v>530</v>
       </c>
       <c r="D74" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E74" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>53.5</v>
+        <v>53.8</v>
       </c>
       <c r="G74" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="75">
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>545</v>
+        <v>510</v>
       </c>
       <c r="D75" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="E75" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="F75" t="n">
-        <v>54.5</v>
+        <v>54.3</v>
       </c>
       <c r="G75" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>560</v>
+        <v>522</v>
       </c>
       <c r="D76" t="n">
         <v>52.7</v>
@@ -3391,10 +3391,10 @@
         <v>47.3</v>
       </c>
       <c r="F76" t="n">
-        <v>54.6</v>
+        <v>55.2</v>
       </c>
       <c r="G76" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1085</v>
+        <v>1042</v>
       </c>
       <c r="D77" t="n">
         <v>51.2</v>
@@ -3430,10 +3430,10 @@
         <v>48.8</v>
       </c>
       <c r="F77" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="G77" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1396</v>
+        <v>1344</v>
       </c>
       <c r="D78" t="n">
-        <v>48.9</v>
+        <v>48.2</v>
       </c>
       <c r="E78" t="n">
-        <v>51.1</v>
+        <v>51.8</v>
       </c>
       <c r="F78" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="D79" t="n">
-        <v>48.3</v>
+        <v>48.8</v>
       </c>
       <c r="E79" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="F79" t="n">
-        <v>58.1</v>
+        <v>59.3</v>
       </c>
       <c r="G79" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1134</v>
+        <v>1091</v>
       </c>
       <c r="D80" t="n">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="E80" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="F80" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1088</v>
+        <v>1054</v>
       </c>
       <c r="D81" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="E81" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="F81" t="n">
         <v>63</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82">
@@ -3612,23 +3612,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="D82" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="E82" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="F82" t="n">
-        <v>50.3</v>
+        <v>49.6</v>
       </c>
       <c r="G82" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -3651,23 +3651,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="D83" t="n">
-        <v>49.9</v>
+        <v>47</v>
       </c>
       <c r="E83" t="n">
-        <v>50.1</v>
+        <v>53</v>
       </c>
       <c r="F83" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -3690,23 +3690,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="D84" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="E84" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="F84" t="n">
-        <v>49.2</v>
+        <v>48.1</v>
       </c>
       <c r="G84" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="D85" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="E85" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="G85" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86">
@@ -3768,23 +3768,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D86" t="n">
-        <v>51.5</v>
+        <v>45.4</v>
       </c>
       <c r="E86" t="n">
-        <v>48.5</v>
+        <v>54.6</v>
       </c>
       <c r="F86" t="n">
-        <v>56.7</v>
+        <v>56.2</v>
       </c>
       <c r="G86" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
@@ -3807,23 +3807,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="D87" t="n">
-        <v>46.2</v>
+        <v>51.5</v>
       </c>
       <c r="E87" t="n">
-        <v>53.8</v>
+        <v>48.5</v>
       </c>
       <c r="F87" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="G87" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88">
@@ -3846,23 +3846,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>406</v>
+        <v>367</v>
       </c>
       <c r="D88" t="n">
-        <v>50.2</v>
+        <v>48.8</v>
       </c>
       <c r="E88" t="n">
-        <v>49.8</v>
+        <v>51.2</v>
       </c>
       <c r="F88" t="n">
-        <v>61.1</v>
+        <v>60.5</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89">
@@ -3885,23 +3885,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="D89" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="E89" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="F89" t="n">
-        <v>61.7</v>
+        <v>61.9</v>
       </c>
       <c r="G89" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="D90" t="n">
-        <v>49.8</v>
+        <v>50.3</v>
       </c>
       <c r="E90" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="F90" t="n">
-        <v>61.9</v>
+        <v>62.2</v>
       </c>
       <c r="G90" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="D91" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
       <c r="E91" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="F91" t="n">
-        <v>62.6</v>
+        <v>62.9</v>
       </c>
       <c r="G91" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="92">
@@ -4006,19 +4006,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="D92" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="E92" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="F92" t="n">
-        <v>62.7</v>
+        <v>63.3</v>
       </c>
       <c r="G92" t="n">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="D93" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="E93" t="n">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="F93" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="G93" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4084,19 +4084,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1500</v>
+        <v>1444</v>
       </c>
       <c r="D94" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
       <c r="E94" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="F94" t="n">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="G94" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="95">
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1458</v>
+        <v>1401</v>
       </c>
       <c r="D95" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="E95" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="F95" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="G95" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96">
@@ -4162,19 +4162,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1336</v>
+        <v>1283</v>
       </c>
       <c r="D96" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="F96" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
@@ -4201,19 +4201,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="D97" t="n">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
       <c r="E97" t="n">
-        <v>50.6</v>
+        <v>51.5</v>
       </c>
       <c r="F97" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="G97" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1501</v>
+        <v>1427</v>
       </c>
       <c r="D98" t="n">
-        <v>49.4</v>
+        <v>48.3</v>
       </c>
       <c r="E98" t="n">
-        <v>50.6</v>
+        <v>51.7</v>
       </c>
       <c r="F98" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="G98" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4275,23 +4275,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1484</v>
+        <v>1445</v>
       </c>
       <c r="D99" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="E99" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="F99" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="G99" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100">
@@ -4314,23 +4314,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1494</v>
+        <v>1444</v>
       </c>
       <c r="D100" t="n">
-        <v>49.9</v>
+        <v>49.1</v>
       </c>
       <c r="E100" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="F100" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="G100" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101">
@@ -4353,23 +4353,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="D101" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="E101" t="n">
-        <v>50.3</v>
+        <v>51</v>
       </c>
       <c r="F101" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="G101" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102">
@@ -4392,23 +4392,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1500</v>
+        <v>1389</v>
       </c>
       <c r="D102" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="F102" t="n">
-        <v>60.6</v>
+        <v>61.3</v>
       </c>
       <c r="G102" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1480</v>
+        <v>1428</v>
       </c>
       <c r="D103" t="n">
-        <v>50.1</v>
+        <v>49.2</v>
       </c>
       <c r="E103" t="n">
-        <v>49.9</v>
+        <v>50.8</v>
       </c>
       <c r="F103" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="G103" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38044</v>
+        <v>38074</v>
       </c>
       <c r="D2" t="n">
         <v>50</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37593</v>
+        <v>37625</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37760</v>
+        <v>37792</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38326</v>
+        <v>38358</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38377</v>
+        <v>38409</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38240</v>
+        <v>38272</v>
       </c>
       <c r="D7" t="n">
         <v>50.7</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38390</v>
+        <v>38422</v>
       </c>
       <c r="D8" t="n">
         <v>51.4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37775</v>
+        <v>37806</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38214</v>
+        <v>38245</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38273</v>
+        <v>38305</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38298</v>
+        <v>38330</v>
       </c>
       <c r="D12" t="n">
         <v>51.2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38099</v>
+        <v>38131</v>
       </c>
       <c r="D13" t="n">
         <v>50.2</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38048</v>
+        <v>38078</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38177</v>
+        <v>38208</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38193</v>
+        <v>38225</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38315</v>
+        <v>38347</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5139,10 +5139,10 @@
         <v>52.8</v>
       </c>
       <c r="F17" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8080</v>
+        <v>8085</v>
       </c>
       <c r="D18" t="n">
         <v>51.3</v>
@@ -5178,10 +5178,10 @@
         <v>48.7</v>
       </c>
       <c r="F18" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37996</v>
+        <v>38028</v>
       </c>
       <c r="D19" t="n">
         <v>50</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37504</v>
+        <v>37533</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38159</v>
+        <v>38190</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34794</v>
+        <v>34818</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38321</v>
+        <v>38352</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38058</v>
+        <v>38088</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38091</v>
+        <v>38123</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38319</v>
+        <v>38351</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38017</v>
+        <v>38049</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37674</v>
+        <v>37705</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37824</v>
+        <v>37855</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38197</v>
+        <v>38229</v>
       </c>
       <c r="D30" t="n">
         <v>50.6</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38382</v>
+        <v>38414</v>
       </c>
       <c r="D31" t="n">
         <v>49.6</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38240</v>
+        <v>38272</v>
       </c>
       <c r="D32" t="n">
         <v>51.1</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38356</v>
+        <v>38387</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5763,10 +5763,10 @@
         <v>50.6</v>
       </c>
       <c r="F33" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="G33" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38359</v>
+        <v>38391</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38323</v>
+        <v>38355</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38606</v>
+        <v>38638</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38598</v>
+        <v>38630</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35638</v>
+        <v>35666</v>
       </c>
       <c r="D38" t="n">
         <v>50.3</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34908</v>
+        <v>34932</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38078</v>
+        <v>38110</v>
       </c>
       <c r="D40" t="n">
         <v>49.4</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37943</v>
+        <v>37974</v>
       </c>
       <c r="D41" t="n">
         <v>50.3</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38122</v>
+        <v>38154</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38516</v>
+        <v>38548</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38573</v>
+        <v>38605</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38562</v>
+        <v>38594</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38382</v>
+        <v>38413</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,13 +6300,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38332</v>
+        <v>38363</v>
       </c>
       <c r="D47" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E47" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F47" t="n">
         <v>40.2</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38516</v>
+        <v>38547</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34740</v>
+        <v>34764</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>37993</v>
+        <v>38024</v>
       </c>
       <c r="D50" t="n">
         <v>49.6</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37985</v>
+        <v>38017</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38031</v>
+        <v>38063</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38444</v>
+        <v>38476</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36467</v>
+        <v>36497</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38211</v>
+        <v>38242</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37915</v>
+        <v>37947</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38276</v>
+        <v>38308</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38356</v>
+        <v>38388</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38558</v>
+        <v>38590</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36867</v>
+        <v>36946</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>34991</v>
+        <v>35019</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37374</v>
+        <v>37404</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23329</v>
+        <v>23333</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23752</v>
+        <v>23756</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23776</v>
+        <v>23780</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38261</v>
+        <v>38293</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -7080,13 +7080,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>37766</v>
+        <v>37798</v>
       </c>
       <c r="D67" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E67" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F67" t="n">
         <v>56</v>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21154</v>
+        <v>21158</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -7158,13 +7158,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36035</v>
+        <v>36066</v>
       </c>
       <c r="D69" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -7197,13 +7197,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30447</v>
+        <v>30473</v>
       </c>
       <c r="D70" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E70" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F70" t="n">
         <v>56.7</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37386</v>
+        <v>37462</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32913</v>
+        <v>32942</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25954</v>
+        <v>25973</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26548</v>
+        <v>26571</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,13 +7509,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35759</v>
+        <v>35788</v>
       </c>
       <c r="D78" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E78" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F78" t="n">
         <v>65.5</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28528</v>
+        <v>28553</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27768</v>
+        <v>27793</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37796</v>
+        <v>37827</v>
       </c>
       <c r="D94" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F94" t="n">
         <v>53.7</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38401</v>
+        <v>38433</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36020</v>
+        <v>36043</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38517</v>
+        <v>38549</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37726</v>
+        <v>37756</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38310</v>
+        <v>38341</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37911</v>
+        <v>37943</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38594</v>
+        <v>38626</v>
       </c>
       <c r="D101" t="n">
         <v>50.1</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38172</v>
+        <v>38204</v>
       </c>
       <c r="D102" t="n">
         <v>49.7</v>
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38615</v>
+        <v>38696</v>
       </c>
       <c r="D103" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E103" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F103" t="n">
         <v>54.9</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1474</v>
+        <v>1416</v>
       </c>
       <c r="D2" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="F2" t="n">
-        <v>36.6</v>
+        <v>36.9</v>
       </c>
       <c r="G2" t="n">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -8629,23 +8629,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1490</v>
+        <v>1413</v>
       </c>
       <c r="D3" t="n">
-        <v>50.3</v>
+        <v>51.5</v>
       </c>
       <c r="E3" t="n">
-        <v>49.7</v>
+        <v>48.5</v>
       </c>
       <c r="F3" t="n">
-        <v>39.1</v>
+        <v>40.1</v>
       </c>
       <c r="G3" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8659,7 +8659,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -8668,11 +8668,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1466</v>
+        <v>1434</v>
       </c>
       <c r="D4" t="n">
         <v>50.8</v>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1460</v>
+        <v>1407</v>
       </c>
       <c r="D5" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E5" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8737,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1464</v>
+        <v>1407</v>
       </c>
       <c r="D6" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="E6" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="F6" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8785,11 +8785,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1477</v>
+        <v>1382</v>
       </c>
       <c r="D7" t="n">
         <v>50.4</v>
@@ -8798,10 +8798,10 @@
         <v>49.6</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>46.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8824,23 +8824,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1434</v>
+        <v>1423</v>
       </c>
       <c r="D8" t="n">
-        <v>49.4</v>
+        <v>50.2</v>
       </c>
       <c r="E8" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="F8" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -8867,19 +8867,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1490</v>
+        <v>1435</v>
       </c>
       <c r="D9" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E9" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,19 +8906,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1490</v>
+        <v>1434</v>
       </c>
       <c r="D10" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
       <c r="E10" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="F10" t="n">
-        <v>47.5</v>
+        <v>48.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1491</v>
+        <v>1435</v>
       </c>
       <c r="D11" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E11" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F11" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1494</v>
+        <v>1438</v>
       </c>
       <c r="D12" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="E12" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="F12" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1467</v>
+        <v>1411</v>
       </c>
       <c r="D13" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E13" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="F13" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1494</v>
+        <v>1438</v>
       </c>
       <c r="D14" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E14" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>55.6</v>
+        <v>55.3</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9101,13 +9101,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1472</v>
+        <v>1416</v>
       </c>
       <c r="D15" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="E15" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="F15" t="n">
         <v>63.3</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16">
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1468</v>
+        <v>1413</v>
       </c>
       <c r="D16" t="n">
-        <v>47.6</v>
+        <v>46.7</v>
       </c>
       <c r="E16" t="n">
-        <v>52.4</v>
+        <v>53.3</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>63.8</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1397</v>
+        <v>1343</v>
       </c>
       <c r="D17" t="n">
-        <v>50.6</v>
+        <v>51.7</v>
       </c>
       <c r="E17" t="n">
-        <v>49.4</v>
+        <v>48.3</v>
       </c>
       <c r="F17" t="n">
-        <v>31.3</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1500</v>
+        <v>1444</v>
       </c>
       <c r="D18" t="n">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="E18" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="F18" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="G18" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,19 +9257,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1498</v>
+        <v>1442</v>
       </c>
       <c r="D19" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
       <c r="E19" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="F19" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="G19" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1462</v>
+        <v>1409</v>
       </c>
       <c r="D20" t="n">
-        <v>49.4</v>
+        <v>50.2</v>
       </c>
       <c r="E20" t="n">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="F20" t="n">
-        <v>35.8</v>
+        <v>36.6</v>
       </c>
       <c r="G20" t="n">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="E21" t="n">
-        <v>48</v>
+        <v>47.5</v>
       </c>
       <c r="F21" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="G21" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9361,7 +9361,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -9374,19 +9374,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1499</v>
+        <v>1443</v>
       </c>
       <c r="D22" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="E22" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="F22" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="G22" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9413,19 +9413,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1343</v>
+        <v>1287</v>
       </c>
       <c r="D23" t="n">
-        <v>51.6</v>
+        <v>52.3</v>
       </c>
       <c r="E23" t="n">
-        <v>48.4</v>
+        <v>47.7</v>
       </c>
       <c r="F23" t="n">
-        <v>37.2</v>
+        <v>37.3</v>
       </c>
       <c r="G23" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9448,23 +9448,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1490</v>
+        <v>1438</v>
       </c>
       <c r="D24" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E24" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F24" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="G24" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9487,23 +9487,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1495</v>
+        <v>1424</v>
       </c>
       <c r="D25" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
       </c>
       <c r="E25" t="n">
-        <v>49.4</v>
+        <v>51.1</v>
       </c>
       <c r="F25" t="n">
-        <v>37.5</v>
+        <v>37.7</v>
       </c>
       <c r="G25" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9526,23 +9526,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1481</v>
+        <v>1433</v>
       </c>
       <c r="D26" t="n">
-        <v>48.5</v>
+        <v>52.3</v>
       </c>
       <c r="E26" t="n">
-        <v>51.5</v>
+        <v>47.7</v>
       </c>
       <c r="F26" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="G26" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="D27" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="E27" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="F27" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="G27" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1494</v>
+        <v>1439</v>
       </c>
       <c r="D28" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="E28" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="F28" t="n">
-        <v>38.6</v>
+        <v>39.1</v>
       </c>
       <c r="G28" t="n">
-        <v>11.4</v>
+        <v>10.9</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1487</v>
+        <v>1430</v>
       </c>
       <c r="D29" t="n">
-        <v>48.4</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>51.6</v>
+        <v>51</v>
       </c>
       <c r="F29" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="G29" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1483</v>
+        <v>1428</v>
       </c>
       <c r="D30" t="n">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="E30" t="n">
-        <v>52.5</v>
+        <v>51.6</v>
       </c>
       <c r="F30" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="G30" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9712,7 +9712,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1488</v>
+        <v>1434</v>
       </c>
       <c r="D31" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="E31" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="F31" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="G31" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
@@ -9760,23 +9760,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1347</v>
+        <v>1439</v>
       </c>
       <c r="D32" t="n">
-        <v>49.7</v>
+        <v>48.6</v>
       </c>
       <c r="E32" t="n">
-        <v>50.3</v>
+        <v>51.4</v>
       </c>
       <c r="F32" t="n">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="G32" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9787,10 +9787,10 @@
         </is>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1486</v>
+        <v>1430</v>
       </c>
       <c r="D33" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="E33" t="n">
-        <v>52</v>
+        <v>51.2</v>
       </c>
       <c r="F33" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9838,17 +9838,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1495</v>
+        <v>1291</v>
       </c>
       <c r="D34" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
       <c r="E34" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="F34" t="n">
         <v>43.5</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="J34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>24</v>
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1471</v>
+        <v>1420</v>
       </c>
       <c r="D35" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="E35" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="F35" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="G35" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1486</v>
+        <v>1429</v>
       </c>
       <c r="D36" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="E36" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="F36" t="n">
-        <v>44.7</v>
+        <v>44.6</v>
       </c>
       <c r="G36" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1476</v>
+        <v>1420</v>
       </c>
       <c r="D37" t="n">
         <v>50</v>
@@ -9968,10 +9968,10 @@
         <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="G37" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1345</v>
+        <v>1289</v>
       </c>
       <c r="D38" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="E38" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="F38" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="G38" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -10037,7 +10037,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1445</v>
+        <v>1389</v>
       </c>
       <c r="D39" t="n">
         <v>49.6</v>
@@ -10046,10 +10046,10 @@
         <v>50.4</v>
       </c>
       <c r="F39" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10072,17 +10072,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1455</v>
+        <v>1440</v>
       </c>
       <c r="D40" t="n">
-        <v>51.3</v>
+        <v>46.7</v>
       </c>
       <c r="E40" t="n">
-        <v>48.7</v>
+        <v>53.3</v>
       </c>
       <c r="F40" t="n">
         <v>51.4</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>39</v>
@@ -10111,23 +10111,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1496</v>
+        <v>1399</v>
       </c>
       <c r="D41" t="n">
-        <v>46.9</v>
+        <v>50.7</v>
       </c>
       <c r="E41" t="n">
-        <v>53.1</v>
+        <v>49.3</v>
       </c>
       <c r="F41" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="G41" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>40</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>389</v>
+        <v>362</v>
       </c>
       <c r="D42" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="E42" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>52.2</v>
+        <v>53</v>
       </c>
       <c r="G42" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10189,23 +10189,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1482</v>
+        <v>1408</v>
       </c>
       <c r="D43" t="n">
-        <v>51.6</v>
+        <v>47.1</v>
       </c>
       <c r="E43" t="n">
-        <v>48.4</v>
+        <v>52.9</v>
       </c>
       <c r="F43" t="n">
-        <v>54.2</v>
+        <v>54.1</v>
       </c>
       <c r="G43" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10228,23 +10228,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1462</v>
+        <v>1430</v>
       </c>
       <c r="D44" t="n">
-        <v>46.4</v>
+        <v>51.3</v>
       </c>
       <c r="E44" t="n">
-        <v>53.6</v>
+        <v>48.7</v>
       </c>
       <c r="F44" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="G44" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10267,23 +10267,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1459</v>
+        <v>1425</v>
       </c>
       <c r="D45" t="n">
-        <v>52.1</v>
+        <v>49.1</v>
       </c>
       <c r="E45" t="n">
-        <v>47.9</v>
+        <v>50.9</v>
       </c>
       <c r="F45" t="n">
-        <v>56.2</v>
+        <v>56</v>
       </c>
       <c r="G45" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10306,23 +10306,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1480</v>
+        <v>1403</v>
       </c>
       <c r="D46" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="E46" t="n">
         <v>48.8</v>
       </c>
-      <c r="E46" t="n">
-        <v>51.2</v>
-      </c>
       <c r="F46" t="n">
-        <v>56.4</v>
+        <v>56.1</v>
       </c>
       <c r="G46" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10349,19 +10349,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1489</v>
+        <v>1433</v>
       </c>
       <c r="D47" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E47" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F47" t="n">
-        <v>56.7</v>
+        <v>57.4</v>
       </c>
       <c r="G47" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -10388,19 +10388,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1484</v>
+        <v>1429</v>
       </c>
       <c r="D48" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="E48" t="n">
-        <v>54</v>
+        <v>53.7</v>
       </c>
       <c r="F48" t="n">
-        <v>58.5</v>
+        <v>58.1</v>
       </c>
       <c r="G48" t="n">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1360</v>
+        <v>1310</v>
       </c>
       <c r="D49" t="n">
-        <v>47.9</v>
+        <v>47.6</v>
       </c>
       <c r="E49" t="n">
-        <v>52.1</v>
+        <v>52.4</v>
       </c>
       <c r="F49" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="G49" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50">
@@ -10466,19 +10466,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1470</v>
+        <v>1415</v>
       </c>
       <c r="D50" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E50" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F50" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="G50" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51">
@@ -10505,13 +10505,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1473</v>
+        <v>1418</v>
       </c>
       <c r="D51" t="n">
-        <v>49.4</v>
+        <v>48.9</v>
       </c>
       <c r="E51" t="n">
-        <v>50.6</v>
+        <v>51.1</v>
       </c>
       <c r="F51" t="n">
         <v>60</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1462</v>
+        <v>1410</v>
       </c>
       <c r="D52" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="E52" t="n">
-        <v>48.8</v>
+        <v>49.6</v>
       </c>
       <c r="F52" t="n">
-        <v>62.2</v>
+        <v>62.1</v>
       </c>
       <c r="G52" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1471</v>
+        <v>1421</v>
       </c>
       <c r="D53" t="n">
-        <v>49.6</v>
+        <v>48.6</v>
       </c>
       <c r="E53" t="n">
-        <v>50.4</v>
+        <v>51.4</v>
       </c>
       <c r="F53" t="n">
         <v>66.09999999999999</v>
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1473</v>
+        <v>1420</v>
       </c>
       <c r="D54" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="E54" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F54" t="n">
-        <v>67.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55">
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1490</v>
+        <v>1434</v>
       </c>
       <c r="D55" t="n">
-        <v>49.3</v>
+        <v>48.7</v>
       </c>
       <c r="E55" t="n">
-        <v>50.7</v>
+        <v>51.3</v>
       </c>
       <c r="F55" t="n">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
       <c r="G55" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,19 +10700,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1480</v>
+        <v>1426</v>
       </c>
       <c r="D56" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E56" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F56" t="n">
-        <v>74.8</v>
+        <v>75</v>
       </c>
       <c r="G56" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1495</v>
+        <v>1439</v>
       </c>
       <c r="D57" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E57" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F57" t="n">
-        <v>82.7</v>
+        <v>82.3</v>
       </c>
       <c r="G57" t="n">
-        <v>32.7</v>
+        <v>32.3</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1498</v>
+        <v>1442</v>
       </c>
       <c r="D58" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="E58" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="F58" t="n">
-        <v>83.5</v>
+        <v>83.2</v>
       </c>
       <c r="G58" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1498</v>
+        <v>1442</v>
       </c>
       <c r="D59" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="E59" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="F59" t="n">
-        <v>94.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10852,23 +10852,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1372</v>
+        <v>1450</v>
       </c>
       <c r="D60" t="n">
-        <v>51.4</v>
+        <v>50.6</v>
       </c>
       <c r="E60" t="n">
-        <v>48.6</v>
+        <v>49.4</v>
       </c>
       <c r="F60" t="n">
-        <v>42.5</v>
+        <v>41.9</v>
       </c>
       <c r="G60" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61">
@@ -10891,23 +10891,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1457</v>
+        <v>1321</v>
       </c>
       <c r="D61" t="n">
-        <v>50.2</v>
+        <v>51.6</v>
       </c>
       <c r="E61" t="n">
-        <v>49.8</v>
+        <v>48.4</v>
       </c>
       <c r="F61" t="n">
-        <v>42.8</v>
+        <v>42</v>
       </c>
       <c r="G61" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -10934,13 +10934,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>929</v>
+        <v>878</v>
       </c>
       <c r="D62" t="n">
-        <v>49.6</v>
+        <v>48.7</v>
       </c>
       <c r="E62" t="n">
-        <v>50.4</v>
+        <v>51.3</v>
       </c>
       <c r="F62" t="n">
         <v>58</v>
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>919</v>
+        <v>869</v>
       </c>
       <c r="D63" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
       <c r="E63" t="n">
-        <v>52.1</v>
+        <v>52.8</v>
       </c>
       <c r="F63" t="n">
-        <v>58.1</v>
+        <v>58.9</v>
       </c>
       <c r="G63" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64">
@@ -11008,23 +11008,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>942</v>
+        <v>1284</v>
       </c>
       <c r="D64" t="n">
-        <v>52.9</v>
+        <v>48.5</v>
       </c>
       <c r="E64" t="n">
-        <v>47.1</v>
+        <v>51.5</v>
       </c>
       <c r="F64" t="n">
-        <v>59.2</v>
+        <v>60</v>
       </c>
       <c r="G64" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65">
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1338</v>
+        <v>870</v>
       </c>
       <c r="D65" t="n">
-        <v>48.8</v>
+        <v>51.4</v>
       </c>
       <c r="E65" t="n">
-        <v>51.2</v>
+        <v>48.6</v>
       </c>
       <c r="F65" t="n">
-        <v>59.4</v>
+        <v>60.5</v>
       </c>
       <c r="G65" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
@@ -11086,23 +11086,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>922</v>
+        <v>891</v>
       </c>
       <c r="D66" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="E66" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="F66" t="n">
-        <v>59.9</v>
+        <v>60.5</v>
       </c>
       <c r="G66" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
@@ -11125,23 +11125,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1463</v>
+        <v>1025</v>
       </c>
       <c r="D67" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="E67" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="F67" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G67" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1492</v>
+        <v>1406</v>
       </c>
       <c r="D68" t="n">
-        <v>50.9</v>
+        <v>48.5</v>
       </c>
       <c r="E68" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
       <c r="F68" t="n">
-        <v>62.3</v>
+        <v>63</v>
       </c>
       <c r="G68" t="n">
-        <v>12.3</v>
+        <v>13</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69">
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1069</v>
+        <v>1436</v>
       </c>
       <c r="D69" t="n">
-        <v>48.9</v>
+        <v>50.6</v>
       </c>
       <c r="E69" t="n">
-        <v>51.1</v>
+        <v>49.4</v>
       </c>
       <c r="F69" t="n">
-        <v>62.6</v>
+        <v>63</v>
       </c>
       <c r="G69" t="n">
-        <v>12.6</v>
+        <v>13</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70">
@@ -11246,19 +11246,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1280</v>
+        <v>1229</v>
       </c>
       <c r="D70" t="n">
-        <v>48.6</v>
+        <v>47.8</v>
       </c>
       <c r="E70" t="n">
-        <v>51.4</v>
+        <v>52.2</v>
       </c>
       <c r="F70" t="n">
-        <v>62.8</v>
+        <v>63.5</v>
       </c>
       <c r="G70" t="n">
-        <v>12.8</v>
+        <v>13.5</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71">
@@ -11285,19 +11285,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1475</v>
+        <v>1419</v>
       </c>
       <c r="D71" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="E71" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F71" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="G71" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11324,19 +11324,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1460</v>
+        <v>1451</v>
       </c>
       <c r="D72" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="E72" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="F72" t="n">
-        <v>63.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73">
@@ -11363,13 +11363,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1282</v>
+        <v>1235</v>
       </c>
       <c r="D73" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
       <c r="E73" t="n">
-        <v>51.6</v>
+        <v>52.1</v>
       </c>
       <c r="F73" t="n">
         <v>66.59999999999999</v>
@@ -11389,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74">
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>566</v>
+        <v>530</v>
       </c>
       <c r="D74" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E74" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F74" t="n">
-        <v>53.5</v>
+        <v>53.8</v>
       </c>
       <c r="G74" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75">
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>545</v>
+        <v>510</v>
       </c>
       <c r="D75" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="E75" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="F75" t="n">
-        <v>54.5</v>
+        <v>54.3</v>
       </c>
       <c r="G75" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>560</v>
+        <v>522</v>
       </c>
       <c r="D76" t="n">
         <v>52.7</v>
@@ -11489,10 +11489,10 @@
         <v>47.3</v>
       </c>
       <c r="F76" t="n">
-        <v>54.6</v>
+        <v>55.2</v>
       </c>
       <c r="G76" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77">
@@ -11519,7 +11519,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1085</v>
+        <v>1042</v>
       </c>
       <c r="D77" t="n">
         <v>51.2</v>
@@ -11528,10 +11528,10 @@
         <v>48.8</v>
       </c>
       <c r="F77" t="n">
-        <v>56.1</v>
+        <v>55.5</v>
       </c>
       <c r="G77" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1396</v>
+        <v>1344</v>
       </c>
       <c r="D78" t="n">
-        <v>48.9</v>
+        <v>48.2</v>
       </c>
       <c r="E78" t="n">
-        <v>51.1</v>
+        <v>51.8</v>
       </c>
       <c r="F78" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>544</v>
+        <v>508</v>
       </c>
       <c r="D79" t="n">
-        <v>48.3</v>
+        <v>48.8</v>
       </c>
       <c r="E79" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="F79" t="n">
-        <v>58.1</v>
+        <v>59.3</v>
       </c>
       <c r="G79" t="n">
-        <v>8.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1134</v>
+        <v>1091</v>
       </c>
       <c r="D80" t="n">
-        <v>46.6</v>
+        <v>46.1</v>
       </c>
       <c r="E80" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="F80" t="n">
-        <v>60.2</v>
+        <v>60</v>
       </c>
       <c r="G80" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="81">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1088</v>
+        <v>1054</v>
       </c>
       <c r="D81" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="E81" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="F81" t="n">
         <v>63</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82">
@@ -11710,23 +11710,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLE</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>386</v>
+        <v>368</v>
       </c>
       <c r="D82" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="E82" t="n">
-        <v>52.6</v>
+        <v>50</v>
       </c>
       <c r="F82" t="n">
-        <v>49.2</v>
+        <v>48.1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
@@ -11749,23 +11749,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLE</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>393</v>
+        <v>361</v>
       </c>
       <c r="D83" t="n">
-        <v>49.9</v>
+        <v>48.5</v>
       </c>
       <c r="E83" t="n">
-        <v>50.1</v>
+        <v>51.5</v>
       </c>
       <c r="F83" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="G83" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>392</v>
+        <v>368</v>
       </c>
       <c r="D84" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E84" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F84" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="G84" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85">
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>408</v>
+        <v>383</v>
       </c>
       <c r="D85" t="n">
-        <v>47.5</v>
+        <v>47.3</v>
       </c>
       <c r="E85" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="G85" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="86">
@@ -11866,23 +11866,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>390</v>
+        <v>372</v>
       </c>
       <c r="D86" t="n">
-        <v>51.5</v>
+        <v>45.4</v>
       </c>
       <c r="E86" t="n">
-        <v>48.5</v>
+        <v>54.6</v>
       </c>
       <c r="F86" t="n">
-        <v>56.7</v>
+        <v>56.2</v>
       </c>
       <c r="G86" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87">
@@ -11905,23 +11905,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>398</v>
+        <v>367</v>
       </c>
       <c r="D87" t="n">
-        <v>46.2</v>
+        <v>51.5</v>
       </c>
       <c r="E87" t="n">
-        <v>53.8</v>
+        <v>48.5</v>
       </c>
       <c r="F87" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="G87" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="88">
@@ -11944,23 +11944,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>406</v>
+        <v>367</v>
       </c>
       <c r="D88" t="n">
-        <v>50.2</v>
+        <v>48.8</v>
       </c>
       <c r="E88" t="n">
-        <v>49.8</v>
+        <v>51.2</v>
       </c>
       <c r="F88" t="n">
-        <v>61.1</v>
+        <v>60.5</v>
       </c>
       <c r="G88" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="89">
@@ -11983,23 +11983,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="D89" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="E89" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="F89" t="n">
-        <v>61.7</v>
+        <v>61.9</v>
       </c>
       <c r="G89" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12026,19 +12026,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="D90" t="n">
-        <v>49.8</v>
+        <v>50.3</v>
       </c>
       <c r="E90" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="F90" t="n">
-        <v>61.9</v>
+        <v>62.2</v>
       </c>
       <c r="G90" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="91">
@@ -12065,19 +12065,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="D91" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
       <c r="E91" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="F91" t="n">
-        <v>62.6</v>
+        <v>62.9</v>
       </c>
       <c r="G91" t="n">
-        <v>12.6</v>
+        <v>12.9</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="92">
@@ -12104,19 +12104,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="D92" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="E92" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="F92" t="n">
-        <v>62.7</v>
+        <v>63.3</v>
       </c>
       <c r="G92" t="n">
-        <v>12.7</v>
+        <v>13.3</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>378</v>
+        <v>354</v>
       </c>
       <c r="D93" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="E93" t="n">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="F93" t="n">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="G93" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12182,19 +12182,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1500</v>
+        <v>1444</v>
       </c>
       <c r="D94" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
       <c r="E94" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="F94" t="n">
-        <v>58.6</v>
+        <v>58.2</v>
       </c>
       <c r="G94" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95">
@@ -12221,19 +12221,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1458</v>
+        <v>1401</v>
       </c>
       <c r="D95" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="E95" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="F95" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="G95" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="96">
@@ -12260,19 +12260,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1336</v>
+        <v>1283</v>
       </c>
       <c r="D96" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="F96" t="n">
-        <v>59</v>
+        <v>59.3</v>
       </c>
       <c r="G96" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97">
@@ -12299,19 +12299,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1501</v>
+        <v>1494</v>
       </c>
       <c r="D97" t="n">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
       <c r="E97" t="n">
-        <v>50.6</v>
+        <v>51.5</v>
       </c>
       <c r="F97" t="n">
-        <v>59.6</v>
+        <v>60.2</v>
       </c>
       <c r="G97" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1501</v>
+        <v>1427</v>
       </c>
       <c r="D98" t="n">
-        <v>49.4</v>
+        <v>48.3</v>
       </c>
       <c r="E98" t="n">
-        <v>50.6</v>
+        <v>51.7</v>
       </c>
       <c r="F98" t="n">
-        <v>60</v>
+        <v>60.3</v>
       </c>
       <c r="G98" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="99">
@@ -12373,23 +12373,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1484</v>
+        <v>1445</v>
       </c>
       <c r="D99" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="E99" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="F99" t="n">
-        <v>60.1</v>
+        <v>60.5</v>
       </c>
       <c r="G99" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="100">
@@ -12412,23 +12412,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1494</v>
+        <v>1444</v>
       </c>
       <c r="D100" t="n">
-        <v>49.9</v>
+        <v>49.1</v>
       </c>
       <c r="E100" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="F100" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="G100" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="101">
@@ -12451,23 +12451,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="D101" t="n">
-        <v>49.7</v>
+        <v>49</v>
       </c>
       <c r="E101" t="n">
-        <v>50.3</v>
+        <v>51</v>
       </c>
       <c r="F101" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="G101" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="102">
@@ -12490,23 +12490,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1500</v>
+        <v>1389</v>
       </c>
       <c r="D102" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="F102" t="n">
-        <v>60.6</v>
+        <v>61.3</v>
       </c>
       <c r="G102" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1480</v>
+        <v>1428</v>
       </c>
       <c r="D103" t="n">
-        <v>50.1</v>
+        <v>49.2</v>
       </c>
       <c r="E103" t="n">
-        <v>49.9</v>
+        <v>50.8</v>
       </c>
       <c r="F103" t="n">
-        <v>61.8</v>
+        <v>61.9</v>
       </c>
       <c r="G103" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38048</v>
+        <v>38078</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38099</v>
+        <v>38131</v>
       </c>
       <c r="D3" t="n">
         <v>50.2</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38298</v>
+        <v>38330</v>
       </c>
       <c r="D4" t="n">
         <v>51.2</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37775</v>
+        <v>37806</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38240</v>
+        <v>38272</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37760</v>
+        <v>37792</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37593</v>
+        <v>37625</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38044</v>
+        <v>38074</v>
       </c>
       <c r="D9" t="n">
         <v>50</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38326</v>
+        <v>38358</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38377</v>
+        <v>38409</v>
       </c>
       <c r="D11" t="n">
         <v>50.7</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38390</v>
+        <v>38422</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38214</v>
+        <v>38245</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38273</v>
+        <v>38305</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38177</v>
+        <v>38208</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38193</v>
+        <v>38225</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36467</v>
+        <v>36497</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38444</v>
+        <v>38476</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>37985</v>
+        <v>38017</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34740</v>
+        <v>34764</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38516</v>
+        <v>38547</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,13 +13423,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38332</v>
+        <v>38363</v>
       </c>
       <c r="D22" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E22" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F22" t="n">
         <v>40.2</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38382</v>
+        <v>38413</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38562</v>
+        <v>38594</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38516</v>
+        <v>38548</v>
       </c>
       <c r="D25" t="n">
         <v>49.9</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38573</v>
+        <v>38605</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34908</v>
+        <v>34932</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38598</v>
+        <v>38630</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38606</v>
+        <v>38638</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38323</v>
+        <v>38355</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13770,17 +13770,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38356</v>
+        <v>38391</v>
       </c>
       <c r="D31" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="E31" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F31" t="n">
         <v>44.5</v>
@@ -13809,23 +13809,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38359</v>
+        <v>38387</v>
       </c>
       <c r="D32" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E32" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F32" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="G32" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38382</v>
+        <v>38414</v>
       </c>
       <c r="D33" t="n">
         <v>49.6</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38319</v>
+        <v>38351</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38321</v>
+        <v>38352</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34794</v>
+        <v>34818</v>
       </c>
       <c r="D36" t="n">
         <v>49.8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38159</v>
+        <v>38190</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37504</v>
+        <v>37533</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38315</v>
+        <v>38347</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14095,10 +14095,10 @@
         <v>52.8</v>
       </c>
       <c r="F39" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -14112,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40">
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8080</v>
+        <v>8085</v>
       </c>
       <c r="D40" t="n">
         <v>51.3</v>
@@ -14134,10 +14134,10 @@
         <v>48.7</v>
       </c>
       <c r="F40" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37996</v>
+        <v>38028</v>
       </c>
       <c r="D41" t="n">
         <v>50</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38058</v>
+        <v>38088</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38091</v>
+        <v>38123</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38017</v>
+        <v>38049</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37674</v>
+        <v>37705</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37824</v>
+        <v>37855</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38197</v>
+        <v>38229</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38240</v>
+        <v>38272</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35638</v>
+        <v>35666</v>
       </c>
       <c r="D49" t="n">
         <v>50.3</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38078</v>
+        <v>38110</v>
       </c>
       <c r="D50" t="n">
         <v>49.4</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37943</v>
+        <v>37974</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38122</v>
+        <v>38154</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>37993</v>
+        <v>38024</v>
       </c>
       <c r="D53" t="n">
         <v>49.6</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38031</v>
+        <v>38063</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38211</v>
+        <v>38242</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37915</v>
+        <v>37947</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38276</v>
+        <v>38308</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38356</v>
+        <v>38388</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38558</v>
+        <v>38590</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>34991</v>
+        <v>35019</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14931,7 +14931,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61">
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36867</v>
+        <v>36946</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37374</v>
+        <v>37404</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23329</v>
+        <v>23333</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23752</v>
+        <v>23756</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23776</v>
+        <v>23780</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38261</v>
+        <v>38293</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -15178,13 +15178,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>37766</v>
+        <v>37798</v>
       </c>
       <c r="D67" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E67" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F67" t="n">
         <v>56</v>
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21154</v>
+        <v>21158</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -15256,13 +15256,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36035</v>
+        <v>36066</v>
       </c>
       <c r="D69" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -15295,13 +15295,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30447</v>
+        <v>30473</v>
       </c>
       <c r="D70" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E70" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F70" t="n">
         <v>56.7</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37386</v>
+        <v>37462</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32913</v>
+        <v>32942</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25954</v>
+        <v>25973</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26548</v>
+        <v>26571</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,13 +15607,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35759</v>
+        <v>35788</v>
       </c>
       <c r="D78" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E78" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F78" t="n">
         <v>65.5</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28528</v>
+        <v>28553</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27768</v>
+        <v>27793</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -16231,13 +16231,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37796</v>
+        <v>37827</v>
       </c>
       <c r="D94" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F94" t="n">
         <v>53.7</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38401</v>
+        <v>38433</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36020</v>
+        <v>36043</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38517</v>
+        <v>38549</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37726</v>
+        <v>37756</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38310</v>
+        <v>38341</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37911</v>
+        <v>37943</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38594</v>
+        <v>38626</v>
       </c>
       <c r="D101" t="n">
         <v>50.1</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38172</v>
+        <v>38204</v>
       </c>
       <c r="D102" t="n">
         <v>49.7</v>
@@ -16582,13 +16582,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38615</v>
+        <v>38696</v>
       </c>
       <c r="D103" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E103" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F103" t="n">
         <v>54.9</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1435</v>
+        <v>1490</v>
       </c>
       <c r="D2" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E2" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F2" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -535,13 +535,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1434</v>
+        <v>1490</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F3" t="n">
         <v>48.5</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1435</v>
+        <v>1490</v>
       </c>
       <c r="D4" t="n">
         <v>49.3</v>
@@ -583,10 +583,10 @@
         <v>50.7</v>
       </c>
       <c r="F4" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1423</v>
+        <v>1494</v>
       </c>
       <c r="D5" t="n">
-        <v>50.2</v>
+        <v>47.3</v>
       </c>
       <c r="E5" t="n">
-        <v>49.8</v>
+        <v>52.7</v>
       </c>
       <c r="F5" t="n">
-        <v>46.9</v>
+        <v>52.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHFJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1438</v>
+        <v>1478</v>
       </c>
       <c r="D6" t="n">
-        <v>47.4</v>
+        <v>50.3</v>
       </c>
       <c r="E6" t="n">
-        <v>52.6</v>
+        <v>49.7</v>
       </c>
       <c r="F6" t="n">
-        <v>53.2</v>
+        <v>47.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1382</v>
+        <v>1438</v>
       </c>
       <c r="D7" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="E7" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="F7" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1411</v>
+        <v>1467</v>
       </c>
       <c r="D8" t="n">
         <v>48.5</v>
@@ -739,10 +739,10 @@
         <v>51.5</v>
       </c>
       <c r="F8" t="n">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
       <c r="G8" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1438</v>
+        <v>1494</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="E9" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="F9" t="n">
-        <v>55.3</v>
+        <v>55</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1407</v>
+        <v>1462</v>
       </c>
       <c r="D10" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="E10" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1407</v>
+        <v>1462</v>
       </c>
       <c r="D11" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
       <c r="E11" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="F11" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="G11" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -882,23 +882,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1434</v>
+        <v>1553</v>
       </c>
       <c r="D12" t="n">
-        <v>50.8</v>
+        <v>52</v>
       </c>
       <c r="E12" t="n">
-        <v>49.2</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>40.2</v>
+        <v>40.8</v>
       </c>
       <c r="G12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -921,17 +921,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1413</v>
+        <v>1577</v>
       </c>
       <c r="D13" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="E13" t="n">
-        <v>48.5</v>
+        <v>49.4</v>
       </c>
       <c r="F13" t="n">
         <v>40.1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1416</v>
+        <v>1558</v>
       </c>
       <c r="D14" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="E14" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="F14" t="n">
-        <v>36.9</v>
+        <v>37.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1416</v>
+        <v>1558</v>
       </c>
       <c r="D15" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="E15" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="F15" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
       <c r="G15" t="n">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1413</v>
+        <v>1555</v>
       </c>
       <c r="D16" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="E16" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="F16" t="n">
-        <v>63.8</v>
+        <v>63.5</v>
       </c>
       <c r="G16" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1289</v>
+        <v>1345</v>
       </c>
       <c r="D17" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="E17" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F17" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1389</v>
+        <v>1442</v>
       </c>
       <c r="D18" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E18" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F18" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1440</v>
+        <v>1496</v>
       </c>
       <c r="D19" t="n">
-        <v>46.7</v>
+        <v>46.3</v>
       </c>
       <c r="E19" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="F19" t="n">
-        <v>51.4</v>
+        <v>51.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1185,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1399</v>
+        <v>1453</v>
       </c>
       <c r="D20" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1420</v>
+        <v>380</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>48.9</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>51.1</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>52.4</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>11</v>
@@ -1272,20 +1272,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>362</v>
+        <v>1475</v>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F22" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
         <v>3</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1315,19 +1315,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1408</v>
+        <v>1463</v>
       </c>
       <c r="D23" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="E23" t="n">
-        <v>52.9</v>
+        <v>52.4</v>
       </c>
       <c r="F23" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="G23" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1430</v>
+        <v>1485</v>
       </c>
       <c r="D24" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E24" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F24" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="G24" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1429</v>
+        <v>1485</v>
       </c>
       <c r="D25" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="E25" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="F25" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="G25" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1420</v>
+        <v>1474</v>
       </c>
       <c r="D26" t="n">
-        <v>52.2</v>
+        <v>52.6</v>
       </c>
       <c r="E26" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="F26" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="G26" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1425</v>
+        <v>1480</v>
       </c>
       <c r="D27" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E27" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F27" t="n">
-        <v>56</v>
+        <v>55.7</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1403</v>
+        <v>1454</v>
       </c>
       <c r="D28" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E28" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F28" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1291</v>
+        <v>1347</v>
       </c>
       <c r="D29" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E29" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F29" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>1</v>
       </c>
       <c r="K29" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1430</v>
+        <v>1485</v>
       </c>
       <c r="D30" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="E30" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="F30" t="n">
         <v>43.4</v>
@@ -1627,19 +1627,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1439</v>
+        <v>1495</v>
       </c>
       <c r="D31" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E31" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F31" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="G31" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1433</v>
+        <v>1488</v>
       </c>
       <c r="D32" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E32" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F32" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
       <c r="G32" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1701,23 +1701,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1434</v>
+        <v>1485</v>
       </c>
       <c r="D33" t="n">
-        <v>50.8</v>
+        <v>46.2</v>
       </c>
       <c r="E33" t="n">
-        <v>49.2</v>
+        <v>53.8</v>
       </c>
       <c r="F33" t="n">
-        <v>42</v>
+        <v>57.4</v>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34">
@@ -1740,23 +1740,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1429</v>
+        <v>1490</v>
       </c>
       <c r="D34" t="n">
-        <v>46.3</v>
+        <v>50.8</v>
       </c>
       <c r="E34" t="n">
-        <v>53.7</v>
+        <v>49.2</v>
       </c>
       <c r="F34" t="n">
-        <v>58.1</v>
+        <v>42.4</v>
       </c>
       <c r="G34" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
@@ -1779,23 +1779,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1310</v>
+        <v>1470</v>
       </c>
       <c r="D35" t="n">
-        <v>47.6</v>
+        <v>49.5</v>
       </c>
       <c r="E35" t="n">
-        <v>52.4</v>
+        <v>50.5</v>
       </c>
       <c r="F35" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1818,23 +1818,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1415</v>
+        <v>1354</v>
       </c>
       <c r="D36" t="n">
-        <v>49.5</v>
+        <v>47.7</v>
       </c>
       <c r="E36" t="n">
-        <v>50.5</v>
+        <v>52.3</v>
       </c>
       <c r="F36" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="G36" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1428</v>
+        <v>1483</v>
       </c>
       <c r="D37" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="E37" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="F37" t="n">
         <v>40.1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -1896,20 +1896,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AUDCAD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1418</v>
+        <v>1486</v>
       </c>
       <c r="D38" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="E38" t="n">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
       <c r="F38" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G38" t="n">
         <v>10</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
@@ -1935,11 +1935,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1430</v>
+        <v>1472</v>
       </c>
       <c r="D39" t="n">
         <v>49</v>
@@ -1948,10 +1948,10 @@
         <v>51</v>
       </c>
       <c r="F39" t="n">
-        <v>39.4</v>
+        <v>60.1</v>
       </c>
       <c r="G39" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1439</v>
+        <v>1495</v>
       </c>
       <c r="D40" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="E40" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="F40" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="G40" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1445</v>
+        <v>1464</v>
       </c>
       <c r="D41" t="n">
-        <v>51.2</v>
+        <v>50.3</v>
       </c>
       <c r="E41" t="n">
-        <v>48.8</v>
+        <v>49.7</v>
       </c>
       <c r="F41" t="n">
-        <v>38.1</v>
+        <v>61.6</v>
       </c>
       <c r="G41" t="n">
-        <v>11.9</v>
+        <v>11.6</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1410</v>
+        <v>1489</v>
       </c>
       <c r="D42" t="n">
-        <v>50.4</v>
+        <v>52</v>
       </c>
       <c r="E42" t="n">
-        <v>49.6</v>
+        <v>48</v>
       </c>
       <c r="F42" t="n">
-        <v>62.1</v>
+        <v>38</v>
       </c>
       <c r="G42" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="43">
@@ -2091,23 +2091,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1433</v>
+        <v>1501</v>
       </c>
       <c r="D43" t="n">
-        <v>52.3</v>
+        <v>51.2</v>
       </c>
       <c r="E43" t="n">
-        <v>47.7</v>
+        <v>48.8</v>
       </c>
       <c r="F43" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="G43" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="44">
@@ -2130,23 +2130,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1424</v>
+        <v>1343</v>
       </c>
       <c r="D44" t="n">
-        <v>48.9</v>
+        <v>52.1</v>
       </c>
       <c r="E44" t="n">
-        <v>51.1</v>
+        <v>47.9</v>
       </c>
       <c r="F44" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="G44" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1438</v>
+        <v>1494</v>
       </c>
       <c r="D45" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E45" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F45" t="n">
         <v>37.6</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1287</v>
+        <v>1480</v>
       </c>
       <c r="D46" t="n">
-        <v>52.3</v>
+        <v>48.8</v>
       </c>
       <c r="E46" t="n">
-        <v>47.7</v>
+        <v>51.2</v>
       </c>
       <c r="F46" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="G46" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47">
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1443</v>
+        <v>1499</v>
       </c>
       <c r="D47" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="E47" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="F47" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="G47" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
@@ -2286,23 +2286,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1445</v>
+        <v>1463</v>
       </c>
       <c r="D48" t="n">
-        <v>52.5</v>
+        <v>50.1</v>
       </c>
       <c r="E48" t="n">
-        <v>47.5</v>
+        <v>49.9</v>
       </c>
       <c r="F48" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="G48" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="J48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="49">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1409</v>
+        <v>1501</v>
       </c>
       <c r="D49" t="n">
-        <v>50.2</v>
+        <v>52.2</v>
       </c>
       <c r="E49" t="n">
-        <v>49.8</v>
+        <v>47.8</v>
       </c>
       <c r="F49" t="n">
-        <v>36.6</v>
+        <v>36.2</v>
       </c>
       <c r="G49" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="J49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50">
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="D50" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="E50" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="F50" t="n">
         <v>35.4</v>
@@ -2394,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51">
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1421</v>
+        <v>1477</v>
       </c>
       <c r="D51" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E51" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F51" t="n">
-        <v>66.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G51" t="n">
-        <v>16.1</v>
+        <v>15.6</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1420</v>
+        <v>1476</v>
       </c>
       <c r="D52" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="E52" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="F52" t="n">
-        <v>66.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1444</v>
+        <v>1500</v>
       </c>
       <c r="D53" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="E53" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="F53" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="G53" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1343</v>
+        <v>1396</v>
       </c>
       <c r="D54" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="E54" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="F54" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="G54" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1434</v>
+        <v>1490</v>
       </c>
       <c r="D55" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="E55" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="F55" t="n">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="G55" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1426</v>
+        <v>1481</v>
       </c>
       <c r="D56" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="E56" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F56" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1439</v>
+        <v>1494</v>
       </c>
       <c r="D57" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E57" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F57" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="D58" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="E58" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="F58" t="n">
         <v>83.2</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="D59" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E59" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="F59" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="G59" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1321</v>
+        <v>1544</v>
       </c>
       <c r="D60" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="E60" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
       <c r="F60" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="G60" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1450</v>
+        <v>1376</v>
       </c>
       <c r="D61" t="n">
-        <v>50.6</v>
+        <v>51.5</v>
       </c>
       <c r="E61" t="n">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
       <c r="F61" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="G61" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>878</v>
+        <v>929</v>
       </c>
       <c r="D62" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="E62" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="F62" t="n">
-        <v>58</v>
+        <v>58.6</v>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>869</v>
+        <v>921</v>
       </c>
       <c r="D63" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="E63" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="F63" t="n">
-        <v>58.9</v>
+        <v>59.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1284</v>
+        <v>1339</v>
       </c>
       <c r="D64" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="E64" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="F64" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="G64" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65">
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>870</v>
+        <v>943</v>
       </c>
       <c r="D65" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="E65" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="F65" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="G65" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>891</v>
+        <v>921</v>
       </c>
       <c r="D66" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="E66" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F66" t="n">
-        <v>60.5</v>
+        <v>61</v>
       </c>
       <c r="G66" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67">
@@ -3031,19 +3031,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1025</v>
+        <v>1070</v>
       </c>
       <c r="D67" t="n">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
       <c r="E67" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="F67" t="n">
-        <v>62.5</v>
+        <v>63</v>
       </c>
       <c r="G67" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68">
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1406</v>
+        <v>1460</v>
       </c>
       <c r="D68" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E68" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="F68" t="n">
-        <v>63</v>
+        <v>63.2</v>
       </c>
       <c r="G68" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69">
@@ -3109,19 +3109,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1436</v>
+        <v>1492</v>
       </c>
       <c r="D69" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E69" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F69" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="G69" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="70">
@@ -3148,7 +3148,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1229</v>
+        <v>1281</v>
       </c>
       <c r="D70" t="n">
         <v>47.8</v>
@@ -3157,10 +3157,10 @@
         <v>52.2</v>
       </c>
       <c r="F70" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
       <c r="G70" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71">
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1419</v>
+        <v>1475</v>
       </c>
       <c r="D71" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="E71" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="F71" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="G71" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72">
@@ -3226,19 +3226,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1451</v>
+        <v>1544</v>
       </c>
       <c r="D72" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E72" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F72" t="n">
-        <v>64.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1235</v>
+        <v>1282</v>
       </c>
       <c r="D73" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="E73" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>66.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="G73" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>530</v>
+        <v>566</v>
       </c>
       <c r="D74" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="F74" t="n">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="D75" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="E75" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="F75" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="G75" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>522</v>
+        <v>557</v>
       </c>
       <c r="D76" t="n">
-        <v>52.7</v>
+        <v>52.2</v>
       </c>
       <c r="E76" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="F76" t="n">
-        <v>55.2</v>
+        <v>54.9</v>
       </c>
       <c r="G76" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1042</v>
+        <v>1085</v>
       </c>
       <c r="D77" t="n">
         <v>51.2</v>
@@ -3430,10 +3430,10 @@
         <v>48.8</v>
       </c>
       <c r="F77" t="n">
-        <v>55.5</v>
+        <v>55.2</v>
       </c>
       <c r="G77" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1344</v>
+        <v>1399</v>
       </c>
       <c r="D78" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E78" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F78" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="G78" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="D79" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E79" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="F79" t="n">
-        <v>59.3</v>
+        <v>60.1</v>
       </c>
       <c r="G79" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1091</v>
+        <v>1142</v>
       </c>
       <c r="D80" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="E80" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
       <c r="F80" t="n">
-        <v>60</v>
+        <v>60.6</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1054</v>
+        <v>1105</v>
       </c>
       <c r="D81" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="E81" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="F81" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="G81" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82">
@@ -3612,23 +3612,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>361</v>
+        <v>394</v>
       </c>
       <c r="D82" t="n">
-        <v>48.5</v>
+        <v>46.2</v>
       </c>
       <c r="E82" t="n">
-        <v>51.5</v>
+        <v>53.8</v>
       </c>
       <c r="F82" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="G82" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3651,23 +3651,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D83" t="n">
-        <v>47</v>
+        <v>48.2</v>
       </c>
       <c r="E83" t="n">
-        <v>53</v>
+        <v>51.8</v>
       </c>
       <c r="F83" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="D84" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E84" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="G84" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -3733,7 +3733,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="D85" t="n">
         <v>47.3</v>
@@ -3742,10 +3742,10 @@
         <v>52.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.6</v>
+        <v>54.2</v>
       </c>
       <c r="G85" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86">
@@ -3768,23 +3768,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="D86" t="n">
-        <v>45.4</v>
+        <v>50.9</v>
       </c>
       <c r="E86" t="n">
-        <v>54.6</v>
+        <v>49.1</v>
       </c>
       <c r="F86" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="G86" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3807,23 +3807,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="D87" t="n">
-        <v>51.5</v>
+        <v>44.5</v>
       </c>
       <c r="E87" t="n">
-        <v>48.5</v>
+        <v>55.5</v>
       </c>
       <c r="F87" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="D88" t="n">
-        <v>48.8</v>
+        <v>49.4</v>
       </c>
       <c r="E88" t="n">
-        <v>51.2</v>
+        <v>50.6</v>
       </c>
       <c r="F88" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="G88" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3889,19 +3889,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D89" t="n">
-        <v>49.9</v>
+        <v>49.1</v>
       </c>
       <c r="E89" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="F89" t="n">
-        <v>61.9</v>
+        <v>62.4</v>
       </c>
       <c r="G89" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90">
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="E90" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="F90" t="n">
-        <v>62.2</v>
+        <v>62.9</v>
       </c>
       <c r="G90" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="D91" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="E91" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="G91" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="92">
@@ -4006,19 +4006,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="D92" t="n">
-        <v>51.8</v>
+        <v>51</v>
       </c>
       <c r="E92" t="n">
-        <v>48.2</v>
+        <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>63.3</v>
+        <v>63.7</v>
       </c>
       <c r="G92" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="D93" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="E93" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="F93" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="G93" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4084,13 +4084,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1444</v>
+        <v>1500</v>
       </c>
       <c r="D94" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E94" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F94" t="n">
         <v>58.2</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="95">
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1401</v>
+        <v>1457</v>
       </c>
       <c r="D95" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E95" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F95" t="n">
-        <v>58.7</v>
+        <v>59</v>
       </c>
       <c r="G95" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1283</v>
+        <v>1333</v>
       </c>
       <c r="D96" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E96" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F96" t="n">
         <v>59.3</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="97">
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1494</v>
+        <v>1501</v>
       </c>
       <c r="D97" t="n">
         <v>48.5</v>
@@ -4240,19 +4240,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1427</v>
+        <v>1482</v>
       </c>
       <c r="D98" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E98" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F98" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="G98" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4279,13 +4279,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1445</v>
+        <v>1501</v>
       </c>
       <c r="D99" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="E99" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="F99" t="n">
         <v>60.5</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="100">
@@ -4314,23 +4314,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1444</v>
+        <v>1494</v>
       </c>
       <c r="D100" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E100" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F100" t="n">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
       <c r="G100" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4353,11 +4353,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1438</v>
+        <v>1500</v>
       </c>
       <c r="D101" t="n">
         <v>49</v>
@@ -4366,10 +4366,10 @@
         <v>51</v>
       </c>
       <c r="F101" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4396,19 +4396,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1389</v>
+        <v>1445</v>
       </c>
       <c r="D102" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E102" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F102" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="G102" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4435,13 +4435,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="D103" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E103" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F103" t="n">
         <v>61.9</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38074</v>
+        <v>38129</v>
       </c>
       <c r="D2" t="n">
         <v>50</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37625</v>
+        <v>37681</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37792</v>
+        <v>37847</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38358</v>
+        <v>38414</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38409</v>
+        <v>38465</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38272</v>
+        <v>38327</v>
       </c>
       <c r="D7" t="n">
         <v>50.7</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38422</v>
+        <v>38477</v>
       </c>
       <c r="D8" t="n">
         <v>51.4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37806</v>
+        <v>37861</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38245</v>
+        <v>38301</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38305</v>
+        <v>38361</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38330</v>
+        <v>38473</v>
       </c>
       <c r="D12" t="n">
         <v>51.2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38131</v>
+        <v>38271</v>
       </c>
       <c r="D13" t="n">
         <v>50.2</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38078</v>
+        <v>38220</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38208</v>
+        <v>38350</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38225</v>
+        <v>38367</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38347</v>
+        <v>38403</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5139,10 +5139,10 @@
         <v>52.8</v>
       </c>
       <c r="F17" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -5169,19 +5169,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8085</v>
+        <v>8103</v>
       </c>
       <c r="D18" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E18" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F18" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38028</v>
+        <v>38082</v>
       </c>
       <c r="D19" t="n">
         <v>50</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37533</v>
+        <v>37586</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38190</v>
+        <v>38245</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34818</v>
+        <v>34874</v>
       </c>
       <c r="D22" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E22" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F22" t="n">
         <v>47.6</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38352</v>
+        <v>38408</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38088</v>
+        <v>38143</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38123</v>
+        <v>38179</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38351</v>
+        <v>38406</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38049</v>
+        <v>38104</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37705</v>
+        <v>37756</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37855</v>
+        <v>37909</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5633,20 +5633,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38229</v>
+        <v>38470</v>
       </c>
       <c r="D30" t="n">
-        <v>50.6</v>
+        <v>49.6</v>
       </c>
       <c r="E30" t="n">
-        <v>49.4</v>
+        <v>50.4</v>
       </c>
       <c r="F30" t="n">
-        <v>55.1</v>
+        <v>44.9</v>
       </c>
       <c r="G30" t="n">
         <v>5.1</v>
@@ -5672,23 +5672,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38414</v>
+        <v>38284</v>
       </c>
       <c r="D31" t="n">
-        <v>49.6</v>
+        <v>50.6</v>
       </c>
       <c r="E31" t="n">
-        <v>50.4</v>
+        <v>49.4</v>
       </c>
       <c r="F31" t="n">
-        <v>44.8</v>
+        <v>55.1</v>
       </c>
       <c r="G31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38272</v>
+        <v>38327</v>
       </c>
       <c r="D32" t="n">
         <v>51.1</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38387</v>
+        <v>38443</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38391</v>
+        <v>38447</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38355</v>
+        <v>38410</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5858,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38638</v>
+        <v>38694</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38630</v>
+        <v>38686</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5919,10 +5919,10 @@
         <v>50.9</v>
       </c>
       <c r="F37" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35666</v>
+        <v>35710</v>
       </c>
       <c r="D38" t="n">
         <v>50.3</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34932</v>
+        <v>34988</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38110</v>
+        <v>38165</v>
       </c>
       <c r="D40" t="n">
         <v>49.4</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37974</v>
+        <v>38028</v>
       </c>
       <c r="D41" t="n">
         <v>50.3</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38154</v>
+        <v>38208</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38548</v>
+        <v>38604</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38605</v>
+        <v>38661</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38594</v>
+        <v>38650</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38413</v>
+        <v>38469</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6270,10 +6270,10 @@
         <v>50.4</v>
       </c>
       <c r="F46" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="G46" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38363</v>
+        <v>38419</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38547</v>
+        <v>38603</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34764</v>
+        <v>34820</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38024</v>
+        <v>38080</v>
       </c>
       <c r="D50" t="n">
         <v>49.6</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38017</v>
+        <v>38071</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38063</v>
+        <v>38119</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38476</v>
+        <v>38532</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6543,10 +6543,10 @@
         <v>50.9</v>
       </c>
       <c r="F53" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="G53" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36497</v>
+        <v>36550</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38242</v>
+        <v>38298</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37947</v>
+        <v>38002</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38308</v>
+        <v>38363</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38388</v>
+        <v>38444</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38590</v>
+        <v>38646</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36946</v>
+        <v>37040</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6816,10 +6816,10 @@
         <v>49.6</v>
       </c>
       <c r="F60" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="G60" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35019</v>
+        <v>35074</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6855,10 +6855,10 @@
         <v>49.2</v>
       </c>
       <c r="F61" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="G61" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37404</v>
+        <v>37458</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23333</v>
+        <v>23384</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23756</v>
+        <v>23807</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23780</v>
+        <v>38349</v>
       </c>
       <c r="D65" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E65" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F65" t="n">
         <v>55.9</v>
@@ -7037,23 +7037,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38293</v>
+        <v>23832</v>
       </c>
       <c r="D66" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E66" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="G66" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -7067,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -7076,23 +7076,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>37798</v>
+        <v>21210</v>
       </c>
       <c r="D67" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="E67" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="F67" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68">
@@ -7115,17 +7115,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21158</v>
+        <v>37854</v>
       </c>
       <c r="D68" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="E68" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="F68" t="n">
         <v>56.1</v>
@@ -7158,13 +7158,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36066</v>
+        <v>36121</v>
       </c>
       <c r="D69" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E69" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30473</v>
+        <v>30525</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37462</v>
+        <v>37555</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32942</v>
+        <v>32989</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25973</v>
+        <v>26018</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14168</v>
+        <v>14202</v>
       </c>
       <c r="D74" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E74" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F74" t="n">
         <v>51</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14045</v>
+        <v>14080</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15100</v>
+        <v>15136</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26571</v>
+        <v>26614</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35788</v>
+        <v>35843</v>
       </c>
       <c r="D78" t="n">
         <v>50.5</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28553</v>
+        <v>28604</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15722</v>
+        <v>15760</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7596,10 +7596,10 @@
         <v>50.3</v>
       </c>
       <c r="F80" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="G80" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81">
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27793</v>
+        <v>27844</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7635,10 +7635,10 @@
         <v>50.6</v>
       </c>
       <c r="F81" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
       <c r="G81" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10396</v>
+        <v>10420</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10397</v>
+        <v>10423</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,19 +7743,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10181</v>
+        <v>10206</v>
       </c>
       <c r="D84" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="E84" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="F84" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="G84" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -7769,7 +7769,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10695</v>
+        <v>10720</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10181</v>
+        <v>10203</v>
       </c>
       <c r="D86" t="n">
         <v>51.2</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87">
@@ -7860,13 +7860,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10648</v>
+        <v>10674</v>
       </c>
       <c r="D87" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E87" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F87" t="n">
         <v>57.3</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10756</v>
+        <v>10782</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10892</v>
+        <v>10918</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10893</v>
+        <v>10919</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10819</v>
+        <v>10845</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10242</v>
+        <v>10266</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10172</v>
+        <v>10196</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37827</v>
+        <v>37883</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38433</v>
+        <v>38489</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36043</v>
+        <v>36093</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38549</v>
+        <v>38605</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8276,7 +8276,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98">
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37756</v>
+        <v>37812</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38341</v>
+        <v>38396</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37943</v>
+        <v>37999</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8402,17 +8402,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38626</v>
+        <v>38260</v>
       </c>
       <c r="D101" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="E101" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="F101" t="n">
         <v>54.5</v>
@@ -8441,23 +8441,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38204</v>
+        <v>38682</v>
       </c>
       <c r="D102" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="F102" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="G102" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38696</v>
+        <v>38703</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1416</v>
+        <v>1558</v>
       </c>
       <c r="D2" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="E2" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="F2" t="n">
-        <v>36.9</v>
+        <v>37.4</v>
       </c>
       <c r="G2" t="n">
-        <v>13.1</v>
+        <v>12.6</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -8629,17 +8629,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>USDCAD</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1413</v>
+        <v>1577</v>
       </c>
       <c r="D3" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="E3" t="n">
-        <v>48.5</v>
+        <v>49.4</v>
       </c>
       <c r="F3" t="n">
         <v>40.1</v>
@@ -8668,23 +8668,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>USDCAD</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1434</v>
+        <v>1553</v>
       </c>
       <c r="D4" t="n">
-        <v>50.8</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>49.2</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>40.2</v>
+        <v>40.8</v>
       </c>
       <c r="G4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1407</v>
+        <v>1462</v>
       </c>
       <c r="D5" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
       <c r="E5" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="F5" t="n">
-        <v>42.2</v>
+        <v>42.5</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1407</v>
+        <v>1462</v>
       </c>
       <c r="D6" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="E6" t="n">
-        <v>47.9</v>
+        <v>47.7</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>44.3</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1382</v>
+        <v>1438</v>
       </c>
       <c r="D7" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="E7" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="F7" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -8828,19 +8828,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1423</v>
+        <v>1478</v>
       </c>
       <c r="D8" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E8" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F8" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8854,7 +8854,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9">
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1435</v>
+        <v>1490</v>
       </c>
       <c r="D9" t="n">
         <v>49.3</v>
@@ -8876,10 +8876,10 @@
         <v>50.7</v>
       </c>
       <c r="F9" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,13 +8906,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1434</v>
+        <v>1490</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F10" t="n">
         <v>48.5</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1435</v>
+        <v>1490</v>
       </c>
       <c r="D11" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E11" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F11" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1438</v>
+        <v>1494</v>
       </c>
       <c r="D12" t="n">
-        <v>47.4</v>
+        <v>47.3</v>
       </c>
       <c r="E12" t="n">
-        <v>52.6</v>
+        <v>52.7</v>
       </c>
       <c r="F12" t="n">
-        <v>53.2</v>
+        <v>52.7</v>
       </c>
       <c r="G12" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,7 +9023,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1411</v>
+        <v>1467</v>
       </c>
       <c r="D13" t="n">
         <v>48.5</v>
@@ -9032,10 +9032,10 @@
         <v>51.5</v>
       </c>
       <c r="F13" t="n">
-        <v>53.6</v>
+        <v>53.4</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1438</v>
+        <v>1494</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="E14" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="F14" t="n">
-        <v>55.3</v>
+        <v>55</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1416</v>
+        <v>1558</v>
       </c>
       <c r="D15" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="E15" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="F15" t="n">
-        <v>63.3</v>
+        <v>62.8</v>
       </c>
       <c r="G15" t="n">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1413</v>
+        <v>1555</v>
       </c>
       <c r="D16" t="n">
-        <v>46.7</v>
+        <v>46.8</v>
       </c>
       <c r="E16" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="F16" t="n">
-        <v>63.8</v>
+        <v>63.5</v>
       </c>
       <c r="G16" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1343</v>
+        <v>1396</v>
       </c>
       <c r="D17" t="n">
-        <v>51.7</v>
+        <v>51.4</v>
       </c>
       <c r="E17" t="n">
-        <v>48.3</v>
+        <v>48.6</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1444</v>
+        <v>1500</v>
       </c>
       <c r="D18" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="E18" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="F18" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="G18" t="n">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,13 +9257,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="D19" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="E19" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="F19" t="n">
         <v>35.4</v>
@@ -9292,23 +9292,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1409</v>
+        <v>1501</v>
       </c>
       <c r="D20" t="n">
-        <v>50.2</v>
+        <v>52.2</v>
       </c>
       <c r="E20" t="n">
-        <v>49.8</v>
+        <v>47.8</v>
       </c>
       <c r="F20" t="n">
-        <v>36.6</v>
+        <v>36.2</v>
       </c>
       <c r="G20" t="n">
-        <v>13.4</v>
+        <v>13.8</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
@@ -9331,23 +9331,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1445</v>
+        <v>1463</v>
       </c>
       <c r="D21" t="n">
-        <v>52.5</v>
+        <v>50.1</v>
       </c>
       <c r="E21" t="n">
-        <v>47.5</v>
+        <v>49.9</v>
       </c>
       <c r="F21" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="G21" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9358,7 +9358,7 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
@@ -9374,19 +9374,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1443</v>
+        <v>1499</v>
       </c>
       <c r="D22" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="E22" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="F22" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="G22" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9400,7 +9400,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -9409,23 +9409,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1287</v>
+        <v>1480</v>
       </c>
       <c r="D23" t="n">
-        <v>52.3</v>
+        <v>48.8</v>
       </c>
       <c r="E23" t="n">
-        <v>47.7</v>
+        <v>51.2</v>
       </c>
       <c r="F23" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
       </c>
       <c r="G23" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9452,13 +9452,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1438</v>
+        <v>1494</v>
       </c>
       <c r="D24" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E24" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F24" t="n">
         <v>37.6</v>
@@ -9487,23 +9487,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1424</v>
+        <v>1501</v>
       </c>
       <c r="D25" t="n">
-        <v>48.9</v>
+        <v>51.2</v>
       </c>
       <c r="E25" t="n">
-        <v>51.1</v>
+        <v>48.8</v>
       </c>
       <c r="F25" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="G25" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>10</v>
@@ -9526,23 +9526,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1433</v>
+        <v>1343</v>
       </c>
       <c r="D26" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="E26" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="F26" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="G26" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9565,23 +9565,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1445</v>
+        <v>1489</v>
       </c>
       <c r="D27" t="n">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="G27" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9592,7 +9592,7 @@
         </is>
       </c>
       <c r="J27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>12</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1439</v>
+        <v>1495</v>
       </c>
       <c r="D28" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="E28" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="F28" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="G28" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1430</v>
+        <v>1486</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="E29" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="F29" t="n">
-        <v>39.4</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>10.6</v>
+        <v>10</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1428</v>
+        <v>1483</v>
       </c>
       <c r="D30" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="E30" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="F30" t="n">
         <v>40.1</v>
@@ -9725,7 +9725,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1434</v>
+        <v>1490</v>
       </c>
       <c r="D31" t="n">
         <v>50.8</v>
@@ -9734,10 +9734,10 @@
         <v>49.2</v>
       </c>
       <c r="F31" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -9764,19 +9764,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1439</v>
+        <v>1495</v>
       </c>
       <c r="D32" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="E32" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="F32" t="n">
-        <v>43.1</v>
+        <v>43.3</v>
       </c>
       <c r="G32" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1430</v>
+        <v>1485</v>
       </c>
       <c r="D33" t="n">
-        <v>48.8</v>
+        <v>48.4</v>
       </c>
       <c r="E33" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="F33" t="n">
         <v>43.4</v>
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1291</v>
+        <v>1347</v>
       </c>
       <c r="D34" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E34" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F34" t="n">
-        <v>43.5</v>
+        <v>43.6</v>
       </c>
       <c r="G34" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1420</v>
+        <v>1474</v>
       </c>
       <c r="D35" t="n">
-        <v>52.2</v>
+        <v>52.6</v>
       </c>
       <c r="E35" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="F35" t="n">
-        <v>44.2</v>
+        <v>44.4</v>
       </c>
       <c r="G35" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1429</v>
+        <v>1485</v>
       </c>
       <c r="D36" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="E36" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="F36" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="G36" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,13 +9959,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1420</v>
+        <v>1475</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F37" t="n">
         <v>47</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38">
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1289</v>
+        <v>1345</v>
       </c>
       <c r="D38" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="E38" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F38" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="G38" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1389</v>
+        <v>1442</v>
       </c>
       <c r="D39" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="E39" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="F39" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10076,19 +10076,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1440</v>
+        <v>1496</v>
       </c>
       <c r="D40" t="n">
-        <v>46.7</v>
+        <v>46.3</v>
       </c>
       <c r="E40" t="n">
-        <v>53.3</v>
+        <v>53.7</v>
       </c>
       <c r="F40" t="n">
-        <v>51.4</v>
+        <v>51.8</v>
       </c>
       <c r="G40" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10115,19 +10115,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1399</v>
+        <v>1453</v>
       </c>
       <c r="D41" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="E41" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="D42" t="n">
-        <v>50</v>
+        <v>48.9</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>51.1</v>
       </c>
       <c r="F42" t="n">
-        <v>53</v>
+        <v>52.4</v>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10193,19 +10193,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1408</v>
+        <v>1463</v>
       </c>
       <c r="D43" t="n">
-        <v>47.1</v>
+        <v>47.6</v>
       </c>
       <c r="E43" t="n">
-        <v>52.9</v>
+        <v>52.4</v>
       </c>
       <c r="F43" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="G43" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10232,19 +10232,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1430</v>
+        <v>1485</v>
       </c>
       <c r="D44" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E44" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F44" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="G44" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1425</v>
+        <v>1480</v>
       </c>
       <c r="D45" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E45" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F45" t="n">
-        <v>56</v>
+        <v>55.7</v>
       </c>
       <c r="G45" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1403</v>
+        <v>1454</v>
       </c>
       <c r="D46" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E46" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F46" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G46" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10349,19 +10349,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1433</v>
+        <v>1488</v>
       </c>
       <c r="D47" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E47" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F47" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
       <c r="G47" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10388,19 +10388,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1429</v>
+        <v>1485</v>
       </c>
       <c r="D48" t="n">
-        <v>46.3</v>
+        <v>46.2</v>
       </c>
       <c r="E48" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="F48" t="n">
-        <v>58.1</v>
+        <v>57.4</v>
       </c>
       <c r="G48" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49">
@@ -10423,23 +10423,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1310</v>
+        <v>1470</v>
       </c>
       <c r="D49" t="n">
-        <v>47.6</v>
+        <v>49.5</v>
       </c>
       <c r="E49" t="n">
-        <v>52.4</v>
+        <v>50.5</v>
       </c>
       <c r="F49" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G49" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50">
@@ -10462,23 +10462,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1415</v>
+        <v>1354</v>
       </c>
       <c r="D50" t="n">
-        <v>49.5</v>
+        <v>47.7</v>
       </c>
       <c r="E50" t="n">
-        <v>50.5</v>
+        <v>52.3</v>
       </c>
       <c r="F50" t="n">
-        <v>59.5</v>
+        <v>59.6</v>
       </c>
       <c r="G50" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1418</v>
+        <v>1472</v>
       </c>
       <c r="D51" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E51" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1410</v>
+        <v>1464</v>
       </c>
       <c r="D52" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="E52" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F52" t="n">
-        <v>62.1</v>
+        <v>61.6</v>
       </c>
       <c r="G52" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53">
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1421</v>
+        <v>1477</v>
       </c>
       <c r="D53" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E53" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F53" t="n">
-        <v>66.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>16.1</v>
+        <v>15.6</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1420</v>
+        <v>1476</v>
       </c>
       <c r="D54" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="E54" t="n">
-        <v>52</v>
+        <v>51.9</v>
       </c>
       <c r="F54" t="n">
-        <v>66.59999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>16.6</v>
+        <v>15.9</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1434</v>
+        <v>1490</v>
       </c>
       <c r="D55" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="E55" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="F55" t="n">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="G55" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,19 +10700,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1426</v>
+        <v>1481</v>
       </c>
       <c r="D56" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="E56" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F56" t="n">
-        <v>75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="G56" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1439</v>
+        <v>1494</v>
       </c>
       <c r="D57" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="E57" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="F57" t="n">
-        <v>82.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="D58" t="n">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="E58" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="F58" t="n">
         <v>83.2</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1442</v>
+        <v>1498</v>
       </c>
       <c r="D59" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E59" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="F59" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="G59" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10852,23 +10852,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1450</v>
+        <v>1376</v>
       </c>
       <c r="D60" t="n">
-        <v>50.6</v>
+        <v>51.5</v>
       </c>
       <c r="E60" t="n">
-        <v>49.4</v>
+        <v>48.5</v>
       </c>
       <c r="F60" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="G60" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10891,23 +10891,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1321</v>
+        <v>1544</v>
       </c>
       <c r="D61" t="n">
-        <v>51.6</v>
+        <v>50.3</v>
       </c>
       <c r="E61" t="n">
-        <v>48.4</v>
+        <v>49.7</v>
       </c>
       <c r="F61" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="G61" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>878</v>
+        <v>929</v>
       </c>
       <c r="D62" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="E62" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="F62" t="n">
-        <v>58</v>
+        <v>58.6</v>
       </c>
       <c r="G62" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>869</v>
+        <v>921</v>
       </c>
       <c r="D63" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="E63" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="F63" t="n">
-        <v>58.9</v>
+        <v>59.5</v>
       </c>
       <c r="G63" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64">
@@ -11012,19 +11012,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1284</v>
+        <v>1339</v>
       </c>
       <c r="D64" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="E64" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="F64" t="n">
-        <v>60</v>
+        <v>60.2</v>
       </c>
       <c r="G64" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>870</v>
+        <v>943</v>
       </c>
       <c r="D65" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="E65" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="F65" t="n">
-        <v>60.5</v>
+        <v>60.8</v>
       </c>
       <c r="G65" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66">
@@ -11086,23 +11086,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>891</v>
+        <v>921</v>
       </c>
       <c r="D66" t="n">
-        <v>52</v>
+        <v>51.4</v>
       </c>
       <c r="E66" t="n">
-        <v>48</v>
+        <v>48.6</v>
       </c>
       <c r="F66" t="n">
-        <v>60.5</v>
+        <v>61</v>
       </c>
       <c r="G66" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
@@ -11129,19 +11129,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1025</v>
+        <v>1070</v>
       </c>
       <c r="D67" t="n">
-        <v>48.6</v>
+        <v>49.1</v>
       </c>
       <c r="E67" t="n">
-        <v>51.4</v>
+        <v>50.9</v>
       </c>
       <c r="F67" t="n">
-        <v>62.5</v>
+        <v>63</v>
       </c>
       <c r="G67" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
@@ -11168,19 +11168,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1406</v>
+        <v>1460</v>
       </c>
       <c r="D68" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E68" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="F68" t="n">
-        <v>63</v>
+        <v>63.2</v>
       </c>
       <c r="G68" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11207,19 +11207,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1436</v>
+        <v>1492</v>
       </c>
       <c r="D69" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E69" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F69" t="n">
-        <v>63</v>
+        <v>63.3</v>
       </c>
       <c r="G69" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11246,7 +11246,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1229</v>
+        <v>1281</v>
       </c>
       <c r="D70" t="n">
         <v>47.8</v>
@@ -11255,10 +11255,10 @@
         <v>52.2</v>
       </c>
       <c r="F70" t="n">
-        <v>63.5</v>
+        <v>63.7</v>
       </c>
       <c r="G70" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11285,19 +11285,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1419</v>
+        <v>1475</v>
       </c>
       <c r="D71" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="E71" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="F71" t="n">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="G71" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11324,19 +11324,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1451</v>
+        <v>1544</v>
       </c>
       <c r="D72" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E72" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F72" t="n">
-        <v>64.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1235</v>
+        <v>1282</v>
       </c>
       <c r="D73" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="E73" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>66.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="G73" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>530</v>
+        <v>566</v>
       </c>
       <c r="D74" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="F74" t="n">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
       <c r="G74" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="D75" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="E75" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="F75" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="G75" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76">
@@ -11480,19 +11480,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>522</v>
+        <v>557</v>
       </c>
       <c r="D76" t="n">
-        <v>52.7</v>
+        <v>52.2</v>
       </c>
       <c r="E76" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="F76" t="n">
-        <v>55.2</v>
+        <v>54.9</v>
       </c>
       <c r="G76" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11519,7 +11519,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1042</v>
+        <v>1085</v>
       </c>
       <c r="D77" t="n">
         <v>51.2</v>
@@ -11528,10 +11528,10 @@
         <v>48.8</v>
       </c>
       <c r="F77" t="n">
-        <v>55.5</v>
+        <v>55.2</v>
       </c>
       <c r="G77" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1344</v>
+        <v>1399</v>
       </c>
       <c r="D78" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E78" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F78" t="n">
-        <v>70.59999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="G78" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="D79" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E79" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="F79" t="n">
-        <v>59.3</v>
+        <v>60.1</v>
       </c>
       <c r="G79" t="n">
-        <v>9.300000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1091</v>
+        <v>1142</v>
       </c>
       <c r="D80" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="E80" t="n">
-        <v>53.9</v>
+        <v>53.8</v>
       </c>
       <c r="F80" t="n">
-        <v>60</v>
+        <v>60.6</v>
       </c>
       <c r="G80" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81">
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1054</v>
+        <v>1105</v>
       </c>
       <c r="D81" t="n">
-        <v>46.6</v>
+        <v>46.9</v>
       </c>
       <c r="E81" t="n">
-        <v>53.4</v>
+        <v>53.1</v>
       </c>
       <c r="F81" t="n">
-        <v>63</v>
+        <v>63.4</v>
       </c>
       <c r="G81" t="n">
-        <v>13</v>
+        <v>13.4</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="D82" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E82" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11753,19 +11753,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="D83" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="E83" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
       <c r="F83" t="n">
-        <v>49.6</v>
+        <v>49</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84">
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="D84" t="n">
-        <v>47</v>
+        <v>46.2</v>
       </c>
       <c r="E84" t="n">
-        <v>53</v>
+        <v>53.8</v>
       </c>
       <c r="F84" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="G84" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11831,7 +11831,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>383</v>
+        <v>408</v>
       </c>
       <c r="D85" t="n">
         <v>47.3</v>
@@ -11840,10 +11840,10 @@
         <v>52.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.6</v>
+        <v>54.2</v>
       </c>
       <c r="G85" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="86">
@@ -11866,23 +11866,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="D86" t="n">
-        <v>45.4</v>
+        <v>50.9</v>
       </c>
       <c r="E86" t="n">
-        <v>54.6</v>
+        <v>49.1</v>
       </c>
       <c r="F86" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="G86" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11905,23 +11905,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>367</v>
+        <v>398</v>
       </c>
       <c r="D87" t="n">
-        <v>51.5</v>
+        <v>44.5</v>
       </c>
       <c r="E87" t="n">
-        <v>48.5</v>
+        <v>55.5</v>
       </c>
       <c r="F87" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="D88" t="n">
-        <v>48.8</v>
+        <v>49.4</v>
       </c>
       <c r="E88" t="n">
-        <v>51.2</v>
+        <v>50.6</v>
       </c>
       <c r="F88" t="n">
-        <v>60.5</v>
+        <v>60.6</v>
       </c>
       <c r="G88" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89">
@@ -11987,19 +11987,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D89" t="n">
-        <v>49.9</v>
+        <v>49.1</v>
       </c>
       <c r="E89" t="n">
-        <v>50.1</v>
+        <v>50.9</v>
       </c>
       <c r="F89" t="n">
-        <v>61.9</v>
+        <v>62.4</v>
       </c>
       <c r="G89" t="n">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
@@ -12026,19 +12026,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="E90" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="F90" t="n">
-        <v>62.2</v>
+        <v>62.9</v>
       </c>
       <c r="G90" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
@@ -12065,19 +12065,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="D91" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="E91" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="F91" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="G91" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92">
@@ -12104,19 +12104,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="D92" t="n">
-        <v>51.8</v>
+        <v>51</v>
       </c>
       <c r="E92" t="n">
-        <v>48.2</v>
+        <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>63.3</v>
+        <v>63.7</v>
       </c>
       <c r="G92" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="D93" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="E93" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="F93" t="n">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="G93" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12182,13 +12182,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1444</v>
+        <v>1500</v>
       </c>
       <c r="D94" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E94" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F94" t="n">
         <v>58.2</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95">
@@ -12221,19 +12221,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1401</v>
+        <v>1457</v>
       </c>
       <c r="D95" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E95" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F95" t="n">
-        <v>58.7</v>
+        <v>59</v>
       </c>
       <c r="G95" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12260,13 +12260,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1283</v>
+        <v>1333</v>
       </c>
       <c r="D96" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E96" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F96" t="n">
         <v>59.3</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97">
@@ -12299,7 +12299,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1494</v>
+        <v>1501</v>
       </c>
       <c r="D97" t="n">
         <v>48.5</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="98">
@@ -12338,19 +12338,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1427</v>
+        <v>1482</v>
       </c>
       <c r="D98" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="E98" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="F98" t="n">
-        <v>60.3</v>
+        <v>60.2</v>
       </c>
       <c r="G98" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99">
@@ -12377,13 +12377,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1445</v>
+        <v>1501</v>
       </c>
       <c r="D99" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="E99" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="F99" t="n">
         <v>60.5</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="100">
@@ -12412,23 +12412,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1444</v>
+        <v>1494</v>
       </c>
       <c r="D100" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E100" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F100" t="n">
-        <v>60.6</v>
+        <v>60.8</v>
       </c>
       <c r="G100" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="101">
@@ -12451,11 +12451,11 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1438</v>
+        <v>1500</v>
       </c>
       <c r="D101" t="n">
         <v>49</v>
@@ -12464,10 +12464,10 @@
         <v>51</v>
       </c>
       <c r="F101" t="n">
-        <v>60.7</v>
+        <v>60.8</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1389</v>
+        <v>1445</v>
       </c>
       <c r="D102" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E102" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F102" t="n">
-        <v>61.3</v>
+        <v>61.5</v>
       </c>
       <c r="G102" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1428</v>
+        <v>1484</v>
       </c>
       <c r="D103" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E103" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F103" t="n">
         <v>61.9</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38078</v>
+        <v>38220</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38131</v>
+        <v>38271</v>
       </c>
       <c r="D3" t="n">
         <v>50.2</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38330</v>
+        <v>38473</v>
       </c>
       <c r="D4" t="n">
         <v>51.2</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37806</v>
+        <v>37861</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38272</v>
+        <v>38327</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37792</v>
+        <v>37847</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37625</v>
+        <v>37681</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38074</v>
+        <v>38129</v>
       </c>
       <c r="D9" t="n">
         <v>50</v>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38358</v>
+        <v>38414</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38409</v>
+        <v>38465</v>
       </c>
       <c r="D11" t="n">
         <v>50.7</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38422</v>
+        <v>38477</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38245</v>
+        <v>38301</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38305</v>
+        <v>38361</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38208</v>
+        <v>38350</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38225</v>
+        <v>38367</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36497</v>
+        <v>36550</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38476</v>
+        <v>38532</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13276,10 +13276,10 @@
         <v>50.9</v>
       </c>
       <c r="F18" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="G18" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38017</v>
+        <v>38071</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34764</v>
+        <v>34820</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38547</v>
+        <v>38603</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38363</v>
+        <v>38419</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38413</v>
+        <v>38469</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13471,10 +13471,10 @@
         <v>50.4</v>
       </c>
       <c r="F23" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="G23" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38594</v>
+        <v>38650</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38548</v>
+        <v>38604</v>
       </c>
       <c r="D25" t="n">
         <v>49.9</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38605</v>
+        <v>38661</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34932</v>
+        <v>34988</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38630</v>
+        <v>38686</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13666,10 +13666,10 @@
         <v>50.9</v>
       </c>
       <c r="F28" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38638</v>
+        <v>38694</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38355</v>
+        <v>38410</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38391</v>
+        <v>38447</v>
       </c>
       <c r="D31" t="n">
         <v>49.2</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38387</v>
+        <v>38443</v>
       </c>
       <c r="D32" t="n">
         <v>49.4</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38414</v>
+        <v>38470</v>
       </c>
       <c r="D33" t="n">
         <v>49.6</v>
@@ -13861,10 +13861,10 @@
         <v>50.4</v>
       </c>
       <c r="F33" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="G33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38351</v>
+        <v>38406</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38352</v>
+        <v>38408</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,13 +13969,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34818</v>
+        <v>34874</v>
       </c>
       <c r="D36" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="E36" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="F36" t="n">
         <v>47.6</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38190</v>
+        <v>38245</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37533</v>
+        <v>37586</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38347</v>
+        <v>38403</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14095,10 +14095,10 @@
         <v>52.8</v>
       </c>
       <c r="F39" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -14112,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
@@ -14125,19 +14125,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8085</v>
+        <v>8103</v>
       </c>
       <c r="D40" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E40" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F40" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38028</v>
+        <v>38082</v>
       </c>
       <c r="D41" t="n">
         <v>50</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38088</v>
+        <v>38143</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38123</v>
+        <v>38179</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38049</v>
+        <v>38104</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37705</v>
+        <v>37756</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37855</v>
+        <v>37909</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38229</v>
+        <v>38284</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38272</v>
+        <v>38327</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35666</v>
+        <v>35710</v>
       </c>
       <c r="D49" t="n">
         <v>50.3</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38110</v>
+        <v>38165</v>
       </c>
       <c r="D50" t="n">
         <v>49.4</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>37974</v>
+        <v>38028</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38154</v>
+        <v>38208</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38024</v>
+        <v>38080</v>
       </c>
       <c r="D53" t="n">
         <v>49.6</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38063</v>
+        <v>38119</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38242</v>
+        <v>38298</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>37947</v>
+        <v>38002</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38308</v>
+        <v>38363</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38388</v>
+        <v>38444</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38590</v>
+        <v>38646</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35019</v>
+        <v>35074</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14914,10 +14914,10 @@
         <v>49.2</v>
       </c>
       <c r="F60" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -14931,7 +14931,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61">
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>36946</v>
+        <v>37040</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14953,10 +14953,10 @@
         <v>49.6</v>
       </c>
       <c r="F61" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -14970,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="62">
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37404</v>
+        <v>37458</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23333</v>
+        <v>23384</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23756</v>
+        <v>23807</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15096,17 +15096,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23780</v>
+        <v>38349</v>
       </c>
       <c r="D65" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E65" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F65" t="n">
         <v>55.9</v>
@@ -15135,23 +15135,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38293</v>
+        <v>23832</v>
       </c>
       <c r="D66" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E66" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="G66" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -15174,23 +15174,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>37798</v>
+        <v>21210</v>
       </c>
       <c r="D67" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="E67" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="F67" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G67" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68">
@@ -15213,17 +15213,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21158</v>
+        <v>37854</v>
       </c>
       <c r="D68" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="E68" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="F68" t="n">
         <v>56.1</v>
@@ -15256,13 +15256,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36066</v>
+        <v>36121</v>
       </c>
       <c r="D69" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E69" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F69" t="n">
         <v>56.6</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30473</v>
+        <v>30525</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37462</v>
+        <v>37555</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32942</v>
+        <v>32989</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25973</v>
+        <v>26018</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15451,13 +15451,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14168</v>
+        <v>14202</v>
       </c>
       <c r="D74" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E74" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F74" t="n">
         <v>51</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14045</v>
+        <v>14080</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15100</v>
+        <v>15136</v>
       </c>
       <c r="D76" t="n">
         <v>50.6</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26571</v>
+        <v>26614</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35788</v>
+        <v>35843</v>
       </c>
       <c r="D78" t="n">
         <v>50.5</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28553</v>
+        <v>28604</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15722</v>
+        <v>15760</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15694,10 +15694,10 @@
         <v>50.3</v>
       </c>
       <c r="F80" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="G80" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27793</v>
+        <v>27844</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15733,10 +15733,10 @@
         <v>50.6</v>
       </c>
       <c r="F81" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
       <c r="G81" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10396</v>
+        <v>10420</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10397</v>
+        <v>10423</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,19 +15841,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10181</v>
+        <v>10206</v>
       </c>
       <c r="D84" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="E84" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="F84" t="n">
-        <v>54</v>
+        <v>53.9</v>
       </c>
       <c r="G84" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -15867,7 +15867,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10695</v>
+        <v>10720</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10181</v>
+        <v>10203</v>
       </c>
       <c r="D86" t="n">
         <v>51.2</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87">
@@ -15958,13 +15958,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10648</v>
+        <v>10674</v>
       </c>
       <c r="D87" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E87" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F87" t="n">
         <v>57.3</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10756</v>
+        <v>10782</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10892</v>
+        <v>10918</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10893</v>
+        <v>10919</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10819</v>
+        <v>10845</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10242</v>
+        <v>10266</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10172</v>
+        <v>10196</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37827</v>
+        <v>37883</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38433</v>
+        <v>38489</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36043</v>
+        <v>36093</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38549</v>
+        <v>38605</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16374,7 +16374,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98">
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37756</v>
+        <v>37812</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38341</v>
+        <v>38396</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37943</v>
+        <v>37999</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16500,17 +16500,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38626</v>
+        <v>38260</v>
       </c>
       <c r="D101" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="E101" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="F101" t="n">
         <v>54.5</v>
@@ -16539,23 +16539,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38204</v>
+        <v>38682</v>
       </c>
       <c r="D102" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="F102" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="G102" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38696</v>
+        <v>38703</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1490</v>
+        <v>1581</v>
       </c>
       <c r="D2" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="E2" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="F2" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1490</v>
+        <v>1582</v>
       </c>
       <c r="D3" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="E3" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="F3" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1490</v>
+        <v>1580</v>
       </c>
       <c r="D4" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E4" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F4" t="n">
-        <v>47.7</v>
+        <v>47.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHFJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1494</v>
+        <v>1568</v>
       </c>
       <c r="D5" t="n">
-        <v>47.3</v>
+        <v>50.4</v>
       </c>
       <c r="E5" t="n">
-        <v>52.7</v>
+        <v>49.6</v>
       </c>
       <c r="F5" t="n">
-        <v>52.7</v>
+        <v>47.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1478</v>
+        <v>1586</v>
       </c>
       <c r="D6" t="n">
-        <v>50.3</v>
+        <v>47.2</v>
       </c>
       <c r="E6" t="n">
-        <v>49.7</v>
+        <v>52.8</v>
       </c>
       <c r="F6" t="n">
-        <v>47.3</v>
+        <v>53</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1438</v>
+        <v>1524</v>
       </c>
       <c r="D7" t="n">
         <v>50.2</v>
@@ -700,10 +700,10 @@
         <v>49.8</v>
       </c>
       <c r="F7" t="n">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1467</v>
+        <v>1559</v>
       </c>
       <c r="D8" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E8" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="F8" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1494</v>
+        <v>1586</v>
       </c>
       <c r="D9" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="E9" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>55.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -808,13 +808,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1462</v>
+        <v>1551</v>
       </c>
       <c r="D10" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="E10" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="F10" t="n">
         <v>44.3</v>
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1462</v>
+        <v>1553</v>
       </c>
       <c r="D11" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="E11" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="F11" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1553</v>
+        <v>1640</v>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="F12" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="G12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1577</v>
+        <v>1665</v>
       </c>
       <c r="D13" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E13" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="F13" t="n">
-        <v>40.1</v>
+        <v>40.5</v>
       </c>
       <c r="G13" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1558</v>
+        <v>1645</v>
       </c>
       <c r="D14" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="E14" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="F14" t="n">
         <v>37.4</v>
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1558</v>
+        <v>1645</v>
       </c>
       <c r="D15" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E15" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="F15" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1555</v>
+        <v>1643</v>
       </c>
       <c r="D16" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="E16" t="n">
-        <v>53.2</v>
+        <v>52.6</v>
       </c>
       <c r="F16" t="n">
-        <v>63.5</v>
+        <v>63.1</v>
       </c>
       <c r="G16" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1345</v>
+        <v>1424</v>
       </c>
       <c r="D17" t="n">
         <v>49.6</v>
@@ -1090,10 +1090,10 @@
         <v>50.4</v>
       </c>
       <c r="F17" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -1116,23 +1116,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1442</v>
+        <v>1588</v>
       </c>
       <c r="D18" t="n">
-        <v>49.7</v>
+        <v>46.2</v>
       </c>
       <c r="E18" t="n">
-        <v>50.3</v>
+        <v>53.8</v>
       </c>
       <c r="F18" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1496</v>
+        <v>1531</v>
       </c>
       <c r="D19" t="n">
-        <v>46.3</v>
+        <v>49.7</v>
       </c>
       <c r="E19" t="n">
-        <v>53.7</v>
+        <v>50.3</v>
       </c>
       <c r="F19" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1453</v>
+        <v>1540</v>
       </c>
       <c r="D20" t="n">
         <v>51</v>
@@ -1207,10 +1207,10 @@
         <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1233,23 +1233,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>380</v>
+        <v>1567</v>
       </c>
       <c r="D21" t="n">
-        <v>48.9</v>
+        <v>49.8</v>
       </c>
       <c r="E21" t="n">
-        <v>51.1</v>
+        <v>50.2</v>
       </c>
       <c r="F21" t="n">
-        <v>52.4</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1475</v>
+        <v>410</v>
       </c>
       <c r="D22" t="n">
-        <v>50.1</v>
+        <v>49</v>
       </c>
       <c r="E22" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>53.2</v>
       </c>
       <c r="G22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1311,17 +1311,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1463</v>
+        <v>1576</v>
       </c>
       <c r="D23" t="n">
-        <v>47.6</v>
+        <v>51.4</v>
       </c>
       <c r="E23" t="n">
-        <v>52.4</v>
+        <v>48.6</v>
       </c>
       <c r="F23" t="n">
         <v>53.9</v>
@@ -1350,23 +1350,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1485</v>
+        <v>1554</v>
       </c>
       <c r="D24" t="n">
-        <v>51.4</v>
+        <v>47.4</v>
       </c>
       <c r="E24" t="n">
-        <v>48.6</v>
+        <v>52.6</v>
       </c>
       <c r="F24" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="G24" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1485</v>
+        <v>1566</v>
       </c>
       <c r="D25" t="n">
-        <v>52.1</v>
+        <v>52.8</v>
       </c>
       <c r="E25" t="n">
-        <v>47.9</v>
+        <v>47.2</v>
       </c>
       <c r="F25" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="G25" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1474</v>
+        <v>1578</v>
       </c>
       <c r="D26" t="n">
-        <v>52.6</v>
+        <v>51.8</v>
       </c>
       <c r="E26" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="F26" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="G26" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1480</v>
+        <v>1573</v>
       </c>
       <c r="D27" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E27" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F27" t="n">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="G27" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1454</v>
+        <v>1545</v>
       </c>
       <c r="D28" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="E28" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="F28" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1545,17 +1545,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1347</v>
+        <v>1587</v>
       </c>
       <c r="D29" t="n">
-        <v>49.8</v>
+        <v>48.2</v>
       </c>
       <c r="E29" t="n">
-        <v>50.2</v>
+        <v>51.8</v>
       </c>
       <c r="F29" t="n">
         <v>43.6</v>
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30">
@@ -1588,13 +1588,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1485</v>
+        <v>1577</v>
       </c>
       <c r="D30" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="E30" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="F30" t="n">
         <v>43.4</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31">
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1495</v>
+        <v>1427</v>
       </c>
       <c r="D31" t="n">
-        <v>48.3</v>
+        <v>49.8</v>
       </c>
       <c r="E31" t="n">
-        <v>51.7</v>
+        <v>50.2</v>
       </c>
       <c r="F31" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="G31" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1650,10 +1650,10 @@
         </is>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1488</v>
+        <v>1576</v>
       </c>
       <c r="D32" t="n">
-        <v>49.3</v>
+        <v>46.4</v>
       </c>
       <c r="E32" t="n">
-        <v>50.7</v>
+        <v>53.6</v>
       </c>
       <c r="F32" t="n">
         <v>57.2</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -1701,23 +1701,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1485</v>
+        <v>1580</v>
       </c>
       <c r="D33" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="E33" t="n">
-        <v>53.8</v>
+        <v>50.8</v>
       </c>
       <c r="F33" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
       <c r="G33" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1490</v>
+        <v>1582</v>
       </c>
       <c r="D34" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="E34" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="F34" t="n">
         <v>42.4</v>
@@ -1779,23 +1779,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>EURAUD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1470</v>
+        <v>1575</v>
       </c>
       <c r="D35" t="n">
-        <v>49.5</v>
+        <v>48.8</v>
       </c>
       <c r="E35" t="n">
-        <v>50.5</v>
+        <v>51.2</v>
       </c>
       <c r="F35" t="n">
-        <v>59.3</v>
+        <v>40.6</v>
       </c>
       <c r="G35" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1354</v>
+        <v>1440</v>
       </c>
       <c r="D36" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="E36" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="F36" t="n">
-        <v>59.6</v>
+        <v>59.4</v>
       </c>
       <c r="G36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EURAUD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1483</v>
+        <v>1562</v>
       </c>
       <c r="D37" t="n">
-        <v>48.2</v>
+        <v>49.3</v>
       </c>
       <c r="E37" t="n">
-        <v>51.8</v>
+        <v>50.7</v>
       </c>
       <c r="F37" t="n">
-        <v>40.1</v>
+        <v>59.5</v>
       </c>
       <c r="G37" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -1896,20 +1896,20 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1486</v>
+        <v>1564</v>
       </c>
       <c r="D38" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="E38" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G38" t="n">
         <v>10</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="39">
@@ -1935,23 +1935,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUDCAD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1472</v>
+        <v>1579</v>
       </c>
       <c r="D39" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E39" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F39" t="n">
-        <v>60.1</v>
+        <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1495</v>
+        <v>1588</v>
       </c>
       <c r="D40" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E40" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="F40" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="G40" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41">
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1464</v>
+        <v>1556</v>
       </c>
       <c r="D41" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E41" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F41" t="n">
-        <v>61.6</v>
+        <v>61.1</v>
       </c>
       <c r="G41" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1489</v>
+        <v>1579</v>
       </c>
       <c r="D42" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="E42" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="F42" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="G42" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1501</v>
+        <v>1594</v>
       </c>
       <c r="D43" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E43" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F43" t="n">
         <v>37.8</v>
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1343</v>
+        <v>1422</v>
       </c>
       <c r="D44" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="E44" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="F44" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="G44" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1494</v>
+        <v>1586</v>
       </c>
       <c r="D45" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E45" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F45" t="n">
         <v>37.6</v>
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1480</v>
+        <v>1570</v>
       </c>
       <c r="D46" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="E46" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="F46" t="n">
         <v>37.4</v>
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1499</v>
+        <v>1592</v>
       </c>
       <c r="D47" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E47" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F47" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="48">
@@ -2290,19 +2290,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1463</v>
+        <v>1553</v>
       </c>
       <c r="D48" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="E48" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="F48" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="G48" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49">
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1501</v>
+        <v>1594</v>
       </c>
       <c r="D49" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="E49" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="F49" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="G49" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1498</v>
+        <v>1591</v>
       </c>
       <c r="D50" t="n">
         <v>50.3</v>
@@ -2377,10 +2377,10 @@
         <v>49.7</v>
       </c>
       <c r="F50" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="G50" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1477</v>
+        <v>1568</v>
       </c>
       <c r="D51" t="n">
         <v>48.7</v>
@@ -2416,10 +2416,10 @@
         <v>51.3</v>
       </c>
       <c r="F51" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1476</v>
+        <v>1568</v>
       </c>
       <c r="D52" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="E52" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="F52" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1500</v>
+        <v>1593</v>
       </c>
       <c r="D53" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="E53" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="F53" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="G53" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1396</v>
+        <v>1479</v>
       </c>
       <c r="D54" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E54" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F54" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="G54" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1490</v>
+        <v>1583</v>
       </c>
       <c r="D55" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F55" t="n">
         <v>69.7</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1481</v>
+        <v>1573</v>
       </c>
       <c r="D56" t="n">
         <v>48.4</v>
@@ -2611,10 +2611,10 @@
         <v>51.6</v>
       </c>
       <c r="F56" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="G56" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1494</v>
+        <v>1586</v>
       </c>
       <c r="D57" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="E57" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="F57" t="n">
-        <v>82.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1498</v>
+        <v>1591</v>
       </c>
       <c r="D58" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E58" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="G58" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1498</v>
+        <v>1591</v>
       </c>
       <c r="D59" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E59" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F59" t="n">
         <v>94.5</v>
@@ -2754,17 +2754,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1544</v>
+        <v>1459</v>
       </c>
       <c r="D60" t="n">
-        <v>50.3</v>
+        <v>51.3</v>
       </c>
       <c r="E60" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="F60" t="n">
         <v>41.8</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1376</v>
+        <v>1630</v>
       </c>
       <c r="D61" t="n">
-        <v>51.5</v>
+        <v>50.2</v>
       </c>
       <c r="E61" t="n">
-        <v>48.5</v>
+        <v>49.8</v>
       </c>
       <c r="F61" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="G61" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62">
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>929</v>
+        <v>985</v>
       </c>
       <c r="D62" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E62" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F62" t="n">
-        <v>58.6</v>
+        <v>59.1</v>
       </c>
       <c r="G62" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>921</v>
+        <v>972</v>
       </c>
       <c r="D63" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="E63" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="F63" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="G63" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1339</v>
+        <v>1429</v>
       </c>
       <c r="D64" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="E64" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="F64" t="n">
-        <v>60.2</v>
+        <v>60.6</v>
       </c>
       <c r="G64" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
@@ -2953,19 +2953,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>943</v>
+        <v>999</v>
       </c>
       <c r="D65" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="E65" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="F65" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="66">
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>921</v>
+        <v>973</v>
       </c>
       <c r="D66" t="n">
         <v>51.4</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67">
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1070</v>
+        <v>1553</v>
       </c>
       <c r="D67" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="E67" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="F67" t="n">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="G67" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1460</v>
+        <v>1133</v>
       </c>
       <c r="D68" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E68" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F68" t="n">
-        <v>63.2</v>
+        <v>63.4</v>
       </c>
       <c r="G68" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1492</v>
+        <v>1357</v>
       </c>
       <c r="D69" t="n">
-        <v>50.7</v>
+        <v>48</v>
       </c>
       <c r="E69" t="n">
-        <v>49.3</v>
+        <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="G69" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70">
@@ -3144,23 +3144,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1281</v>
+        <v>1585</v>
       </c>
       <c r="D70" t="n">
-        <v>47.8</v>
+        <v>50.9</v>
       </c>
       <c r="E70" t="n">
-        <v>52.2</v>
+        <v>49.1</v>
       </c>
       <c r="F70" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="G70" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71">
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1475</v>
+        <v>1567</v>
       </c>
       <c r="D71" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E71" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="F71" t="n">
-        <v>63.7</v>
+        <v>63.9</v>
       </c>
       <c r="G71" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72">
@@ -3226,13 +3226,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1544</v>
+        <v>1632</v>
       </c>
       <c r="D72" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="E72" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="F72" t="n">
         <v>64.59999999999999</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1282</v>
+        <v>1365</v>
       </c>
       <c r="D73" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="E73" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="F73" t="n">
-        <v>66.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>566</v>
+        <v>602</v>
       </c>
       <c r="D74" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="E74" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="F74" t="n">
-        <v>53.5</v>
+        <v>53.7</v>
       </c>
       <c r="G74" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75">
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>544</v>
+        <v>578</v>
       </c>
       <c r="D75" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E75" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76">
@@ -3378,23 +3378,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>557</v>
+        <v>1155</v>
       </c>
       <c r="D76" t="n">
-        <v>52.2</v>
+        <v>50.8</v>
       </c>
       <c r="E76" t="n">
-        <v>47.8</v>
+        <v>49.2</v>
       </c>
       <c r="F76" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="G76" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
@@ -3417,23 +3417,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1085</v>
+        <v>557</v>
       </c>
       <c r="D77" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="E77" t="n">
-        <v>48.8</v>
+        <v>47.8</v>
       </c>
       <c r="F77" t="n">
-        <v>55.2</v>
+        <v>54.9</v>
       </c>
       <c r="G77" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1399</v>
+        <v>1485</v>
       </c>
       <c r="D78" t="n">
         <v>48.5</v>
@@ -3469,10 +3469,10 @@
         <v>51.5</v>
       </c>
       <c r="F78" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="G78" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>546</v>
+        <v>584</v>
       </c>
       <c r="D79" t="n">
-        <v>49.1</v>
+        <v>49.7</v>
       </c>
       <c r="E79" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
       <c r="F79" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
       <c r="G79" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1142</v>
+        <v>1214</v>
       </c>
       <c r="D80" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="E80" t="n">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
       <c r="F80" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
       <c r="G80" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1105</v>
+        <v>1182</v>
       </c>
       <c r="D81" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="E81" t="n">
-        <v>53.1</v>
+        <v>52.7</v>
       </c>
       <c r="F81" t="n">
         <v>63.4</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="D82" t="n">
-        <v>46.2</v>
+        <v>46.8</v>
       </c>
       <c r="E82" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="F82" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3655,19 +3655,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="D83" t="n">
-        <v>48.2</v>
+        <v>47.6</v>
       </c>
       <c r="E83" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="F83" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="D84" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E84" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F84" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="G84" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="D85" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="E85" t="n">
-        <v>52.7</v>
+        <v>52.2</v>
       </c>
       <c r="F85" t="n">
-        <v>54.2</v>
+        <v>55</v>
       </c>
       <c r="G85" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
@@ -3772,19 +3772,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="D86" t="n">
-        <v>50.9</v>
+        <v>49.6</v>
       </c>
       <c r="E86" t="n">
-        <v>49.1</v>
+        <v>50.4</v>
       </c>
       <c r="F86" t="n">
-        <v>56.3</v>
+        <v>57.1</v>
       </c>
       <c r="G86" t="n">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="87">
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="D87" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
       <c r="E87" t="n">
-        <v>55.5</v>
+        <v>55.2</v>
       </c>
       <c r="F87" t="n">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="D88" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="E88" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F88" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="89">
@@ -3889,13 +3889,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="D89" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
       <c r="E89" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="F89" t="n">
         <v>62.4</v>
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="D90" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="E90" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="F90" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="G90" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="D91" t="n">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="E91" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="F91" t="n">
-        <v>63.5</v>
+        <v>63.6</v>
       </c>
       <c r="G91" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92">
@@ -4002,23 +4002,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="D92" t="n">
-        <v>51</v>
+        <v>49.7</v>
       </c>
       <c r="E92" t="n">
-        <v>49</v>
+        <v>50.3</v>
       </c>
       <c r="F92" t="n">
-        <v>63.7</v>
+        <v>64</v>
       </c>
       <c r="G92" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="D93" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="E93" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="F93" t="n">
-        <v>72</v>
+        <v>71.7</v>
       </c>
       <c r="G93" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1500</v>
+        <v>1593</v>
       </c>
       <c r="D94" t="n">
         <v>48.7</v>
@@ -4093,10 +4093,10 @@
         <v>51.3</v>
       </c>
       <c r="F94" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="G94" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="95">
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1457</v>
+        <v>1546</v>
       </c>
       <c r="D95" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E95" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F95" t="n">
-        <v>59</v>
+        <v>58.4</v>
       </c>
       <c r="G95" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="96">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1333</v>
+        <v>1575</v>
       </c>
       <c r="D96" t="n">
-        <v>49.1</v>
+        <v>48.2</v>
       </c>
       <c r="E96" t="n">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
       <c r="F96" t="n">
-        <v>59.3</v>
+        <v>59.7</v>
       </c>
       <c r="G96" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="97">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1501</v>
+        <v>1415</v>
       </c>
       <c r="D97" t="n">
-        <v>48.5</v>
+        <v>49.7</v>
       </c>
       <c r="E97" t="n">
-        <v>51.5</v>
+        <v>50.3</v>
       </c>
       <c r="F97" t="n">
-        <v>60.2</v>
+        <v>59.9</v>
       </c>
       <c r="G97" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1482</v>
+        <v>1594</v>
       </c>
       <c r="D98" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="E98" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="F98" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="G98" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="99">
@@ -4275,23 +4275,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1501</v>
+        <v>1587</v>
       </c>
       <c r="D99" t="n">
-        <v>48.6</v>
+        <v>49.5</v>
       </c>
       <c r="E99" t="n">
-        <v>51.4</v>
+        <v>50.5</v>
       </c>
       <c r="F99" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="G99" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="100">
@@ -4314,23 +4314,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1494</v>
+        <v>1594</v>
       </c>
       <c r="D100" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
       <c r="E100" t="n">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
       <c r="F100" t="n">
-        <v>60.8</v>
+        <v>60.2</v>
       </c>
       <c r="G100" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="101">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1500</v>
+        <v>1593</v>
       </c>
       <c r="D101" t="n">
         <v>49</v>
@@ -4366,10 +4366,10 @@
         <v>51</v>
       </c>
       <c r="F101" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="G101" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="102">
@@ -4396,19 +4396,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1445</v>
+        <v>1533</v>
       </c>
       <c r="D102" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F102" t="n">
-        <v>61.5</v>
+        <v>61.2</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1484</v>
+        <v>1574</v>
       </c>
       <c r="D103" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="E103" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="F103" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="G103" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38129</v>
+        <v>38219</v>
       </c>
       <c r="D2" t="n">
         <v>50</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37681</v>
+        <v>37767</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37847</v>
+        <v>37938</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38414</v>
+        <v>38506</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38465</v>
+        <v>38557</v>
       </c>
       <c r="D6" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="E6" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="F6" t="n">
         <v>51.8</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38327</v>
+        <v>38417</v>
       </c>
       <c r="D7" t="n">
         <v>50.7</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38477</v>
+        <v>38568</v>
       </c>
       <c r="D8" t="n">
         <v>51.4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37861</v>
+        <v>37950</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38301</v>
+        <v>38393</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38361</v>
+        <v>38453</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38473</v>
+        <v>38561</v>
       </c>
       <c r="D12" t="n">
         <v>51.2</v>
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38271</v>
+        <v>38358</v>
       </c>
       <c r="D13" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E13" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F13" t="n">
         <v>40.7</v>
@@ -5000,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38220</v>
+        <v>38307</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38350</v>
+        <v>38437</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38367</v>
+        <v>38455</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38403</v>
+        <v>38495</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5139,10 +5139,10 @@
         <v>52.8</v>
       </c>
       <c r="F17" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8103</v>
+        <v>8133</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5178,10 +5178,10 @@
         <v>48.8</v>
       </c>
       <c r="F18" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38082</v>
+        <v>38174</v>
       </c>
       <c r="D19" t="n">
         <v>50</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37586</v>
+        <v>37675</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38245</v>
+        <v>38337</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34874</v>
+        <v>34953</v>
       </c>
       <c r="D22" t="n">
         <v>49.9</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38408</v>
+        <v>38501</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38143</v>
+        <v>38234</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38179</v>
+        <v>38270</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38406</v>
+        <v>38498</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5490,10 +5490,10 @@
         <v>50.8</v>
       </c>
       <c r="F26" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38104</v>
+        <v>38197</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37756</v>
+        <v>37847</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37909</v>
+        <v>37996</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5637,13 +5637,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38470</v>
+        <v>38562</v>
       </c>
       <c r="D30" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E30" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F30" t="n">
         <v>44.9</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38284</v>
+        <v>38376</v>
       </c>
       <c r="D31" t="n">
         <v>50.6</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38327</v>
+        <v>38418</v>
       </c>
       <c r="D32" t="n">
         <v>51.1</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38443</v>
+        <v>38536</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38447</v>
+        <v>38539</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38410</v>
+        <v>38502</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5858,7 +5858,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36">
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38694</v>
+        <v>38787</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38686</v>
+        <v>38779</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35710</v>
+        <v>35796</v>
       </c>
       <c r="D38" t="n">
         <v>50.3</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>34988</v>
+        <v>35068</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38165</v>
+        <v>38120</v>
       </c>
       <c r="D40" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="E40" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="F40" t="n">
         <v>58.3</v>
@@ -6062,23 +6062,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38028</v>
+        <v>38257</v>
       </c>
       <c r="D41" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="E41" t="n">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="F41" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="G41" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38208</v>
+        <v>38300</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38604</v>
+        <v>38697</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38661</v>
+        <v>38754</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6192,10 +6192,10 @@
         <v>50.8</v>
       </c>
       <c r="F44" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G44" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38650</v>
+        <v>38743</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38469</v>
+        <v>38559</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38419</v>
+        <v>38509</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38603</v>
+        <v>38695</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34820</v>
+        <v>34899</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38080</v>
+        <v>38172</v>
       </c>
       <c r="D50" t="n">
         <v>49.6</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38071</v>
+        <v>38161</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38119</v>
+        <v>38210</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38532</v>
+        <v>38625</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36550</v>
+        <v>36633</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38298</v>
+        <v>38391</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38002</v>
+        <v>38094</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6660,10 +6660,10 @@
         <v>49.1</v>
       </c>
       <c r="F56" t="n">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="G56" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38363</v>
+        <v>38455</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38444</v>
+        <v>38537</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38646</v>
+        <v>38739</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6777,10 +6777,10 @@
         <v>48.7</v>
       </c>
       <c r="F59" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="G59" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37040</v>
+        <v>37126</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35074</v>
+        <v>35157</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37458</v>
+        <v>37551</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6894,10 +6894,10 @@
         <v>49.2</v>
       </c>
       <c r="F62" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G62" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63">
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23384</v>
+        <v>23440</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6933,10 +6933,10 @@
         <v>49.1</v>
       </c>
       <c r="F63" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23807</v>
+        <v>23859</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -6998,23 +6998,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>38349</v>
+        <v>23883</v>
       </c>
       <c r="D65" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E65" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="G65" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66">
@@ -7037,17 +7037,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>23832</v>
+        <v>38442</v>
       </c>
       <c r="D66" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
         <v>56</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21210</v>
+        <v>21266</v>
       </c>
       <c r="D67" t="n">
         <v>51.8</v>
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37854</v>
+        <v>37946</v>
       </c>
       <c r="D68" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E68" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F68" t="n">
         <v>56.1</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36121</v>
+        <v>36211</v>
       </c>
       <c r="D69" t="n">
         <v>50.5</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30525</v>
+        <v>30601</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37555</v>
+        <v>37643</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32989</v>
+        <v>33072</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26018</v>
+        <v>26081</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14202</v>
+        <v>14236</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7431,13 +7431,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15136</v>
+        <v>15172</v>
       </c>
       <c r="D76" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E76" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F76" t="n">
         <v>53</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26614</v>
+        <v>26684</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35843</v>
+        <v>35929</v>
       </c>
       <c r="D78" t="n">
         <v>50.5</v>
@@ -7518,10 +7518,10 @@
         <v>49.5</v>
       </c>
       <c r="F78" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28604</v>
+        <v>28676</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15760</v>
+        <v>15798</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27844</v>
+        <v>27921</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10420</v>
+        <v>10445</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10423</v>
+        <v>10448</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10206</v>
+        <v>10230</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10720</v>
+        <v>10745</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10203</v>
+        <v>10229</v>
       </c>
       <c r="D86" t="n">
         <v>51.2</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10674</v>
+        <v>10700</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -7869,10 +7869,10 @@
         <v>49.3</v>
       </c>
       <c r="F87" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="G87" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -7899,13 +7899,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10782</v>
+        <v>10806</v>
       </c>
       <c r="D88" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E88" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F88" t="n">
         <v>57.8</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10918</v>
+        <v>10944</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10919</v>
+        <v>10945</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -7986,10 +7986,10 @@
         <v>48.5</v>
       </c>
       <c r="F90" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G90" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10845</v>
+        <v>10870</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -8025,10 +8025,10 @@
         <v>48.4</v>
       </c>
       <c r="F91" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10266</v>
+        <v>10292</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10196</v>
+        <v>10221</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37883</v>
+        <v>37972</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38489</v>
+        <v>38582</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36093</v>
+        <v>36175</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38605</v>
+        <v>38698</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37812</v>
+        <v>37900</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8298,10 +8298,10 @@
         <v>50.7</v>
       </c>
       <c r="F98" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38396</v>
+        <v>38489</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37999</v>
+        <v>38092</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38260</v>
+        <v>38350</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38682</v>
+        <v>38775</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38703</v>
+        <v>38796</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8493,10 +8493,10 @@
         <v>50.3</v>
       </c>
       <c r="F103" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G103" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -8594,13 +8594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1558</v>
+        <v>1645</v>
       </c>
       <c r="D2" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="E2" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="F2" t="n">
         <v>37.4</v>
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1577</v>
+        <v>1665</v>
       </c>
       <c r="D3" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E3" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="F3" t="n">
-        <v>40.1</v>
+        <v>40.5</v>
       </c>
       <c r="G3" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1553</v>
+        <v>1640</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="F4" t="n">
-        <v>40.8</v>
+        <v>40.7</v>
       </c>
       <c r="G4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1462</v>
+        <v>1553</v>
       </c>
       <c r="D5" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="E5" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="F5" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="G5" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,13 +8750,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1462</v>
+        <v>1551</v>
       </c>
       <c r="D6" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="E6" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="F6" t="n">
         <v>44.3</v>
@@ -8789,7 +8789,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1438</v>
+        <v>1524</v>
       </c>
       <c r="D7" t="n">
         <v>50.2</v>
@@ -8798,10 +8798,10 @@
         <v>49.8</v>
       </c>
       <c r="F7" t="n">
-        <v>47.1</v>
+        <v>46.6</v>
       </c>
       <c r="G7" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -8824,23 +8824,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1478</v>
+        <v>1580</v>
       </c>
       <c r="D8" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
       <c r="E8" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="F8" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8863,23 +8863,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1490</v>
+        <v>1568</v>
       </c>
       <c r="D9" t="n">
-        <v>49.3</v>
+        <v>50.4</v>
       </c>
       <c r="E9" t="n">
-        <v>50.7</v>
+        <v>49.6</v>
       </c>
       <c r="F9" t="n">
-        <v>47.7</v>
+        <v>47.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,19 +8906,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1490</v>
+        <v>1582</v>
       </c>
       <c r="D10" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="E10" t="n">
-        <v>50.9</v>
+        <v>51.4</v>
       </c>
       <c r="F10" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1490</v>
+        <v>1581</v>
       </c>
       <c r="D11" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="E11" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="F11" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1494</v>
+        <v>1586</v>
       </c>
       <c r="D12" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="E12" t="n">
-        <v>52.7</v>
+        <v>52.8</v>
       </c>
       <c r="F12" t="n">
-        <v>52.7</v>
+        <v>53</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1467</v>
+        <v>1559</v>
       </c>
       <c r="D13" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E13" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="F13" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1494</v>
+        <v>1586</v>
       </c>
       <c r="D14" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="E14" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>55.3</v>
       </c>
       <c r="G14" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15">
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1558</v>
+        <v>1645</v>
       </c>
       <c r="D15" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E15" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="F15" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="G15" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1555</v>
+        <v>1643</v>
       </c>
       <c r="D16" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="E16" t="n">
-        <v>53.2</v>
+        <v>52.6</v>
       </c>
       <c r="F16" t="n">
-        <v>63.5</v>
+        <v>63.1</v>
       </c>
       <c r="G16" t="n">
-        <v>13.5</v>
+        <v>13.1</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1396</v>
+        <v>1479</v>
       </c>
       <c r="D17" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E17" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F17" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="G17" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1500</v>
+        <v>1593</v>
       </c>
       <c r="D18" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="E18" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="F18" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="G18" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1498</v>
+        <v>1591</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -9266,10 +9266,10 @@
         <v>49.7</v>
       </c>
       <c r="F19" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="G19" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1501</v>
+        <v>1594</v>
       </c>
       <c r="D20" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="E20" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="F20" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1463</v>
+        <v>1553</v>
       </c>
       <c r="D21" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="E21" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="F21" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="G21" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9374,19 +9374,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1499</v>
+        <v>1592</v>
       </c>
       <c r="D22" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E22" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F22" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="G22" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1480</v>
+        <v>1570</v>
       </c>
       <c r="D23" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="E23" t="n">
-        <v>51.2</v>
+        <v>51.4</v>
       </c>
       <c r="F23" t="n">
         <v>37.4</v>
@@ -9452,13 +9452,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1494</v>
+        <v>1586</v>
       </c>
       <c r="D24" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E24" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F24" t="n">
         <v>37.6</v>
@@ -9487,23 +9487,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1501</v>
+        <v>1422</v>
       </c>
       <c r="D25" t="n">
-        <v>51.2</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="F25" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="G25" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>10</v>
@@ -9526,17 +9526,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1343</v>
+        <v>1594</v>
       </c>
       <c r="D26" t="n">
-        <v>52.1</v>
+        <v>51.1</v>
       </c>
       <c r="E26" t="n">
-        <v>47.9</v>
+        <v>48.9</v>
       </c>
       <c r="F26" t="n">
         <v>37.8</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>11</v>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1489</v>
+        <v>1579</v>
       </c>
       <c r="D27" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="E27" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="F27" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="G27" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1495</v>
+        <v>1588</v>
       </c>
       <c r="D28" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E28" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="F28" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="G28" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1486</v>
+        <v>1579</v>
       </c>
       <c r="D29" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E29" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F29" t="n">
         <v>40</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1483</v>
+        <v>1575</v>
       </c>
       <c r="D30" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="E30" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="F30" t="n">
-        <v>40.1</v>
+        <v>40.6</v>
       </c>
       <c r="G30" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9725,13 +9725,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1490</v>
+        <v>1582</v>
       </c>
       <c r="D31" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="E31" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="F31" t="n">
         <v>42.4</v>
@@ -9760,23 +9760,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1495</v>
+        <v>1427</v>
       </c>
       <c r="D32" t="n">
-        <v>48.3</v>
+        <v>49.8</v>
       </c>
       <c r="E32" t="n">
-        <v>51.7</v>
+        <v>50.2</v>
       </c>
       <c r="F32" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="G32" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>22</v>
@@ -9803,13 +9803,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1485</v>
+        <v>1577</v>
       </c>
       <c r="D33" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="E33" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="F33" t="n">
         <v>43.4</v>
@@ -9838,17 +9838,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1347</v>
+        <v>1587</v>
       </c>
       <c r="D34" t="n">
-        <v>49.8</v>
+        <v>48.2</v>
       </c>
       <c r="E34" t="n">
-        <v>50.2</v>
+        <v>51.8</v>
       </c>
       <c r="F34" t="n">
         <v>43.6</v>
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>24</v>
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1474</v>
+        <v>1566</v>
       </c>
       <c r="D35" t="n">
-        <v>52.6</v>
+        <v>52.8</v>
       </c>
       <c r="E35" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="F35" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="G35" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1485</v>
+        <v>1578</v>
       </c>
       <c r="D36" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="E36" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="F36" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="G36" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,13 +9959,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1475</v>
+        <v>1567</v>
       </c>
       <c r="D37" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
       <c r="E37" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="F37" t="n">
         <v>47</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1345</v>
+        <v>1424</v>
       </c>
       <c r="D38" t="n">
         <v>49.6</v>
@@ -10007,10 +10007,10 @@
         <v>50.4</v>
       </c>
       <c r="F38" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
@@ -10033,23 +10033,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1442</v>
+        <v>1588</v>
       </c>
       <c r="D39" t="n">
-        <v>49.7</v>
+        <v>46.2</v>
       </c>
       <c r="E39" t="n">
-        <v>50.3</v>
+        <v>53.8</v>
       </c>
       <c r="F39" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="G39" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10072,23 +10072,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1496</v>
+        <v>1531</v>
       </c>
       <c r="D40" t="n">
-        <v>46.3</v>
+        <v>49.7</v>
       </c>
       <c r="E40" t="n">
-        <v>53.7</v>
+        <v>50.3</v>
       </c>
       <c r="F40" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="G40" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10115,7 +10115,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1453</v>
+        <v>1540</v>
       </c>
       <c r="D41" t="n">
         <v>51</v>
@@ -10124,10 +10124,10 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="G41" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>380</v>
+        <v>410</v>
       </c>
       <c r="D42" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E42" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>52.4</v>
+        <v>53.2</v>
       </c>
       <c r="G42" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10180,7 +10180,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43">
@@ -10189,17 +10189,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1463</v>
+        <v>1576</v>
       </c>
       <c r="D43" t="n">
-        <v>47.6</v>
+        <v>51.4</v>
       </c>
       <c r="E43" t="n">
-        <v>52.4</v>
+        <v>48.6</v>
       </c>
       <c r="F43" t="n">
         <v>53.9</v>
@@ -10228,23 +10228,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1485</v>
+        <v>1554</v>
       </c>
       <c r="D44" t="n">
-        <v>51.4</v>
+        <v>47.4</v>
       </c>
       <c r="E44" t="n">
-        <v>48.6</v>
+        <v>52.6</v>
       </c>
       <c r="F44" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="G44" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1480</v>
+        <v>1573</v>
       </c>
       <c r="D45" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E45" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F45" t="n">
-        <v>55.7</v>
+        <v>55.9</v>
       </c>
       <c r="G45" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1454</v>
+        <v>1545</v>
       </c>
       <c r="D46" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="E46" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="F46" t="n">
-        <v>56.2</v>
+        <v>56.1</v>
       </c>
       <c r="G46" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10345,17 +10345,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1488</v>
+        <v>1576</v>
       </c>
       <c r="D47" t="n">
-        <v>49.3</v>
+        <v>46.4</v>
       </c>
       <c r="E47" t="n">
-        <v>50.7</v>
+        <v>53.6</v>
       </c>
       <c r="F47" t="n">
         <v>57.2</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="48">
@@ -10384,23 +10384,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1485</v>
+        <v>1580</v>
       </c>
       <c r="D48" t="n">
-        <v>46.2</v>
+        <v>49.2</v>
       </c>
       <c r="E48" t="n">
-        <v>53.8</v>
+        <v>50.8</v>
       </c>
       <c r="F48" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
       <c r="G48" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="49">
@@ -10423,23 +10423,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1470</v>
+        <v>1440</v>
       </c>
       <c r="D49" t="n">
-        <v>49.5</v>
+        <v>47.8</v>
       </c>
       <c r="E49" t="n">
-        <v>50.5</v>
+        <v>52.2</v>
       </c>
       <c r="F49" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G49" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10462,23 +10462,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1354</v>
+        <v>1562</v>
       </c>
       <c r="D50" t="n">
-        <v>47.7</v>
+        <v>49.3</v>
       </c>
       <c r="E50" t="n">
-        <v>52.3</v>
+        <v>50.7</v>
       </c>
       <c r="F50" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
       <c r="G50" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51">
@@ -10505,7 +10505,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1472</v>
+        <v>1564</v>
       </c>
       <c r="D51" t="n">
         <v>49</v>
@@ -10514,10 +10514,10 @@
         <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>60.1</v>
+        <v>60</v>
       </c>
       <c r="G51" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1464</v>
+        <v>1556</v>
       </c>
       <c r="D52" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E52" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F52" t="n">
-        <v>61.6</v>
+        <v>61.1</v>
       </c>
       <c r="G52" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53">
@@ -10583,7 +10583,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1477</v>
+        <v>1568</v>
       </c>
       <c r="D53" t="n">
         <v>48.7</v>
@@ -10592,10 +10592,10 @@
         <v>51.3</v>
       </c>
       <c r="F53" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G53" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1476</v>
+        <v>1568</v>
       </c>
       <c r="D54" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="E54" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="F54" t="n">
-        <v>65.90000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,13 +10661,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1490</v>
+        <v>1583</v>
       </c>
       <c r="D55" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E55" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F55" t="n">
         <v>69.7</v>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1481</v>
+        <v>1573</v>
       </c>
       <c r="D56" t="n">
         <v>48.4</v>
@@ -10709,10 +10709,10 @@
         <v>51.6</v>
       </c>
       <c r="F56" t="n">
-        <v>74.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="G56" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1494</v>
+        <v>1586</v>
       </c>
       <c r="D57" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="E57" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="F57" t="n">
-        <v>82.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>32.4</v>
+        <v>32.1</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1498</v>
+        <v>1591</v>
       </c>
       <c r="D58" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E58" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="F58" t="n">
-        <v>83.2</v>
+        <v>82.8</v>
       </c>
       <c r="G58" t="n">
-        <v>33.2</v>
+        <v>32.8</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1498</v>
+        <v>1591</v>
       </c>
       <c r="D59" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E59" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F59" t="n">
         <v>94.5</v>
@@ -10852,23 +10852,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1376</v>
+        <v>1630</v>
       </c>
       <c r="D60" t="n">
-        <v>51.5</v>
+        <v>50.2</v>
       </c>
       <c r="E60" t="n">
-        <v>48.5</v>
+        <v>49.8</v>
       </c>
       <c r="F60" t="n">
-        <v>41.7</v>
+        <v>41.2</v>
       </c>
       <c r="G60" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10891,17 +10891,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1544</v>
+        <v>1459</v>
       </c>
       <c r="D61" t="n">
-        <v>50.3</v>
+        <v>51.3</v>
       </c>
       <c r="E61" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="F61" t="n">
         <v>41.8</v>
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>929</v>
+        <v>985</v>
       </c>
       <c r="D62" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E62" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F62" t="n">
-        <v>58.6</v>
+        <v>59.1</v>
       </c>
       <c r="G62" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="63">
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>921</v>
+        <v>972</v>
       </c>
       <c r="D63" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="E63" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="F63" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="G63" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -11012,19 +11012,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1339</v>
+        <v>1429</v>
       </c>
       <c r="D64" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="E64" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="F64" t="n">
-        <v>60.2</v>
+        <v>60.6</v>
       </c>
       <c r="G64" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="65">
@@ -11051,19 +11051,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>943</v>
+        <v>999</v>
       </c>
       <c r="D65" t="n">
-        <v>51.6</v>
+        <v>51.9</v>
       </c>
       <c r="E65" t="n">
-        <v>48.4</v>
+        <v>48.1</v>
       </c>
       <c r="F65" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G65" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66">
@@ -11090,7 +11090,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>921</v>
+        <v>973</v>
       </c>
       <c r="D66" t="n">
         <v>51.4</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67">
@@ -11125,23 +11125,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1070</v>
+        <v>1553</v>
       </c>
       <c r="D67" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="E67" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="F67" t="n">
-        <v>63</v>
+        <v>62.9</v>
       </c>
       <c r="G67" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="68">
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1460</v>
+        <v>1133</v>
       </c>
       <c r="D68" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E68" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F68" t="n">
-        <v>63.2</v>
+        <v>63.4</v>
       </c>
       <c r="G68" t="n">
-        <v>13.2</v>
+        <v>13.4</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1492</v>
+        <v>1357</v>
       </c>
       <c r="D69" t="n">
-        <v>50.7</v>
+        <v>48</v>
       </c>
       <c r="E69" t="n">
-        <v>49.3</v>
+        <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>63.3</v>
+        <v>63.5</v>
       </c>
       <c r="G69" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70">
@@ -11242,23 +11242,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1281</v>
+        <v>1585</v>
       </c>
       <c r="D70" t="n">
-        <v>47.8</v>
+        <v>50.9</v>
       </c>
       <c r="E70" t="n">
-        <v>52.2</v>
+        <v>49.1</v>
       </c>
       <c r="F70" t="n">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="G70" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71">
@@ -11285,19 +11285,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1475</v>
+        <v>1567</v>
       </c>
       <c r="D71" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E71" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="F71" t="n">
-        <v>63.7</v>
+        <v>63.9</v>
       </c>
       <c r="G71" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11324,13 +11324,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1544</v>
+        <v>1632</v>
       </c>
       <c r="D72" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="E72" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="F72" t="n">
         <v>64.59999999999999</v>
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1282</v>
+        <v>1365</v>
       </c>
       <c r="D73" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="E73" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="F73" t="n">
-        <v>66.7</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>16.7</v>
+        <v>16.1</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>566</v>
+        <v>602</v>
       </c>
       <c r="D74" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="E74" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="F74" t="n">
-        <v>53.5</v>
+        <v>53.7</v>
       </c>
       <c r="G74" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>544</v>
+        <v>578</v>
       </c>
       <c r="D75" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E75" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="G75" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76">
@@ -11476,23 +11476,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>557</v>
+        <v>1155</v>
       </c>
       <c r="D76" t="n">
-        <v>52.2</v>
+        <v>50.8</v>
       </c>
       <c r="E76" t="n">
-        <v>47.8</v>
+        <v>49.2</v>
       </c>
       <c r="F76" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="G76" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -11515,23 +11515,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1085</v>
+        <v>557</v>
       </c>
       <c r="D77" t="n">
-        <v>51.2</v>
+        <v>52.2</v>
       </c>
       <c r="E77" t="n">
-        <v>48.8</v>
+        <v>47.8</v>
       </c>
       <c r="F77" t="n">
-        <v>55.2</v>
+        <v>54.9</v>
       </c>
       <c r="G77" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="78">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1399</v>
+        <v>1485</v>
       </c>
       <c r="D78" t="n">
         <v>48.5</v>
@@ -11567,10 +11567,10 @@
         <v>51.5</v>
       </c>
       <c r="F78" t="n">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="G78" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>546</v>
+        <v>584</v>
       </c>
       <c r="D79" t="n">
-        <v>49.1</v>
+        <v>49.7</v>
       </c>
       <c r="E79" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
       <c r="F79" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
       <c r="G79" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1142</v>
+        <v>1214</v>
       </c>
       <c r="D80" t="n">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="E80" t="n">
-        <v>53.8</v>
+        <v>53.5</v>
       </c>
       <c r="F80" t="n">
-        <v>60.6</v>
+        <v>61</v>
       </c>
       <c r="G80" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="81">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1105</v>
+        <v>1182</v>
       </c>
       <c r="D81" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="E81" t="n">
-        <v>53.1</v>
+        <v>52.7</v>
       </c>
       <c r="F81" t="n">
         <v>63.4</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="82">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="D82" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E82" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F82" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="G82" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11753,19 +11753,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="D83" t="n">
-        <v>48.2</v>
+        <v>47.6</v>
       </c>
       <c r="E83" t="n">
-        <v>51.8</v>
+        <v>52.4</v>
       </c>
       <c r="F83" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84">
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>394</v>
+        <v>419</v>
       </c>
       <c r="D84" t="n">
-        <v>46.2</v>
+        <v>46.8</v>
       </c>
       <c r="E84" t="n">
-        <v>53.8</v>
+        <v>53.2</v>
       </c>
       <c r="F84" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>408</v>
+        <v>433</v>
       </c>
       <c r="D85" t="n">
-        <v>47.3</v>
+        <v>47.8</v>
       </c>
       <c r="E85" t="n">
-        <v>52.7</v>
+        <v>52.2</v>
       </c>
       <c r="F85" t="n">
-        <v>54.2</v>
+        <v>55</v>
       </c>
       <c r="G85" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86">
@@ -11870,19 +11870,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="D86" t="n">
-        <v>50.9</v>
+        <v>49.6</v>
       </c>
       <c r="E86" t="n">
-        <v>49.1</v>
+        <v>50.4</v>
       </c>
       <c r="F86" t="n">
-        <v>56.3</v>
+        <v>57.1</v>
       </c>
       <c r="G86" t="n">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11909,19 +11909,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="D87" t="n">
-        <v>44.5</v>
+        <v>44.8</v>
       </c>
       <c r="E87" t="n">
-        <v>55.5</v>
+        <v>55.2</v>
       </c>
       <c r="F87" t="n">
-        <v>56.5</v>
+        <v>57.5</v>
       </c>
       <c r="G87" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="88">
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="D88" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="E88" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F88" t="n">
-        <v>60.6</v>
+        <v>60.7</v>
       </c>
       <c r="G88" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11987,13 +11987,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="D89" t="n">
-        <v>49.1</v>
+        <v>48.5</v>
       </c>
       <c r="E89" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="F89" t="n">
         <v>62.4</v>
@@ -12026,19 +12026,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="D90" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="E90" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="F90" t="n">
-        <v>62.9</v>
+        <v>63.5</v>
       </c>
       <c r="G90" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="91">
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IWB</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>406</v>
+        <v>442</v>
       </c>
       <c r="D91" t="n">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="E91" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="F91" t="n">
-        <v>63.5</v>
+        <v>63.6</v>
       </c>
       <c r="G91" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
@@ -12100,23 +12100,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWB</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>416</v>
+        <v>431</v>
       </c>
       <c r="D92" t="n">
-        <v>51</v>
+        <v>49.7</v>
       </c>
       <c r="E92" t="n">
-        <v>49</v>
+        <v>50.3</v>
       </c>
       <c r="F92" t="n">
-        <v>63.7</v>
+        <v>64</v>
       </c>
       <c r="G92" t="n">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="D93" t="n">
-        <v>47.6</v>
+        <v>47.1</v>
       </c>
       <c r="E93" t="n">
-        <v>52.4</v>
+        <v>52.9</v>
       </c>
       <c r="F93" t="n">
-        <v>72</v>
+        <v>71.7</v>
       </c>
       <c r="G93" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1500</v>
+        <v>1593</v>
       </c>
       <c r="D94" t="n">
         <v>48.7</v>
@@ -12191,10 +12191,10 @@
         <v>51.3</v>
       </c>
       <c r="F94" t="n">
-        <v>58.2</v>
+        <v>58.1</v>
       </c>
       <c r="G94" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12221,33 +12221,33 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1457</v>
+        <v>1546</v>
       </c>
       <c r="D95" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E95" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F95" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="G95" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H95" t="b">
+        <v>1</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="J95" t="b">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>59</v>
-      </c>
-      <c r="G95" t="n">
-        <v>9</v>
-      </c>
-      <c r="H95" t="b">
-        <v>1</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="J95" t="b">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>60</v>
       </c>
     </row>
     <row r="96">
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1333</v>
+        <v>1575</v>
       </c>
       <c r="D96" t="n">
-        <v>49.1</v>
+        <v>48.2</v>
       </c>
       <c r="E96" t="n">
-        <v>50.9</v>
+        <v>51.8</v>
       </c>
       <c r="F96" t="n">
-        <v>59.3</v>
+        <v>59.7</v>
       </c>
       <c r="G96" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="97">
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1501</v>
+        <v>1415</v>
       </c>
       <c r="D97" t="n">
-        <v>48.5</v>
+        <v>49.7</v>
       </c>
       <c r="E97" t="n">
-        <v>51.5</v>
+        <v>50.3</v>
       </c>
       <c r="F97" t="n">
-        <v>60.2</v>
+        <v>59.9</v>
       </c>
       <c r="G97" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1482</v>
+        <v>1594</v>
       </c>
       <c r="D98" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="E98" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="F98" t="n">
-        <v>60.2</v>
+        <v>60.1</v>
       </c>
       <c r="G98" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="99">
@@ -12373,23 +12373,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1501</v>
+        <v>1587</v>
       </c>
       <c r="D99" t="n">
-        <v>48.6</v>
+        <v>49.5</v>
       </c>
       <c r="E99" t="n">
-        <v>51.4</v>
+        <v>50.5</v>
       </c>
       <c r="F99" t="n">
-        <v>60.5</v>
+        <v>60.2</v>
       </c>
       <c r="G99" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100">
@@ -12412,23 +12412,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1494</v>
+        <v>1594</v>
       </c>
       <c r="D100" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
       <c r="E100" t="n">
-        <v>50.7</v>
+        <v>51.2</v>
       </c>
       <c r="F100" t="n">
-        <v>60.8</v>
+        <v>60.2</v>
       </c>
       <c r="G100" t="n">
-        <v>10.8</v>
+        <v>10.2</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="101">
@@ -12455,7 +12455,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1500</v>
+        <v>1593</v>
       </c>
       <c r="D101" t="n">
         <v>49</v>
@@ -12464,10 +12464,10 @@
         <v>51</v>
       </c>
       <c r="F101" t="n">
-        <v>60.8</v>
+        <v>60.7</v>
       </c>
       <c r="G101" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1445</v>
+        <v>1533</v>
       </c>
       <c r="D102" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F102" t="n">
-        <v>61.5</v>
+        <v>61.2</v>
       </c>
       <c r="G102" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1484</v>
+        <v>1574</v>
       </c>
       <c r="D103" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="E103" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="F103" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="G103" t="n">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38220</v>
+        <v>38307</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12682,13 +12682,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38271</v>
+        <v>38358</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E3" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F3" t="n">
         <v>40.7</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38473</v>
+        <v>38561</v>
       </c>
       <c r="D4" t="n">
         <v>51.2</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37861</v>
+        <v>37950</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12786,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38327</v>
+        <v>38417</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37847</v>
+        <v>37938</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37681</v>
+        <v>37767</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38129</v>
+        <v>38219</v>
       </c>
       <c r="D9" t="n">
         <v>50</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38414</v>
+        <v>38506</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,13 +12994,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38465</v>
+        <v>38557</v>
       </c>
       <c r="D11" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="E11" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="F11" t="n">
         <v>51.8</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38477</v>
+        <v>38568</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38301</v>
+        <v>38393</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38361</v>
+        <v>38453</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13137,7 +13137,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38350</v>
+        <v>38437</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38367</v>
+        <v>38455</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36550</v>
+        <v>36633</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38532</v>
+        <v>38625</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38071</v>
+        <v>38161</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34820</v>
+        <v>34899</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38603</v>
+        <v>38695</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38419</v>
+        <v>38509</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38469</v>
+        <v>38559</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38650</v>
+        <v>38743</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13536,23 +13536,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38604</v>
+        <v>38754</v>
       </c>
       <c r="D25" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="E25" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="F25" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G25" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -13575,17 +13575,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38661</v>
+        <v>38697</v>
       </c>
       <c r="D26" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="E26" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="F26" t="n">
         <v>40.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>34988</v>
+        <v>35068</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38686</v>
+        <v>38779</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38694</v>
+        <v>38787</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38410</v>
+        <v>38502</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38447</v>
+        <v>38539</v>
       </c>
       <c r="D31" t="n">
         <v>49.2</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38443</v>
+        <v>38536</v>
       </c>
       <c r="D32" t="n">
         <v>49.4</v>
@@ -13852,13 +13852,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38470</v>
+        <v>38562</v>
       </c>
       <c r="D33" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E33" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F33" t="n">
         <v>44.9</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38406</v>
+        <v>38498</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -13900,10 +13900,10 @@
         <v>50.8</v>
       </c>
       <c r="F34" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -13917,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38408</v>
+        <v>38501</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34874</v>
+        <v>34953</v>
       </c>
       <c r="D36" t="n">
         <v>49.9</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38245</v>
+        <v>38337</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37586</v>
+        <v>37675</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38403</v>
+        <v>38495</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14095,10 +14095,10 @@
         <v>52.8</v>
       </c>
       <c r="F39" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8103</v>
+        <v>8133</v>
       </c>
       <c r="D40" t="n">
         <v>51.2</v>
@@ -14134,10 +14134,10 @@
         <v>48.8</v>
       </c>
       <c r="F40" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38082</v>
+        <v>38174</v>
       </c>
       <c r="D41" t="n">
         <v>50</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38143</v>
+        <v>38234</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38179</v>
+        <v>38270</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38104</v>
+        <v>38197</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37756</v>
+        <v>37847</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37909</v>
+        <v>37996</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38284</v>
+        <v>38376</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14424,7 +14424,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38327</v>
+        <v>38418</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35710</v>
+        <v>35796</v>
       </c>
       <c r="D49" t="n">
         <v>50.3</v>
@@ -14511,17 +14511,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38165</v>
+        <v>38120</v>
       </c>
       <c r="D50" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="E50" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="F50" t="n">
         <v>58.3</v>
@@ -14550,23 +14550,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38028</v>
+        <v>38257</v>
       </c>
       <c r="D51" t="n">
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
       <c r="E51" t="n">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="F51" t="n">
-        <v>58.4</v>
+        <v>58.3</v>
       </c>
       <c r="G51" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38208</v>
+        <v>38300</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38080</v>
+        <v>38172</v>
       </c>
       <c r="D53" t="n">
         <v>49.6</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38119</v>
+        <v>38210</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38298</v>
+        <v>38391</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14736,7 +14736,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38002</v>
+        <v>38094</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14758,10 +14758,10 @@
         <v>49.1</v>
       </c>
       <c r="F56" t="n">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="G56" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38363</v>
+        <v>38455</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38444</v>
+        <v>38537</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38646</v>
+        <v>38739</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14875,10 +14875,10 @@
         <v>48.7</v>
       </c>
       <c r="F59" t="n">
-        <v>87.7</v>
+        <v>87.8</v>
       </c>
       <c r="G59" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35074</v>
+        <v>35157</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37040</v>
+        <v>37126</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37458</v>
+        <v>37551</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -14992,10 +14992,10 @@
         <v>49.2</v>
       </c>
       <c r="F62" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G62" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -15009,7 +15009,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63">
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23384</v>
+        <v>23440</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15031,10 +15031,10 @@
         <v>49.1</v>
       </c>
       <c r="F63" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="G63" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -15048,7 +15048,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="64">
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23807</v>
+        <v>23859</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15096,23 +15096,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>38349</v>
+        <v>23883</v>
       </c>
       <c r="D65" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E65" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="G65" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>23832</v>
+        <v>38442</v>
       </c>
       <c r="D66" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
         <v>56</v>
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21210</v>
+        <v>21266</v>
       </c>
       <c r="D67" t="n">
         <v>51.8</v>
@@ -15217,13 +15217,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37854</v>
+        <v>37946</v>
       </c>
       <c r="D68" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E68" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F68" t="n">
         <v>56.1</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36121</v>
+        <v>36211</v>
       </c>
       <c r="D69" t="n">
         <v>50.5</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30525</v>
+        <v>30601</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37555</v>
+        <v>37643</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>32989</v>
+        <v>33072</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26018</v>
+        <v>26081</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74">
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14202</v>
+        <v>14236</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15529,13 +15529,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15136</v>
+        <v>15172</v>
       </c>
       <c r="D76" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="E76" t="n">
-        <v>49.4</v>
+        <v>49.5</v>
       </c>
       <c r="F76" t="n">
         <v>53</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26614</v>
+        <v>26684</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35843</v>
+        <v>35929</v>
       </c>
       <c r="D78" t="n">
         <v>50.5</v>
@@ -15616,10 +15616,10 @@
         <v>49.5</v>
       </c>
       <c r="F78" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="79">
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28604</v>
+        <v>28676</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15760</v>
+        <v>15798</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27844</v>
+        <v>27921</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10420</v>
+        <v>10445</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10423</v>
+        <v>10448</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10206</v>
+        <v>10230</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10720</v>
+        <v>10745</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10203</v>
+        <v>10229</v>
       </c>
       <c r="D86" t="n">
         <v>51.2</v>
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10674</v>
+        <v>10700</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -15967,10 +15967,10 @@
         <v>49.3</v>
       </c>
       <c r="F87" t="n">
-        <v>57.3</v>
+        <v>57.4</v>
       </c>
       <c r="G87" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -15997,13 +15997,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10782</v>
+        <v>10806</v>
       </c>
       <c r="D88" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E88" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F88" t="n">
         <v>57.8</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10918</v>
+        <v>10944</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10919</v>
+        <v>10945</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -16084,10 +16084,10 @@
         <v>48.5</v>
       </c>
       <c r="F90" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G90" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10845</v>
+        <v>10870</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -16123,10 +16123,10 @@
         <v>48.4</v>
       </c>
       <c r="F91" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10266</v>
+        <v>10292</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10196</v>
+        <v>10221</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37883</v>
+        <v>37972</v>
       </c>
       <c r="D94" t="n">
         <v>49.9</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38489</v>
+        <v>38582</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36093</v>
+        <v>36175</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38605</v>
+        <v>38698</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37812</v>
+        <v>37900</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16396,10 +16396,10 @@
         <v>50.7</v>
       </c>
       <c r="F98" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="G98" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38396</v>
+        <v>38489</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>37999</v>
+        <v>38092</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38260</v>
+        <v>38350</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38682</v>
+        <v>38775</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38703</v>
+        <v>38796</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -16591,10 +16591,10 @@
         <v>50.3</v>
       </c>
       <c r="F103" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G103" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="D2" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="E2" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="F2" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="D3" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E3" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F3" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -570,23 +570,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1580</v>
+        <v>1566</v>
       </c>
       <c r="D4" t="n">
-        <v>49.1</v>
+        <v>50.4</v>
       </c>
       <c r="E4" t="n">
-        <v>50.9</v>
+        <v>49.6</v>
       </c>
       <c r="F4" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -609,11 +609,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1568</v>
+        <v>1525</v>
       </c>
       <c r="D5" t="n">
         <v>50.4</v>
@@ -622,10 +622,10 @@
         <v>49.6</v>
       </c>
       <c r="F5" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="D6" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="E6" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>52.6</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -687,23 +687,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1524</v>
+        <v>1578</v>
       </c>
       <c r="D7" t="n">
-        <v>50.2</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>49.8</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -730,13 +730,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="D8" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="E8" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="F8" t="n">
         <v>53.9</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -772,16 +772,16 @@
         <v>1586</v>
       </c>
       <c r="D9" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E9" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F9" t="n">
-        <v>55.3</v>
+        <v>54.7</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="D10" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="E10" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="F10" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="G10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -850,16 +850,16 @@
         <v>1553</v>
       </c>
       <c r="D11" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="E11" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="F11" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="G11" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="D12" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="E12" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="F12" t="n">
-        <v>40.7</v>
+        <v>41.6</v>
       </c>
       <c r="G12" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1665</v>
+        <v>1661</v>
       </c>
       <c r="D13" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="E13" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="F13" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="G13" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="D14" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="E14" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="F14" t="n">
-        <v>37.4</v>
+        <v>38.1</v>
       </c>
       <c r="G14" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="D15" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E15" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>62.4</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -1042,7 +1042,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D16" t="n">
         <v>47.4</v>
@@ -1051,10 +1051,10 @@
         <v>52.6</v>
       </c>
       <c r="F16" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="G16" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -1084,16 +1084,16 @@
         <v>1424</v>
       </c>
       <c r="D17" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="E17" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="F17" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="D18" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="E18" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="F18" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="D19" t="n">
-        <v>49.7</v>
+        <v>51.4</v>
       </c>
       <c r="E19" t="n">
-        <v>50.3</v>
+        <v>48.6</v>
       </c>
       <c r="F19" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="G19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1540</v>
+        <v>1526</v>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="F20" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="D21" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>47.8</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>410</v>
+        <v>1553</v>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>47.4</v>
       </c>
       <c r="E22" t="n">
-        <v>51</v>
+        <v>52.6</v>
       </c>
       <c r="F22" t="n">
         <v>53.2</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1311,23 +1311,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1576</v>
+        <v>409</v>
       </c>
       <c r="D23" t="n">
-        <v>51.4</v>
+        <v>49.4</v>
       </c>
       <c r="E23" t="n">
-        <v>48.6</v>
+        <v>50.6</v>
       </c>
       <c r="F23" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="G23" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="J23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1350,23 +1350,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1554</v>
+        <v>1576</v>
       </c>
       <c r="D24" t="n">
-        <v>47.4</v>
+        <v>51.9</v>
       </c>
       <c r="E24" t="n">
-        <v>52.6</v>
+        <v>48.1</v>
       </c>
       <c r="F24" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="G24" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1566</v>
+        <v>1569</v>
       </c>
       <c r="D25" t="n">
-        <v>52.8</v>
+        <v>49.3</v>
       </c>
       <c r="E25" t="n">
-        <v>47.2</v>
+        <v>50.7</v>
       </c>
       <c r="F25" t="n">
-        <v>44.6</v>
+        <v>54.7</v>
       </c>
       <c r="G25" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1578</v>
+        <v>1564</v>
       </c>
       <c r="D26" t="n">
-        <v>51.8</v>
+        <v>52.8</v>
       </c>
       <c r="E26" t="n">
-        <v>48.2</v>
+        <v>47.2</v>
       </c>
       <c r="F26" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="G26" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1467,23 +1467,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D27" t="n">
-        <v>49.1</v>
+        <v>51.8</v>
       </c>
       <c r="E27" t="n">
-        <v>50.9</v>
+        <v>48.2</v>
       </c>
       <c r="F27" t="n">
-        <v>55.9</v>
+        <v>44.3</v>
       </c>
       <c r="G27" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -1506,23 +1506,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1545</v>
+        <v>1576</v>
       </c>
       <c r="D28" t="n">
-        <v>51.5</v>
+        <v>46.8</v>
       </c>
       <c r="E28" t="n">
-        <v>48.5</v>
+        <v>53.2</v>
       </c>
       <c r="F28" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
       <c r="G28" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1545,23 +1545,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1587</v>
+        <v>1541</v>
       </c>
       <c r="D29" t="n">
-        <v>48.2</v>
+        <v>51.7</v>
       </c>
       <c r="E29" t="n">
-        <v>51.8</v>
+        <v>48.3</v>
       </c>
       <c r="F29" t="n">
-        <v>43.6</v>
+        <v>56.3</v>
       </c>
       <c r="G29" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1591,16 +1591,16 @@
         <v>1577</v>
       </c>
       <c r="D30" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="E30" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="F30" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1427</v>
+        <v>1579</v>
       </c>
       <c r="D31" t="n">
-        <v>49.8</v>
+        <v>49.2</v>
       </c>
       <c r="E31" t="n">
-        <v>50.2</v>
+        <v>50.8</v>
       </c>
       <c r="F31" t="n">
-        <v>43.2</v>
+        <v>56.6</v>
       </c>
       <c r="G31" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>32</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1576</v>
+        <v>1584</v>
       </c>
       <c r="D32" t="n">
-        <v>46.4</v>
+        <v>47.7</v>
       </c>
       <c r="E32" t="n">
-        <v>53.6</v>
+        <v>52.3</v>
       </c>
       <c r="F32" t="n">
-        <v>57.2</v>
+        <v>43.2</v>
       </c>
       <c r="G32" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33">
@@ -1701,23 +1701,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1580</v>
+        <v>1427</v>
       </c>
       <c r="D33" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E33" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F33" t="n">
-        <v>57.2</v>
+        <v>43.2</v>
       </c>
       <c r="G33" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D34" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E34" t="n">
         <v>50.3</v>
       </c>
-      <c r="E34" t="n">
-        <v>49.7</v>
-      </c>
       <c r="F34" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="G34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1779,23 +1779,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EURAUD</t>
+          <t>ZARJPY</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1575</v>
+        <v>1440</v>
       </c>
       <c r="D35" t="n">
-        <v>48.8</v>
+        <v>48.1</v>
       </c>
       <c r="E35" t="n">
-        <v>51.2</v>
+        <v>51.9</v>
       </c>
       <c r="F35" t="n">
-        <v>40.6</v>
+        <v>59</v>
       </c>
       <c r="G35" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -1818,23 +1818,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ZARJPY</t>
+          <t>EURAUD</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1440</v>
+        <v>1573</v>
       </c>
       <c r="D36" t="n">
-        <v>47.8</v>
+        <v>48.5</v>
       </c>
       <c r="E36" t="n">
-        <v>52.2</v>
+        <v>51.5</v>
       </c>
       <c r="F36" t="n">
-        <v>59.4</v>
+        <v>40.9</v>
       </c>
       <c r="G36" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="D37" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
         <v>59.5</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -1896,11 +1896,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AUDCAD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1564</v>
+        <v>1576</v>
       </c>
       <c r="D38" t="n">
         <v>49</v>
@@ -1909,10 +1909,10 @@
         <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>60</v>
+        <v>40.2</v>
       </c>
       <c r="G38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39">
@@ -1935,20 +1935,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1579</v>
+        <v>1564</v>
       </c>
       <c r="D39" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="E39" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="G39" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40">
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="D40" t="n">
         <v>50.4</v>
@@ -1987,10 +1987,10 @@
         <v>49.6</v>
       </c>
       <c r="F40" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="G40" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="41">
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="D41" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
       <c r="E41" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="F41" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="G41" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="D42" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="E42" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="F42" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="G42" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43">
@@ -2091,23 +2091,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1594</v>
+        <v>1584</v>
       </c>
       <c r="D43" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E43" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F43" t="n">
-        <v>37.8</v>
+        <v>38.2</v>
       </c>
       <c r="G43" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="44">
@@ -2130,23 +2130,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1422</v>
+        <v>1592</v>
       </c>
       <c r="D44" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
       <c r="E44" t="n">
-        <v>48</v>
+        <v>49.2</v>
       </c>
       <c r="F44" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="G44" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="J44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="45">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1586</v>
+        <v>1422</v>
       </c>
       <c r="D45" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="E45" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="F45" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="G45" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46">
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1570</v>
+        <v>1589</v>
       </c>
       <c r="D46" t="n">
-        <v>48.6</v>
+        <v>50.8</v>
       </c>
       <c r="E46" t="n">
-        <v>51.4</v>
+        <v>49.2</v>
       </c>
       <c r="F46" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="G46" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="D47" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="E47" t="n">
-        <v>48.8</v>
+        <v>51.8</v>
       </c>
       <c r="F47" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="G47" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D48" t="n">
-        <v>50.8</v>
+        <v>49.9</v>
       </c>
       <c r="E48" t="n">
-        <v>49.2</v>
+        <v>50.1</v>
       </c>
       <c r="F48" t="n">
         <v>36.4</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="D49" t="n">
-        <v>52.1</v>
+        <v>51.6</v>
       </c>
       <c r="E49" t="n">
-        <v>47.9</v>
+        <v>48.4</v>
       </c>
       <c r="F49" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="G49" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
@@ -2368,19 +2368,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D50" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E50" t="n">
         <v>50.3</v>
       </c>
-      <c r="E50" t="n">
-        <v>49.7</v>
-      </c>
       <c r="F50" t="n">
-        <v>35.3</v>
+        <v>35.9</v>
       </c>
       <c r="G50" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D51" t="n">
-        <v>48.7</v>
+        <v>49.5</v>
       </c>
       <c r="E51" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="F51" t="n">
-        <v>65.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G51" t="n">
-        <v>15.4</v>
+        <v>14.5</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D52" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="E52" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="F52" t="n">
-        <v>66.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="D53" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="E53" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="F53" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="G53" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="D54" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="E54" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="F54" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="G54" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="E55" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="F55" t="n">
-        <v>69.7</v>
+        <v>70</v>
       </c>
       <c r="G55" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="D56" t="n">
         <v>48.4</v>
@@ -2611,10 +2611,10 @@
         <v>51.6</v>
       </c>
       <c r="F56" t="n">
-        <v>74.7</v>
+        <v>74.8</v>
       </c>
       <c r="G56" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="D57" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E57" t="n">
         <v>49.9</v>
       </c>
-      <c r="E57" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F57" t="n">
-        <v>82.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D58" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E58" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F58" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="G58" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="D59" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="E59" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="F59" t="n">
         <v>94.5</v>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="D60" t="n">
         <v>51.3</v>
@@ -2767,10 +2767,10 @@
         <v>48.7</v>
       </c>
       <c r="F60" t="n">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="G60" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61">
@@ -2797,19 +2797,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="D61" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="E61" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="F61" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="G61" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62">
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D62" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E62" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F62" t="n">
-        <v>59.1</v>
+        <v>59.4</v>
       </c>
       <c r="G62" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -2875,7 +2875,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D63" t="n">
         <v>47.3</v>
@@ -2884,10 +2884,10 @@
         <v>52.7</v>
       </c>
       <c r="F63" t="n">
-        <v>59.4</v>
+        <v>59.8</v>
       </c>
       <c r="G63" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64">
@@ -2917,16 +2917,16 @@
         <v>1429</v>
       </c>
       <c r="D64" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="E64" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="F64" t="n">
-        <v>60.6</v>
+        <v>61.2</v>
       </c>
       <c r="G64" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="65">
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>999</v>
+        <v>974</v>
       </c>
       <c r="D65" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
       <c r="E65" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="F65" t="n">
-        <v>60.9</v>
+        <v>61.9</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66">
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>973</v>
+        <v>999</v>
       </c>
       <c r="D66" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E66" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F66" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1553</v>
+        <v>1133</v>
       </c>
       <c r="D67" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="E67" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="F67" t="n">
-        <v>62.9</v>
+        <v>63.6</v>
       </c>
       <c r="G67" t="n">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1133</v>
+        <v>1551</v>
       </c>
       <c r="D68" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="E68" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="F68" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="G68" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D69" t="n">
         <v>48</v>
@@ -3118,10 +3118,10 @@
         <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>63.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70">
@@ -3148,19 +3148,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="D70" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E70" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="F70" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71">
@@ -3190,16 +3190,16 @@
         <v>1567</v>
       </c>
       <c r="D71" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="E71" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="F71" t="n">
-        <v>63.9</v>
+        <v>64.8</v>
       </c>
       <c r="G71" t="n">
-        <v>13.9</v>
+        <v>14.8</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72">
@@ -3226,19 +3226,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="D72" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
       <c r="E72" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="F72" t="n">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D73" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E73" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="F73" t="n">
-        <v>66.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="G73" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D74" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="E74" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="F74" t="n">
-        <v>53.7</v>
+        <v>53.2</v>
       </c>
       <c r="G74" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3339,23 +3339,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>578</v>
+        <v>1156</v>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="F75" t="n">
-        <v>54.8</v>
+        <v>53.5</v>
       </c>
       <c r="G75" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -3378,23 +3378,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1155</v>
+        <v>579</v>
       </c>
       <c r="D76" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="E76" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="F76" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="G76" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>557</v>
+        <v>521</v>
       </c>
       <c r="D77" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="E77" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="F77" t="n">
-        <v>54.9</v>
+        <v>55.3</v>
       </c>
       <c r="G77" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D78" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="E78" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="F78" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D79" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E79" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>60.4</v>
+        <v>61.1</v>
       </c>
       <c r="G79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="D80" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="E80" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="F80" t="n">
-        <v>61</v>
+        <v>61.6</v>
       </c>
       <c r="G80" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81">
@@ -3577,7 +3577,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="D81" t="n">
         <v>47.3</v>
@@ -3586,10 +3586,10 @@
         <v>52.7</v>
       </c>
       <c r="F81" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="G81" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D82" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="E82" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="F82" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3655,19 +3655,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D83" t="n">
-        <v>47.6</v>
+        <v>46.8</v>
       </c>
       <c r="E83" t="n">
-        <v>52.4</v>
+        <v>53.2</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D84" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E84" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>48.2</v>
+        <v>47.4</v>
       </c>
       <c r="G84" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85">
@@ -3736,16 +3736,16 @@
         <v>433</v>
       </c>
       <c r="D85" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="E85" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>55</v>
+        <v>56.1</v>
       </c>
       <c r="G85" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86">
@@ -3768,23 +3768,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="D86" t="n">
-        <v>49.6</v>
+        <v>45.6</v>
       </c>
       <c r="E86" t="n">
-        <v>50.4</v>
+        <v>54.4</v>
       </c>
       <c r="F86" t="n">
-        <v>57.1</v>
+        <v>57.4</v>
       </c>
       <c r="G86" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87">
@@ -3807,23 +3807,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="D87" t="n">
-        <v>44.8</v>
+        <v>48.4</v>
       </c>
       <c r="E87" t="n">
-        <v>55.2</v>
+        <v>51.6</v>
       </c>
       <c r="F87" t="n">
-        <v>57.5</v>
+        <v>57.8</v>
       </c>
       <c r="G87" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D88" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="E88" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="F88" t="n">
-        <v>60.7</v>
+        <v>62</v>
       </c>
       <c r="G88" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89">
@@ -3889,19 +3889,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D89" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E89" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F89" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="G89" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90">
@@ -3924,23 +3924,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D90" t="n">
-        <v>49.3</v>
+        <v>51.4</v>
       </c>
       <c r="E90" t="n">
-        <v>50.7</v>
+        <v>48.6</v>
       </c>
       <c r="F90" t="n">
-        <v>63.5</v>
+        <v>64.3</v>
       </c>
       <c r="G90" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D91" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="E91" t="n">
-        <v>49.3</v>
+        <v>49.9</v>
       </c>
       <c r="F91" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="G91" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -4009,16 +4009,16 @@
         <v>431</v>
       </c>
       <c r="D92" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="E92" t="n">
         <v>49.7</v>
       </c>
-      <c r="E92" t="n">
-        <v>50.3</v>
-      </c>
       <c r="F92" t="n">
-        <v>64</v>
+        <v>65.2</v>
       </c>
       <c r="G92" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D93" t="n">
-        <v>47.1</v>
+        <v>48.2</v>
       </c>
       <c r="E93" t="n">
-        <v>52.9</v>
+        <v>51.7</v>
       </c>
       <c r="F93" t="n">
-        <v>71.7</v>
+        <v>72</v>
       </c>
       <c r="G93" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4084,19 +4084,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D94" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="E94" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="F94" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="G94" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="95">
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D95" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="E95" t="n">
-        <v>49.5</v>
+        <v>48.9</v>
       </c>
       <c r="F95" t="n">
-        <v>58.4</v>
+        <v>58.6</v>
       </c>
       <c r="G95" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1575</v>
+        <v>1413</v>
       </c>
       <c r="D96" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
       <c r="E96" t="n">
-        <v>51.8</v>
+        <v>50.2</v>
       </c>
       <c r="F96" t="n">
-        <v>59.7</v>
+        <v>58.9</v>
       </c>
       <c r="G96" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1415</v>
+        <v>1573</v>
       </c>
       <c r="D97" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="E97" t="n">
-        <v>50.3</v>
+        <v>51.8</v>
       </c>
       <c r="F97" t="n">
-        <v>59.9</v>
+        <v>59.4</v>
       </c>
       <c r="G97" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1594</v>
+        <v>1610</v>
       </c>
       <c r="D98" t="n">
-        <v>48.3</v>
+        <v>48.8</v>
       </c>
       <c r="E98" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="F98" t="n">
-        <v>60.1</v>
+        <v>59.5</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="99">
@@ -4275,23 +4275,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="D99" t="n">
-        <v>49.5</v>
+        <v>48.4</v>
       </c>
       <c r="E99" t="n">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
       <c r="F99" t="n">
-        <v>60.2</v>
+        <v>59.7</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="100">
@@ -4314,17 +4314,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="D100" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="E100" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="F100" t="n">
         <v>60.2</v>
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D101" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="E101" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="F101" t="n">
-        <v>60.7</v>
+        <v>60.2</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="102">
@@ -4396,19 +4396,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="D102" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="E102" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
       <c r="F102" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="G102" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="D103" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E103" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F103" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="G103" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38219</v>
+        <v>38309</v>
       </c>
       <c r="D2" t="n">
         <v>50</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37767</v>
+        <v>37854</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>37938</v>
+        <v>38028</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38506</v>
+        <v>38595</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38557</v>
+        <v>38648</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38417</v>
+        <v>38506</v>
       </c>
       <c r="D7" t="n">
         <v>50.7</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38568</v>
+        <v>38657</v>
       </c>
       <c r="D8" t="n">
         <v>51.4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>37950</v>
+        <v>38036</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38393</v>
+        <v>38484</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38453</v>
+        <v>38544</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38561</v>
+        <v>38649</v>
       </c>
       <c r="D12" t="n">
         <v>51.2</v>
@@ -4961,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38358</v>
+        <v>38444</v>
       </c>
       <c r="D13" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E13" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F13" t="n">
         <v>40.7</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38307</v>
+        <v>38395</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38437</v>
+        <v>38523</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38455</v>
+        <v>38543</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38495</v>
+        <v>38584</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5139,10 +5139,10 @@
         <v>52.8</v>
       </c>
       <c r="F17" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -5156,7 +5156,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8133</v>
+        <v>8153</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38174</v>
+        <v>38262</v>
       </c>
       <c r="D19" t="n">
         <v>50</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37675</v>
+        <v>37762</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38337</v>
+        <v>38425</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5295,10 +5295,10 @@
         <v>48.3</v>
       </c>
       <c r="F21" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -5312,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>34953</v>
+        <v>35033</v>
       </c>
       <c r="D22" t="n">
         <v>49.9</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38501</v>
+        <v>38589</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38234</v>
+        <v>38321</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38270</v>
+        <v>38360</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38498</v>
+        <v>38588</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38197</v>
+        <v>38285</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37847</v>
+        <v>37932</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>37996</v>
+        <v>38085</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5607,10 +5607,10 @@
         <v>49.9</v>
       </c>
       <c r="F29" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="G29" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
@@ -5633,20 +5633,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38562</v>
+        <v>38466</v>
       </c>
       <c r="D30" t="n">
-        <v>49.5</v>
+        <v>50.6</v>
       </c>
       <c r="E30" t="n">
-        <v>50.5</v>
+        <v>49.4</v>
       </c>
       <c r="F30" t="n">
-        <v>44.9</v>
+        <v>55.1</v>
       </c>
       <c r="G30" t="n">
         <v>5.1</v>
@@ -5672,23 +5672,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38376</v>
+        <v>38651</v>
       </c>
       <c r="D31" t="n">
-        <v>50.6</v>
+        <v>49.5</v>
       </c>
       <c r="E31" t="n">
-        <v>49.4</v>
+        <v>50.5</v>
       </c>
       <c r="F31" t="n">
-        <v>55.1</v>
+        <v>44.8</v>
       </c>
       <c r="G31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38418</v>
+        <v>38507</v>
       </c>
       <c r="D32" t="n">
         <v>51.1</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38536</v>
+        <v>38624</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38539</v>
+        <v>38628</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38502</v>
+        <v>38591</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38787</v>
+        <v>38877</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38779</v>
+        <v>38869</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5949,13 +5949,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35796</v>
+        <v>35878</v>
       </c>
       <c r="D38" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="E38" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="F38" t="n">
         <v>57.3</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35068</v>
+        <v>35148</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -5997,10 +5997,10 @@
         <v>50.1</v>
       </c>
       <c r="F39" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="G39" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -6014,7 +6014,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40">
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38120</v>
+        <v>38208</v>
       </c>
       <c r="D40" t="n">
         <v>50.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38257</v>
+        <v>38346</v>
       </c>
       <c r="D41" t="n">
         <v>49.4</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38300</v>
+        <v>38389</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38697</v>
+        <v>38787</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38754</v>
+        <v>38844</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38743</v>
+        <v>38832</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38559</v>
+        <v>38648</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38509</v>
+        <v>38599</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38695</v>
+        <v>38785</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34899</v>
+        <v>34979</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38172</v>
+        <v>38262</v>
       </c>
       <c r="D50" t="n">
         <v>49.6</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38161</v>
+        <v>38250</v>
       </c>
       <c r="D51" t="n">
         <v>50.3</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38210</v>
+        <v>38299</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38625</v>
+        <v>38715</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36633</v>
+        <v>36715</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38391</v>
+        <v>38480</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6621,10 +6621,10 @@
         <v>49.9</v>
       </c>
       <c r="F55" t="n">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="G55" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -6638,7 +6638,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38094</v>
+        <v>38181</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38455</v>
+        <v>38545</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38537</v>
+        <v>38627</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38739</v>
+        <v>38829</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37126</v>
+        <v>37211</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35157</v>
+        <v>35243</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37551</v>
+        <v>37638</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63">
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23440</v>
+        <v>23495</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23859</v>
+        <v>23912</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23883</v>
+        <v>23936</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38442</v>
+        <v>38532</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -7076,17 +7076,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21266</v>
+        <v>38036</v>
       </c>
       <c r="D67" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="E67" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="F67" t="n">
         <v>56.1</v>
@@ -7115,23 +7115,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37946</v>
+        <v>21322</v>
       </c>
       <c r="D68" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="E68" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="F68" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G68" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -7158,19 +7158,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36211</v>
+        <v>36297</v>
       </c>
       <c r="D69" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="G69" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -7184,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70">
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30601</v>
+        <v>30675</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7206,10 +7206,10 @@
         <v>49.2</v>
       </c>
       <c r="F70" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="G70" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37643</v>
+        <v>37729</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33072</v>
+        <v>33151</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26081</v>
+        <v>26142</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7323,10 +7323,10 @@
         <v>49.9</v>
       </c>
       <c r="F73" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G73" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14236</v>
+        <v>14271</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15172</v>
+        <v>15207</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26684</v>
+        <v>26752</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,13 +7509,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35929</v>
+        <v>36009</v>
       </c>
       <c r="D78" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E78" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F78" t="n">
         <v>65.59999999999999</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28676</v>
+        <v>28745</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7557,10 +7557,10 @@
         <v>50.7</v>
       </c>
       <c r="F79" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G79" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15798</v>
+        <v>15838</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27921</v>
+        <v>27994</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7665,13 +7665,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10445</v>
+        <v>10469</v>
       </c>
       <c r="D82" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E82" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F82" t="n">
         <v>51.9</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10448</v>
+        <v>10474</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10230</v>
+        <v>10254</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10745</v>
+        <v>10771</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7791,10 +7791,10 @@
         <v>49.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="G85" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10229</v>
+        <v>10255</v>
       </c>
       <c r="D86" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E86" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F86" t="n">
         <v>56</v>
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10700</v>
+        <v>10726</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -7869,10 +7869,10 @@
         <v>49.3</v>
       </c>
       <c r="F87" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="G87" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10806</v>
+        <v>10830</v>
       </c>
       <c r="D88" t="n">
         <v>51.5</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10944</v>
+        <v>10970</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10945</v>
+        <v>10970</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="91">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10870</v>
+        <v>10896</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10292</v>
+        <v>10316</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10221</v>
+        <v>10243</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37972</v>
+        <v>38062</v>
       </c>
       <c r="D94" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
         <v>53.7</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38582</v>
+        <v>38672</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36175</v>
+        <v>36257</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38698</v>
+        <v>38788</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8259,10 +8259,10 @@
         <v>49.7</v>
       </c>
       <c r="F97" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="G97" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37900</v>
+        <v>37986</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38489</v>
+        <v>38579</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38092</v>
+        <v>38182</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38350</v>
+        <v>38438</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,13 +8445,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38775</v>
+        <v>38865</v>
       </c>
       <c r="D102" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E102" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F102" t="n">
         <v>54.6</v>
@@ -8471,7 +8471,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103">
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38796</v>
+        <v>38904</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1645</v>
+        <v>1642</v>
       </c>
       <c r="D2" t="n">
-        <v>52.1</v>
+        <v>51.8</v>
       </c>
       <c r="E2" t="n">
-        <v>47.9</v>
+        <v>48.2</v>
       </c>
       <c r="F2" t="n">
-        <v>37.4</v>
+        <v>38.1</v>
       </c>
       <c r="G2" t="n">
-        <v>12.6</v>
+        <v>11.9</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1665</v>
+        <v>1661</v>
       </c>
       <c r="D3" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="E3" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="F3" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="G3" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="D4" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="E4" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="F4" t="n">
-        <v>40.7</v>
+        <v>41.6</v>
       </c>
       <c r="G4" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -8714,16 +8714,16 @@
         <v>1553</v>
       </c>
       <c r="D5" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="E5" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="F5" t="n">
-        <v>42.6</v>
+        <v>42.9</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1551</v>
+        <v>1546</v>
       </c>
       <c r="D6" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="E6" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="F6" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8785,23 +8785,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1524</v>
+        <v>1578</v>
       </c>
       <c r="D7" t="n">
-        <v>50.2</v>
+        <v>49</v>
       </c>
       <c r="E7" t="n">
-        <v>49.8</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>46.6</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8824,23 +8824,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1580</v>
+        <v>1525</v>
       </c>
       <c r="D8" t="n">
-        <v>49.1</v>
+        <v>50.4</v>
       </c>
       <c r="E8" t="n">
-        <v>50.9</v>
+        <v>49.6</v>
       </c>
       <c r="F8" t="n">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D9" t="n">
         <v>50.4</v>
@@ -8876,10 +8876,10 @@
         <v>49.6</v>
       </c>
       <c r="F9" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,19 +8906,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="D10" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E10" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F10" t="n">
-        <v>48.7</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="D11" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="E11" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="F11" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="D12" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="E12" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
       <c r="F12" t="n">
-        <v>53</v>
+        <v>52.6</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,13 +9023,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="D13" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="E13" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="F13" t="n">
         <v>53.9</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -9065,16 +9065,16 @@
         <v>1586</v>
       </c>
       <c r="D14" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="E14" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="F14" t="n">
-        <v>55.3</v>
+        <v>54.7</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="D15" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E15" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F15" t="n">
-        <v>63</v>
+        <v>62.4</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>12.4</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -9140,7 +9140,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1643</v>
+        <v>1640</v>
       </c>
       <c r="D16" t="n">
         <v>47.4</v>
@@ -9149,10 +9149,10 @@
         <v>52.6</v>
       </c>
       <c r="F16" t="n">
-        <v>63.1</v>
+        <v>62.7</v>
       </c>
       <c r="G16" t="n">
-        <v>13.1</v>
+        <v>12.7</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="D17" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="E17" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="F17" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="G17" t="n">
-        <v>19</v>
+        <v>19.3</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="D18" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="E18" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="F18" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="G18" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,19 +9257,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D19" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E19" t="n">
         <v>50.3</v>
       </c>
-      <c r="E19" t="n">
-        <v>49.7</v>
-      </c>
       <c r="F19" t="n">
-        <v>35.3</v>
+        <v>35.9</v>
       </c>
       <c r="G19" t="n">
-        <v>14.7</v>
+        <v>14.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="D20" t="n">
-        <v>52.1</v>
+        <v>51.6</v>
       </c>
       <c r="E20" t="n">
-        <v>47.9</v>
+        <v>48.4</v>
       </c>
       <c r="F20" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="G20" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="D21" t="n">
-        <v>50.8</v>
+        <v>49.9</v>
       </c>
       <c r="E21" t="n">
-        <v>49.2</v>
+        <v>50.1</v>
       </c>
       <c r="F21" t="n">
         <v>36.4</v>
@@ -9370,23 +9370,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1592</v>
+        <v>1568</v>
       </c>
       <c r="D22" t="n">
-        <v>51.2</v>
+        <v>48.2</v>
       </c>
       <c r="E22" t="n">
-        <v>48.8</v>
+        <v>51.8</v>
       </c>
       <c r="F22" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="G22" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9409,23 +9409,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1570</v>
+        <v>1589</v>
       </c>
       <c r="D23" t="n">
-        <v>48.6</v>
+        <v>50.8</v>
       </c>
       <c r="E23" t="n">
-        <v>51.4</v>
+        <v>49.2</v>
       </c>
       <c r="F23" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="G23" t="n">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9439,7 +9439,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -9448,23 +9448,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1586</v>
+        <v>1422</v>
       </c>
       <c r="D24" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="E24" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="F24" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="G24" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9478,7 +9478,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -9487,23 +9487,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1422</v>
+        <v>1592</v>
       </c>
       <c r="D25" t="n">
-        <v>52</v>
+        <v>50.8</v>
       </c>
       <c r="E25" t="n">
-        <v>48</v>
+        <v>49.2</v>
       </c>
       <c r="F25" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>12.3</v>
+        <v>12</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9514,10 +9514,10 @@
         </is>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -9526,23 +9526,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1594</v>
+        <v>1584</v>
       </c>
       <c r="D26" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E26" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F26" t="n">
-        <v>37.8</v>
+        <v>38.2</v>
       </c>
       <c r="G26" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="J26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>11</v>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="D27" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="E27" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="F27" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="G27" t="n">
-        <v>12.1</v>
+        <v>11.4</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="D28" t="n">
         <v>50.4</v>
@@ -9617,10 +9617,10 @@
         <v>49.6</v>
       </c>
       <c r="F28" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1579</v>
+        <v>1576</v>
       </c>
       <c r="D29" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="E29" t="n">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>40.2</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="D30" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="E30" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="F30" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
       </c>
       <c r="G30" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="D31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="E31" t="n">
         <v>50.3</v>
       </c>
-      <c r="E31" t="n">
-        <v>49.7</v>
-      </c>
       <c r="F31" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="G31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9760,17 +9760,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1427</v>
+        <v>1584</v>
       </c>
       <c r="D32" t="n">
-        <v>49.8</v>
+        <v>47.7</v>
       </c>
       <c r="E32" t="n">
-        <v>50.2</v>
+        <v>52.3</v>
       </c>
       <c r="F32" t="n">
         <v>43.2</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>22</v>
@@ -9799,23 +9799,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1577</v>
+        <v>1427</v>
       </c>
       <c r="D33" t="n">
-        <v>48.1</v>
+        <v>49.4</v>
       </c>
       <c r="E33" t="n">
-        <v>51.9</v>
+        <v>50.6</v>
       </c>
       <c r="F33" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="G33" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>23</v>
@@ -9838,17 +9838,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1587</v>
+        <v>1577</v>
       </c>
       <c r="D34" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="E34" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="F34" t="n">
         <v>43.6</v>
@@ -9877,23 +9877,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="D35" t="n">
-        <v>52.8</v>
+        <v>51.8</v>
       </c>
       <c r="E35" t="n">
-        <v>47.2</v>
+        <v>48.2</v>
       </c>
       <c r="F35" t="n">
-        <v>44.6</v>
+        <v>44.3</v>
       </c>
       <c r="G35" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9916,23 +9916,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1578</v>
+        <v>1564</v>
       </c>
       <c r="D36" t="n">
-        <v>51.8</v>
+        <v>52.8</v>
       </c>
       <c r="E36" t="n">
-        <v>48.2</v>
+        <v>47.2</v>
       </c>
       <c r="F36" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="G36" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1567</v>
+        <v>1564</v>
       </c>
       <c r="D37" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>47</v>
+        <v>47.8</v>
       </c>
       <c r="G37" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38">
@@ -10001,16 +10001,16 @@
         <v>1424</v>
       </c>
       <c r="D38" t="n">
-        <v>49.6</v>
+        <v>49.4</v>
       </c>
       <c r="E38" t="n">
-        <v>50.4</v>
+        <v>50.6</v>
       </c>
       <c r="F38" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="G38" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1588</v>
+        <v>1585</v>
       </c>
       <c r="D39" t="n">
-        <v>46.2</v>
+        <v>46</v>
       </c>
       <c r="E39" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="F39" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="G39" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10072,23 +10072,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1531</v>
+        <v>1540</v>
       </c>
       <c r="D40" t="n">
-        <v>49.7</v>
+        <v>51.4</v>
       </c>
       <c r="E40" t="n">
-        <v>50.3</v>
+        <v>48.6</v>
       </c>
       <c r="F40" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="G40" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>39</v>
@@ -10111,23 +10111,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1540</v>
+        <v>1526</v>
       </c>
       <c r="D41" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="E41" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="F41" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>40</v>
@@ -10150,17 +10150,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>410</v>
+        <v>1553</v>
       </c>
       <c r="D42" t="n">
-        <v>49</v>
+        <v>47.4</v>
       </c>
       <c r="E42" t="n">
-        <v>51</v>
+        <v>52.6</v>
       </c>
       <c r="F42" t="n">
         <v>53.2</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="J42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>42</v>
@@ -10189,23 +10189,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1576</v>
+        <v>409</v>
       </c>
       <c r="D43" t="n">
-        <v>51.4</v>
+        <v>49.4</v>
       </c>
       <c r="E43" t="n">
-        <v>48.6</v>
+        <v>50.6</v>
       </c>
       <c r="F43" t="n">
-        <v>53.9</v>
+        <v>53.5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10216,10 +10216,10 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -10228,23 +10228,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1554</v>
+        <v>1576</v>
       </c>
       <c r="D44" t="n">
-        <v>47.4</v>
+        <v>51.9</v>
       </c>
       <c r="E44" t="n">
-        <v>52.6</v>
+        <v>48.1</v>
       </c>
       <c r="F44" t="n">
-        <v>53.9</v>
+        <v>53.6</v>
       </c>
       <c r="G44" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="D45" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E45" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F45" t="n">
-        <v>55.9</v>
+        <v>54.7</v>
       </c>
       <c r="G45" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="46">
@@ -10306,23 +10306,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1545</v>
+        <v>1576</v>
       </c>
       <c r="D46" t="n">
-        <v>51.5</v>
+        <v>46.8</v>
       </c>
       <c r="E46" t="n">
-        <v>48.5</v>
+        <v>53.2</v>
       </c>
       <c r="F46" t="n">
-        <v>56.1</v>
+        <v>56.3</v>
       </c>
       <c r="G46" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10345,23 +10345,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1576</v>
+        <v>1541</v>
       </c>
       <c r="D47" t="n">
-        <v>46.4</v>
+        <v>51.7</v>
       </c>
       <c r="E47" t="n">
-        <v>53.6</v>
+        <v>48.3</v>
       </c>
       <c r="F47" t="n">
-        <v>57.2</v>
+        <v>56.3</v>
       </c>
       <c r="G47" t="n">
-        <v>7.2</v>
+        <v>6.3</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48">
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="D48" t="n">
         <v>49.2</v>
@@ -10397,10 +10397,10 @@
         <v>50.8</v>
       </c>
       <c r="F48" t="n">
-        <v>57.2</v>
+        <v>56.6</v>
       </c>
       <c r="G48" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="49">
@@ -10430,16 +10430,16 @@
         <v>1440</v>
       </c>
       <c r="D49" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="E49" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="F49" t="n">
-        <v>59.4</v>
+        <v>59</v>
       </c>
       <c r="G49" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10466,13 +10466,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="D50" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E50" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F50" t="n">
         <v>59.5</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51">
@@ -10508,10 +10508,10 @@
         <v>1564</v>
       </c>
       <c r="D51" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="E51" t="n">
-        <v>51</v>
+        <v>50.6</v>
       </c>
       <c r="F51" t="n">
         <v>60</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1556</v>
+        <v>1554</v>
       </c>
       <c r="D52" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
       <c r="E52" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="F52" t="n">
-        <v>61.1</v>
+        <v>60.6</v>
       </c>
       <c r="G52" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53">
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="D53" t="n">
-        <v>48.7</v>
+        <v>49.5</v>
       </c>
       <c r="E53" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="F53" t="n">
-        <v>65.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="G53" t="n">
-        <v>15.4</v>
+        <v>14.5</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="D54" t="n">
-        <v>47.9</v>
+        <v>48.3</v>
       </c>
       <c r="E54" t="n">
-        <v>52.1</v>
+        <v>51.7</v>
       </c>
       <c r="F54" t="n">
-        <v>66.09999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1583</v>
+        <v>1580</v>
       </c>
       <c r="D55" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="E55" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="F55" t="n">
-        <v>69.7</v>
+        <v>70</v>
       </c>
       <c r="G55" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="D56" t="n">
         <v>48.4</v>
@@ -10709,10 +10709,10 @@
         <v>51.6</v>
       </c>
       <c r="F56" t="n">
-        <v>74.7</v>
+        <v>74.8</v>
       </c>
       <c r="G56" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="D57" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E57" t="n">
         <v>49.9</v>
       </c>
-      <c r="E57" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F57" t="n">
-        <v>82.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="D58" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E58" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F58" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="G58" t="n">
-        <v>32.8</v>
+        <v>33</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,13 +10817,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="D59" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="E59" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="F59" t="n">
         <v>94.5</v>
@@ -10856,19 +10856,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="D60" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="E60" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="F60" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="G60" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
@@ -10895,7 +10895,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1459</v>
+        <v>1462</v>
       </c>
       <c r="D61" t="n">
         <v>51.3</v>
@@ -10904,10 +10904,10 @@
         <v>48.7</v>
       </c>
       <c r="F61" t="n">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="G61" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62">
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D62" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="E62" t="n">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="F62" t="n">
-        <v>59.1</v>
+        <v>59.4</v>
       </c>
       <c r="G62" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
@@ -10973,7 +10973,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D63" t="n">
         <v>47.3</v>
@@ -10982,10 +10982,10 @@
         <v>52.7</v>
       </c>
       <c r="F63" t="n">
-        <v>59.4</v>
+        <v>59.8</v>
       </c>
       <c r="G63" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64">
@@ -11015,16 +11015,16 @@
         <v>1429</v>
       </c>
       <c r="D64" t="n">
-        <v>49.2</v>
+        <v>48.7</v>
       </c>
       <c r="E64" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="F64" t="n">
-        <v>60.6</v>
+        <v>61.2</v>
       </c>
       <c r="G64" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65">
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>999</v>
+        <v>974</v>
       </c>
       <c r="D65" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
       <c r="E65" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="F65" t="n">
-        <v>60.9</v>
+        <v>61.9</v>
       </c>
       <c r="G65" t="n">
-        <v>10.9</v>
+        <v>11.9</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66">
@@ -11086,23 +11086,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>973</v>
+        <v>999</v>
       </c>
       <c r="D66" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E66" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F66" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G66" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67">
@@ -11125,23 +11125,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1553</v>
+        <v>1133</v>
       </c>
       <c r="D67" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="E67" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="F67" t="n">
-        <v>62.9</v>
+        <v>63.6</v>
       </c>
       <c r="G67" t="n">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1133</v>
+        <v>1551</v>
       </c>
       <c r="D68" t="n">
-        <v>49</v>
+        <v>49.5</v>
       </c>
       <c r="E68" t="n">
-        <v>51</v>
+        <v>50.5</v>
       </c>
       <c r="F68" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="G68" t="n">
-        <v>13.4</v>
+        <v>14</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -11207,7 +11207,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="D69" t="n">
         <v>48</v>
@@ -11216,10 +11216,10 @@
         <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>63.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70">
@@ -11246,19 +11246,19 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="D70" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E70" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="F70" t="n">
-        <v>63.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71">
@@ -11288,16 +11288,16 @@
         <v>1567</v>
       </c>
       <c r="D71" t="n">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="E71" t="n">
-        <v>51.6</v>
+        <v>51.3</v>
       </c>
       <c r="F71" t="n">
-        <v>63.9</v>
+        <v>64.8</v>
       </c>
       <c r="G71" t="n">
-        <v>13.9</v>
+        <v>14.8</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72">
@@ -11324,19 +11324,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1632</v>
+        <v>1629</v>
       </c>
       <c r="D72" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
       <c r="E72" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="F72" t="n">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D73" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E73" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="F73" t="n">
-        <v>66.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="G73" t="n">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="D74" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="E74" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="F74" t="n">
-        <v>53.7</v>
+        <v>53.2</v>
       </c>
       <c r="G74" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11437,23 +11437,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>578</v>
+        <v>1156</v>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="F75" t="n">
-        <v>54.8</v>
+        <v>53.5</v>
       </c>
       <c r="G75" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76">
@@ -11476,23 +11476,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>1155</v>
+        <v>579</v>
       </c>
       <c r="D76" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="E76" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="F76" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="G76" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77">
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>557</v>
+        <v>521</v>
       </c>
       <c r="D77" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="E77" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="F77" t="n">
-        <v>54.9</v>
+        <v>55.3</v>
       </c>
       <c r="G77" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78">
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="D78" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="E78" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="F78" t="n">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D79" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E79" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="F79" t="n">
-        <v>60.4</v>
+        <v>61.1</v>
       </c>
       <c r="G79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="D80" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="E80" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="F80" t="n">
-        <v>61</v>
+        <v>61.6</v>
       </c>
       <c r="G80" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1182</v>
+        <v>1187</v>
       </c>
       <c r="D81" t="n">
         <v>47.3</v>
@@ -11684,10 +11684,10 @@
         <v>52.7</v>
       </c>
       <c r="F81" t="n">
-        <v>63.4</v>
+        <v>63.6</v>
       </c>
       <c r="G81" t="n">
-        <v>13.4</v>
+        <v>13.6</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D82" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E82" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>48.2</v>
+        <v>47.4</v>
       </c>
       <c r="G82" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
@@ -11753,19 +11753,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D83" t="n">
-        <v>47.6</v>
+        <v>46.8</v>
       </c>
       <c r="E83" t="n">
-        <v>52.4</v>
+        <v>53.2</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3</v>
+        <v>48.8</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84">
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D84" t="n">
-        <v>46.8</v>
+        <v>46.9</v>
       </c>
       <c r="E84" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="F84" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11834,16 +11834,16 @@
         <v>433</v>
       </c>
       <c r="D85" t="n">
-        <v>47.8</v>
+        <v>48</v>
       </c>
       <c r="E85" t="n">
-        <v>52.2</v>
+        <v>52</v>
       </c>
       <c r="F85" t="n">
-        <v>55</v>
+        <v>56.1</v>
       </c>
       <c r="G85" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="86">
@@ -11866,23 +11866,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="D86" t="n">
-        <v>49.6</v>
+        <v>45.6</v>
       </c>
       <c r="E86" t="n">
-        <v>50.4</v>
+        <v>54.4</v>
       </c>
       <c r="F86" t="n">
-        <v>57.1</v>
+        <v>57.4</v>
       </c>
       <c r="G86" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87">
@@ -11905,23 +11905,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="D87" t="n">
-        <v>44.8</v>
+        <v>48.4</v>
       </c>
       <c r="E87" t="n">
-        <v>55.2</v>
+        <v>51.6</v>
       </c>
       <c r="F87" t="n">
-        <v>57.5</v>
+        <v>57.8</v>
       </c>
       <c r="G87" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88">
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D88" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="E88" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="F88" t="n">
-        <v>60.7</v>
+        <v>62</v>
       </c>
       <c r="G88" t="n">
-        <v>10.7</v>
+        <v>12</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89">
@@ -11987,19 +11987,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D89" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E89" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F89" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="G89" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90">
@@ -12022,23 +12022,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D90" t="n">
-        <v>49.3</v>
+        <v>51.4</v>
       </c>
       <c r="E90" t="n">
-        <v>50.7</v>
+        <v>48.6</v>
       </c>
       <c r="F90" t="n">
-        <v>63.5</v>
+        <v>64.3</v>
       </c>
       <c r="G90" t="n">
-        <v>13.5</v>
+        <v>14.3</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91">
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="D91" t="n">
-        <v>50.7</v>
+        <v>50.1</v>
       </c>
       <c r="E91" t="n">
-        <v>49.3</v>
+        <v>49.9</v>
       </c>
       <c r="F91" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="G91" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
@@ -12107,16 +12107,16 @@
         <v>431</v>
       </c>
       <c r="D92" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="E92" t="n">
         <v>49.7</v>
       </c>
-      <c r="E92" t="n">
-        <v>50.3</v>
-      </c>
       <c r="F92" t="n">
-        <v>64</v>
+        <v>65.2</v>
       </c>
       <c r="G92" t="n">
-        <v>14</v>
+        <v>15.2</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="D93" t="n">
-        <v>47.1</v>
+        <v>48.2</v>
       </c>
       <c r="E93" t="n">
-        <v>52.9</v>
+        <v>51.7</v>
       </c>
       <c r="F93" t="n">
-        <v>71.7</v>
+        <v>72</v>
       </c>
       <c r="G93" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12182,19 +12182,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D94" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="E94" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="F94" t="n">
-        <v>58.1</v>
+        <v>57.5</v>
       </c>
       <c r="G94" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="95">
@@ -12221,19 +12221,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="D95" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="E95" t="n">
-        <v>49.5</v>
+        <v>48.9</v>
       </c>
       <c r="F95" t="n">
-        <v>58.4</v>
+        <v>58.6</v>
       </c>
       <c r="G95" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1575</v>
+        <v>1413</v>
       </c>
       <c r="D96" t="n">
-        <v>48.2</v>
+        <v>49.8</v>
       </c>
       <c r="E96" t="n">
-        <v>51.8</v>
+        <v>50.2</v>
       </c>
       <c r="F96" t="n">
-        <v>59.7</v>
+        <v>58.9</v>
       </c>
       <c r="G96" t="n">
-        <v>9.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97">
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1415</v>
+        <v>1573</v>
       </c>
       <c r="D97" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="E97" t="n">
-        <v>50.3</v>
+        <v>51.8</v>
       </c>
       <c r="F97" t="n">
-        <v>59.9</v>
+        <v>59.4</v>
       </c>
       <c r="G97" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1594</v>
+        <v>1610</v>
       </c>
       <c r="D98" t="n">
-        <v>48.3</v>
+        <v>48.8</v>
       </c>
       <c r="E98" t="n">
-        <v>51.7</v>
+        <v>51.2</v>
       </c>
       <c r="F98" t="n">
-        <v>60.1</v>
+        <v>59.5</v>
       </c>
       <c r="G98" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99">
@@ -12373,23 +12373,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1587</v>
+        <v>1592</v>
       </c>
       <c r="D99" t="n">
-        <v>49.5</v>
+        <v>48.4</v>
       </c>
       <c r="E99" t="n">
-        <v>50.5</v>
+        <v>51.6</v>
       </c>
       <c r="F99" t="n">
-        <v>60.2</v>
+        <v>59.7</v>
       </c>
       <c r="G99" t="n">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="100">
@@ -12412,17 +12412,17 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1594</v>
+        <v>1587</v>
       </c>
       <c r="D100" t="n">
-        <v>48.8</v>
+        <v>49.5</v>
       </c>
       <c r="E100" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="F100" t="n">
         <v>60.2</v>
@@ -12455,19 +12455,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="D101" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="E101" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="F101" t="n">
-        <v>60.7</v>
+        <v>60.2</v>
       </c>
       <c r="G101" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="102">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1533</v>
+        <v>1530</v>
       </c>
       <c r="D102" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="E102" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
       <c r="F102" t="n">
-        <v>61.2</v>
+        <v>61.3</v>
       </c>
       <c r="G102" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1574</v>
+        <v>1571</v>
       </c>
       <c r="D103" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E103" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F103" t="n">
-        <v>61.5</v>
+        <v>61.4</v>
       </c>
       <c r="G103" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38307</v>
+        <v>38395</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12682,13 +12682,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38358</v>
+        <v>38444</v>
       </c>
       <c r="D3" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E3" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F3" t="n">
         <v>40.7</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38561</v>
+        <v>38649</v>
       </c>
       <c r="D4" t="n">
         <v>51.2</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37950</v>
+        <v>38036</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38417</v>
+        <v>38506</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>37938</v>
+        <v>38028</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37767</v>
+        <v>37854</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38219</v>
+        <v>38309</v>
       </c>
       <c r="D9" t="n">
         <v>50</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38506</v>
+        <v>38595</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38557</v>
+        <v>38648</v>
       </c>
       <c r="D11" t="n">
         <v>50.6</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38568</v>
+        <v>38657</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38393</v>
+        <v>38484</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38453</v>
+        <v>38544</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38437</v>
+        <v>38523</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38455</v>
+        <v>38543</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36633</v>
+        <v>36715</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38625</v>
+        <v>38715</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38161</v>
+        <v>38250</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34899</v>
+        <v>34979</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38695</v>
+        <v>38785</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38509</v>
+        <v>38599</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38559</v>
+        <v>38648</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38743</v>
+        <v>38832</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38754</v>
+        <v>38844</v>
       </c>
       <c r="D25" t="n">
         <v>49.2</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38697</v>
+        <v>38787</v>
       </c>
       <c r="D26" t="n">
         <v>49.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35068</v>
+        <v>35148</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13627,10 +13627,10 @@
         <v>50.1</v>
       </c>
       <c r="F27" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="G27" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38779</v>
+        <v>38869</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38787</v>
+        <v>38877</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38502</v>
+        <v>38591</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38539</v>
+        <v>38628</v>
       </c>
       <c r="D31" t="n">
         <v>49.2</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38536</v>
+        <v>38624</v>
       </c>
       <c r="D32" t="n">
         <v>49.4</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38562</v>
+        <v>38651</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13861,10 +13861,10 @@
         <v>50.5</v>
       </c>
       <c r="F33" t="n">
-        <v>44.9</v>
+        <v>44.8</v>
       </c>
       <c r="G33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38498</v>
+        <v>38588</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38501</v>
+        <v>38589</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>34953</v>
+        <v>35033</v>
       </c>
       <c r="D36" t="n">
         <v>49.9</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38337</v>
+        <v>38425</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14017,10 +14017,10 @@
         <v>48.3</v>
       </c>
       <c r="F37" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="G37" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37675</v>
+        <v>37762</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38495</v>
+        <v>38584</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14095,10 +14095,10 @@
         <v>52.8</v>
       </c>
       <c r="F39" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8133</v>
+        <v>8153</v>
       </c>
       <c r="D40" t="n">
         <v>51.2</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38174</v>
+        <v>38262</v>
       </c>
       <c r="D41" t="n">
         <v>50</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38234</v>
+        <v>38321</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38270</v>
+        <v>38360</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38197</v>
+        <v>38285</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37847</v>
+        <v>37932</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37996</v>
+        <v>38085</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14368,10 +14368,10 @@
         <v>49.9</v>
       </c>
       <c r="F46" t="n">
-        <v>54.7</v>
+        <v>54.6</v>
       </c>
       <c r="G46" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -14385,7 +14385,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47">
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38376</v>
+        <v>38466</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38418</v>
+        <v>38507</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35796</v>
+        <v>35878</v>
       </c>
       <c r="D49" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="E49" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="F49" t="n">
         <v>57.3</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38120</v>
+        <v>38208</v>
       </c>
       <c r="D50" t="n">
         <v>50.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38257</v>
+        <v>38346</v>
       </c>
       <c r="D51" t="n">
         <v>49.4</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38300</v>
+        <v>38389</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38172</v>
+        <v>38262</v>
       </c>
       <c r="D53" t="n">
         <v>49.6</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38210</v>
+        <v>38299</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38391</v>
+        <v>38480</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14719,10 +14719,10 @@
         <v>49.9</v>
       </c>
       <c r="F55" t="n">
-        <v>65.59999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="G55" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -14736,7 +14736,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56">
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38094</v>
+        <v>38181</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38455</v>
+        <v>38545</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38537</v>
+        <v>38627</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38739</v>
+        <v>38829</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35157</v>
+        <v>35243</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37126</v>
+        <v>37211</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37551</v>
+        <v>37638</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23440</v>
+        <v>23495</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23859</v>
+        <v>23912</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23883</v>
+        <v>23936</v>
       </c>
       <c r="D65" t="n">
         <v>51</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38442</v>
+        <v>38532</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -15174,17 +15174,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21266</v>
+        <v>38036</v>
       </c>
       <c r="D67" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="E67" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="F67" t="n">
         <v>56.1</v>
@@ -15213,23 +15213,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>37946</v>
+        <v>21322</v>
       </c>
       <c r="D68" t="n">
-        <v>50.5</v>
+        <v>51.8</v>
       </c>
       <c r="E68" t="n">
-        <v>49.5</v>
+        <v>48.2</v>
       </c>
       <c r="F68" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G68" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -15256,19 +15256,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36211</v>
+        <v>36297</v>
       </c>
       <c r="D69" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
-        <v>56.6</v>
+        <v>56.7</v>
       </c>
       <c r="G69" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30601</v>
+        <v>30675</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15304,10 +15304,10 @@
         <v>49.2</v>
       </c>
       <c r="F70" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="G70" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37643</v>
+        <v>37729</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33072</v>
+        <v>33151</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26081</v>
+        <v>26142</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15421,10 +15421,10 @@
         <v>49.9</v>
       </c>
       <c r="F73" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G73" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74">
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14236</v>
+        <v>14271</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15172</v>
+        <v>15207</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26684</v>
+        <v>26752</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,13 +15607,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>35929</v>
+        <v>36009</v>
       </c>
       <c r="D78" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E78" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F78" t="n">
         <v>65.59999999999999</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28676</v>
+        <v>28745</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15655,10 +15655,10 @@
         <v>50.7</v>
       </c>
       <c r="F79" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G79" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15798</v>
+        <v>15838</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27921</v>
+        <v>27994</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,13 +15763,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10445</v>
+        <v>10469</v>
       </c>
       <c r="D82" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E82" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F82" t="n">
         <v>51.9</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10448</v>
+        <v>10474</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10230</v>
+        <v>10254</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10745</v>
+        <v>10771</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15889,10 +15889,10 @@
         <v>49.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.8</v>
+        <v>54.9</v>
       </c>
       <c r="G85" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -15919,13 +15919,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10229</v>
+        <v>10255</v>
       </c>
       <c r="D86" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E86" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F86" t="n">
         <v>56</v>
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10700</v>
+        <v>10726</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -15967,10 +15967,10 @@
         <v>49.3</v>
       </c>
       <c r="F87" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="G87" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10806</v>
+        <v>10830</v>
       </c>
       <c r="D88" t="n">
         <v>51.5</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10944</v>
+        <v>10970</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10945</v>
+        <v>10970</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91">
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10870</v>
+        <v>10896</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10292</v>
+        <v>10316</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10221</v>
+        <v>10243</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -16231,13 +16231,13 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>37972</v>
+        <v>38062</v>
       </c>
       <c r="D94" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
         <v>53.7</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38582</v>
+        <v>38672</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36175</v>
+        <v>36257</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38698</v>
+        <v>38788</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16357,10 +16357,10 @@
         <v>49.7</v>
       </c>
       <c r="F97" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="G97" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37900</v>
+        <v>37986</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38489</v>
+        <v>38579</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38092</v>
+        <v>38182</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38350</v>
+        <v>38438</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,13 +16543,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38775</v>
+        <v>38865</v>
       </c>
       <c r="D102" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E102" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F102" t="n">
         <v>54.6</v>
@@ -16569,7 +16569,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38796</v>
+        <v>38904</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1579</v>
+        <v>1400</v>
       </c>
       <c r="D2" t="n">
-        <v>49.4</v>
+        <v>49.9</v>
       </c>
       <c r="E2" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="F2" t="n">
-        <v>50.7</v>
+        <v>49.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1580</v>
+        <v>1406</v>
       </c>
       <c r="D3" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="E3" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>50.8</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1566</v>
+        <v>1388</v>
       </c>
       <c r="D4" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="E4" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="F4" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1525</v>
+        <v>1400</v>
       </c>
       <c r="D5" t="n">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="E5" t="n">
-        <v>49.6</v>
+        <v>51.5</v>
       </c>
       <c r="F5" t="n">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHFJPY</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1587</v>
+        <v>1354</v>
       </c>
       <c r="D6" t="n">
-        <v>47.5</v>
+        <v>49.7</v>
       </c>
       <c r="E6" t="n">
-        <v>52.5</v>
+        <v>50.3</v>
       </c>
       <c r="F6" t="n">
-        <v>52.6</v>
+        <v>47.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1578</v>
+        <v>1397</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>45.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1560</v>
+        <v>1385</v>
       </c>
       <c r="D8" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
       <c r="E8" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="F8" t="n">
-        <v>53.9</v>
+        <v>54.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1586</v>
+        <v>1402</v>
       </c>
       <c r="D9" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="E9" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="F9" t="n">
-        <v>54.7</v>
+        <v>55.6</v>
       </c>
       <c r="G9" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1546</v>
+        <v>1372</v>
       </c>
       <c r="D10" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
       <c r="E10" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="F10" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
       <c r="G10" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1553</v>
+        <v>1377</v>
       </c>
       <c r="D11" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="E11" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="F11" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="G11" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1636</v>
+        <v>1469</v>
       </c>
       <c r="D12" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="E12" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="F12" t="n">
-        <v>41.6</v>
+        <v>41.9</v>
       </c>
       <c r="G12" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1661</v>
+        <v>1495</v>
       </c>
       <c r="D13" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="E13" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="F13" t="n">
         <v>40.7</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1642</v>
+        <v>1473</v>
       </c>
       <c r="D14" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
       <c r="E14" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="F14" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="G14" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -999,23 +999,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1640</v>
+        <v>1477</v>
       </c>
       <c r="D15" t="n">
-        <v>49.2</v>
+        <v>47.6</v>
       </c>
       <c r="E15" t="n">
-        <v>50.8</v>
+        <v>52.4</v>
       </c>
       <c r="F15" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G15" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1038,23 +1038,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1640</v>
+        <v>1476</v>
       </c>
       <c r="D16" t="n">
-        <v>47.4</v>
+        <v>49.3</v>
       </c>
       <c r="E16" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
       <c r="F16" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="G16" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -1077,23 +1077,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EURNOK</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1424</v>
+        <v>1366</v>
       </c>
       <c r="D17" t="n">
-        <v>49.4</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
-        <v>50.6</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>48.9</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -1116,23 +1116,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>EURNOK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1585</v>
+        <v>1266</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>49.4</v>
       </c>
       <c r="E18" t="n">
-        <v>54</v>
+        <v>50.6</v>
       </c>
       <c r="F18" t="n">
-        <v>51.5</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1540</v>
+        <v>341</v>
       </c>
       <c r="D19" t="n">
-        <v>51.4</v>
+        <v>49.6</v>
       </c>
       <c r="E19" t="n">
-        <v>48.6</v>
+        <v>50.4</v>
       </c>
       <c r="F19" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1526</v>
+        <v>1395</v>
       </c>
       <c r="D20" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="E20" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="F20" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>8</v>
@@ -1233,23 +1233,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1564</v>
+        <v>1402</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>45.4</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>54.6</v>
       </c>
       <c r="F21" t="n">
-        <v>47.8</v>
+        <v>51.9</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1553</v>
+        <v>1379</v>
       </c>
       <c r="D22" t="n">
-        <v>47.4</v>
+        <v>47.8</v>
       </c>
       <c r="E22" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="F22" t="n">
-        <v>53.2</v>
+        <v>52.3</v>
       </c>
       <c r="G22" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1311,23 +1311,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>409</v>
+        <v>1352</v>
       </c>
       <c r="D23" t="n">
-        <v>49.4</v>
+        <v>51.2</v>
       </c>
       <c r="E23" t="n">
-        <v>50.6</v>
+        <v>48.8</v>
       </c>
       <c r="F23" t="n">
-        <v>53.5</v>
+        <v>52.6</v>
       </c>
       <c r="G23" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -1350,23 +1350,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1576</v>
+        <v>1388</v>
       </c>
       <c r="D24" t="n">
-        <v>51.9</v>
+        <v>49.9</v>
       </c>
       <c r="E24" t="n">
-        <v>48.1</v>
+        <v>50.1</v>
       </c>
       <c r="F24" t="n">
-        <v>53.6</v>
+        <v>46.5</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1569</v>
+        <v>1400</v>
       </c>
       <c r="D25" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="E25" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="F25" t="n">
-        <v>54.7</v>
+        <v>53.8</v>
       </c>
       <c r="G25" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1564</v>
+        <v>1394</v>
       </c>
       <c r="D26" t="n">
-        <v>52.8</v>
+        <v>49.6</v>
       </c>
       <c r="E26" t="n">
-        <v>47.2</v>
+        <v>50.4</v>
       </c>
       <c r="F26" t="n">
-        <v>44.8</v>
+        <v>53.9</v>
       </c>
       <c r="G26" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1467,23 +1467,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1574</v>
+        <v>1384</v>
       </c>
       <c r="D27" t="n">
-        <v>51.8</v>
+        <v>52.5</v>
       </c>
       <c r="E27" t="n">
-        <v>48.2</v>
+        <v>47.5</v>
       </c>
       <c r="F27" t="n">
-        <v>44.3</v>
+        <v>45.6</v>
       </c>
       <c r="G27" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -1506,23 +1506,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1576</v>
+        <v>1392</v>
       </c>
       <c r="D28" t="n">
-        <v>46.8</v>
+        <v>51.6</v>
       </c>
       <c r="E28" t="n">
-        <v>53.2</v>
+        <v>48.4</v>
       </c>
       <c r="F28" t="n">
-        <v>56.3</v>
+        <v>44.8</v>
       </c>
       <c r="G28" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -1545,23 +1545,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1541</v>
+        <v>1399</v>
       </c>
       <c r="D29" t="n">
-        <v>51.7</v>
+        <v>47.7</v>
       </c>
       <c r="E29" t="n">
-        <v>48.3</v>
+        <v>52.3</v>
       </c>
       <c r="F29" t="n">
-        <v>56.3</v>
+        <v>55.5</v>
       </c>
       <c r="G29" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1577</v>
+        <v>1368</v>
       </c>
       <c r="D30" t="n">
-        <v>48.3</v>
+        <v>51.1</v>
       </c>
       <c r="E30" t="n">
-        <v>51.7</v>
+        <v>48.9</v>
       </c>
       <c r="F30" t="n">
-        <v>43.6</v>
+        <v>55.6</v>
       </c>
       <c r="G30" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1579</v>
+        <v>1402</v>
       </c>
       <c r="D31" t="n">
-        <v>49.2</v>
+        <v>47.9</v>
       </c>
       <c r="E31" t="n">
-        <v>50.8</v>
+        <v>52.1</v>
       </c>
       <c r="F31" t="n">
-        <v>56.6</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32">
@@ -1662,23 +1662,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1584</v>
+        <v>1396</v>
       </c>
       <c r="D32" t="n">
-        <v>47.7</v>
+        <v>48.6</v>
       </c>
       <c r="E32" t="n">
-        <v>52.3</v>
+        <v>51.4</v>
       </c>
       <c r="F32" t="n">
-        <v>43.2</v>
+        <v>43.9</v>
       </c>
       <c r="G32" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1427</v>
+        <v>1402</v>
       </c>
       <c r="D33" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E33" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F33" t="n">
         <v>43.2</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -1740,23 +1740,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1581</v>
+        <v>1268</v>
       </c>
       <c r="D34" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E34" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F34" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="G34" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="J34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1440</v>
+        <v>1282</v>
       </c>
       <c r="D35" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="E35" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="F35" t="n">
-        <v>59</v>
+        <v>57.8</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="36">
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1573</v>
+        <v>1394</v>
       </c>
       <c r="D36" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="E36" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="F36" t="n">
-        <v>40.9</v>
+        <v>41.4</v>
       </c>
       <c r="G36" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1560</v>
+        <v>1380</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F37" t="n">
-        <v>59.5</v>
+        <v>59.3</v>
       </c>
       <c r="G37" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1576</v>
+        <v>1399</v>
       </c>
       <c r="D38" t="n">
         <v>49</v>
@@ -1909,10 +1909,10 @@
         <v>51</v>
       </c>
       <c r="F38" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
       <c r="G38" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39">
@@ -1935,23 +1935,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUDCAD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1564</v>
+        <v>1388</v>
       </c>
       <c r="D39" t="n">
-        <v>49.4</v>
+        <v>50.1</v>
       </c>
       <c r="E39" t="n">
-        <v>50.6</v>
+        <v>49.9</v>
       </c>
       <c r="F39" t="n">
-        <v>60</v>
+        <v>59.4</v>
       </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1586</v>
+        <v>1404</v>
       </c>
       <c r="D40" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="E40" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="F40" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="G40" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41">
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1554</v>
+        <v>1390</v>
       </c>
       <c r="D41" t="n">
-        <v>50.5</v>
+        <v>48.6</v>
       </c>
       <c r="E41" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
       <c r="F41" t="n">
-        <v>60.6</v>
+        <v>60.4</v>
       </c>
       <c r="G41" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1577</v>
+        <v>1404</v>
       </c>
       <c r="D42" t="n">
-        <v>52.4</v>
+        <v>50.6</v>
       </c>
       <c r="E42" t="n">
-        <v>47.6</v>
+        <v>49.4</v>
       </c>
       <c r="F42" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="G42" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43">
@@ -2091,23 +2091,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1584</v>
+        <v>1398</v>
       </c>
       <c r="D43" t="n">
-        <v>51.2</v>
+        <v>52.4</v>
       </c>
       <c r="E43" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
       <c r="F43" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="G43" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44">
@@ -2134,13 +2134,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D44" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E44" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
         <v>38</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1422</v>
+        <v>1391</v>
       </c>
       <c r="D45" t="n">
-        <v>51.5</v>
+        <v>48</v>
       </c>
       <c r="E45" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="F45" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="G45" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1589</v>
+        <v>1264</v>
       </c>
       <c r="D46" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E46" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F46" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="G46" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1568</v>
+        <v>1500</v>
       </c>
       <c r="D47" t="n">
-        <v>48.2</v>
+        <v>51.1</v>
       </c>
       <c r="E47" t="n">
-        <v>51.8</v>
+        <v>48.9</v>
       </c>
       <c r="F47" t="n">
         <v>37.1</v>
@@ -2286,11 +2286,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1552</v>
+        <v>1407</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -2299,10 +2299,10 @@
         <v>50.1</v>
       </c>
       <c r="F48" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="G48" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
@@ -2329,19 +2329,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D49" t="n">
-        <v>51.6</v>
+        <v>52.1</v>
       </c>
       <c r="E49" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
       <c r="F49" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="G49" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1589</v>
+        <v>1387</v>
       </c>
       <c r="D50" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="E50" t="n">
-        <v>50.3</v>
+        <v>51.3</v>
       </c>
       <c r="F50" t="n">
-        <v>35.9</v>
+        <v>64.2</v>
       </c>
       <c r="G50" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="J50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>83</v>
@@ -2403,23 +2403,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1567</v>
+        <v>1386</v>
       </c>
       <c r="D51" t="n">
-        <v>49.5</v>
+        <v>48.3</v>
       </c>
       <c r="E51" t="n">
-        <v>50.5</v>
+        <v>51.7</v>
       </c>
       <c r="F51" t="n">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -2442,23 +2442,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1566</v>
+        <v>1375</v>
       </c>
       <c r="D52" t="n">
-        <v>48.3</v>
+        <v>50.2</v>
       </c>
       <c r="E52" t="n">
-        <v>51.7</v>
+        <v>49.8</v>
       </c>
       <c r="F52" t="n">
-        <v>65.40000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="G52" t="n">
-        <v>15.4</v>
+        <v>14.4</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53">
@@ -2485,13 +2485,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D53" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="E53" t="n">
-        <v>50</v>
+        <v>48.8</v>
       </c>
       <c r="F53" t="n">
         <v>32.3</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1475</v>
+        <v>1316</v>
       </c>
       <c r="D54" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="E54" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="F54" t="n">
-        <v>30.7</v>
+        <v>30.2</v>
       </c>
       <c r="G54" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2550,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1580</v>
+        <v>1398</v>
       </c>
       <c r="D55" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="E55" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="F55" t="n">
         <v>70</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1569</v>
+        <v>1390</v>
       </c>
       <c r="D56" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="E56" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="F56" t="n">
         <v>74.8</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1584</v>
+        <v>1404</v>
       </c>
       <c r="D57" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="E57" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="F57" t="n">
-        <v>82.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="G57" t="n">
-        <v>32.4</v>
+        <v>32</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1589</v>
+        <v>1408</v>
       </c>
       <c r="D58" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="E58" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="F58" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="G58" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1590</v>
+        <v>1408</v>
       </c>
       <c r="D59" t="n">
-        <v>48.8</v>
+        <v>49.6</v>
       </c>
       <c r="E59" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="F59" t="n">
-        <v>94.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>44.5</v>
+        <v>44.1</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>1462</v>
       </c>
       <c r="D60" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="E60" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="F60" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="G60" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1623</v>
+        <v>1302</v>
       </c>
       <c r="D61" t="n">
-        <v>50.4</v>
+        <v>52.2</v>
       </c>
       <c r="E61" t="n">
-        <v>49.6</v>
+        <v>47.8</v>
       </c>
       <c r="F61" t="n">
-        <v>40.9</v>
+        <v>40.1</v>
       </c>
       <c r="G61" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62">
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>988</v>
+        <v>875</v>
       </c>
       <c r="D62" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="E62" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
       <c r="F62" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="G62" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>971</v>
+        <v>857</v>
       </c>
       <c r="D63" t="n">
-        <v>47.3</v>
+        <v>46.6</v>
       </c>
       <c r="E63" t="n">
-        <v>52.7</v>
+        <v>53.4</v>
       </c>
       <c r="F63" t="n">
-        <v>59.8</v>
+        <v>60.7</v>
       </c>
       <c r="G63" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="64">
@@ -2910,23 +2910,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1429</v>
+        <v>860</v>
       </c>
       <c r="D64" t="n">
-        <v>48.7</v>
+        <v>50.7</v>
       </c>
       <c r="E64" t="n">
-        <v>51.3</v>
+        <v>49.3</v>
       </c>
       <c r="F64" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
       <c r="G64" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>974</v>
+        <v>1255</v>
       </c>
       <c r="D65" t="n">
-        <v>51.5</v>
+        <v>48.3</v>
       </c>
       <c r="E65" t="n">
-        <v>48.5</v>
+        <v>51.7</v>
       </c>
       <c r="F65" t="n">
-        <v>61.9</v>
+        <v>62.2</v>
       </c>
       <c r="G65" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66">
@@ -2992,19 +2992,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>999</v>
+        <v>887</v>
       </c>
       <c r="D66" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
-        <v>62</v>
+        <v>62.8</v>
       </c>
       <c r="G66" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="67">
@@ -3031,19 +3031,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1133</v>
+        <v>1006</v>
       </c>
       <c r="D67" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E67" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F67" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
       <c r="G67" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68">
@@ -3066,17 +3066,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1551</v>
+        <v>1202</v>
       </c>
       <c r="D68" t="n">
-        <v>49.5</v>
+        <v>47.2</v>
       </c>
       <c r="E68" t="n">
-        <v>50.5</v>
+        <v>52.8</v>
       </c>
       <c r="F68" t="n">
         <v>64</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1355</v>
+        <v>1374</v>
       </c>
       <c r="D69" t="n">
-        <v>48</v>
+        <v>49.7</v>
       </c>
       <c r="E69" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="F69" t="n">
-        <v>64.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1583</v>
+        <v>1461</v>
       </c>
       <c r="D70" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="E70" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="F70" t="n">
         <v>64.40000000000001</v>
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1567</v>
+        <v>1402</v>
       </c>
       <c r="D71" t="n">
-        <v>48.7</v>
+        <v>51.9</v>
       </c>
       <c r="E71" t="n">
-        <v>51.3</v>
+        <v>48.1</v>
       </c>
       <c r="F71" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1629</v>
+        <v>1386</v>
       </c>
       <c r="D72" t="n">
-        <v>50.6</v>
+        <v>48.8</v>
       </c>
       <c r="E72" t="n">
-        <v>49.4</v>
+        <v>51.2</v>
       </c>
       <c r="F72" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1363</v>
+        <v>1204</v>
       </c>
       <c r="D73" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="E73" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="G73" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>600</v>
+        <v>526</v>
       </c>
       <c r="D74" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E74" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="F74" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="G74" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1156</v>
+        <v>1022</v>
       </c>
       <c r="D75" t="n">
-        <v>50.4</v>
+        <v>49.3</v>
       </c>
       <c r="E75" t="n">
-        <v>49.6</v>
+        <v>50.7</v>
       </c>
       <c r="F75" t="n">
-        <v>53.5</v>
+        <v>53.3</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
@@ -3378,23 +3378,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>579</v>
+        <v>446</v>
       </c>
       <c r="D76" t="n">
-        <v>50.3</v>
+        <v>51.8</v>
       </c>
       <c r="E76" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="F76" t="n">
-        <v>54.9</v>
+        <v>54.3</v>
       </c>
       <c r="G76" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -3417,23 +3417,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="D77" t="n">
-        <v>52</v>
+        <v>48.6</v>
       </c>
       <c r="E77" t="n">
-        <v>48</v>
+        <v>51.4</v>
       </c>
       <c r="F77" t="n">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
       <c r="G77" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1484</v>
+        <v>1310</v>
       </c>
       <c r="D78" t="n">
-        <v>49.2</v>
+        <v>50.9</v>
       </c>
       <c r="E78" t="n">
-        <v>50.8</v>
+        <v>49.1</v>
       </c>
       <c r="F78" t="n">
-        <v>70.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="G78" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
@@ -3495,23 +3495,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UKGILT.F</t>
+          <t>EUBUND.F</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>586</v>
+        <v>1091</v>
       </c>
       <c r="D79" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="E79" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="F79" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80">
@@ -3534,23 +3534,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EUBUND.F</t>
+          <t>UKGILT.F</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1217</v>
+        <v>553</v>
       </c>
       <c r="D80" t="n">
-        <v>46.6</v>
+        <v>49.5</v>
       </c>
       <c r="E80" t="n">
-        <v>53.4</v>
+        <v>50.5</v>
       </c>
       <c r="F80" t="n">
-        <v>61.6</v>
+        <v>62.2</v>
       </c>
       <c r="G80" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1187</v>
+        <v>1087</v>
       </c>
       <c r="D81" t="n">
-        <v>47.3</v>
+        <v>46.7</v>
       </c>
       <c r="E81" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
       <c r="F81" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="G81" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="D82" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="E82" t="n">
-        <v>53.1</v>
+        <v>52.7</v>
       </c>
       <c r="F82" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="G82" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="D83" t="n">
         <v>46.8</v>
@@ -3664,10 +3664,10 @@
         <v>53.2</v>
       </c>
       <c r="F83" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="G83" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="D84" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="E84" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
       <c r="F84" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="G84" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="D85" t="n">
-        <v>48</v>
+        <v>49.7</v>
       </c>
       <c r="E85" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="F85" t="n">
-        <v>56.1</v>
+        <v>56.8</v>
       </c>
       <c r="G85" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86">
@@ -3772,19 +3772,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="D86" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
       <c r="E86" t="n">
-        <v>54.4</v>
+        <v>54.9</v>
       </c>
       <c r="F86" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="G86" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="87">
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="D87" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="E87" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="F87" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="G87" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="D88" t="n">
-        <v>49.8</v>
+        <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>50.2</v>
+        <v>52</v>
       </c>
       <c r="F88" t="n">
-        <v>62</v>
+        <v>62.4</v>
       </c>
       <c r="G88" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89">
@@ -3889,19 +3889,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="D89" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="E89" t="n">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
       <c r="F89" t="n">
-        <v>62.9</v>
+        <v>63.9</v>
       </c>
       <c r="G89" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="90">
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>442</v>
+        <v>390</v>
       </c>
       <c r="D90" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E90" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F90" t="n">
-        <v>64.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="91">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="D91" t="n">
-        <v>50.1</v>
+        <v>48.7</v>
       </c>
       <c r="E91" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="F91" t="n">
-        <v>64.3</v>
+        <v>65.3</v>
       </c>
       <c r="G91" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="92">
@@ -4006,19 +4006,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>431</v>
+        <v>381</v>
       </c>
       <c r="D92" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
       <c r="E92" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="F92" t="n">
-        <v>65.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
@@ -4045,13 +4045,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="D93" t="n">
-        <v>48.2</v>
+        <v>47.6</v>
       </c>
       <c r="E93" t="n">
-        <v>51.7</v>
+        <v>52.4</v>
       </c>
       <c r="F93" t="n">
         <v>72</v>
@@ -4084,19 +4084,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1591</v>
+        <v>1409</v>
       </c>
       <c r="D94" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="E94" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="F94" t="n">
-        <v>57.5</v>
+        <v>56.8</v>
       </c>
       <c r="G94" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="95">
@@ -4119,23 +4119,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1545</v>
+        <v>1258</v>
       </c>
       <c r="D95" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="E95" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="F95" t="n">
-        <v>58.6</v>
+        <v>57.1</v>
       </c>
       <c r="G95" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1413</v>
+        <v>1371</v>
       </c>
       <c r="D96" t="n">
-        <v>49.8</v>
+        <v>52.4</v>
       </c>
       <c r="E96" t="n">
-        <v>50.2</v>
+        <v>47.6</v>
       </c>
       <c r="F96" t="n">
-        <v>58.9</v>
+        <v>57.8</v>
       </c>
       <c r="G96" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="97">
@@ -4201,19 +4201,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1573</v>
+        <v>1391</v>
       </c>
       <c r="D97" t="n">
-        <v>48.2</v>
+        <v>48.9</v>
       </c>
       <c r="E97" t="n">
-        <v>51.8</v>
+        <v>51.1</v>
       </c>
       <c r="F97" t="n">
-        <v>59.4</v>
+        <v>58.2</v>
       </c>
       <c r="G97" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1610</v>
+        <v>1410</v>
       </c>
       <c r="D98" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="E98" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="F98" t="n">
-        <v>59.5</v>
+        <v>58.9</v>
       </c>
       <c r="G98" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="99">
@@ -4275,23 +4275,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D99" t="n">
-        <v>48.4</v>
+        <v>49.6</v>
       </c>
       <c r="E99" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="F99" t="n">
-        <v>59.7</v>
+        <v>59.1</v>
       </c>
       <c r="G99" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100">
@@ -4314,23 +4314,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1587</v>
+        <v>1410</v>
       </c>
       <c r="D100" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="E100" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="F100" t="n">
-        <v>60.2</v>
+        <v>59.4</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="101">
@@ -4353,23 +4353,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1591</v>
+        <v>1406</v>
       </c>
       <c r="D101" t="n">
-        <v>48.7</v>
+        <v>50.9</v>
       </c>
       <c r="E101" t="n">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
       <c r="F101" t="n">
-        <v>60.2</v>
+        <v>59.6</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102">
@@ -4392,23 +4392,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1530</v>
+        <v>1390</v>
       </c>
       <c r="D102" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E102" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F102" t="n">
-        <v>61.3</v>
+        <v>60.2</v>
       </c>
       <c r="G102" t="n">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="103">
@@ -4431,23 +4431,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1571</v>
+        <v>1360</v>
       </c>
       <c r="D103" t="n">
+        <v>51</v>
+      </c>
+      <c r="E103" t="n">
         <v>49</v>
       </c>
-      <c r="E103" t="n">
-        <v>51</v>
-      </c>
       <c r="F103" t="n">
-        <v>61.4</v>
+        <v>61</v>
       </c>
       <c r="G103" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38309</v>
+        <v>38390</v>
       </c>
       <c r="D2" t="n">
         <v>50</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37854</v>
+        <v>37930</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38028</v>
+        <v>38107</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38595</v>
+        <v>38676</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4688,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38648</v>
+        <v>38729</v>
       </c>
       <c r="D6" t="n">
         <v>50.6</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38506</v>
+        <v>38587</v>
       </c>
       <c r="D7" t="n">
         <v>50.7</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38657</v>
+        <v>38737</v>
       </c>
       <c r="D8" t="n">
         <v>51.4</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38036</v>
+        <v>38114</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4827,10 +4827,10 @@
         <v>50.3</v>
       </c>
       <c r="F9" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38484</v>
+        <v>38560</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38544</v>
+        <v>38622</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38649</v>
+        <v>38740</v>
       </c>
       <c r="D12" t="n">
         <v>51.2</v>
@@ -4944,10 +4944,10 @@
         <v>48.8</v>
       </c>
       <c r="F12" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="G12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -4961,7 +4961,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13">
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38444</v>
+        <v>38534</v>
       </c>
       <c r="D13" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E13" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F13" t="n">
         <v>40.7</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38395</v>
+        <v>38484</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38523</v>
+        <v>38613</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38543</v>
+        <v>38633</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38584</v>
+        <v>38664</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8153</v>
+        <v>8170</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38262</v>
+        <v>38342</v>
       </c>
       <c r="D19" t="n">
         <v>50</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37762</v>
+        <v>37842</v>
       </c>
       <c r="D20" t="n">
         <v>50.7</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38425</v>
+        <v>38506</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5295,10 +5295,10 @@
         <v>48.3</v>
       </c>
       <c r="F21" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -5312,7 +5312,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35033</v>
+        <v>35113</v>
       </c>
       <c r="D22" t="n">
         <v>49.9</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38589</v>
+        <v>38669</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38321</v>
+        <v>38402</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5412,10 +5412,10 @@
         <v>50.2</v>
       </c>
       <c r="F24" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="G24" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38360</v>
+        <v>38441</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38588</v>
+        <v>38668</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38285</v>
+        <v>38365</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>37932</v>
+        <v>38012</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38085</v>
+        <v>38165</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38466</v>
+        <v>38546</v>
       </c>
       <c r="D30" t="n">
         <v>50.6</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38651</v>
+        <v>38732</v>
       </c>
       <c r="D31" t="n">
         <v>49.5</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38507</v>
+        <v>38585</v>
       </c>
       <c r="D32" t="n">
         <v>51.1</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38624</v>
+        <v>38704</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5763,10 +5763,10 @@
         <v>50.6</v>
       </c>
       <c r="F33" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="G33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38628</v>
+        <v>38709</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38591</v>
+        <v>38672</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38877</v>
+        <v>38958</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38869</v>
+        <v>38950</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35878</v>
+        <v>35952</v>
       </c>
       <c r="D38" t="n">
         <v>50.4</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35148</v>
+        <v>35228</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -5997,10 +5997,10 @@
         <v>50.1</v>
       </c>
       <c r="F39" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="G39" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -6014,7 +6014,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38208</v>
+        <v>38289</v>
       </c>
       <c r="D40" t="n">
         <v>50.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38346</v>
+        <v>38427</v>
       </c>
       <c r="D41" t="n">
         <v>49.4</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38389</v>
+        <v>38469</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38787</v>
+        <v>38868</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38844</v>
+        <v>38925</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6192,10 +6192,10 @@
         <v>50.8</v>
       </c>
       <c r="F44" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="G44" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38832</v>
+        <v>39005</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6231,10 +6231,10 @@
         <v>50.5</v>
       </c>
       <c r="F45" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="G45" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38648</v>
+        <v>38729</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38599</v>
+        <v>38680</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38785</v>
+        <v>38866</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>34979</v>
+        <v>35058</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38262</v>
+        <v>38341</v>
       </c>
       <c r="D50" t="n">
         <v>49.6</v>
@@ -6452,23 +6452,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38250</v>
+        <v>38379</v>
       </c>
       <c r="D51" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>38</v>
+        <v>62.1</v>
       </c>
       <c r="G51" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>92</v>
@@ -6491,20 +6491,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38299</v>
+        <v>38330</v>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F52" t="n">
-        <v>62.1</v>
+        <v>37.9</v>
       </c>
       <c r="G52" t="n">
         <v>12.1</v>
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>93</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38715</v>
+        <v>38796</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36715</v>
+        <v>36793</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38480</v>
+        <v>38561</v>
       </c>
       <c r="D55" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E55" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F55" t="n">
         <v>65.7</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38181</v>
+        <v>38261</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38545</v>
+        <v>38626</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38627</v>
+        <v>38708</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38829</v>
+        <v>38910</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37211</v>
+        <v>37301</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35243</v>
+        <v>35323</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37638</v>
+        <v>37718</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23495</v>
+        <v>23547</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23912</v>
+        <v>23965</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,13 +7002,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23936</v>
+        <v>23988</v>
       </c>
       <c r="D65" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E65" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F65" t="n">
         <v>56</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38532</v>
+        <v>38613</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38036</v>
+        <v>38117</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21322</v>
+        <v>21378</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36297</v>
+        <v>36378</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30675</v>
+        <v>30752</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37729</v>
+        <v>37820</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33151</v>
+        <v>33222</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26142</v>
+        <v>26205</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7323,10 +7323,10 @@
         <v>49.9</v>
       </c>
       <c r="F73" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="G73" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14271</v>
+        <v>14306</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14080</v>
+        <v>14110</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15207</v>
+        <v>15244</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -7440,10 +7440,10 @@
         <v>49.5</v>
       </c>
       <c r="F76" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26752</v>
+        <v>26817</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36009</v>
+        <v>36081</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7518,10 +7518,10 @@
         <v>49.4</v>
       </c>
       <c r="F78" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G78" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28745</v>
+        <v>28813</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15838</v>
+        <v>15874</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7596,10 +7596,10 @@
         <v>50.3</v>
       </c>
       <c r="F80" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G80" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="81">
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27994</v>
+        <v>28060</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7665,13 +7665,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10469</v>
+        <v>10494</v>
       </c>
       <c r="D82" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E82" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F82" t="n">
         <v>51.9</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10474</v>
+        <v>10499</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10254</v>
+        <v>10277</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10771</v>
+        <v>10796</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7821,13 +7821,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10255</v>
+        <v>10281</v>
       </c>
       <c r="D86" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E86" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F86" t="n">
         <v>56</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10726</v>
+        <v>10752</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10830</v>
+        <v>10856</v>
       </c>
       <c r="D88" t="n">
         <v>51.5</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10970</v>
+        <v>10996</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10970</v>
+        <v>10996</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10896</v>
+        <v>10922</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="92">
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10316</v>
+        <v>10338</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10243</v>
+        <v>10266</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38062</v>
+        <v>38141</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38672</v>
+        <v>38753</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36257</v>
+        <v>36334</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38788</v>
+        <v>38869</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37986</v>
+        <v>38065</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38579</v>
+        <v>38658</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38182</v>
+        <v>38263</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38438</v>
+        <v>38517</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,13 +8445,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38865</v>
+        <v>38946</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F102" t="n">
         <v>54.6</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38904</v>
+        <v>38967</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1642</v>
+        <v>1473</v>
       </c>
       <c r="D2" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
       <c r="E2" t="n">
-        <v>48.2</v>
+        <v>48.6</v>
       </c>
       <c r="F2" t="n">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="G2" t="n">
-        <v>11.9</v>
+        <v>11.4</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1661</v>
+        <v>1495</v>
       </c>
       <c r="D3" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="E3" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="F3" t="n">
         <v>40.7</v>
@@ -8659,7 +8659,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1636</v>
+        <v>1469</v>
       </c>
       <c r="D4" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="E4" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="F4" t="n">
-        <v>41.6</v>
+        <v>41.9</v>
       </c>
       <c r="G4" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1553</v>
+        <v>1377</v>
       </c>
       <c r="D5" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="E5" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="F5" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8737,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1546</v>
+        <v>1372</v>
       </c>
       <c r="D6" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
       <c r="E6" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="F6" t="n">
-        <v>44.1</v>
+        <v>43.5</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1578</v>
+        <v>1397</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="E7" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>45.7</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8828,19 +8828,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1525</v>
+        <v>1354</v>
       </c>
       <c r="D8" t="n">
-        <v>50.4</v>
+        <v>49.7</v>
       </c>
       <c r="E8" t="n">
-        <v>49.6</v>
+        <v>50.3</v>
       </c>
       <c r="F8" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8863,23 +8863,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1566</v>
+        <v>1400</v>
       </c>
       <c r="D9" t="n">
-        <v>50.4</v>
+        <v>48.5</v>
       </c>
       <c r="E9" t="n">
-        <v>49.6</v>
+        <v>51.5</v>
       </c>
       <c r="F9" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8902,23 +8902,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1580</v>
+        <v>1388</v>
       </c>
       <c r="D10" t="n">
-        <v>48.7</v>
+        <v>50.9</v>
       </c>
       <c r="E10" t="n">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
       <c r="F10" t="n">
-        <v>49</v>
+        <v>47.9</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1579</v>
+        <v>1400</v>
       </c>
       <c r="D11" t="n">
-        <v>49.4</v>
+        <v>49.9</v>
       </c>
       <c r="E11" t="n">
-        <v>50.6</v>
+        <v>50.1</v>
       </c>
       <c r="F11" t="n">
-        <v>50.7</v>
+        <v>49.6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1587</v>
+        <v>1406</v>
       </c>
       <c r="D12" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="E12" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="F12" t="n">
-        <v>52.6</v>
+        <v>50.8</v>
       </c>
       <c r="G12" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1560</v>
+        <v>1385</v>
       </c>
       <c r="D13" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
       <c r="E13" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="F13" t="n">
-        <v>53.9</v>
+        <v>54.9</v>
       </c>
       <c r="G13" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1586</v>
+        <v>1402</v>
       </c>
       <c r="D14" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="E14" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="F14" t="n">
-        <v>54.7</v>
+        <v>55.6</v>
       </c>
       <c r="G14" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15">
@@ -9097,23 +9097,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1640</v>
+        <v>1477</v>
       </c>
       <c r="D15" t="n">
-        <v>49.2</v>
+        <v>47.6</v>
       </c>
       <c r="E15" t="n">
-        <v>50.8</v>
+        <v>52.4</v>
       </c>
       <c r="F15" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G15" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -9136,23 +9136,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1640</v>
+        <v>1476</v>
       </c>
       <c r="D16" t="n">
-        <v>47.4</v>
+        <v>49.3</v>
       </c>
       <c r="E16" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
       <c r="F16" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="G16" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1475</v>
+        <v>1316</v>
       </c>
       <c r="D17" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="E17" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="F17" t="n">
-        <v>30.7</v>
+        <v>30.2</v>
       </c>
       <c r="G17" t="n">
-        <v>19.3</v>
+        <v>19.8</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,13 +9218,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>51.2</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>48.8</v>
       </c>
       <c r="F18" t="n">
         <v>32.3</v>
@@ -9253,23 +9253,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1589</v>
+        <v>1375</v>
       </c>
       <c r="D19" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="E19" t="n">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="F19" t="n">
-        <v>35.9</v>
+        <v>35.6</v>
       </c>
       <c r="G19" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D20" t="n">
-        <v>51.6</v>
+        <v>52.1</v>
       </c>
       <c r="E20" t="n">
-        <v>48.4</v>
+        <v>47.9</v>
       </c>
       <c r="F20" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9331,11 +9331,11 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1552</v>
+        <v>1407</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -9344,10 +9344,10 @@
         <v>50.1</v>
       </c>
       <c r="F21" t="n">
-        <v>36.4</v>
+        <v>36.7</v>
       </c>
       <c r="G21" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9370,17 +9370,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1568</v>
+        <v>1500</v>
       </c>
       <c r="D22" t="n">
-        <v>48.2</v>
+        <v>51.1</v>
       </c>
       <c r="E22" t="n">
-        <v>51.8</v>
+        <v>48.9</v>
       </c>
       <c r="F22" t="n">
         <v>37.1</v>
@@ -9409,23 +9409,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1589</v>
+        <v>1264</v>
       </c>
       <c r="D23" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E23" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F23" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="G23" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9448,23 +9448,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1422</v>
+        <v>1391</v>
       </c>
       <c r="D24" t="n">
-        <v>51.5</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="G24" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9491,13 +9491,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D25" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E25" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
         <v>38</v>
@@ -9526,23 +9526,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1584</v>
+        <v>1398</v>
       </c>
       <c r="D26" t="n">
-        <v>51.2</v>
+        <v>52.4</v>
       </c>
       <c r="E26" t="n">
-        <v>48.8</v>
+        <v>47.6</v>
       </c>
       <c r="F26" t="n">
-        <v>38.2</v>
+        <v>38.4</v>
       </c>
       <c r="G26" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9556,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -9565,23 +9565,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1577</v>
+        <v>1404</v>
       </c>
       <c r="D27" t="n">
-        <v>52.4</v>
+        <v>50.6</v>
       </c>
       <c r="E27" t="n">
-        <v>47.6</v>
+        <v>49.4</v>
       </c>
       <c r="F27" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="G27" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1586</v>
+        <v>1404</v>
       </c>
       <c r="D28" t="n">
-        <v>50.4</v>
+        <v>50.9</v>
       </c>
       <c r="E28" t="n">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="F28" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="G28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,7 +9647,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1576</v>
+        <v>1399</v>
       </c>
       <c r="D29" t="n">
         <v>49</v>
@@ -9656,10 +9656,10 @@
         <v>51</v>
       </c>
       <c r="F29" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
       <c r="G29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9673,7 +9673,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1573</v>
+        <v>1394</v>
       </c>
       <c r="D30" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="E30" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="F30" t="n">
-        <v>40.9</v>
+        <v>41.4</v>
       </c>
       <c r="G30" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9712,7 +9712,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -9721,23 +9721,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1581</v>
+        <v>1268</v>
       </c>
       <c r="D31" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E31" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F31" t="n">
-        <v>42.2</v>
+        <v>43.1</v>
       </c>
       <c r="G31" t="n">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="J31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32">
@@ -9760,17 +9760,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1584</v>
+        <v>1402</v>
       </c>
       <c r="D32" t="n">
-        <v>47.7</v>
+        <v>49.3</v>
       </c>
       <c r="E32" t="n">
-        <v>52.3</v>
+        <v>50.7</v>
       </c>
       <c r="F32" t="n">
         <v>43.2</v>
@@ -9799,23 +9799,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1427</v>
+        <v>1396</v>
       </c>
       <c r="D33" t="n">
-        <v>49.4</v>
+        <v>48.6</v>
       </c>
       <c r="E33" t="n">
-        <v>50.6</v>
+        <v>51.4</v>
       </c>
       <c r="F33" t="n">
-        <v>43.2</v>
+        <v>43.9</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -9838,23 +9838,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1577</v>
+        <v>1402</v>
       </c>
       <c r="D34" t="n">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
       <c r="E34" t="n">
-        <v>51.7</v>
+        <v>52.1</v>
       </c>
       <c r="F34" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="G34" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1574</v>
+        <v>1392</v>
       </c>
       <c r="D35" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="E35" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="F35" t="n">
-        <v>44.3</v>
+        <v>44.8</v>
       </c>
       <c r="G35" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1564</v>
+        <v>1384</v>
       </c>
       <c r="D36" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
       <c r="E36" t="n">
-        <v>47.2</v>
+        <v>47.5</v>
       </c>
       <c r="F36" t="n">
-        <v>44.8</v>
+        <v>45.6</v>
       </c>
       <c r="G36" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1564</v>
+        <v>1388</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F37" t="n">
-        <v>47.8</v>
+        <v>46.5</v>
       </c>
       <c r="G37" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9985,7 +9985,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1424</v>
+        <v>1266</v>
       </c>
       <c r="D38" t="n">
         <v>49.4</v>
@@ -10007,10 +10007,10 @@
         <v>50.6</v>
       </c>
       <c r="F38" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="G38" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10033,23 +10033,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1585</v>
+        <v>1366</v>
       </c>
       <c r="D39" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E39" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="G39" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -10072,23 +10072,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1540</v>
+        <v>341</v>
       </c>
       <c r="D40" t="n">
-        <v>51.4</v>
+        <v>49.6</v>
       </c>
       <c r="E40" t="n">
-        <v>48.6</v>
+        <v>50.4</v>
       </c>
       <c r="F40" t="n">
-        <v>51.8</v>
+        <v>51.3</v>
       </c>
       <c r="G40" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41">
@@ -10111,23 +10111,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1526</v>
+        <v>1395</v>
       </c>
       <c r="D41" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="E41" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="F41" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10138,10 +10138,10 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -10150,23 +10150,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1553</v>
+        <v>1402</v>
       </c>
       <c r="D42" t="n">
-        <v>47.4</v>
+        <v>45.4</v>
       </c>
       <c r="E42" t="n">
-        <v>52.6</v>
+        <v>54.6</v>
       </c>
       <c r="F42" t="n">
-        <v>53.2</v>
+        <v>51.9</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="J42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>42</v>
@@ -10189,23 +10189,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>409</v>
+        <v>1379</v>
       </c>
       <c r="D43" t="n">
-        <v>49.4</v>
+        <v>47.8</v>
       </c>
       <c r="E43" t="n">
-        <v>50.6</v>
+        <v>52.2</v>
       </c>
       <c r="F43" t="n">
-        <v>53.5</v>
+        <v>52.3</v>
       </c>
       <c r="G43" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10216,10 +10216,10 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44">
@@ -10228,23 +10228,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1576</v>
+        <v>1352</v>
       </c>
       <c r="D44" t="n">
-        <v>51.9</v>
+        <v>51.2</v>
       </c>
       <c r="E44" t="n">
-        <v>48.1</v>
+        <v>48.8</v>
       </c>
       <c r="F44" t="n">
-        <v>53.6</v>
+        <v>52.6</v>
       </c>
       <c r="G44" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10255,10 +10255,10 @@
         </is>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -10267,23 +10267,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1569</v>
+        <v>1400</v>
       </c>
       <c r="D45" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="E45" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="F45" t="n">
-        <v>54.7</v>
+        <v>53.8</v>
       </c>
       <c r="G45" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
@@ -10306,23 +10306,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1576</v>
+        <v>1394</v>
       </c>
       <c r="D46" t="n">
-        <v>46.8</v>
+        <v>49.6</v>
       </c>
       <c r="E46" t="n">
-        <v>53.2</v>
+        <v>50.4</v>
       </c>
       <c r="F46" t="n">
-        <v>56.3</v>
+        <v>53.9</v>
       </c>
       <c r="G46" t="n">
-        <v>6.3</v>
+        <v>3.9</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
@@ -10345,23 +10345,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1541</v>
+        <v>1399</v>
       </c>
       <c r="D47" t="n">
-        <v>51.7</v>
+        <v>47.7</v>
       </c>
       <c r="E47" t="n">
-        <v>48.3</v>
+        <v>52.3</v>
       </c>
       <c r="F47" t="n">
-        <v>56.3</v>
+        <v>55.5</v>
       </c>
       <c r="G47" t="n">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48">
@@ -10384,23 +10384,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1579</v>
+        <v>1368</v>
       </c>
       <c r="D48" t="n">
-        <v>49.2</v>
+        <v>51.1</v>
       </c>
       <c r="E48" t="n">
-        <v>50.8</v>
+        <v>48.9</v>
       </c>
       <c r="F48" t="n">
-        <v>56.6</v>
+        <v>55.6</v>
       </c>
       <c r="G48" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49">
@@ -10427,33 +10427,33 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1440</v>
+        <v>1282</v>
       </c>
       <c r="D49" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="E49" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="F49" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="G49" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Forex Minor</t>
+        </is>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>59</v>
-      </c>
-      <c r="G49" t="n">
-        <v>9</v>
-      </c>
-      <c r="H49" t="b">
-        <v>1</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Forex Minor</t>
-        </is>
-      </c>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="50">
@@ -10462,23 +10462,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1560</v>
+        <v>1380</v>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F50" t="n">
-        <v>59.5</v>
+        <v>59.3</v>
       </c>
       <c r="G50" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51">
@@ -10501,23 +10501,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AUDCAD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1564</v>
+        <v>1388</v>
       </c>
       <c r="D51" t="n">
-        <v>49.4</v>
+        <v>50.1</v>
       </c>
       <c r="E51" t="n">
-        <v>50.6</v>
+        <v>49.9</v>
       </c>
       <c r="F51" t="n">
-        <v>60</v>
+        <v>59.4</v>
       </c>
       <c r="G51" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52">
@@ -10540,23 +10540,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1554</v>
+        <v>1390</v>
       </c>
       <c r="D52" t="n">
-        <v>50.5</v>
+        <v>48.6</v>
       </c>
       <c r="E52" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
       <c r="F52" t="n">
-        <v>60.6</v>
+        <v>60.4</v>
       </c>
       <c r="G52" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1567</v>
+        <v>1387</v>
       </c>
       <c r="D53" t="n">
-        <v>49.5</v>
+        <v>48.7</v>
       </c>
       <c r="E53" t="n">
-        <v>50.5</v>
+        <v>51.3</v>
       </c>
       <c r="F53" t="n">
-        <v>64.5</v>
+        <v>64.2</v>
       </c>
       <c r="G53" t="n">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54">
@@ -10622,7 +10622,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1566</v>
+        <v>1386</v>
       </c>
       <c r="D54" t="n">
         <v>48.3</v>
@@ -10631,10 +10631,10 @@
         <v>51.7</v>
       </c>
       <c r="F54" t="n">
-        <v>65.40000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>15.4</v>
+        <v>14.4</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55">
@@ -10661,13 +10661,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1580</v>
+        <v>1398</v>
       </c>
       <c r="D55" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="E55" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="F55" t="n">
         <v>70</v>
@@ -10687,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1569</v>
+        <v>1390</v>
       </c>
       <c r="D56" t="n">
-        <v>48.4</v>
+        <v>49.1</v>
       </c>
       <c r="E56" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="F56" t="n">
         <v>74.8</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1584</v>
+        <v>1404</v>
       </c>
       <c r="D57" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="E57" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="F57" t="n">
-        <v>82.40000000000001</v>
+        <v>82</v>
       </c>
       <c r="G57" t="n">
-        <v>32.4</v>
+        <v>32</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1589</v>
+        <v>1408</v>
       </c>
       <c r="D58" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="E58" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="F58" t="n">
-        <v>83</v>
+        <v>82.5</v>
       </c>
       <c r="G58" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1590</v>
+        <v>1408</v>
       </c>
       <c r="D59" t="n">
-        <v>48.8</v>
+        <v>49.6</v>
       </c>
       <c r="E59" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="F59" t="n">
-        <v>94.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>44.5</v>
+        <v>44.1</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10852,23 +10852,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1623</v>
+        <v>1302</v>
       </c>
       <c r="D60" t="n">
-        <v>50.4</v>
+        <v>52.2</v>
       </c>
       <c r="E60" t="n">
-        <v>49.6</v>
+        <v>47.8</v>
       </c>
       <c r="F60" t="n">
-        <v>40.9</v>
+        <v>40.1</v>
       </c>
       <c r="G60" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="61">
@@ -10891,23 +10891,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>1462</v>
       </c>
       <c r="D61" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="E61" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="F61" t="n">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="G61" t="n">
-        <v>8.9</v>
+        <v>9.4</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>988</v>
+        <v>875</v>
       </c>
       <c r="D62" t="n">
-        <v>49.3</v>
+        <v>48.9</v>
       </c>
       <c r="E62" t="n">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
       <c r="F62" t="n">
-        <v>59.4</v>
+        <v>59.2</v>
       </c>
       <c r="G62" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="63">
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>971</v>
+        <v>857</v>
       </c>
       <c r="D63" t="n">
-        <v>47.3</v>
+        <v>46.6</v>
       </c>
       <c r="E63" t="n">
-        <v>52.7</v>
+        <v>53.4</v>
       </c>
       <c r="F63" t="n">
-        <v>59.8</v>
+        <v>60.7</v>
       </c>
       <c r="G63" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64">
@@ -11008,23 +11008,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1429</v>
+        <v>860</v>
       </c>
       <c r="D64" t="n">
-        <v>48.7</v>
+        <v>50.7</v>
       </c>
       <c r="E64" t="n">
-        <v>51.3</v>
+        <v>49.3</v>
       </c>
       <c r="F64" t="n">
-        <v>61.2</v>
+        <v>61.4</v>
       </c>
       <c r="G64" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65">
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>974</v>
+        <v>1255</v>
       </c>
       <c r="D65" t="n">
-        <v>51.5</v>
+        <v>48.3</v>
       </c>
       <c r="E65" t="n">
-        <v>48.5</v>
+        <v>51.7</v>
       </c>
       <c r="F65" t="n">
-        <v>61.9</v>
+        <v>62.2</v>
       </c>
       <c r="G65" t="n">
-        <v>11.9</v>
+        <v>12.2</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66">
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>999</v>
+        <v>887</v>
       </c>
       <c r="D66" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
-        <v>62</v>
+        <v>62.8</v>
       </c>
       <c r="G66" t="n">
-        <v>12</v>
+        <v>12.8</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67">
@@ -11129,19 +11129,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1133</v>
+        <v>1006</v>
       </c>
       <c r="D67" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="E67" t="n">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="F67" t="n">
-        <v>63.6</v>
+        <v>63.8</v>
       </c>
       <c r="G67" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
@@ -11164,17 +11164,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1551</v>
+        <v>1202</v>
       </c>
       <c r="D68" t="n">
-        <v>49.5</v>
+        <v>47.2</v>
       </c>
       <c r="E68" t="n">
-        <v>50.5</v>
+        <v>52.8</v>
       </c>
       <c r="F68" t="n">
         <v>64</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69">
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1355</v>
+        <v>1374</v>
       </c>
       <c r="D69" t="n">
-        <v>48</v>
+        <v>49.7</v>
       </c>
       <c r="E69" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="F69" t="n">
-        <v>64.40000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70">
@@ -11242,17 +11242,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1583</v>
+        <v>1461</v>
       </c>
       <c r="D70" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="E70" t="n">
-        <v>48.8</v>
+        <v>48.5</v>
       </c>
       <c r="F70" t="n">
         <v>64.40000000000001</v>
@@ -11281,23 +11281,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1567</v>
+        <v>1402</v>
       </c>
       <c r="D71" t="n">
-        <v>48.7</v>
+        <v>51.9</v>
       </c>
       <c r="E71" t="n">
-        <v>51.3</v>
+        <v>48.1</v>
       </c>
       <c r="F71" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72">
@@ -11320,23 +11320,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1629</v>
+        <v>1386</v>
       </c>
       <c r="D72" t="n">
-        <v>50.6</v>
+        <v>48.8</v>
       </c>
       <c r="E72" t="n">
-        <v>49.4</v>
+        <v>51.2</v>
       </c>
       <c r="F72" t="n">
-        <v>64.8</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73">
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1363</v>
+        <v>1204</v>
       </c>
       <c r="D73" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="E73" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="F73" t="n">
-        <v>65.8</v>
+        <v>65.5</v>
       </c>
       <c r="G73" t="n">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11389,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>600</v>
+        <v>526</v>
       </c>
       <c r="D74" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E74" t="n">
-        <v>51.5</v>
+        <v>51.1</v>
       </c>
       <c r="F74" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="G74" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1156</v>
+        <v>1022</v>
       </c>
       <c r="D75" t="n">
-        <v>50.4</v>
+        <v>49.3</v>
       </c>
       <c r="E75" t="n">
-        <v>49.6</v>
+        <v>50.7</v>
       </c>
       <c r="F75" t="n">
-        <v>53.5</v>
+        <v>53.3</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76">
@@ -11476,23 +11476,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cocoa</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>579</v>
+        <v>446</v>
       </c>
       <c r="D76" t="n">
-        <v>50.3</v>
+        <v>51.8</v>
       </c>
       <c r="E76" t="n">
-        <v>49.7</v>
+        <v>48.2</v>
       </c>
       <c r="F76" t="n">
-        <v>54.9</v>
+        <v>54.3</v>
       </c>
       <c r="G76" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77">
@@ -11515,37 +11515,37 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cocoa</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>521</v>
+        <v>510</v>
       </c>
       <c r="D77" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="E77" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="F77" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H77" t="b">
+        <v>1</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Commodities</t>
+        </is>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
         <v>52</v>
-      </c>
-      <c r="E77" t="n">
-        <v>48</v>
-      </c>
-      <c r="F77" t="n">
-        <v>55.3</v>
-      </c>
-      <c r="G77" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="H77" t="b">
-        <v>1</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Commodities</t>
-        </is>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="78">
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1484</v>
+        <v>1310</v>
       </c>
       <c r="D78" t="n">
-        <v>49.2</v>
+        <v>50.9</v>
       </c>
       <c r="E78" t="n">
-        <v>50.8</v>
+        <v>49.1</v>
       </c>
       <c r="F78" t="n">
-        <v>70.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="G78" t="n">
-        <v>20.6</v>
+        <v>19.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -11593,23 +11593,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>UKGILT.F</t>
+          <t>EUBUND.F</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>586</v>
+        <v>1091</v>
       </c>
       <c r="D79" t="n">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="E79" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="F79" t="n">
-        <v>61.1</v>
+        <v>62.2</v>
       </c>
       <c r="G79" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80">
@@ -11632,23 +11632,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EUBUND.F</t>
+          <t>UKGILT.F</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1217</v>
+        <v>553</v>
       </c>
       <c r="D80" t="n">
-        <v>46.6</v>
+        <v>49.5</v>
       </c>
       <c r="E80" t="n">
-        <v>53.4</v>
+        <v>50.5</v>
       </c>
       <c r="F80" t="n">
-        <v>61.6</v>
+        <v>62.2</v>
       </c>
       <c r="G80" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81">
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1187</v>
+        <v>1087</v>
       </c>
       <c r="D81" t="n">
-        <v>47.3</v>
+        <v>46.7</v>
       </c>
       <c r="E81" t="n">
-        <v>52.7</v>
+        <v>53.3</v>
       </c>
       <c r="F81" t="n">
-        <v>63.6</v>
+        <v>64.3</v>
       </c>
       <c r="G81" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="D82" t="n">
-        <v>51</v>
+        <v>50.4</v>
       </c>
       <c r="E82" t="n">
-        <v>49</v>
+        <v>49.6</v>
       </c>
       <c r="F82" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="G82" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="83">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>408</v>
+        <v>363</v>
       </c>
       <c r="D83" t="n">
         <v>46.8</v>
@@ -11762,10 +11762,10 @@
         <v>53.2</v>
       </c>
       <c r="F83" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="G83" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84">
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="D84" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="E84" t="n">
-        <v>53.1</v>
+        <v>52.7</v>
       </c>
       <c r="F84" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="85">
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="D85" t="n">
-        <v>48</v>
+        <v>49.7</v>
       </c>
       <c r="E85" t="n">
-        <v>52</v>
+        <v>50.3</v>
       </c>
       <c r="F85" t="n">
-        <v>56.1</v>
+        <v>56.8</v>
       </c>
       <c r="G85" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="86">
@@ -11870,19 +11870,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="D86" t="n">
-        <v>45.6</v>
+        <v>45.1</v>
       </c>
       <c r="E86" t="n">
-        <v>54.4</v>
+        <v>54.9</v>
       </c>
       <c r="F86" t="n">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="G86" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -11909,19 +11909,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>415</v>
+        <v>369</v>
       </c>
       <c r="D87" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="E87" t="n">
-        <v>51.6</v>
+        <v>51.8</v>
       </c>
       <c r="F87" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="G87" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="88">
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="D88" t="n">
-        <v>49.8</v>
+        <v>48</v>
       </c>
       <c r="E88" t="n">
-        <v>50.2</v>
+        <v>52</v>
       </c>
       <c r="F88" t="n">
-        <v>62</v>
+        <v>62.4</v>
       </c>
       <c r="G88" t="n">
-        <v>12</v>
+        <v>12.4</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="89">
@@ -11987,19 +11987,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>429</v>
+        <v>377</v>
       </c>
       <c r="D89" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="E89" t="n">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
       <c r="F89" t="n">
-        <v>62.9</v>
+        <v>63.9</v>
       </c>
       <c r="G89" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="90">
@@ -12026,19 +12026,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>442</v>
+        <v>390</v>
       </c>
       <c r="D90" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="E90" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="F90" t="n">
-        <v>64.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91">
@@ -12065,19 +12065,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="D91" t="n">
-        <v>50.1</v>
+        <v>48.7</v>
       </c>
       <c r="E91" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="F91" t="n">
-        <v>64.3</v>
+        <v>65.3</v>
       </c>
       <c r="G91" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="92">
@@ -12104,19 +12104,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>431</v>
+        <v>381</v>
       </c>
       <c r="D92" t="n">
-        <v>50.3</v>
+        <v>49.1</v>
       </c>
       <c r="E92" t="n">
-        <v>49.7</v>
+        <v>50.9</v>
       </c>
       <c r="F92" t="n">
-        <v>65.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="93">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>400</v>
+        <v>353</v>
       </c>
       <c r="D93" t="n">
-        <v>48.2</v>
+        <v>47.6</v>
       </c>
       <c r="E93" t="n">
-        <v>51.7</v>
+        <v>52.4</v>
       </c>
       <c r="F93" t="n">
         <v>72</v>
@@ -12182,19 +12182,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1591</v>
+        <v>1409</v>
       </c>
       <c r="D94" t="n">
-        <v>48.5</v>
+        <v>49.5</v>
       </c>
       <c r="E94" t="n">
-        <v>51.5</v>
+        <v>50.5</v>
       </c>
       <c r="F94" t="n">
-        <v>57.5</v>
+        <v>56.8</v>
       </c>
       <c r="G94" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="95">
@@ -12217,23 +12217,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1545</v>
+        <v>1258</v>
       </c>
       <c r="D95" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="E95" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="F95" t="n">
-        <v>58.6</v>
+        <v>57.1</v>
       </c>
       <c r="G95" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96">
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1413</v>
+        <v>1371</v>
       </c>
       <c r="D96" t="n">
-        <v>49.8</v>
+        <v>52.4</v>
       </c>
       <c r="E96" t="n">
-        <v>50.2</v>
+        <v>47.6</v>
       </c>
       <c r="F96" t="n">
-        <v>58.9</v>
+        <v>57.8</v>
       </c>
       <c r="G96" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12299,19 +12299,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1573</v>
+        <v>1391</v>
       </c>
       <c r="D97" t="n">
-        <v>48.2</v>
+        <v>48.9</v>
       </c>
       <c r="E97" t="n">
-        <v>51.8</v>
+        <v>51.1</v>
       </c>
       <c r="F97" t="n">
-        <v>59.4</v>
+        <v>58.2</v>
       </c>
       <c r="G97" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#BTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1610</v>
+        <v>1410</v>
       </c>
       <c r="D98" t="n">
-        <v>48.8</v>
+        <v>49.3</v>
       </c>
       <c r="E98" t="n">
-        <v>51.2</v>
+        <v>50.7</v>
       </c>
       <c r="F98" t="n">
-        <v>59.5</v>
+        <v>58.9</v>
       </c>
       <c r="G98" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99">
@@ -12373,23 +12373,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#BTCUSD</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1592</v>
+        <v>1410</v>
       </c>
       <c r="D99" t="n">
-        <v>48.4</v>
+        <v>49.6</v>
       </c>
       <c r="E99" t="n">
-        <v>51.6</v>
+        <v>50.4</v>
       </c>
       <c r="F99" t="n">
-        <v>59.7</v>
+        <v>59.1</v>
       </c>
       <c r="G99" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100">
@@ -12412,23 +12412,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1587</v>
+        <v>1410</v>
       </c>
       <c r="D100" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="E100" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="F100" t="n">
-        <v>60.2</v>
+        <v>59.4</v>
       </c>
       <c r="G100" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="101">
@@ -12451,23 +12451,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1591</v>
+        <v>1406</v>
       </c>
       <c r="D101" t="n">
-        <v>48.7</v>
+        <v>50.9</v>
       </c>
       <c r="E101" t="n">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
       <c r="F101" t="n">
-        <v>60.2</v>
+        <v>59.6</v>
       </c>
       <c r="G101" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102">
@@ -12490,23 +12490,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1530</v>
+        <v>1390</v>
       </c>
       <c r="D102" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E102" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F102" t="n">
-        <v>61.3</v>
+        <v>60.2</v>
       </c>
       <c r="G102" t="n">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103">
@@ -12529,23 +12529,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1571</v>
+        <v>1360</v>
       </c>
       <c r="D103" t="n">
+        <v>51</v>
+      </c>
+      <c r="E103" t="n">
         <v>49</v>
       </c>
-      <c r="E103" t="n">
-        <v>51</v>
-      </c>
       <c r="F103" t="n">
-        <v>61.4</v>
+        <v>61</v>
       </c>
       <c r="G103" t="n">
-        <v>11.4</v>
+        <v>11</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38395</v>
+        <v>38484</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12682,13 +12682,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38444</v>
+        <v>38534</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="E3" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="F3" t="n">
         <v>40.7</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38649</v>
+        <v>38740</v>
       </c>
       <c r="D4" t="n">
         <v>51.2</v>
@@ -12730,10 +12730,10 @@
         <v>48.8</v>
       </c>
       <c r="F4" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="G4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38036</v>
+        <v>38114</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12769,10 +12769,10 @@
         <v>50.3</v>
       </c>
       <c r="F5" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -12786,7 +12786,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38506</v>
+        <v>38587</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38028</v>
+        <v>38107</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37854</v>
+        <v>37930</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38309</v>
+        <v>38390</v>
       </c>
       <c r="D9" t="n">
         <v>50</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38595</v>
+        <v>38676</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38648</v>
+        <v>38729</v>
       </c>
       <c r="D11" t="n">
         <v>50.6</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38657</v>
+        <v>38737</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38484</v>
+        <v>38560</v>
       </c>
       <c r="D13" t="n">
         <v>49.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38544</v>
+        <v>38622</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38523</v>
+        <v>38613</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38543</v>
+        <v>38633</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36715</v>
+        <v>36793</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38715</v>
+        <v>38796</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38250</v>
+        <v>38330</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13315,10 +13315,10 @@
         <v>49.7</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34979</v>
+        <v>35058</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38785</v>
+        <v>38866</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38599</v>
+        <v>38680</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38648</v>
+        <v>38729</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38832</v>
+        <v>39005</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13510,10 +13510,10 @@
         <v>50.5</v>
       </c>
       <c r="F24" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="G24" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -13536,23 +13536,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38844</v>
+        <v>38868</v>
       </c>
       <c r="D25" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="E25" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="F25" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="G25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -13575,17 +13575,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38787</v>
+        <v>38925</v>
       </c>
       <c r="D26" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="E26" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="F26" t="n">
         <v>40.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35148</v>
+        <v>35228</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13627,10 +13627,10 @@
         <v>50.1</v>
       </c>
       <c r="F27" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="G27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38869</v>
+        <v>38950</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38877</v>
+        <v>38958</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38591</v>
+        <v>38672</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13770,17 +13770,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38628</v>
+        <v>38704</v>
       </c>
       <c r="D31" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E31" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F31" t="n">
         <v>44.5</v>
@@ -13809,23 +13809,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38624</v>
+        <v>38709</v>
       </c>
       <c r="D32" t="n">
-        <v>49.4</v>
+        <v>49.2</v>
       </c>
       <c r="E32" t="n">
-        <v>50.6</v>
+        <v>50.8</v>
       </c>
       <c r="F32" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="G32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38651</v>
+        <v>38732</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38588</v>
+        <v>38668</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -13917,7 +13917,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38589</v>
+        <v>38669</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35033</v>
+        <v>35113</v>
       </c>
       <c r="D36" t="n">
         <v>49.9</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38425</v>
+        <v>38506</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14017,10 +14017,10 @@
         <v>48.3</v>
       </c>
       <c r="F37" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="G37" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37762</v>
+        <v>37842</v>
       </c>
       <c r="D38" t="n">
         <v>50.7</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38584</v>
+        <v>38664</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8153</v>
+        <v>8170</v>
       </c>
       <c r="D40" t="n">
         <v>51.2</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38262</v>
+        <v>38342</v>
       </c>
       <c r="D41" t="n">
         <v>50</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38321</v>
+        <v>38402</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14212,10 +14212,10 @@
         <v>50.2</v>
       </c>
       <c r="F42" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
       <c r="G42" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -14229,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38360</v>
+        <v>38441</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38285</v>
+        <v>38365</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>37932</v>
+        <v>38012</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38085</v>
+        <v>38165</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38466</v>
+        <v>38546</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38507</v>
+        <v>38585</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35878</v>
+        <v>35952</v>
       </c>
       <c r="D49" t="n">
         <v>50.4</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38208</v>
+        <v>38289</v>
       </c>
       <c r="D50" t="n">
         <v>50.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38346</v>
+        <v>38427</v>
       </c>
       <c r="D51" t="n">
         <v>49.4</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38389</v>
+        <v>38469</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38262</v>
+        <v>38341</v>
       </c>
       <c r="D53" t="n">
         <v>49.6</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38299</v>
+        <v>38379</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,13 +14710,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38480</v>
+        <v>38561</v>
       </c>
       <c r="D55" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E55" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F55" t="n">
         <v>65.7</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38181</v>
+        <v>38261</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38545</v>
+        <v>38626</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38627</v>
+        <v>38708</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38829</v>
+        <v>38910</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35243</v>
+        <v>35323</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37211</v>
+        <v>37301</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37638</v>
+        <v>37718</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23495</v>
+        <v>23547</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23912</v>
+        <v>23965</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,13 +15100,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23936</v>
+        <v>23988</v>
       </c>
       <c r="D65" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="E65" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="F65" t="n">
         <v>56</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38532</v>
+        <v>38613</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38036</v>
+        <v>38117</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21322</v>
+        <v>21378</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36297</v>
+        <v>36378</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30675</v>
+        <v>30752</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37729</v>
+        <v>37820</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33151</v>
+        <v>33222</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26142</v>
+        <v>26205</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15421,10 +15421,10 @@
         <v>49.9</v>
       </c>
       <c r="F73" t="n">
-        <v>59.4</v>
+        <v>59.3</v>
       </c>
       <c r="G73" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74">
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14271</v>
+        <v>14306</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14080</v>
+        <v>14110</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15207</v>
+        <v>15244</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -15538,10 +15538,10 @@
         <v>49.5</v>
       </c>
       <c r="F76" t="n">
-        <v>53</v>
+        <v>52.9</v>
       </c>
       <c r="G76" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26752</v>
+        <v>26817</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36009</v>
+        <v>36081</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15616,10 +15616,10 @@
         <v>49.4</v>
       </c>
       <c r="F78" t="n">
-        <v>65.59999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="G78" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28745</v>
+        <v>28813</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15838</v>
+        <v>15874</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15694,10 +15694,10 @@
         <v>50.3</v>
       </c>
       <c r="F80" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G80" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81">
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>27994</v>
+        <v>28060</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,13 +15763,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10469</v>
+        <v>10494</v>
       </c>
       <c r="D82" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E82" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F82" t="n">
         <v>51.9</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10474</v>
+        <v>10499</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10254</v>
+        <v>10277</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10771</v>
+        <v>10796</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15919,13 +15919,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10255</v>
+        <v>10281</v>
       </c>
       <c r="D86" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="E86" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="F86" t="n">
         <v>56</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87">
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10726</v>
+        <v>10752</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10830</v>
+        <v>10856</v>
       </c>
       <c r="D88" t="n">
         <v>51.5</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10970</v>
+        <v>10996</v>
       </c>
       <c r="D89" t="n">
         <v>51.5</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10970</v>
+        <v>10996</v>
       </c>
       <c r="D90" t="n">
         <v>51.5</v>
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10896</v>
+        <v>10922</v>
       </c>
       <c r="D91" t="n">
         <v>51.6</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10316</v>
+        <v>10338</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10243</v>
+        <v>10266</v>
       </c>
       <c r="D93" t="n">
         <v>51.2</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94">
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38062</v>
+        <v>38141</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -16257,7 +16257,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="95">
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38672</v>
+        <v>38753</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36257</v>
+        <v>36334</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38788</v>
+        <v>38869</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>37986</v>
+        <v>38065</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38579</v>
+        <v>38658</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38182</v>
+        <v>38263</v>
       </c>
       <c r="D100" t="n">
         <v>49.2</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38438</v>
+        <v>38517</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,13 +16543,13 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38865</v>
+        <v>38946</v>
       </c>
       <c r="D102" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F102" t="n">
         <v>54.6</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38904</v>
+        <v>38967</v>
       </c>
       <c r="D103" t="n">
         <v>49.7</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -492,23 +492,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GBPJPY</t>
+          <t>CHFJPY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1400</v>
+        <v>1498</v>
       </c>
       <c r="D2" t="n">
-        <v>49.9</v>
+        <v>48.8</v>
       </c>
       <c r="E2" t="n">
-        <v>50.1</v>
+        <v>51.2</v>
       </c>
       <c r="F2" t="n">
-        <v>49.6</v>
+        <v>50.3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -531,23 +531,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHFJPY</t>
+          <t>GBPJPY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1406</v>
+        <v>1491</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>50.4</v>
       </c>
       <c r="E3" t="n">
-        <v>52</v>
+        <v>49.6</v>
       </c>
       <c r="F3" t="n">
-        <v>50.8</v>
+        <v>49.3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1388</v>
+        <v>1477</v>
       </c>
       <c r="D4" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E4" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F4" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1400</v>
+        <v>1490</v>
       </c>
       <c r="D5" t="n">
-        <v>48.5</v>
+        <v>49.1</v>
       </c>
       <c r="E5" t="n">
-        <v>51.5</v>
+        <v>50.9</v>
       </c>
       <c r="F5" t="n">
-        <v>47.7</v>
+        <v>47.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1354</v>
+        <v>1440</v>
       </c>
       <c r="D6" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
         <v>47.2</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1397</v>
+        <v>1488</v>
       </c>
       <c r="D7" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E7" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F7" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1385</v>
+        <v>1472</v>
       </c>
       <c r="D8" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="E8" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="F8" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1402</v>
+        <v>1492</v>
       </c>
       <c r="D9" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E9" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="F9" t="n">
-        <v>55.6</v>
+        <v>56.1</v>
       </c>
       <c r="G9" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1372</v>
+        <v>1461</v>
       </c>
       <c r="D10" t="n">
-        <v>52.2</v>
+        <v>51.8</v>
       </c>
       <c r="E10" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="F10" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="G10" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1377</v>
+        <v>1468</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1366</v>
+        <v>1458</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1120,7 +1120,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1266</v>
+        <v>1346</v>
       </c>
       <c r="D18" t="n">
         <v>49.4</v>
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="D19" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E19" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F19" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1198,19 +1198,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1395</v>
+        <v>1483</v>
       </c>
       <c r="D20" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1402</v>
+        <v>1493</v>
       </c>
       <c r="D21" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="E21" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="F21" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1379</v>
+        <v>1469</v>
       </c>
       <c r="D22" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="E22" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="F22" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
@@ -1315,19 +1315,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1352</v>
+        <v>1437</v>
       </c>
       <c r="D23" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E23" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F23" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1350,23 +1350,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>NZDJPY</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1388</v>
+        <v>1490</v>
       </c>
       <c r="D24" t="n">
-        <v>49.9</v>
+        <v>48.5</v>
       </c>
       <c r="E24" t="n">
-        <v>50.1</v>
+        <v>51.5</v>
       </c>
       <c r="F24" t="n">
-        <v>46.5</v>
+        <v>53.6</v>
       </c>
       <c r="G24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NZDJPY</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1400</v>
+        <v>1483</v>
       </c>
       <c r="D25" t="n">
-        <v>48.6</v>
+        <v>49.6</v>
       </c>
       <c r="E25" t="n">
-        <v>51.4</v>
+        <v>50.4</v>
       </c>
       <c r="F25" t="n">
-        <v>53.8</v>
+        <v>54</v>
       </c>
       <c r="G25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1394</v>
+        <v>1479</v>
       </c>
       <c r="D26" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="E26" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="F26" t="n">
-        <v>53.9</v>
+        <v>46</v>
       </c>
       <c r="G26" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1384</v>
+        <v>1474</v>
       </c>
       <c r="D27" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="E27" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
       <c r="F27" t="n">
-        <v>45.6</v>
+        <v>45.2</v>
       </c>
       <c r="G27" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1392</v>
+        <v>1493</v>
       </c>
       <c r="D28" t="n">
-        <v>51.6</v>
+        <v>47.8</v>
       </c>
       <c r="E28" t="n">
-        <v>48.4</v>
+        <v>52.2</v>
       </c>
       <c r="F28" t="n">
         <v>44.8</v>
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1399</v>
+        <v>1490</v>
       </c>
       <c r="D29" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="E29" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="F29" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="G29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1584,11 +1584,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1368</v>
+        <v>1483</v>
       </c>
       <c r="D30" t="n">
         <v>51.1</v>
@@ -1597,10 +1597,10 @@
         <v>48.9</v>
       </c>
       <c r="F30" t="n">
-        <v>55.6</v>
+        <v>44.6</v>
       </c>
       <c r="G30" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1402</v>
+        <v>1486</v>
       </c>
       <c r="D31" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="E31" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="F31" t="n">
-        <v>44</v>
+        <v>44.4</v>
       </c>
       <c r="G31" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32">
@@ -1662,23 +1662,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1396</v>
+        <v>1457</v>
       </c>
       <c r="D32" t="n">
-        <v>48.6</v>
+        <v>50.5</v>
       </c>
       <c r="E32" t="n">
-        <v>51.4</v>
+        <v>49.5</v>
       </c>
       <c r="F32" t="n">
-        <v>43.9</v>
+        <v>55.6</v>
       </c>
       <c r="G32" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1402</v>
+        <v>1492</v>
       </c>
       <c r="D33" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E33" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F33" t="n">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="G33" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1268</v>
+        <v>1348</v>
       </c>
       <c r="D34" t="n">
-        <v>49.8</v>
+        <v>50.1</v>
       </c>
       <c r="E34" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="F34" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="G34" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1282</v>
+        <v>1369</v>
       </c>
       <c r="D35" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="E35" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="F35" t="n">
-        <v>57.8</v>
+        <v>57.3</v>
       </c>
       <c r="G35" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1394</v>
+        <v>1483</v>
       </c>
       <c r="D36" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="E36" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="F36" t="n">
-        <v>41.4</v>
+        <v>42.1</v>
       </c>
       <c r="G36" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1380</v>
+        <v>1469</v>
       </c>
       <c r="D37" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E37" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F37" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="G37" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38">
@@ -1900,19 +1900,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1399</v>
+        <v>1490</v>
       </c>
       <c r="D38" t="n">
-        <v>49</v>
+        <v>49.7</v>
       </c>
       <c r="E38" t="n">
-        <v>51</v>
+        <v>50.3</v>
       </c>
       <c r="F38" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="G38" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1388</v>
+        <v>1477</v>
       </c>
       <c r="D39" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
       <c r="G39" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1404</v>
+        <v>1496</v>
       </c>
       <c r="D40" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
       <c r="E40" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="F40" t="n">
-        <v>40</v>
+        <v>40.4</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41">
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1390</v>
+        <v>1480</v>
       </c>
       <c r="D41" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E41" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="F41" t="n">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="G41" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1404</v>
+        <v>1496</v>
       </c>
       <c r="D42" t="n">
-        <v>50.6</v>
+        <v>50.2</v>
       </c>
       <c r="E42" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
       <c r="F42" t="n">
         <v>38.7</v>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1398</v>
+        <v>1490</v>
       </c>
       <c r="D43" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="E43" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="F43" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="G43" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2121,7 +2121,7 @@
         <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44">
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D44" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="E44" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="F44" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G44" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45">
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1391</v>
+        <v>1479</v>
       </c>
       <c r="D45" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="E45" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="F45" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="G45" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
@@ -2212,19 +2212,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1264</v>
+        <v>1343</v>
       </c>
       <c r="D46" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E46" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="F46" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="G46" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="D47" t="n">
-        <v>51.1</v>
+        <v>50.1</v>
       </c>
       <c r="E47" t="n">
-        <v>48.9</v>
+        <v>49.9</v>
       </c>
       <c r="F47" t="n">
         <v>37.1</v>
@@ -2286,23 +2286,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1407</v>
+        <v>1500</v>
       </c>
       <c r="D48" t="n">
-        <v>49.9</v>
+        <v>51.1</v>
       </c>
       <c r="E48" t="n">
-        <v>50.1</v>
+        <v>48.9</v>
       </c>
       <c r="F48" t="n">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="G48" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1410</v>
+        <v>1472</v>
       </c>
       <c r="D49" t="n">
-        <v>52.1</v>
+        <v>48.4</v>
       </c>
       <c r="E49" t="n">
-        <v>47.9</v>
+        <v>51.6</v>
       </c>
       <c r="F49" t="n">
-        <v>36</v>
+        <v>63.7</v>
       </c>
       <c r="G49" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1387</v>
+        <v>1502</v>
       </c>
       <c r="D50" t="n">
-        <v>48.7</v>
+        <v>51.4</v>
       </c>
       <c r="E50" t="n">
-        <v>51.3</v>
+        <v>48.6</v>
       </c>
       <c r="F50" t="n">
-        <v>64.2</v>
+        <v>36.3</v>
       </c>
       <c r="G50" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1386</v>
+        <v>1475</v>
       </c>
       <c r="D51" t="n">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
       <c r="E51" t="n">
-        <v>51.7</v>
+        <v>52.1</v>
       </c>
       <c r="F51" t="n">
-        <v>64.40000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="G51" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1375</v>
+        <v>1465</v>
       </c>
       <c r="D52" t="n">
         <v>50.2</v>
@@ -2455,10 +2455,10 @@
         <v>49.8</v>
       </c>
       <c r="F52" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="G52" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D53" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E53" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="G53" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1316</v>
+        <v>1401</v>
       </c>
       <c r="D54" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E54" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F54" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="G54" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1398</v>
+        <v>1489</v>
       </c>
       <c r="D55" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E55" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F55" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1390</v>
+        <v>1482</v>
       </c>
       <c r="D56" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E56" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F56" t="n">
-        <v>74.8</v>
+        <v>75.2</v>
       </c>
       <c r="G56" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1404</v>
+        <v>1495</v>
       </c>
       <c r="D57" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E57" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F57" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,13 +2680,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1408</v>
+        <v>1500</v>
       </c>
       <c r="D58" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E58" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F58" t="n">
         <v>82.5</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1408</v>
+        <v>1500</v>
       </c>
       <c r="D59" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E59" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F59" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="G59" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2797,19 +2797,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1302</v>
+        <v>1386</v>
       </c>
       <c r="D61" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="E61" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="F61" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="G61" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="62">
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>875</v>
+        <v>928</v>
       </c>
       <c r="D62" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="E62" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="F62" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="G62" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>857</v>
+        <v>913</v>
       </c>
       <c r="D63" t="n">
-        <v>46.6</v>
+        <v>47.5</v>
       </c>
       <c r="E63" t="n">
-        <v>53.4</v>
+        <v>52.5</v>
       </c>
       <c r="F63" t="n">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64">
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>860</v>
+        <v>914</v>
       </c>
       <c r="D64" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="E64" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="F64" t="n">
-        <v>61.4</v>
+        <v>61.8</v>
       </c>
       <c r="G64" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">
@@ -2953,19 +2953,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1255</v>
+        <v>1343</v>
       </c>
       <c r="D65" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E65" t="n">
-        <v>51.7</v>
+        <v>50.9</v>
       </c>
       <c r="F65" t="n">
-        <v>62.2</v>
+        <v>61.8</v>
       </c>
       <c r="G65" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2988,23 +2988,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>887</v>
+        <v>1070</v>
       </c>
       <c r="D66" t="n">
-        <v>51.2</v>
+        <v>50.2</v>
       </c>
       <c r="E66" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="F66" t="n">
-        <v>62.8</v>
+        <v>62.3</v>
       </c>
       <c r="G66" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67">
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1006</v>
+        <v>943</v>
       </c>
       <c r="D67" t="n">
-        <v>49.1</v>
+        <v>52.1</v>
       </c>
       <c r="E67" t="n">
-        <v>50.9</v>
+        <v>47.9</v>
       </c>
       <c r="F67" t="n">
-        <v>63.8</v>
+        <v>62.7</v>
       </c>
       <c r="G67" t="n">
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1202</v>
+        <v>1464</v>
       </c>
       <c r="D68" t="n">
-        <v>47.2</v>
+        <v>50.8</v>
       </c>
       <c r="E68" t="n">
-        <v>52.8</v>
+        <v>49.2</v>
       </c>
       <c r="F68" t="n">
-        <v>64</v>
+        <v>63.7</v>
       </c>
       <c r="G68" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1374</v>
+        <v>1278</v>
       </c>
       <c r="D69" t="n">
-        <v>49.7</v>
+        <v>48</v>
       </c>
       <c r="E69" t="n">
-        <v>50.3</v>
+        <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>64.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="G69" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1461</v>
+        <v>1478</v>
       </c>
       <c r="D70" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="E70" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="F70" t="n">
         <v>64.40000000000001</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1402</v>
+        <v>1461</v>
       </c>
       <c r="D71" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
       <c r="E71" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="F71" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1386</v>
+        <v>1493</v>
       </c>
       <c r="D72" t="n">
-        <v>48.8</v>
+        <v>52.5</v>
       </c>
       <c r="E72" t="n">
-        <v>51.2</v>
+        <v>47.5</v>
       </c>
       <c r="F72" t="n">
-        <v>64.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1204</v>
+        <v>1280</v>
       </c>
       <c r="D73" t="n">
-        <v>48</v>
+        <v>48.7</v>
       </c>
       <c r="E73" t="n">
-        <v>52</v>
+        <v>51.3</v>
       </c>
       <c r="F73" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="74">
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>526</v>
+        <v>562</v>
       </c>
       <c r="D74" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E74" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F74" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="G74" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1022</v>
+        <v>1089</v>
       </c>
       <c r="D75" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E75" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="G75" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="D76" t="n">
-        <v>51.8</v>
+        <v>51</v>
       </c>
       <c r="E76" t="n">
-        <v>48.2</v>
+        <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>54.3</v>
+        <v>54.6</v>
       </c>
       <c r="G76" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="D77" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E77" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F77" t="n">
-        <v>55.5</v>
+        <v>56.1</v>
       </c>
       <c r="G77" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
@@ -3460,13 +3460,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1310</v>
+        <v>1397</v>
       </c>
       <c r="D78" t="n">
-        <v>50.9</v>
+        <v>51.3</v>
       </c>
       <c r="E78" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="F78" t="n">
         <v>69.5</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1091</v>
+        <v>1158</v>
       </c>
       <c r="D79" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="E79" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="F79" t="n">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
       <c r="G79" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="D80" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="E80" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="F80" t="n">
-        <v>62.2</v>
+        <v>62.9</v>
       </c>
       <c r="G80" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1087</v>
+        <v>1159</v>
       </c>
       <c r="D81" t="n">
-        <v>46.7</v>
+        <v>47.3</v>
       </c>
       <c r="E81" t="n">
-        <v>53.3</v>
+        <v>52.7</v>
       </c>
       <c r="F81" t="n">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82">
@@ -3612,23 +3612,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="D82" t="n">
-        <v>47.3</v>
+        <v>46.5</v>
       </c>
       <c r="E82" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="F82" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="G82" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3651,23 +3651,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="D83" t="n">
-        <v>46.8</v>
+        <v>47.8</v>
       </c>
       <c r="E83" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="D84" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="E84" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F84" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
@@ -3729,23 +3729,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="D85" t="n">
-        <v>49.7</v>
+        <v>46.3</v>
       </c>
       <c r="E85" t="n">
-        <v>50.3</v>
+        <v>53.7</v>
       </c>
       <c r="F85" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="G85" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="86">
@@ -3768,23 +3768,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="D86" t="n">
-        <v>45.1</v>
+        <v>50.1</v>
       </c>
       <c r="E86" t="n">
-        <v>54.9</v>
+        <v>49.9</v>
       </c>
       <c r="F86" t="n">
-        <v>57.3</v>
+        <v>56.5</v>
       </c>
       <c r="G86" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="87">
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="D87" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E87" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F87" t="n">
         <v>58</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D88" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="E88" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="F88" t="n">
-        <v>62.4</v>
+        <v>61.8</v>
       </c>
       <c r="G88" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89">
@@ -3889,19 +3889,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="D89" t="n">
-        <v>47.7</v>
+        <v>49.5</v>
       </c>
       <c r="E89" t="n">
-        <v>52.3</v>
+        <v>50.5</v>
       </c>
       <c r="F89" t="n">
-        <v>63.9</v>
+        <v>62.9</v>
       </c>
       <c r="G89" t="n">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3924,23 +3924,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="E90" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>65.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="D91" t="n">
-        <v>48.7</v>
+        <v>53.1</v>
       </c>
       <c r="E91" t="n">
-        <v>51.3</v>
+        <v>46.9</v>
       </c>
       <c r="F91" t="n">
-        <v>65.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
@@ -4006,19 +4006,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D92" t="n">
-        <v>49.1</v>
+        <v>51.4</v>
       </c>
       <c r="E92" t="n">
-        <v>50.9</v>
+        <v>48.6</v>
       </c>
       <c r="F92" t="n">
-        <v>65.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="D93" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
       <c r="E93" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="F93" t="n">
-        <v>72</v>
+        <v>70.7</v>
       </c>
       <c r="G93" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4080,23 +4080,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1409</v>
+        <v>1343</v>
       </c>
       <c r="D94" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E94" t="n">
         <v>49.5</v>
       </c>
-      <c r="E94" t="n">
-        <v>50.5</v>
-      </c>
       <c r="F94" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="G94" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95">
@@ -4119,23 +4119,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1258</v>
+        <v>1501</v>
       </c>
       <c r="D95" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="E95" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="F95" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="G95" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="96">
@@ -4162,19 +4162,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1371</v>
+        <v>1462</v>
       </c>
       <c r="D96" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="E96" t="n">
-        <v>47.6</v>
+        <v>47.4</v>
       </c>
       <c r="F96" t="n">
-        <v>57.8</v>
+        <v>57.3</v>
       </c>
       <c r="G96" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4201,19 +4201,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1391</v>
+        <v>1482</v>
       </c>
       <c r="D97" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="E97" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="F97" t="n">
-        <v>58.2</v>
+        <v>57.6</v>
       </c>
       <c r="G97" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="98">
@@ -4240,19 +4240,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D98" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E98" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F98" t="n">
-        <v>58.9</v>
+        <v>58.3</v>
       </c>
       <c r="G98" t="n">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4279,19 +4279,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D99" t="n">
-        <v>49.6</v>
+        <v>50.5</v>
       </c>
       <c r="E99" t="n">
-        <v>50.4</v>
+        <v>49.5</v>
       </c>
       <c r="F99" t="n">
-        <v>59.1</v>
+        <v>58.7</v>
       </c>
       <c r="G99" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4314,23 +4314,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1410</v>
+        <v>1498</v>
       </c>
       <c r="D100" t="n">
-        <v>49.8</v>
+        <v>51</v>
       </c>
       <c r="E100" t="n">
-        <v>50.2</v>
+        <v>49</v>
       </c>
       <c r="F100" t="n">
-        <v>59.4</v>
+        <v>59.1</v>
       </c>
       <c r="G100" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101">
@@ -4353,23 +4353,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1406</v>
+        <v>1502</v>
       </c>
       <c r="D101" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
       <c r="E101" t="n">
-        <v>49.1</v>
+        <v>49.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.6</v>
+        <v>59.3</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="102">
@@ -4396,19 +4396,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1390</v>
+        <v>1481</v>
       </c>
       <c r="D102" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="F102" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
       <c r="G102" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1360</v>
+        <v>1450</v>
       </c>
       <c r="D103" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E103" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F103" t="n">
-        <v>61</v>
+        <v>60.3</v>
       </c>
       <c r="G103" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38390</v>
+        <v>38479</v>
       </c>
       <c r="D2" t="n">
         <v>50</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37930</v>
+        <v>38016</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38107</v>
+        <v>38198</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38676</v>
+        <v>38766</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,13 +4701,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38729</v>
+        <v>38821</v>
       </c>
       <c r="D6" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E6" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F6" t="n">
         <v>51.8</v>
@@ -4736,20 +4736,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>GBPJPY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38587</v>
+        <v>38828</v>
       </c>
       <c r="D7" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="E7" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="F7" t="n">
-        <v>48.1</v>
+        <v>51.9</v>
       </c>
       <c r="G7" t="n">
         <v>1.9</v>
@@ -4775,23 +4775,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GBPJPY</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38737</v>
+        <v>38678</v>
       </c>
       <c r="D8" t="n">
-        <v>51.4</v>
+        <v>50.7</v>
       </c>
       <c r="E8" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="F8" t="n">
-        <v>51.9</v>
+        <v>48</v>
       </c>
       <c r="G8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38114</v>
+        <v>38203</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4844,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -4857,19 +4857,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38560</v>
+        <v>38647</v>
       </c>
       <c r="D10" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E10" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F10" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38622</v>
+        <v>38712</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -5000,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38664</v>
+        <v>38755</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8170</v>
+        <v>8189</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5178,10 +5178,10 @@
         <v>48.8</v>
       </c>
       <c r="F18" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38342</v>
+        <v>38432</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F19" t="n">
         <v>50.6</v>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -5247,13 +5247,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37842</v>
+        <v>37927</v>
       </c>
       <c r="D20" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="E20" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="F20" t="n">
         <v>49.3</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38506</v>
+        <v>38597</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35113</v>
+        <v>35193</v>
       </c>
       <c r="D22" t="n">
         <v>49.9</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38669</v>
+        <v>38760</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38402</v>
+        <v>38492</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38441</v>
+        <v>38532</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38668</v>
+        <v>38758</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5490,10 +5490,10 @@
         <v>50.8</v>
       </c>
       <c r="F26" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="G26" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38365</v>
+        <v>38454</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38012</v>
+        <v>38101</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38165</v>
+        <v>38257</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38546</v>
+        <v>38636</v>
       </c>
       <c r="D30" t="n">
         <v>50.6</v>
@@ -5672,20 +5672,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38732</v>
+        <v>38673</v>
       </c>
       <c r="D31" t="n">
-        <v>49.5</v>
+        <v>51.1</v>
       </c>
       <c r="E31" t="n">
-        <v>50.5</v>
+        <v>48.9</v>
       </c>
       <c r="F31" t="n">
-        <v>44.8</v>
+        <v>55.2</v>
       </c>
       <c r="G31" t="n">
         <v>5.2</v>
@@ -5711,23 +5711,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38585</v>
+        <v>38822</v>
       </c>
       <c r="D32" t="n">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
       <c r="E32" t="n">
-        <v>48.9</v>
+        <v>50.5</v>
       </c>
       <c r="F32" t="n">
-        <v>55.3</v>
+        <v>44.8</v>
       </c>
       <c r="G32" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38704</v>
+        <v>38795</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38709</v>
+        <v>38800</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38672</v>
+        <v>38761</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>38958</v>
+        <v>39050</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38950</v>
+        <v>39042</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>35952</v>
+        <v>36039</v>
       </c>
       <c r="D38" t="n">
         <v>50.4</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35228</v>
+        <v>35308</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38289</v>
+        <v>38378</v>
       </c>
       <c r="D40" t="n">
         <v>50.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38427</v>
+        <v>38516</v>
       </c>
       <c r="D41" t="n">
         <v>49.4</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38469</v>
+        <v>38559</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38868</v>
+        <v>38960</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38925</v>
+        <v>39017</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38729</v>
+        <v>38817</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38680</v>
+        <v>38772</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38866</v>
+        <v>38958</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35058</v>
+        <v>35137</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,13 +6417,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38341</v>
+        <v>38430</v>
       </c>
       <c r="D50" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E50" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F50" t="n">
         <v>61.5</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38379</v>
+        <v>38464</v>
       </c>
       <c r="D51" t="n">
         <v>50</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38330</v>
+        <v>38420</v>
       </c>
       <c r="D52" t="n">
         <v>50.3</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38796</v>
+        <v>38888</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36793</v>
+        <v>36878</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38561</v>
+        <v>38652</v>
       </c>
       <c r="D55" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E55" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F55" t="n">
         <v>65.7</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38261</v>
+        <v>38353</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38626</v>
+        <v>38717</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38708</v>
+        <v>38800</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38910</v>
+        <v>39002</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35323</v>
+        <v>35407</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6855,10 +6855,10 @@
         <v>49.2</v>
       </c>
       <c r="F61" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="G61" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37718</v>
+        <v>37808</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23547</v>
+        <v>23600</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23965</v>
+        <v>24019</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23988</v>
+        <v>24044</v>
       </c>
       <c r="D65" t="n">
         <v>50.9</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38613</v>
+        <v>38704</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38117</v>
+        <v>38209</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68">
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21378</v>
+        <v>21434</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36378</v>
+        <v>36466</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30752</v>
+        <v>30828</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33222</v>
+        <v>33298</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26205</v>
+        <v>26269</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14306</v>
+        <v>14340</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14110</v>
+        <v>14142</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15244</v>
+        <v>15280</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26817</v>
+        <v>26884</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36081</v>
+        <v>36168</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28813</v>
+        <v>28880</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15874</v>
+        <v>15911</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="81">
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28060</v>
+        <v>28132</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10494</v>
+        <v>10519</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -7691,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10499</v>
+        <v>10525</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10277</v>
+        <v>10303</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10796</v>
+        <v>10821</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7821,19 +7821,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10281</v>
+        <v>10305</v>
       </c>
       <c r="D86" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E86" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F86" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G86" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10752</v>
+        <v>10777</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -7899,13 +7899,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10856</v>
+        <v>10881</v>
       </c>
       <c r="D88" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E88" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F88" t="n">
         <v>57.8</v>
@@ -7938,13 +7938,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10996</v>
+        <v>11022</v>
       </c>
       <c r="D89" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E89" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F89" t="n">
         <v>58.4</v>
@@ -7977,19 +7977,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10996</v>
+        <v>11022</v>
       </c>
       <c r="D90" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E90" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F90" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="G90" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91">
@@ -8016,19 +8016,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10922</v>
+        <v>10948</v>
       </c>
       <c r="D91" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="E91" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="F91" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="G91" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10338</v>
+        <v>10364</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,13 +8094,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10266</v>
+        <v>10289</v>
       </c>
       <c r="D93" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E93" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F93" t="n">
         <v>65.5</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38141</v>
+        <v>38232</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38753</v>
+        <v>38845</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36334</v>
+        <v>36419</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38869</v>
+        <v>38961</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38065</v>
+        <v>38155</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38658</v>
+        <v>38749</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8367,13 +8367,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38263</v>
+        <v>38355</v>
       </c>
       <c r="D100" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E100" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F100" t="n">
         <v>54.4</v>
@@ -8393,7 +8393,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="101">
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38517</v>
+        <v>38608</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38946</v>
+        <v>39038</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38967</v>
+        <v>39059</v>
       </c>
       <c r="D103" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E103" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F103" t="n">
         <v>55</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -8707,17 +8707,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EURCHF</t>
+          <t>CADCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1377</v>
+        <v>1461</v>
       </c>
       <c r="D5" t="n">
-        <v>50.1</v>
+        <v>51.8</v>
       </c>
       <c r="E5" t="n">
-        <v>49.9</v>
+        <v>48.2</v>
       </c>
       <c r="F5" t="n">
         <v>43.1</v>
@@ -8737,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -8746,23 +8746,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CADCHF</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1372</v>
+        <v>1468</v>
       </c>
       <c r="D6" t="n">
-        <v>52.2</v>
+        <v>50.1</v>
       </c>
       <c r="E6" t="n">
-        <v>47.8</v>
+        <v>49.9</v>
       </c>
       <c r="F6" t="n">
-        <v>43.5</v>
+        <v>43.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1397</v>
+        <v>1488</v>
       </c>
       <c r="D7" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E7" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F7" t="n">
-        <v>45.7</v>
+        <v>45.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1354</v>
+        <v>1440</v>
       </c>
       <c r="D8" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
         <v>47.2</v>
@@ -8867,19 +8867,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1400</v>
+        <v>1490</v>
       </c>
       <c r="D9" t="n">
-        <v>48.5</v>
+        <v>49.1</v>
       </c>
       <c r="E9" t="n">
-        <v>51.5</v>
+        <v>50.9</v>
       </c>
       <c r="F9" t="n">
-        <v>47.7</v>
+        <v>47.4</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8906,19 +8906,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1388</v>
+        <v>1477</v>
       </c>
       <c r="D10" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E10" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F10" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1400</v>
+        <v>1491</v>
       </c>
       <c r="D11" t="n">
-        <v>49.9</v>
+        <v>50.4</v>
       </c>
       <c r="E11" t="n">
-        <v>50.1</v>
+        <v>49.6</v>
       </c>
       <c r="F11" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1406</v>
+        <v>1498</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="E12" t="n">
-        <v>52</v>
+        <v>51.2</v>
       </c>
       <c r="F12" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1385</v>
+        <v>1472</v>
       </c>
       <c r="D13" t="n">
-        <v>48.9</v>
+        <v>49.4</v>
       </c>
       <c r="E13" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="F13" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1402</v>
+        <v>1492</v>
       </c>
       <c r="D14" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="E14" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="F14" t="n">
-        <v>55.6</v>
+        <v>56.1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1316</v>
+        <v>1401</v>
       </c>
       <c r="D17" t="n">
-        <v>51.5</v>
+        <v>51.2</v>
       </c>
       <c r="E17" t="n">
-        <v>48.5</v>
+        <v>48.8</v>
       </c>
       <c r="F17" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="G17" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D18" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E18" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>32.3</v>
+        <v>32.6</v>
       </c>
       <c r="G18" t="n">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,7 +9257,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1375</v>
+        <v>1465</v>
       </c>
       <c r="D19" t="n">
         <v>50.2</v>
@@ -9266,10 +9266,10 @@
         <v>49.8</v>
       </c>
       <c r="F19" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="G19" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D20" t="n">
-        <v>52.1</v>
+        <v>51.4</v>
       </c>
       <c r="E20" t="n">
-        <v>47.9</v>
+        <v>48.6</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>36.3</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1407</v>
+        <v>1499</v>
       </c>
       <c r="D21" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E21" t="n">
         <v>49.9</v>
       </c>
-      <c r="E21" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F21" t="n">
-        <v>36.7</v>
+        <v>37.1</v>
       </c>
       <c r="G21" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9413,19 +9413,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1264</v>
+        <v>1343</v>
       </c>
       <c r="D23" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E23" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="F23" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="G23" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9452,19 +9452,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1391</v>
+        <v>1479</v>
       </c>
       <c r="D24" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="E24" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="F24" t="n">
-        <v>37.5</v>
+        <v>37.6</v>
       </c>
       <c r="G24" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9491,19 +9491,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D25" t="n">
-        <v>51</v>
+        <v>50.7</v>
       </c>
       <c r="E25" t="n">
-        <v>49</v>
+        <v>49.3</v>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9530,19 +9530,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1398</v>
+        <v>1490</v>
       </c>
       <c r="D26" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="E26" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="F26" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="G26" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9556,7 +9556,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
@@ -9569,13 +9569,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1404</v>
+        <v>1496</v>
       </c>
       <c r="D27" t="n">
-        <v>50.6</v>
+        <v>50.2</v>
       </c>
       <c r="E27" t="n">
-        <v>49.4</v>
+        <v>49.8</v>
       </c>
       <c r="F27" t="n">
         <v>38.7</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1404</v>
+        <v>1496</v>
       </c>
       <c r="D28" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
       <c r="E28" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>40.4</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="29">
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1399</v>
+        <v>1490</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>49.7</v>
       </c>
       <c r="E29" t="n">
-        <v>51</v>
+        <v>50.3</v>
       </c>
       <c r="F29" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="G29" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1394</v>
+        <v>1483</v>
       </c>
       <c r="D30" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="E30" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="F30" t="n">
-        <v>41.4</v>
+        <v>42.1</v>
       </c>
       <c r="G30" t="n">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9712,7 +9712,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1268</v>
+        <v>1348</v>
       </c>
       <c r="D31" t="n">
-        <v>49.8</v>
+        <v>50.1</v>
       </c>
       <c r="E31" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="F31" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="G31" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -9764,19 +9764,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1402</v>
+        <v>1492</v>
       </c>
       <c r="D32" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E32" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F32" t="n">
-        <v>43.2</v>
+        <v>43.5</v>
       </c>
       <c r="G32" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9790,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33">
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1396</v>
+        <v>1486</v>
       </c>
       <c r="D33" t="n">
-        <v>48.6</v>
+        <v>48.1</v>
       </c>
       <c r="E33" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
       <c r="F33" t="n">
-        <v>43.9</v>
+        <v>44.4</v>
       </c>
       <c r="G33" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9838,23 +9838,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1402</v>
+        <v>1483</v>
       </c>
       <c r="D34" t="n">
-        <v>47.9</v>
+        <v>51.1</v>
       </c>
       <c r="E34" t="n">
-        <v>52.1</v>
+        <v>48.9</v>
       </c>
       <c r="F34" t="n">
-        <v>44</v>
+        <v>44.6</v>
       </c>
       <c r="G34" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9877,17 +9877,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1392</v>
+        <v>1493</v>
       </c>
       <c r="D35" t="n">
-        <v>51.6</v>
+        <v>47.8</v>
       </c>
       <c r="E35" t="n">
-        <v>48.4</v>
+        <v>52.2</v>
       </c>
       <c r="F35" t="n">
         <v>44.8</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1384</v>
+        <v>1474</v>
       </c>
       <c r="D36" t="n">
-        <v>52.5</v>
+        <v>52.8</v>
       </c>
       <c r="E36" t="n">
-        <v>47.5</v>
+        <v>47.2</v>
       </c>
       <c r="F36" t="n">
-        <v>45.6</v>
+        <v>45.2</v>
       </c>
       <c r="G36" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37">
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1388</v>
+        <v>1479</v>
       </c>
       <c r="D37" t="n">
-        <v>49.9</v>
+        <v>50.2</v>
       </c>
       <c r="E37" t="n">
-        <v>50.1</v>
+        <v>49.8</v>
       </c>
       <c r="F37" t="n">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="G37" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1266</v>
+        <v>1346</v>
       </c>
       <c r="D38" t="n">
         <v>49.4</v>
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1366</v>
+        <v>1458</v>
       </c>
       <c r="D39" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E39" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F39" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10076,19 +10076,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>341</v>
+        <v>360</v>
       </c>
       <c r="D40" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="E40" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="F40" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="G40" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10115,19 +10115,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1395</v>
+        <v>1483</v>
       </c>
       <c r="D41" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="E41" t="n">
-        <v>49.3</v>
+        <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>51.8</v>
+        <v>51.2</v>
       </c>
       <c r="G41" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1402</v>
+        <v>1493</v>
       </c>
       <c r="D42" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="E42" t="n">
-        <v>54.6</v>
+        <v>54.7</v>
       </c>
       <c r="F42" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="G42" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10193,19 +10193,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1379</v>
+        <v>1469</v>
       </c>
       <c r="D43" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="E43" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="F43" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="G43" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10232,19 +10232,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1352</v>
+        <v>1437</v>
       </c>
       <c r="D44" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E44" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F44" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="G44" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1400</v>
+        <v>1490</v>
       </c>
       <c r="D45" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="E45" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="F45" t="n">
-        <v>53.8</v>
+        <v>53.6</v>
       </c>
       <c r="G45" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10310,7 +10310,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1394</v>
+        <v>1483</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -10319,10 +10319,10 @@
         <v>50.4</v>
       </c>
       <c r="F46" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="G46" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10349,19 +10349,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1399</v>
+        <v>1490</v>
       </c>
       <c r="D47" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="E47" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="F47" t="n">
-        <v>55.5</v>
+        <v>55.4</v>
       </c>
       <c r="G47" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10388,13 +10388,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1368</v>
+        <v>1457</v>
       </c>
       <c r="D48" t="n">
-        <v>51.1</v>
+        <v>50.5</v>
       </c>
       <c r="E48" t="n">
-        <v>48.9</v>
+        <v>49.5</v>
       </c>
       <c r="F48" t="n">
         <v>55.6</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="49">
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1282</v>
+        <v>1369</v>
       </c>
       <c r="D49" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="E49" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="F49" t="n">
-        <v>57.8</v>
+        <v>57.3</v>
       </c>
       <c r="G49" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10466,19 +10466,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1380</v>
+        <v>1469</v>
       </c>
       <c r="D50" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E50" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F50" t="n">
-        <v>59.3</v>
+        <v>58.8</v>
       </c>
       <c r="G50" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1388</v>
+        <v>1477</v>
       </c>
       <c r="D51" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>59.4</v>
+        <v>59.6</v>
       </c>
       <c r="G51" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1390</v>
+        <v>1480</v>
       </c>
       <c r="D52" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E52" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="F52" t="n">
-        <v>60.4</v>
+        <v>59.9</v>
       </c>
       <c r="G52" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1387</v>
+        <v>1472</v>
       </c>
       <c r="D53" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="E53" t="n">
-        <v>51.3</v>
+        <v>51.6</v>
       </c>
       <c r="F53" t="n">
-        <v>64.2</v>
+        <v>63.7</v>
       </c>
       <c r="G53" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54">
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1386</v>
+        <v>1475</v>
       </c>
       <c r="D54" t="n">
-        <v>48.3</v>
+        <v>47.9</v>
       </c>
       <c r="E54" t="n">
-        <v>51.7</v>
+        <v>52.1</v>
       </c>
       <c r="F54" t="n">
-        <v>64.40000000000001</v>
+        <v>63.8</v>
       </c>
       <c r="G54" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55">
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1398</v>
+        <v>1489</v>
       </c>
       <c r="D55" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E55" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F55" t="n">
-        <v>70</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,19 +10700,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1390</v>
+        <v>1482</v>
       </c>
       <c r="D56" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E56" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F56" t="n">
-        <v>74.8</v>
+        <v>75.2</v>
       </c>
       <c r="G56" t="n">
-        <v>24.8</v>
+        <v>25.2</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1404</v>
+        <v>1495</v>
       </c>
       <c r="D57" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E57" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F57" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G57" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,13 +10778,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1408</v>
+        <v>1500</v>
       </c>
       <c r="D58" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E58" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F58" t="n">
         <v>82.5</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1408</v>
+        <v>1500</v>
       </c>
       <c r="D59" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E59" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F59" t="n">
-        <v>94.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="G59" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10856,19 +10856,19 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1302</v>
+        <v>1386</v>
       </c>
       <c r="D60" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="E60" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="F60" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="G60" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>875</v>
+        <v>928</v>
       </c>
       <c r="D62" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="E62" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="F62" t="n">
-        <v>59.2</v>
+        <v>59.5</v>
       </c>
       <c r="G62" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>857</v>
+        <v>913</v>
       </c>
       <c r="D63" t="n">
-        <v>46.6</v>
+        <v>47.5</v>
       </c>
       <c r="E63" t="n">
-        <v>53.4</v>
+        <v>52.5</v>
       </c>
       <c r="F63" t="n">
-        <v>60.7</v>
+        <v>60.9</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -10999,7 +10999,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="64">
@@ -11012,19 +11012,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>860</v>
+        <v>914</v>
       </c>
       <c r="D64" t="n">
-        <v>50.7</v>
+        <v>51.4</v>
       </c>
       <c r="E64" t="n">
-        <v>49.3</v>
+        <v>48.6</v>
       </c>
       <c r="F64" t="n">
-        <v>61.4</v>
+        <v>61.8</v>
       </c>
       <c r="G64" t="n">
-        <v>11.4</v>
+        <v>11.8</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11051,19 +11051,19 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1255</v>
+        <v>1343</v>
       </c>
       <c r="D65" t="n">
-        <v>48.3</v>
+        <v>49.1</v>
       </c>
       <c r="E65" t="n">
-        <v>51.7</v>
+        <v>50.9</v>
       </c>
       <c r="F65" t="n">
-        <v>62.2</v>
+        <v>61.8</v>
       </c>
       <c r="G65" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11086,23 +11086,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>887</v>
+        <v>1070</v>
       </c>
       <c r="D66" t="n">
-        <v>51.2</v>
+        <v>50.2</v>
       </c>
       <c r="E66" t="n">
-        <v>48.8</v>
+        <v>49.8</v>
       </c>
       <c r="F66" t="n">
-        <v>62.8</v>
+        <v>62.3</v>
       </c>
       <c r="G66" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67">
@@ -11125,23 +11125,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1006</v>
+        <v>943</v>
       </c>
       <c r="D67" t="n">
-        <v>49.1</v>
+        <v>52.1</v>
       </c>
       <c r="E67" t="n">
-        <v>50.9</v>
+        <v>47.9</v>
       </c>
       <c r="F67" t="n">
-        <v>63.8</v>
+        <v>62.7</v>
       </c>
       <c r="G67" t="n">
-        <v>13.8</v>
+        <v>12.7</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1202</v>
+        <v>1464</v>
       </c>
       <c r="D68" t="n">
-        <v>47.2</v>
+        <v>50.8</v>
       </c>
       <c r="E68" t="n">
-        <v>52.8</v>
+        <v>49.2</v>
       </c>
       <c r="F68" t="n">
-        <v>64</v>
+        <v>63.7</v>
       </c>
       <c r="G68" t="n">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1374</v>
+        <v>1278</v>
       </c>
       <c r="D69" t="n">
-        <v>49.7</v>
+        <v>48</v>
       </c>
       <c r="E69" t="n">
-        <v>50.3</v>
+        <v>52</v>
       </c>
       <c r="F69" t="n">
-        <v>64.09999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="G69" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70">
@@ -11242,17 +11242,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1461</v>
+        <v>1478</v>
       </c>
       <c r="D70" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="E70" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="F70" t="n">
         <v>64.40000000000001</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71">
@@ -11281,23 +11281,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1402</v>
+        <v>1461</v>
       </c>
       <c r="D71" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
       <c r="E71" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="F71" t="n">
-        <v>64.90000000000001</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G71" t="n">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72">
@@ -11320,23 +11320,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1386</v>
+        <v>1493</v>
       </c>
       <c r="D72" t="n">
-        <v>48.8</v>
+        <v>52.5</v>
       </c>
       <c r="E72" t="n">
-        <v>51.2</v>
+        <v>47.5</v>
       </c>
       <c r="F72" t="n">
-        <v>64.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="73">
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1204</v>
+        <v>1280</v>
       </c>
       <c r="D73" t="n">
-        <v>48</v>
+        <v>48.7</v>
       </c>
       <c r="E73" t="n">
-        <v>52</v>
+        <v>51.3</v>
       </c>
       <c r="F73" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11389,7 +11389,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="74">
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>526</v>
+        <v>562</v>
       </c>
       <c r="D74" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E74" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F74" t="n">
-        <v>52.9</v>
+        <v>53</v>
       </c>
       <c r="G74" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1022</v>
+        <v>1089</v>
       </c>
       <c r="D75" t="n">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="E75" t="n">
-        <v>50.7</v>
+        <v>50</v>
       </c>
       <c r="F75" t="n">
-        <v>53.3</v>
+        <v>53.2</v>
       </c>
       <c r="G75" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11480,19 +11480,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>446</v>
+        <v>478</v>
       </c>
       <c r="D76" t="n">
-        <v>51.8</v>
+        <v>51</v>
       </c>
       <c r="E76" t="n">
-        <v>48.2</v>
+        <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>54.3</v>
+        <v>54.6</v>
       </c>
       <c r="G76" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>510</v>
+        <v>544</v>
       </c>
       <c r="D77" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="E77" t="n">
-        <v>51.4</v>
+        <v>51.3</v>
       </c>
       <c r="F77" t="n">
-        <v>55.5</v>
+        <v>56.1</v>
       </c>
       <c r="G77" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1310</v>
+        <v>1397</v>
       </c>
       <c r="D78" t="n">
-        <v>50.9</v>
+        <v>51.3</v>
       </c>
       <c r="E78" t="n">
-        <v>49.1</v>
+        <v>48.7</v>
       </c>
       <c r="F78" t="n">
         <v>69.5</v>
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1091</v>
+        <v>1158</v>
       </c>
       <c r="D79" t="n">
-        <v>46.7</v>
+        <v>47.1</v>
       </c>
       <c r="E79" t="n">
-        <v>53.3</v>
+        <v>52.9</v>
       </c>
       <c r="F79" t="n">
-        <v>62.2</v>
+        <v>62.4</v>
       </c>
       <c r="G79" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>553</v>
+        <v>590</v>
       </c>
       <c r="D80" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="E80" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="F80" t="n">
-        <v>62.2</v>
+        <v>62.9</v>
       </c>
       <c r="G80" t="n">
-        <v>12.2</v>
+        <v>12.9</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81">
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1087</v>
+        <v>1159</v>
       </c>
       <c r="D81" t="n">
-        <v>46.7</v>
+        <v>47.3</v>
       </c>
       <c r="E81" t="n">
-        <v>53.3</v>
+        <v>52.7</v>
       </c>
       <c r="F81" t="n">
-        <v>64.3</v>
+        <v>64.2</v>
       </c>
       <c r="G81" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="D82" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="E82" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F82" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11749,23 +11749,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>363</v>
+        <v>400</v>
       </c>
       <c r="D83" t="n">
-        <v>46.8</v>
+        <v>47.8</v>
       </c>
       <c r="E83" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="84">
@@ -11788,23 +11788,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="D84" t="n">
-        <v>47.3</v>
+        <v>46.5</v>
       </c>
       <c r="E84" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="F84" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="G84" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11827,23 +11827,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="D85" t="n">
-        <v>49.7</v>
+        <v>46.3</v>
       </c>
       <c r="E85" t="n">
-        <v>50.3</v>
+        <v>53.7</v>
       </c>
       <c r="F85" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="G85" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11866,23 +11866,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>379</v>
+        <v>407</v>
       </c>
       <c r="D86" t="n">
-        <v>45.1</v>
+        <v>50.1</v>
       </c>
       <c r="E86" t="n">
-        <v>54.9</v>
+        <v>49.9</v>
       </c>
       <c r="F86" t="n">
-        <v>57.3</v>
+        <v>56.5</v>
       </c>
       <c r="G86" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87">
@@ -11909,13 +11909,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="D87" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="E87" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="F87" t="n">
         <v>58</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88">
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D88" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="E88" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="F88" t="n">
-        <v>62.4</v>
+        <v>61.8</v>
       </c>
       <c r="G88" t="n">
-        <v>12.4</v>
+        <v>11.8</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89">
@@ -11987,19 +11987,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>377</v>
+        <v>402</v>
       </c>
       <c r="D89" t="n">
-        <v>47.7</v>
+        <v>49.5</v>
       </c>
       <c r="E89" t="n">
-        <v>52.3</v>
+        <v>50.5</v>
       </c>
       <c r="F89" t="n">
-        <v>63.9</v>
+        <v>62.9</v>
       </c>
       <c r="G89" t="n">
-        <v>13.9</v>
+        <v>12.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12022,23 +12022,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="E90" t="n">
-        <v>48.5</v>
+        <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>65.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>15.1</v>
+        <v>14.1</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91">
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>386</v>
+        <v>416</v>
       </c>
       <c r="D91" t="n">
-        <v>48.7</v>
+        <v>53.1</v>
       </c>
       <c r="E91" t="n">
-        <v>51.3</v>
+        <v>46.9</v>
       </c>
       <c r="F91" t="n">
-        <v>65.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G91" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92">
@@ -12104,19 +12104,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D92" t="n">
-        <v>49.1</v>
+        <v>51.4</v>
       </c>
       <c r="E92" t="n">
-        <v>50.9</v>
+        <v>48.6</v>
       </c>
       <c r="F92" t="n">
-        <v>65.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>15.9</v>
+        <v>14.6</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="D93" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
       <c r="E93" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="F93" t="n">
-        <v>72</v>
+        <v>70.7</v>
       </c>
       <c r="G93" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12178,23 +12178,23 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1409</v>
+        <v>1343</v>
       </c>
       <c r="D94" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="E94" t="n">
         <v>49.5</v>
       </c>
-      <c r="E94" t="n">
-        <v>50.5</v>
-      </c>
       <c r="F94" t="n">
-        <v>56.8</v>
+        <v>56.4</v>
       </c>
       <c r="G94" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12217,23 +12217,23 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1258</v>
+        <v>1501</v>
       </c>
       <c r="D95" t="n">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="E95" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="F95" t="n">
-        <v>57.1</v>
+        <v>56.6</v>
       </c>
       <c r="G95" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="96">
@@ -12260,19 +12260,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1371</v>
+        <v>1462</v>
       </c>
       <c r="D96" t="n">
-        <v>52.4</v>
+        <v>52.6</v>
       </c>
       <c r="E96" t="n">
-        <v>47.6</v>
+        <v>47.4</v>
       </c>
       <c r="F96" t="n">
-        <v>57.8</v>
+        <v>57.3</v>
       </c>
       <c r="G96" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12299,19 +12299,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1391</v>
+        <v>1482</v>
       </c>
       <c r="D97" t="n">
-        <v>48.9</v>
+        <v>49.7</v>
       </c>
       <c r="E97" t="n">
-        <v>51.1</v>
+        <v>50.3</v>
       </c>
       <c r="F97" t="n">
-        <v>58.2</v>
+        <v>57.6</v>
       </c>
       <c r="G97" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98">
@@ -12338,19 +12338,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D98" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E98" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F98" t="n">
-        <v>58.9</v>
+        <v>58.3</v>
       </c>
       <c r="G98" t="n">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12377,19 +12377,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1410</v>
+        <v>1502</v>
       </c>
       <c r="D99" t="n">
-        <v>49.6</v>
+        <v>50.5</v>
       </c>
       <c r="E99" t="n">
-        <v>50.4</v>
+        <v>49.5</v>
       </c>
       <c r="F99" t="n">
-        <v>59.1</v>
+        <v>58.7</v>
       </c>
       <c r="G99" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12412,23 +12412,23 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#BNBUSD</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1410</v>
+        <v>1498</v>
       </c>
       <c r="D100" t="n">
-        <v>49.8</v>
+        <v>51</v>
       </c>
       <c r="E100" t="n">
-        <v>50.2</v>
+        <v>49</v>
       </c>
       <c r="F100" t="n">
-        <v>59.4</v>
+        <v>59.1</v>
       </c>
       <c r="G100" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="101">
@@ -12451,23 +12451,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#BNBUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1406</v>
+        <v>1502</v>
       </c>
       <c r="D101" t="n">
-        <v>50.9</v>
+        <v>50.3</v>
       </c>
       <c r="E101" t="n">
-        <v>49.1</v>
+        <v>49.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.6</v>
+        <v>59.3</v>
       </c>
       <c r="G101" t="n">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1390</v>
+        <v>1481</v>
       </c>
       <c r="D102" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="E102" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="F102" t="n">
-        <v>60.2</v>
+        <v>59.8</v>
       </c>
       <c r="G102" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1360</v>
+        <v>1450</v>
       </c>
       <c r="D103" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E103" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F103" t="n">
-        <v>61</v>
+        <v>60.3</v>
       </c>
       <c r="G103" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38114</v>
+        <v>38203</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38587</v>
+        <v>38678</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12808,10 +12808,10 @@
         <v>49.3</v>
       </c>
       <c r="F6" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38107</v>
+        <v>38198</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>37930</v>
+        <v>38016</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38390</v>
+        <v>38479</v>
       </c>
       <c r="D9" t="n">
         <v>50</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38676</v>
+        <v>38766</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,13 +12994,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38729</v>
+        <v>38821</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E11" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F11" t="n">
         <v>51.8</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38737</v>
+        <v>38828</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,19 +13072,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38560</v>
+        <v>38647</v>
       </c>
       <c r="D13" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E13" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F13" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -13098,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38622</v>
+        <v>38712</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36793</v>
+        <v>36878</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38796</v>
+        <v>38888</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38330</v>
+        <v>38420</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35058</v>
+        <v>35137</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38866</v>
+        <v>38958</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38680</v>
+        <v>38772</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38729</v>
+        <v>38817</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38868</v>
+        <v>38960</v>
       </c>
       <c r="D25" t="n">
         <v>49.9</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38925</v>
+        <v>39017</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35228</v>
+        <v>35308</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38950</v>
+        <v>39042</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38958</v>
+        <v>39050</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38672</v>
+        <v>38761</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38704</v>
+        <v>38795</v>
       </c>
       <c r="D31" t="n">
         <v>49.4</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38709</v>
+        <v>38800</v>
       </c>
       <c r="D32" t="n">
         <v>49.2</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38732</v>
+        <v>38822</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38668</v>
+        <v>38758</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -13900,10 +13900,10 @@
         <v>50.8</v>
       </c>
       <c r="F34" t="n">
-        <v>45.7</v>
+        <v>45.8</v>
       </c>
       <c r="G34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38669</v>
+        <v>38760</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35113</v>
+        <v>35193</v>
       </c>
       <c r="D36" t="n">
         <v>49.9</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38506</v>
+        <v>38597</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,13 +14047,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37842</v>
+        <v>37927</v>
       </c>
       <c r="D38" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="E38" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="F38" t="n">
         <v>49.3</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38664</v>
+        <v>38755</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8170</v>
+        <v>8189</v>
       </c>
       <c r="D40" t="n">
         <v>51.2</v>
@@ -14134,10 +14134,10 @@
         <v>48.8</v>
       </c>
       <c r="F40" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38342</v>
+        <v>38432</v>
       </c>
       <c r="D41" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F41" t="n">
         <v>50.6</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38402</v>
+        <v>38492</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38441</v>
+        <v>38532</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38365</v>
+        <v>38454</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14307,7 +14307,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45">
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38012</v>
+        <v>38101</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38165</v>
+        <v>38257</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38546</v>
+        <v>38636</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38585</v>
+        <v>38673</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14446,10 +14446,10 @@
         <v>48.9</v>
       </c>
       <c r="F48" t="n">
-        <v>55.3</v>
+        <v>55.2</v>
       </c>
       <c r="G48" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35952</v>
+        <v>36039</v>
       </c>
       <c r="D49" t="n">
         <v>50.4</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38289</v>
+        <v>38378</v>
       </c>
       <c r="D50" t="n">
         <v>50.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38427</v>
+        <v>38516</v>
       </c>
       <c r="D51" t="n">
         <v>49.4</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38469</v>
+        <v>38559</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38341</v>
+        <v>38430</v>
       </c>
       <c r="D53" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E53" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F53" t="n">
         <v>61.5</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38379</v>
+        <v>38464</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,13 +14710,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38561</v>
+        <v>38652</v>
       </c>
       <c r="D55" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E55" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F55" t="n">
         <v>65.7</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38261</v>
+        <v>38353</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38626</v>
+        <v>38717</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38708</v>
+        <v>38800</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>38910</v>
+        <v>39002</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35323</v>
+        <v>35407</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14914,10 +14914,10 @@
         <v>49.2</v>
       </c>
       <c r="F60" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37718</v>
+        <v>37808</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23547</v>
+        <v>23600</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>23965</v>
+        <v>24019</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>23988</v>
+        <v>24044</v>
       </c>
       <c r="D65" t="n">
         <v>50.9</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38613</v>
+        <v>38704</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38117</v>
+        <v>38209</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68">
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21378</v>
+        <v>21434</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36378</v>
+        <v>36466</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30752</v>
+        <v>30828</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33222</v>
+        <v>33298</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26205</v>
+        <v>26269</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74">
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14306</v>
+        <v>14340</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14110</v>
+        <v>14142</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15244</v>
+        <v>15280</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26817</v>
+        <v>26884</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36081</v>
+        <v>36168</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28813</v>
+        <v>28880</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15874</v>
+        <v>15911</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81">
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28060</v>
+        <v>28132</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10494</v>
+        <v>10519</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10499</v>
+        <v>10525</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10277</v>
+        <v>10303</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10796</v>
+        <v>10821</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15919,19 +15919,19 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10281</v>
+        <v>10305</v>
       </c>
       <c r="D86" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="E86" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="F86" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G86" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="87">
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10752</v>
+        <v>10777</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -15997,13 +15997,13 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10856</v>
+        <v>10881</v>
       </c>
       <c r="D88" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E88" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F88" t="n">
         <v>57.8</v>
@@ -16036,13 +16036,13 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10996</v>
+        <v>11022</v>
       </c>
       <c r="D89" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E89" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F89" t="n">
         <v>58.4</v>
@@ -16075,19 +16075,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10996</v>
+        <v>11022</v>
       </c>
       <c r="D90" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E90" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F90" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="G90" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91">
@@ -16114,19 +16114,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10922</v>
+        <v>10948</v>
       </c>
       <c r="D91" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="E91" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="F91" t="n">
-        <v>59.5</v>
+        <v>59.4</v>
       </c>
       <c r="G91" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10338</v>
+        <v>10364</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,13 +16192,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10266</v>
+        <v>10289</v>
       </c>
       <c r="D93" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E93" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F93" t="n">
         <v>65.5</v>
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38141</v>
+        <v>38232</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38753</v>
+        <v>38845</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36334</v>
+        <v>36419</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38869</v>
+        <v>38961</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38065</v>
+        <v>38155</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38658</v>
+        <v>38749</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16465,13 +16465,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38263</v>
+        <v>38355</v>
       </c>
       <c r="D100" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E100" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F100" t="n">
         <v>54.4</v>
@@ -16491,7 +16491,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101">
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38517</v>
+        <v>38608</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>38946</v>
+        <v>39038</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -16582,13 +16582,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>38967</v>
+        <v>39059</v>
       </c>
       <c r="D103" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E103" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F103" t="n">
         <v>55</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1498</v>
+        <v>1438</v>
       </c>
       <c r="D2" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="E2" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="F2" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1491</v>
+        <v>1431</v>
       </c>
       <c r="D3" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="E3" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="F3" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -570,23 +570,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1477</v>
+        <v>1431</v>
       </c>
       <c r="D4" t="n">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
       <c r="E4" t="n">
-        <v>48.9</v>
+        <v>50.5</v>
       </c>
       <c r="F4" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1490</v>
+        <v>1382</v>
       </c>
       <c r="D5" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="E5" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="F5" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -639,7 +639,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -648,17 +648,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1440</v>
+        <v>1418</v>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>51.5</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="F6" t="n">
         <v>47.2</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -687,20 +687,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>EURCAD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1488</v>
+        <v>1415</v>
       </c>
       <c r="D7" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>45.1</v>
+        <v>54.9</v>
       </c>
       <c r="G7" t="n">
         <v>4.9</v>
@@ -726,23 +726,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURCAD</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1472</v>
+        <v>1428</v>
       </c>
       <c r="D8" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>44.8</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1492</v>
+        <v>1431</v>
       </c>
       <c r="D9" t="n">
-        <v>49.1</v>
+        <v>49.8</v>
       </c>
       <c r="E9" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="F9" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1461</v>
+        <v>1401</v>
       </c>
       <c r="D10" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="E10" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F10" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="G10" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1468</v>
+        <v>1408</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -856,10 +856,10 @@
         <v>49.9</v>
       </c>
       <c r="F11" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12">
@@ -889,16 +889,16 @@
         <v>1469</v>
       </c>
       <c r="D12" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="E12" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F12" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="G12" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D13" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="E13" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="F13" t="n">
-        <v>40.7</v>
+        <v>40.3</v>
       </c>
       <c r="G13" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -964,19 +964,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="D14" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="E14" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="F14" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="G14" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="D15" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
       <c r="E15" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="F15" t="n">
-        <v>62.6</v>
+        <v>62.3</v>
       </c>
       <c r="G15" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="D16" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="E16" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F16" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="G16" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1458</v>
+        <v>1406</v>
       </c>
       <c r="D17" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E17" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F17" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1346</v>
+        <v>1285</v>
       </c>
       <c r="D18" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F18" t="n">
         <v>49.4</v>
       </c>
-      <c r="E18" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="F18" t="n">
-        <v>49</v>
-      </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1146,7 +1146,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>360</v>
+        <v>1422</v>
       </c>
       <c r="D19" t="n">
-        <v>49.2</v>
+        <v>51.3</v>
       </c>
       <c r="E19" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="F19" t="n">
         <v>51.1</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>7</v>
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1483</v>
+        <v>341</v>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>49.9</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>50.1</v>
       </c>
       <c r="F20" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -1237,19 +1237,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1493</v>
+        <v>1434</v>
       </c>
       <c r="D21" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="E21" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="F21" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1469</v>
+        <v>1409</v>
       </c>
       <c r="D22" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="E22" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="F22" t="n">
-        <v>52.5</v>
+        <v>52.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1315,19 +1315,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1437</v>
+        <v>1379</v>
       </c>
       <c r="D23" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E23" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F23" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1490</v>
+        <v>1430</v>
       </c>
       <c r="D24" t="n">
         <v>48.5</v>
@@ -1363,10 +1363,10 @@
         <v>51.5</v>
       </c>
       <c r="F24" t="n">
-        <v>53.6</v>
+        <v>53.1</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1483</v>
+        <v>1422</v>
       </c>
       <c r="D25" t="n">
-        <v>49.6</v>
+        <v>50</v>
       </c>
       <c r="E25" t="n">
-        <v>50.4</v>
+        <v>50</v>
       </c>
       <c r="F25" t="n">
-        <v>54</v>
+        <v>46.3</v>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1479</v>
+        <v>1424</v>
       </c>
       <c r="D26" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="E26" t="n">
-        <v>49.8</v>
+        <v>50.5</v>
       </c>
       <c r="F26" t="n">
-        <v>46</v>
+        <v>54.2</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1474</v>
+        <v>1419</v>
       </c>
       <c r="D27" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="E27" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="F27" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="G27" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1506,23 +1506,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1493</v>
+        <v>1399</v>
       </c>
       <c r="D28" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E28" t="n">
-        <v>52.2</v>
+        <v>49.7</v>
       </c>
       <c r="F28" t="n">
-        <v>44.8</v>
+        <v>55</v>
       </c>
       <c r="G28" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -1545,23 +1545,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1490</v>
+        <v>1434</v>
       </c>
       <c r="D29" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="E29" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="F29" t="n">
-        <v>55.4</v>
+        <v>44.9</v>
       </c>
       <c r="G29" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1483</v>
+        <v>1424</v>
       </c>
       <c r="D30" t="n">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="E30" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="F30" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="G30" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1486</v>
+        <v>1428</v>
       </c>
       <c r="D31" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="F31" t="n">
-        <v>44.4</v>
+        <v>55.5</v>
       </c>
       <c r="G31" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1457</v>
+        <v>1426</v>
       </c>
       <c r="D32" t="n">
-        <v>50.5</v>
+        <v>47.9</v>
       </c>
       <c r="E32" t="n">
-        <v>49.5</v>
+        <v>52.1</v>
       </c>
       <c r="F32" t="n">
-        <v>55.6</v>
+        <v>44.5</v>
       </c>
       <c r="G32" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1492</v>
+        <v>1432</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -1714,10 +1714,10 @@
         <v>50.5</v>
       </c>
       <c r="F33" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="G33" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1348</v>
+        <v>1288</v>
       </c>
       <c r="D34" t="n">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
       <c r="E34" t="n">
-        <v>49.9</v>
+        <v>50.7</v>
       </c>
       <c r="F34" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="G34" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1369</v>
+        <v>1319</v>
       </c>
       <c r="D35" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E35" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F35" t="n">
-        <v>57.3</v>
+        <v>57.5</v>
       </c>
       <c r="G35" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
@@ -1822,13 +1822,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1483</v>
+        <v>1422</v>
       </c>
       <c r="D36" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E36" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F36" t="n">
         <v>42.1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1469</v>
+        <v>1430</v>
       </c>
       <c r="D37" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="E37" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="F37" t="n">
-        <v>58.8</v>
+        <v>41.5</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38">
@@ -1896,23 +1896,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1490</v>
+        <v>1410</v>
       </c>
       <c r="D38" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="E38" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="F38" t="n">
-        <v>40.8</v>
+        <v>58.6</v>
       </c>
       <c r="G38" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -1939,33 +1939,33 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1477</v>
+        <v>1417</v>
       </c>
       <c r="D39" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F39" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="G39" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Forex Minor</t>
+        </is>
+      </c>
+      <c r="J39" t="b">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>50</v>
-      </c>
-      <c r="E39" t="n">
-        <v>50</v>
-      </c>
-      <c r="F39" t="n">
-        <v>59.6</v>
-      </c>
-      <c r="G39" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Forex Minor</t>
-        </is>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>55</v>
       </c>
     </row>
     <row r="40">
@@ -1974,20 +1974,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>AUDCAD</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1496</v>
+        <v>1420</v>
       </c>
       <c r="D40" t="n">
-        <v>50.5</v>
+        <v>48.8</v>
       </c>
       <c r="E40" t="n">
-        <v>49.5</v>
+        <v>51.2</v>
       </c>
       <c r="F40" t="n">
-        <v>40.4</v>
+        <v>59.6</v>
       </c>
       <c r="G40" t="n">
         <v>9.6</v>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDCAD</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1480</v>
+        <v>1436</v>
       </c>
       <c r="D41" t="n">
-        <v>48.9</v>
+        <v>50.1</v>
       </c>
       <c r="E41" t="n">
-        <v>51.1</v>
+        <v>49.9</v>
       </c>
       <c r="F41" t="n">
-        <v>59.9</v>
+        <v>39.9</v>
       </c>
       <c r="G41" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2040,7 +2040,7 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>59</v>
@@ -2052,23 +2052,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1496</v>
+        <v>1431</v>
       </c>
       <c r="D42" t="n">
-        <v>50.2</v>
+        <v>51.9</v>
       </c>
       <c r="E42" t="n">
-        <v>49.8</v>
+        <v>48.1</v>
       </c>
       <c r="F42" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="G42" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2091,23 +2091,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1490</v>
+        <v>1442</v>
       </c>
       <c r="D43" t="n">
-        <v>52.1</v>
+        <v>50.8</v>
       </c>
       <c r="E43" t="n">
-        <v>47.9</v>
+        <v>49.2</v>
       </c>
       <c r="F43" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="G43" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>64</v>
@@ -2130,23 +2130,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1502</v>
+        <v>1435</v>
       </c>
       <c r="D44" t="n">
-        <v>50.7</v>
+        <v>49.8</v>
       </c>
       <c r="E44" t="n">
-        <v>49.3</v>
+        <v>50.2</v>
       </c>
       <c r="F44" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="G44" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="J44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>65</v>
@@ -2169,23 +2169,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1479</v>
+        <v>1283</v>
       </c>
       <c r="D45" t="n">
-        <v>48.3</v>
+        <v>50.6</v>
       </c>
       <c r="E45" t="n">
-        <v>51.7</v>
+        <v>49.4</v>
       </c>
       <c r="F45" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="G45" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1343</v>
+        <v>1500</v>
       </c>
       <c r="D46" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E46" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F46" t="n">
-        <v>37.5</v>
+        <v>37.1</v>
       </c>
       <c r="G46" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1499</v>
+        <v>1416</v>
       </c>
       <c r="D47" t="n">
-        <v>50.1</v>
+        <v>48</v>
       </c>
       <c r="E47" t="n">
-        <v>49.9</v>
+        <v>52</v>
       </c>
       <c r="F47" t="n">
-        <v>37.1</v>
+        <v>63.3</v>
       </c>
       <c r="G47" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="J47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48">
@@ -2286,23 +2286,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1500</v>
+        <v>1422</v>
       </c>
       <c r="D48" t="n">
-        <v>51.1</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>48.9</v>
+        <v>52</v>
       </c>
       <c r="F48" t="n">
-        <v>37.1</v>
+        <v>36.7</v>
       </c>
       <c r="G48" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="49">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1472</v>
+        <v>1439</v>
       </c>
       <c r="D49" t="n">
-        <v>48.4</v>
+        <v>50</v>
       </c>
       <c r="E49" t="n">
-        <v>51.6</v>
+        <v>50</v>
       </c>
       <c r="F49" t="n">
-        <v>63.7</v>
+        <v>36.4</v>
       </c>
       <c r="G49" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
@@ -2364,20 +2364,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1502</v>
+        <v>1412</v>
       </c>
       <c r="D50" t="n">
-        <v>51.4</v>
+        <v>48.5</v>
       </c>
       <c r="E50" t="n">
-        <v>48.6</v>
+        <v>51.5</v>
       </c>
       <c r="F50" t="n">
-        <v>36.3</v>
+        <v>63.7</v>
       </c>
       <c r="G50" t="n">
         <v>13.7</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51">
@@ -2403,23 +2403,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1475</v>
+        <v>1442</v>
       </c>
       <c r="D51" t="n">
-        <v>47.9</v>
+        <v>51.4</v>
       </c>
       <c r="E51" t="n">
-        <v>52.1</v>
+        <v>48.6</v>
       </c>
       <c r="F51" t="n">
-        <v>63.8</v>
+        <v>36.1</v>
       </c>
       <c r="G51" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1465</v>
+        <v>1407</v>
       </c>
       <c r="D52" t="n">
-        <v>50.2</v>
+        <v>49.5</v>
       </c>
       <c r="E52" t="n">
-        <v>49.8</v>
+        <v>50.5</v>
       </c>
       <c r="F52" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="G52" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D53" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E53" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F53" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="G53" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1401</v>
+        <v>1344</v>
       </c>
       <c r="D54" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E54" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="G54" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2550,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="55">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1489</v>
+        <v>1429</v>
       </c>
       <c r="D55" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="E55" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="F55" t="n">
-        <v>69.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1482</v>
+        <v>1422</v>
       </c>
       <c r="D56" t="n">
         <v>49.2</v>
@@ -2611,10 +2611,10 @@
         <v>50.8</v>
       </c>
       <c r="F56" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="G56" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1495</v>
+        <v>1434</v>
       </c>
       <c r="D57" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E57" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F57" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="G57" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1500</v>
+        <v>1441</v>
       </c>
       <c r="D58" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E58" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F58" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="D59" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E59" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F59" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1462</v>
+        <v>1333</v>
       </c>
       <c r="D60" t="n">
-        <v>50.9</v>
+        <v>52.7</v>
       </c>
       <c r="E60" t="n">
-        <v>49.1</v>
+        <v>47.3</v>
       </c>
       <c r="F60" t="n">
-        <v>40.6</v>
+        <v>40.1</v>
       </c>
       <c r="G60" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D61" t="n">
-        <v>51.9</v>
+        <v>51.3</v>
       </c>
       <c r="E61" t="n">
-        <v>48.1</v>
+        <v>48.7</v>
       </c>
       <c r="F61" t="n">
-        <v>40.3</v>
+        <v>39.5</v>
       </c>
       <c r="G61" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>928</v>
+        <v>872</v>
       </c>
       <c r="D62" t="n">
         <v>49.7</v>
@@ -2845,10 +2845,10 @@
         <v>50.3</v>
       </c>
       <c r="F62" t="n">
-        <v>59.5</v>
+        <v>59.9</v>
       </c>
       <c r="G62" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>913</v>
+        <v>859</v>
       </c>
       <c r="D63" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="E63" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="F63" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="G63" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2914,19 +2914,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>914</v>
+        <v>860</v>
       </c>
       <c r="D64" t="n">
-        <v>51.4</v>
+        <v>50.7</v>
       </c>
       <c r="E64" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="F64" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
       <c r="G64" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65">
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1343</v>
+        <v>1284</v>
       </c>
       <c r="D65" t="n">
         <v>49.1</v>
@@ -2962,10 +2962,10 @@
         <v>50.9</v>
       </c>
       <c r="F65" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
       <c r="G65" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66">
@@ -2992,19 +2992,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1070</v>
+        <v>1021</v>
       </c>
       <c r="D66" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E66" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
-        <v>62.3</v>
+        <v>62.8</v>
       </c>
       <c r="G66" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="67">
@@ -3031,19 +3031,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>943</v>
+        <v>888</v>
       </c>
       <c r="D67" t="n">
-        <v>52.1</v>
+        <v>51.4</v>
       </c>
       <c r="E67" t="n">
-        <v>47.9</v>
+        <v>48.6</v>
       </c>
       <c r="F67" t="n">
-        <v>62.7</v>
+        <v>63.2</v>
       </c>
       <c r="G67" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68">
@@ -3070,19 +3070,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1464</v>
+        <v>1407</v>
       </c>
       <c r="D68" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="E68" t="n">
-        <v>49.2</v>
+        <v>49.6</v>
       </c>
       <c r="F68" t="n">
-        <v>63.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1278</v>
+        <v>1433</v>
       </c>
       <c r="D69" t="n">
-        <v>48</v>
+        <v>52.8</v>
       </c>
       <c r="E69" t="n">
-        <v>52</v>
+        <v>47.2</v>
       </c>
       <c r="F69" t="n">
-        <v>63.9</v>
+        <v>64.3</v>
       </c>
       <c r="G69" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70">
@@ -3144,17 +3144,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1478</v>
+        <v>1222</v>
       </c>
       <c r="D70" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="E70" t="n">
-        <v>50.5</v>
+        <v>52.5</v>
       </c>
       <c r="F70" t="n">
         <v>64.40000000000001</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1461</v>
+        <v>1419</v>
       </c>
       <c r="D71" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="E71" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>64.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G71" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1493</v>
+        <v>1463</v>
       </c>
       <c r="D72" t="n">
-        <v>52.5</v>
+        <v>51.2</v>
       </c>
       <c r="E72" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="F72" t="n">
-        <v>64.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73">
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1280</v>
+        <v>1229</v>
       </c>
       <c r="D73" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="E73" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="F73" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3300,23 +3300,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>562</v>
+        <v>1040</v>
       </c>
       <c r="D74" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="E74" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="F74" t="n">
-        <v>53</v>
+        <v>51.8</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75">
@@ -3339,23 +3339,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1089</v>
+        <v>526</v>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>48.7</v>
       </c>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>51.3</v>
       </c>
       <c r="F75" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="76">
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="D76" t="n">
-        <v>51</v>
+        <v>51.8</v>
       </c>
       <c r="E76" t="n">
-        <v>49</v>
+        <v>48.2</v>
       </c>
       <c r="F76" t="n">
-        <v>54.6</v>
+        <v>54.3</v>
       </c>
       <c r="G76" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>544</v>
+        <v>509</v>
       </c>
       <c r="D77" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="E77" t="n">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
       <c r="F77" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G77" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1397</v>
+        <v>1336</v>
       </c>
       <c r="D78" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="E78" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="F78" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -3495,23 +3495,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EUBUND.F</t>
+          <t>UKGILT.F</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1158</v>
+        <v>564</v>
       </c>
       <c r="D79" t="n">
-        <v>47.1</v>
+        <v>49.8</v>
       </c>
       <c r="E79" t="n">
-        <v>52.9</v>
+        <v>50.2</v>
       </c>
       <c r="F79" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G79" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="80">
@@ -3534,23 +3534,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UKGILT.F</t>
+          <t>EUBUND.F</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>590</v>
+        <v>1114</v>
       </c>
       <c r="D80" t="n">
-        <v>49.8</v>
+        <v>46.9</v>
       </c>
       <c r="E80" t="n">
-        <v>50.2</v>
+        <v>53.1</v>
       </c>
       <c r="F80" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="G80" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1159</v>
+        <v>1120</v>
       </c>
       <c r="D81" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="E81" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="F81" t="n">
-        <v>64.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="82">
@@ -3612,23 +3612,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="D82" t="n">
-        <v>46.5</v>
+        <v>47.5</v>
       </c>
       <c r="E82" t="n">
-        <v>53.5</v>
+        <v>52.5</v>
       </c>
       <c r="F82" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -3651,23 +3651,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>400</v>
+        <v>365</v>
       </c>
       <c r="D83" t="n">
-        <v>47.8</v>
+        <v>47.1</v>
       </c>
       <c r="E83" t="n">
-        <v>52.2</v>
+        <v>52.9</v>
       </c>
       <c r="F83" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="D84" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="E84" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="F84" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="G84" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="D85" t="n">
-        <v>46.3</v>
+        <v>45.2</v>
       </c>
       <c r="E85" t="n">
-        <v>53.7</v>
+        <v>54.8</v>
       </c>
       <c r="F85" t="n">
-        <v>56.4</v>
+        <v>55.8</v>
       </c>
       <c r="G85" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="D86" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="E86" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="F86" t="n">
         <v>56.5</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87">
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D87" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="E87" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="F87" t="n">
         <v>58</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="D88" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E88" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="F88" t="n">
-        <v>61.8</v>
+        <v>61.4</v>
       </c>
       <c r="G88" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="89">
@@ -3889,19 +3889,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="D89" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="E89" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="F89" t="n">
-        <v>62.9</v>
+        <v>61.8</v>
       </c>
       <c r="G89" t="n">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
     </row>
     <row r="90">
@@ -3928,7 +3928,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="D90" t="n">
         <v>51</v>
@@ -3937,10 +3937,10 @@
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>64.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="G90" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="91">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="D91" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="E91" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="F91" t="n">
-        <v>64.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="G91" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="92">
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="D92" t="n">
         <v>51.4</v>
@@ -4015,10 +4015,10 @@
         <v>48.6</v>
       </c>
       <c r="F92" t="n">
-        <v>64.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="G92" t="n">
-        <v>14.6</v>
+        <v>13.8</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="D93" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E93" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F93" t="n">
-        <v>70.7</v>
+        <v>69.5</v>
       </c>
       <c r="G93" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94">
@@ -4084,19 +4084,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1343</v>
+        <v>1298</v>
       </c>
       <c r="D94" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="E94" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="F94" t="n">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="G94" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1501</v>
+        <v>1442</v>
       </c>
       <c r="D95" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E95" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F95" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="G95" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="96">
@@ -4158,23 +4158,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1462</v>
+        <v>1426</v>
       </c>
       <c r="D96" t="n">
-        <v>52.6</v>
+        <v>50.3</v>
       </c>
       <c r="E96" t="n">
-        <v>47.4</v>
+        <v>49.7</v>
       </c>
       <c r="F96" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="G96" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="97">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1482</v>
+        <v>1402</v>
       </c>
       <c r="D97" t="n">
-        <v>49.7</v>
+        <v>52.4</v>
       </c>
       <c r="E97" t="n">
-        <v>50.3</v>
+        <v>47.6</v>
       </c>
       <c r="F97" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
       <c r="G97" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98">
@@ -4240,19 +4240,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D98" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="E98" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="F98" t="n">
-        <v>58.3</v>
+        <v>57.7</v>
       </c>
       <c r="G98" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4266,7 +4266,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="99">
@@ -4279,19 +4279,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D99" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E99" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F99" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="G99" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100">
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1498</v>
+        <v>1438</v>
       </c>
       <c r="D100" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E100" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F100" t="n">
         <v>59.1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D101" t="n">
         <v>50.3</v>
@@ -4366,10 +4366,10 @@
         <v>49.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="G101" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4396,19 +4396,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1481</v>
+        <v>1421</v>
       </c>
       <c r="D102" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="E102" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="F102" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="G102" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1450</v>
+        <v>1392</v>
       </c>
       <c r="D103" t="n">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="E103" t="n">
-        <v>48.7</v>
+        <v>48.2</v>
       </c>
       <c r="F103" t="n">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="G103" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38479</v>
+        <v>38507</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F2" t="n">
         <v>49.8</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38016</v>
+        <v>38044</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38198</v>
+        <v>38225</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38766</v>
+        <v>38794</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38821</v>
+        <v>38848</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38828</v>
+        <v>38856</v>
       </c>
       <c r="D7" t="n">
         <v>51.4</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38678</v>
+        <v>38706</v>
       </c>
       <c r="D8" t="n">
         <v>50.7</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38203</v>
+        <v>38230</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4844,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38647</v>
+        <v>38675</v>
       </c>
       <c r="D10" t="n">
         <v>49.6</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38712</v>
+        <v>38739</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38740</v>
+        <v>38826</v>
       </c>
       <c r="D12" t="n">
         <v>51.2</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38534</v>
+        <v>38619</v>
       </c>
       <c r="D13" t="n">
         <v>50.3</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38484</v>
+        <v>38571</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38613</v>
+        <v>38701</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38633</v>
+        <v>38720</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38755</v>
+        <v>38783</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8189</v>
+        <v>8193</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5178,10 +5178,10 @@
         <v>48.8</v>
       </c>
       <c r="F18" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38432</v>
+        <v>38460</v>
       </c>
       <c r="D19" t="n">
         <v>50.1</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37927</v>
+        <v>37955</v>
       </c>
       <c r="D20" t="n">
         <v>50.8</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38597</v>
+        <v>38624</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,13 +5325,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35193</v>
+        <v>35212</v>
       </c>
       <c r="D22" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E22" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F22" t="n">
         <v>47.6</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38760</v>
+        <v>38788</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38492</v>
+        <v>38520</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38532</v>
+        <v>38558</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,13 +5481,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38758</v>
+        <v>38786</v>
       </c>
       <c r="D26" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E26" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F26" t="n">
         <v>45.8</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38454</v>
+        <v>38481</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38101</v>
+        <v>38128</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38257</v>
+        <v>38285</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38636</v>
+        <v>38664</v>
       </c>
       <c r="D30" t="n">
         <v>50.6</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38673</v>
+        <v>38700</v>
       </c>
       <c r="D31" t="n">
         <v>51.1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38822</v>
+        <v>38850</v>
       </c>
       <c r="D32" t="n">
         <v>49.5</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38795</v>
+        <v>38823</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38800</v>
+        <v>38828</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38761</v>
+        <v>38788</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39050</v>
+        <v>39078</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39042</v>
+        <v>39070</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36039</v>
+        <v>36066</v>
       </c>
       <c r="D38" t="n">
         <v>50.4</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35308</v>
+        <v>35327</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38378</v>
+        <v>38405</v>
       </c>
       <c r="D40" t="n">
         <v>50.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38516</v>
+        <v>38543</v>
       </c>
       <c r="D41" t="n">
         <v>49.4</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38559</v>
+        <v>38587</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38960</v>
+        <v>38988</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>39017</v>
+        <v>39045</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6192,10 +6192,10 @@
         <v>50.8</v>
       </c>
       <c r="F44" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G44" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39005</v>
+        <v>39093</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38817</v>
+        <v>38845</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38772</v>
+        <v>38800</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38958</v>
+        <v>38985</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35137</v>
+        <v>35157</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,13 +6417,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38430</v>
+        <v>38458</v>
       </c>
       <c r="D50" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E50" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F50" t="n">
         <v>61.5</v>
@@ -6452,23 +6452,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38464</v>
+        <v>38448</v>
       </c>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F51" t="n">
-        <v>62.1</v>
+        <v>38</v>
       </c>
       <c r="G51" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>92</v>
@@ -6491,20 +6491,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38420</v>
+        <v>38491</v>
       </c>
       <c r="D52" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>37.9</v>
+        <v>62.1</v>
       </c>
       <c r="G52" t="n">
         <v>12.1</v>
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="J52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>93</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38888</v>
+        <v>38916</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36878</v>
+        <v>36904</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38652</v>
+        <v>38679</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38353</v>
+        <v>38381</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38717</v>
+        <v>38744</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38800</v>
+        <v>38828</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39002</v>
+        <v>39030</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37301</v>
+        <v>37386</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6816,10 +6816,10 @@
         <v>49.6</v>
       </c>
       <c r="F60" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35407</v>
+        <v>35431</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37808</v>
+        <v>37836</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24019</v>
+        <v>24020</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38704</v>
+        <v>38732</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38209</v>
+        <v>38237</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -7119,7 +7119,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21434</v>
+        <v>21435</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36466</v>
+        <v>36488</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30828</v>
+        <v>30848</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37820</v>
+        <v>37908</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33298</v>
+        <v>33322</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26269</v>
+        <v>26284</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26884</v>
+        <v>26902</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36168</v>
+        <v>36192</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28880</v>
+        <v>28899</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28132</v>
+        <v>28147</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38232</v>
+        <v>38258</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38845</v>
+        <v>38873</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36419</v>
+        <v>36447</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38961</v>
+        <v>38989</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38155</v>
+        <v>38182</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,7 +8328,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38749</v>
+        <v>38777</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -8337,10 +8337,10 @@
         <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100">
@@ -8367,13 +8367,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38355</v>
+        <v>38383</v>
       </c>
       <c r="D100" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E100" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F100" t="n">
         <v>54.4</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38608</v>
+        <v>38636</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39038</v>
+        <v>39066</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39059</v>
+        <v>39087</v>
       </c>
       <c r="D103" t="n">
         <v>49.8</v>
@@ -8493,10 +8493,10 @@
         <v>50.2</v>
       </c>
       <c r="F103" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="G103" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -8594,19 +8594,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="D2" t="n">
-        <v>51.4</v>
+        <v>51.2</v>
       </c>
       <c r="E2" t="n">
-        <v>48.6</v>
+        <v>48.8</v>
       </c>
       <c r="F2" t="n">
-        <v>38.6</v>
+        <v>37.9</v>
       </c>
       <c r="G2" t="n">
-        <v>11.4</v>
+        <v>12.1</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1495</v>
+        <v>1493</v>
       </c>
       <c r="D3" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="E3" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="F3" t="n">
-        <v>40.7</v>
+        <v>40.3</v>
       </c>
       <c r="G3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8675,16 +8675,16 @@
         <v>1469</v>
       </c>
       <c r="D4" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="E4" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F4" t="n">
-        <v>41.9</v>
+        <v>42.3</v>
       </c>
       <c r="G4" t="n">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8698,7 +8698,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -8707,23 +8707,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CADCHF</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1461</v>
+        <v>1408</v>
       </c>
       <c r="D5" t="n">
-        <v>51.8</v>
+        <v>50.1</v>
       </c>
       <c r="E5" t="n">
-        <v>48.2</v>
+        <v>49.9</v>
       </c>
       <c r="F5" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="G5" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8737,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -8746,23 +8746,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EURCHF</t>
+          <t>CADCHF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1468</v>
+        <v>1401</v>
       </c>
       <c r="D6" t="n">
-        <v>50.1</v>
+        <v>51.9</v>
       </c>
       <c r="E6" t="n">
-        <v>49.9</v>
+        <v>48.1</v>
       </c>
       <c r="F6" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1488</v>
+        <v>1428</v>
       </c>
       <c r="D7" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1440</v>
+        <v>1382</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>49.6</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="F8" t="n">
         <v>47.2</v>
@@ -8863,23 +8863,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1490</v>
+        <v>1418</v>
       </c>
       <c r="D9" t="n">
-        <v>49.1</v>
+        <v>51.5</v>
       </c>
       <c r="E9" t="n">
-        <v>50.9</v>
+        <v>48.5</v>
       </c>
       <c r="F9" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="G9" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8902,23 +8902,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1477</v>
+        <v>1431</v>
       </c>
       <c r="D10" t="n">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
       <c r="E10" t="n">
-        <v>48.9</v>
+        <v>50.5</v>
       </c>
       <c r="F10" t="n">
-        <v>47.8</v>
+        <v>47.4</v>
       </c>
       <c r="G10" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1491</v>
+        <v>1431</v>
       </c>
       <c r="D11" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="E11" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="F11" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1498</v>
+        <v>1438</v>
       </c>
       <c r="D12" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="E12" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="F12" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1472</v>
+        <v>1415</v>
       </c>
       <c r="D13" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="E13" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9062,19 +9062,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1492</v>
+        <v>1431</v>
       </c>
       <c r="D14" t="n">
-        <v>49.1</v>
+        <v>49.8</v>
       </c>
       <c r="E14" t="n">
-        <v>50.9</v>
+        <v>50.2</v>
       </c>
       <c r="F14" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="D15" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
       <c r="E15" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="F15" t="n">
-        <v>62.6</v>
+        <v>62.3</v>
       </c>
       <c r="G15" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="D16" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="E16" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F16" t="n">
-        <v>62.8</v>
+        <v>62.9</v>
       </c>
       <c r="G16" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1401</v>
+        <v>1344</v>
       </c>
       <c r="D17" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>30.3</v>
+        <v>29.8</v>
       </c>
       <c r="G17" t="n">
-        <v>19.7</v>
+        <v>20.2</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>50.8</v>
       </c>
       <c r="E18" t="n">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="F18" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="G18" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9253,23 +9253,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1465</v>
+        <v>1442</v>
       </c>
       <c r="D19" t="n">
-        <v>50.2</v>
+        <v>51.4</v>
       </c>
       <c r="E19" t="n">
-        <v>49.8</v>
+        <v>48.6</v>
       </c>
       <c r="F19" t="n">
-        <v>35.8</v>
+        <v>36.1</v>
       </c>
       <c r="G19" t="n">
-        <v>14.2</v>
+        <v>13.9</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -9292,23 +9292,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1502</v>
+        <v>1407</v>
       </c>
       <c r="D20" t="n">
-        <v>51.4</v>
+        <v>49.5</v>
       </c>
       <c r="E20" t="n">
-        <v>48.6</v>
+        <v>50.5</v>
       </c>
       <c r="F20" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="G20" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1499</v>
+        <v>1439</v>
       </c>
       <c r="D21" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E21" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F21" t="n">
-        <v>37.1</v>
+        <v>36.4</v>
       </c>
       <c r="G21" t="n">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9370,23 +9370,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1500</v>
+        <v>1422</v>
       </c>
       <c r="D22" t="n">
-        <v>51.1</v>
+        <v>48</v>
       </c>
       <c r="E22" t="n">
-        <v>48.9</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
-        <v>37.1</v>
+        <v>36.7</v>
       </c>
       <c r="G22" t="n">
-        <v>12.9</v>
+        <v>13.3</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9409,23 +9409,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDDKK</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1343</v>
+        <v>1500</v>
       </c>
       <c r="D23" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E23" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F23" t="n">
-        <v>37.5</v>
+        <v>37.1</v>
       </c>
       <c r="G23" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9448,23 +9448,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDDKK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1479</v>
+        <v>1283</v>
       </c>
       <c r="D24" t="n">
-        <v>48.3</v>
+        <v>50.6</v>
       </c>
       <c r="E24" t="n">
-        <v>51.7</v>
+        <v>49.4</v>
       </c>
       <c r="F24" t="n">
-        <v>37.6</v>
+        <v>37.8</v>
       </c>
       <c r="G24" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9491,19 +9491,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D25" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="E25" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="F25" t="n">
-        <v>38.5</v>
+        <v>38.3</v>
       </c>
       <c r="G25" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9517,7 +9517,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -9526,23 +9526,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDCZK</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1490</v>
+        <v>1435</v>
       </c>
       <c r="D26" t="n">
-        <v>52.1</v>
+        <v>49.8</v>
       </c>
       <c r="E26" t="n">
-        <v>47.9</v>
+        <v>50.2</v>
       </c>
       <c r="F26" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="G26" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9565,23 +9565,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>USDCZK</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1496</v>
+        <v>1431</v>
       </c>
       <c r="D27" t="n">
-        <v>50.2</v>
+        <v>51.9</v>
       </c>
       <c r="E27" t="n">
-        <v>49.8</v>
+        <v>48.1</v>
       </c>
       <c r="F27" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="G27" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1496</v>
+        <v>1436</v>
       </c>
       <c r="D28" t="n">
-        <v>50.5</v>
+        <v>50.1</v>
       </c>
       <c r="E28" t="n">
-        <v>49.5</v>
+        <v>49.9</v>
       </c>
       <c r="F28" t="n">
-        <v>40.4</v>
+        <v>39.9</v>
       </c>
       <c r="G28" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1490</v>
+        <v>1430</v>
       </c>
       <c r="D29" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="E29" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="F29" t="n">
-        <v>40.8</v>
+        <v>41.5</v>
       </c>
       <c r="G29" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,13 +9686,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1483</v>
+        <v>1422</v>
       </c>
       <c r="D30" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E30" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F30" t="n">
         <v>42.1</v>
@@ -9712,7 +9712,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1348</v>
+        <v>1288</v>
       </c>
       <c r="D31" t="n">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
       <c r="E31" t="n">
-        <v>49.9</v>
+        <v>50.7</v>
       </c>
       <c r="F31" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="G31" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9751,7 +9751,7 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -9764,7 +9764,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1492</v>
+        <v>1432</v>
       </c>
       <c r="D32" t="n">
         <v>49.5</v>
@@ -9773,10 +9773,10 @@
         <v>50.5</v>
       </c>
       <c r="F32" t="n">
-        <v>43.5</v>
+        <v>44.1</v>
       </c>
       <c r="G32" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1486</v>
+        <v>1426</v>
       </c>
       <c r="D33" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="E33" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="F33" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="G33" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1483</v>
+        <v>1424</v>
       </c>
       <c r="D34" t="n">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="E34" t="n">
-        <v>48.9</v>
+        <v>49.2</v>
       </c>
       <c r="F34" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="G34" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1493</v>
+        <v>1434</v>
       </c>
       <c r="D35" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="E35" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="F35" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="G35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1474</v>
+        <v>1419</v>
       </c>
       <c r="D36" t="n">
-        <v>52.8</v>
+        <v>52.9</v>
       </c>
       <c r="E36" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="F36" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="G36" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1479</v>
+        <v>1422</v>
       </c>
       <c r="D37" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="G37" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1346</v>
+        <v>1285</v>
       </c>
       <c r="D38" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="E38" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="F38" t="n">
         <v>49.4</v>
       </c>
-      <c r="E38" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="F38" t="n">
-        <v>49</v>
-      </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39">
@@ -10037,19 +10037,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1458</v>
+        <v>1406</v>
       </c>
       <c r="D39" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E39" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F39" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10072,17 +10072,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>360</v>
+        <v>1422</v>
       </c>
       <c r="D40" t="n">
-        <v>49.2</v>
+        <v>51.3</v>
       </c>
       <c r="E40" t="n">
-        <v>50.8</v>
+        <v>48.7</v>
       </c>
       <c r="F40" t="n">
         <v>51.1</v>
@@ -10099,7 +10099,7 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>40</v>
@@ -10111,23 +10111,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1483</v>
+        <v>341</v>
       </c>
       <c r="D41" t="n">
-        <v>51</v>
+        <v>49.9</v>
       </c>
       <c r="E41" t="n">
-        <v>49</v>
+        <v>50.1</v>
       </c>
       <c r="F41" t="n">
-        <v>51.2</v>
+        <v>51.6</v>
       </c>
       <c r="G41" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>41</v>
@@ -10154,19 +10154,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1493</v>
+        <v>1434</v>
       </c>
       <c r="D42" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="E42" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="F42" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10193,19 +10193,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1469</v>
+        <v>1409</v>
       </c>
       <c r="D43" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="E43" t="n">
-        <v>52.4</v>
+        <v>52.1</v>
       </c>
       <c r="F43" t="n">
-        <v>52.5</v>
+        <v>52.1</v>
       </c>
       <c r="G43" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10219,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -10232,19 +10232,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1437</v>
+        <v>1379</v>
       </c>
       <c r="D44" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="E44" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="F44" t="n">
-        <v>52.5</v>
+        <v>52.7</v>
       </c>
       <c r="G44" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10258,7 +10258,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45">
@@ -10271,7 +10271,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1490</v>
+        <v>1430</v>
       </c>
       <c r="D45" t="n">
         <v>48.5</v>
@@ -10280,10 +10280,10 @@
         <v>51.5</v>
       </c>
       <c r="F45" t="n">
-        <v>53.6</v>
+        <v>53.1</v>
       </c>
       <c r="G45" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="46">
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1483</v>
+        <v>1424</v>
       </c>
       <c r="D46" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E46" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F46" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10345,23 +10345,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1490</v>
+        <v>1399</v>
       </c>
       <c r="D47" t="n">
-        <v>47.8</v>
+        <v>50.3</v>
       </c>
       <c r="E47" t="n">
-        <v>52.2</v>
+        <v>49.7</v>
       </c>
       <c r="F47" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
       <c r="G47" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10384,23 +10384,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1457</v>
+        <v>1428</v>
       </c>
       <c r="D48" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="E48" t="n">
-        <v>49.5</v>
+        <v>52</v>
       </c>
       <c r="F48" t="n">
-        <v>55.6</v>
+        <v>55.5</v>
       </c>
       <c r="G48" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1369</v>
+        <v>1319</v>
       </c>
       <c r="D49" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E49" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F49" t="n">
-        <v>57.3</v>
+        <v>57.5</v>
       </c>
       <c r="G49" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50">
@@ -10466,19 +10466,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1469</v>
+        <v>1410</v>
       </c>
       <c r="D50" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="E50" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F50" t="n">
-        <v>58.8</v>
+        <v>58.6</v>
       </c>
       <c r="G50" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1477</v>
+        <v>1417</v>
       </c>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="F51" t="n">
-        <v>59.6</v>
+        <v>58.9</v>
       </c>
       <c r="G51" t="n">
-        <v>9.6</v>
+        <v>8.9</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1480</v>
+        <v>1420</v>
       </c>
       <c r="D52" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="E52" t="n">
-        <v>51.1</v>
+        <v>51.2</v>
       </c>
       <c r="F52" t="n">
-        <v>59.9</v>
+        <v>59.6</v>
       </c>
       <c r="G52" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="53">
@@ -10579,23 +10579,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1472</v>
+        <v>1416</v>
       </c>
       <c r="D53" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="E53" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="F53" t="n">
-        <v>63.7</v>
+        <v>63.3</v>
       </c>
       <c r="G53" t="n">
-        <v>13.7</v>
+        <v>13.3</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54">
@@ -10618,23 +10618,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1475</v>
+        <v>1412</v>
       </c>
       <c r="D54" t="n">
-        <v>47.9</v>
+        <v>48.5</v>
       </c>
       <c r="E54" t="n">
-        <v>52.1</v>
+        <v>51.5</v>
       </c>
       <c r="F54" t="n">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="G54" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="55">
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1489</v>
+        <v>1429</v>
       </c>
       <c r="D55" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="E55" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="F55" t="n">
-        <v>69.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>19.9</v>
+        <v>20.4</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10687,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="56">
@@ -10700,7 +10700,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1482</v>
+        <v>1422</v>
       </c>
       <c r="D56" t="n">
         <v>49.2</v>
@@ -10709,10 +10709,10 @@
         <v>50.8</v>
       </c>
       <c r="F56" t="n">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="G56" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1495</v>
+        <v>1434</v>
       </c>
       <c r="D57" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E57" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="F57" t="n">
-        <v>81.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="G57" t="n">
-        <v>31.9</v>
+        <v>31.7</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1500</v>
+        <v>1441</v>
       </c>
       <c r="D58" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E58" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F58" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1500</v>
+        <v>1440</v>
       </c>
       <c r="D59" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E59" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F59" t="n">
-        <v>94.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10852,23 +10852,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1386</v>
+        <v>1464</v>
       </c>
       <c r="D60" t="n">
-        <v>51.9</v>
+        <v>51.3</v>
       </c>
       <c r="E60" t="n">
-        <v>48.1</v>
+        <v>48.7</v>
       </c>
       <c r="F60" t="n">
-        <v>40.3</v>
+        <v>39.5</v>
       </c>
       <c r="G60" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10891,23 +10891,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1462</v>
+        <v>1333</v>
       </c>
       <c r="D61" t="n">
-        <v>50.9</v>
+        <v>52.7</v>
       </c>
       <c r="E61" t="n">
-        <v>49.1</v>
+        <v>47.3</v>
       </c>
       <c r="F61" t="n">
-        <v>40.6</v>
+        <v>40.1</v>
       </c>
       <c r="G61" t="n">
-        <v>9.4</v>
+        <v>9.9</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>928</v>
+        <v>872</v>
       </c>
       <c r="D62" t="n">
         <v>49.7</v>
@@ -10943,10 +10943,10 @@
         <v>50.3</v>
       </c>
       <c r="F62" t="n">
-        <v>59.5</v>
+        <v>59.9</v>
       </c>
       <c r="G62" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63">
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>913</v>
+        <v>859</v>
       </c>
       <c r="D63" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="E63" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="F63" t="n">
-        <v>60.9</v>
+        <v>60.7</v>
       </c>
       <c r="G63" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -11012,19 +11012,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>914</v>
+        <v>860</v>
       </c>
       <c r="D64" t="n">
-        <v>51.4</v>
+        <v>50.7</v>
       </c>
       <c r="E64" t="n">
-        <v>48.6</v>
+        <v>49.3</v>
       </c>
       <c r="F64" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
       <c r="G64" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65">
@@ -11051,7 +11051,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1343</v>
+        <v>1284</v>
       </c>
       <c r="D65" t="n">
         <v>49.1</v>
@@ -11060,10 +11060,10 @@
         <v>50.9</v>
       </c>
       <c r="F65" t="n">
-        <v>61.8</v>
+        <v>62</v>
       </c>
       <c r="G65" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66">
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1070</v>
+        <v>1021</v>
       </c>
       <c r="D66" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E66" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F66" t="n">
-        <v>62.3</v>
+        <v>62.8</v>
       </c>
       <c r="G66" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67">
@@ -11129,19 +11129,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>943</v>
+        <v>888</v>
       </c>
       <c r="D67" t="n">
-        <v>52.1</v>
+        <v>51.4</v>
       </c>
       <c r="E67" t="n">
-        <v>47.9</v>
+        <v>48.6</v>
       </c>
       <c r="F67" t="n">
-        <v>62.7</v>
+        <v>63.2</v>
       </c>
       <c r="G67" t="n">
-        <v>12.7</v>
+        <v>13.2</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
@@ -11168,19 +11168,19 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1464</v>
+        <v>1407</v>
       </c>
       <c r="D68" t="n">
-        <v>50.8</v>
+        <v>50.4</v>
       </c>
       <c r="E68" t="n">
-        <v>49.2</v>
+        <v>49.6</v>
       </c>
       <c r="F68" t="n">
-        <v>63.7</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69">
@@ -11203,23 +11203,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1278</v>
+        <v>1433</v>
       </c>
       <c r="D69" t="n">
-        <v>48</v>
+        <v>52.8</v>
       </c>
       <c r="E69" t="n">
-        <v>52</v>
+        <v>47.2</v>
       </c>
       <c r="F69" t="n">
-        <v>63.9</v>
+        <v>64.3</v>
       </c>
       <c r="G69" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70">
@@ -11242,17 +11242,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1478</v>
+        <v>1222</v>
       </c>
       <c r="D70" t="n">
-        <v>49.5</v>
+        <v>47.5</v>
       </c>
       <c r="E70" t="n">
-        <v>50.5</v>
+        <v>52.5</v>
       </c>
       <c r="F70" t="n">
         <v>64.40000000000001</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71">
@@ -11281,23 +11281,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1461</v>
+        <v>1419</v>
       </c>
       <c r="D71" t="n">
-        <v>51.5</v>
+        <v>50</v>
       </c>
       <c r="E71" t="n">
-        <v>48.5</v>
+        <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>64.40000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G71" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="72">
@@ -11320,23 +11320,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1493</v>
+        <v>1463</v>
       </c>
       <c r="D72" t="n">
-        <v>52.5</v>
+        <v>51.2</v>
       </c>
       <c r="E72" t="n">
-        <v>47.5</v>
+        <v>48.8</v>
       </c>
       <c r="F72" t="n">
-        <v>64.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="G72" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73">
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1280</v>
+        <v>1229</v>
       </c>
       <c r="D73" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="E73" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="F73" t="n">
-        <v>65.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11398,23 +11398,23 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Cotton</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>562</v>
+        <v>1040</v>
       </c>
       <c r="D74" t="n">
-        <v>49.1</v>
+        <v>49.9</v>
       </c>
       <c r="E74" t="n">
-        <v>50.9</v>
+        <v>50.1</v>
       </c>
       <c r="F74" t="n">
-        <v>53</v>
+        <v>51.8</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11428,7 +11428,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75">
@@ -11437,23 +11437,23 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cotton</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>1089</v>
+        <v>526</v>
       </c>
       <c r="D75" t="n">
-        <v>50</v>
+        <v>48.7</v>
       </c>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>51.3</v>
       </c>
       <c r="F75" t="n">
-        <v>53.2</v>
+        <v>53.4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="76">
@@ -11480,19 +11480,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>478</v>
+        <v>442</v>
       </c>
       <c r="D76" t="n">
-        <v>51</v>
+        <v>51.8</v>
       </c>
       <c r="E76" t="n">
-        <v>49</v>
+        <v>48.2</v>
       </c>
       <c r="F76" t="n">
-        <v>54.6</v>
+        <v>54.3</v>
       </c>
       <c r="G76" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>544</v>
+        <v>509</v>
       </c>
       <c r="D77" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="E77" t="n">
-        <v>51.3</v>
+        <v>51.9</v>
       </c>
       <c r="F77" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G77" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78">
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1397</v>
+        <v>1336</v>
       </c>
       <c r="D78" t="n">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="E78" t="n">
-        <v>48.7</v>
+        <v>48</v>
       </c>
       <c r="F78" t="n">
-        <v>69.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
@@ -11593,23 +11593,23 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EUBUND.F</t>
+          <t>UKGILT.F</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1158</v>
+        <v>564</v>
       </c>
       <c r="D79" t="n">
-        <v>47.1</v>
+        <v>49.8</v>
       </c>
       <c r="E79" t="n">
-        <v>52.9</v>
+        <v>50.2</v>
       </c>
       <c r="F79" t="n">
-        <v>62.4</v>
+        <v>62.6</v>
       </c>
       <c r="G79" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="80">
@@ -11632,23 +11632,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>UKGILT.F</t>
+          <t>EUBUND.F</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>590</v>
+        <v>1114</v>
       </c>
       <c r="D80" t="n">
-        <v>49.8</v>
+        <v>46.9</v>
       </c>
       <c r="E80" t="n">
-        <v>50.2</v>
+        <v>53.1</v>
       </c>
       <c r="F80" t="n">
-        <v>62.9</v>
+        <v>62.8</v>
       </c>
       <c r="G80" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="81">
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1159</v>
+        <v>1120</v>
       </c>
       <c r="D81" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="E81" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="F81" t="n">
-        <v>64.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="82">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>396</v>
+        <v>371</v>
       </c>
       <c r="D82" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="E82" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="F82" t="n">
-        <v>48.2</v>
+        <v>48.8</v>
       </c>
       <c r="G82" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11753,19 +11753,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="D83" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="E83" t="n">
-        <v>52.2</v>
+        <v>52.5</v>
       </c>
       <c r="F83" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="G83" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84">
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>389</v>
+        <v>365</v>
       </c>
       <c r="D84" t="n">
-        <v>46.5</v>
+        <v>47.1</v>
       </c>
       <c r="E84" t="n">
-        <v>53.5</v>
+        <v>52.9</v>
       </c>
       <c r="F84" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="85">
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="D85" t="n">
-        <v>46.3</v>
+        <v>45.2</v>
       </c>
       <c r="E85" t="n">
-        <v>53.7</v>
+        <v>54.8</v>
       </c>
       <c r="F85" t="n">
-        <v>56.4</v>
+        <v>55.8</v>
       </c>
       <c r="G85" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="86">
@@ -11870,13 +11870,13 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>407</v>
+        <v>382</v>
       </c>
       <c r="D86" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="E86" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="F86" t="n">
         <v>56.5</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -11909,13 +11909,13 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="D87" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="E87" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="F87" t="n">
         <v>58</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="88">
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="D88" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E88" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="F88" t="n">
-        <v>61.8</v>
+        <v>61.4</v>
       </c>
       <c r="G88" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89">
@@ -11987,19 +11987,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>402</v>
+        <v>377</v>
       </c>
       <c r="D89" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="E89" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="F89" t="n">
-        <v>62.9</v>
+        <v>61.8</v>
       </c>
       <c r="G89" t="n">
-        <v>12.9</v>
+        <v>11.8</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="90">
@@ -12026,7 +12026,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="D90" t="n">
         <v>51</v>
@@ -12035,10 +12035,10 @@
         <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>64.09999999999999</v>
+        <v>63.2</v>
       </c>
       <c r="G90" t="n">
-        <v>14.1</v>
+        <v>13.2</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91">
@@ -12065,19 +12065,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="D91" t="n">
-        <v>53.1</v>
+        <v>53.3</v>
       </c>
       <c r="E91" t="n">
-        <v>46.9</v>
+        <v>46.7</v>
       </c>
       <c r="F91" t="n">
-        <v>64.40000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="G91" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92">
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="D92" t="n">
         <v>51.4</v>
@@ -12113,10 +12113,10 @@
         <v>48.6</v>
       </c>
       <c r="F92" t="n">
-        <v>64.59999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="G92" t="n">
-        <v>14.6</v>
+        <v>13.8</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>376</v>
+        <v>354</v>
       </c>
       <c r="D93" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E93" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F93" t="n">
-        <v>70.7</v>
+        <v>69.5</v>
       </c>
       <c r="G93" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12169,7 +12169,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -12182,19 +12182,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1343</v>
+        <v>1298</v>
       </c>
       <c r="D94" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="E94" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="F94" t="n">
-        <v>56.4</v>
+        <v>56</v>
       </c>
       <c r="G94" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="95">
@@ -12221,19 +12221,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1501</v>
+        <v>1442</v>
       </c>
       <c r="D95" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="E95" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="F95" t="n">
-        <v>56.6</v>
+        <v>56.4</v>
       </c>
       <c r="G95" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="96">
@@ -12256,23 +12256,23 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#XRPUSD</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1462</v>
+        <v>1426</v>
       </c>
       <c r="D96" t="n">
-        <v>52.6</v>
+        <v>50.3</v>
       </c>
       <c r="E96" t="n">
-        <v>47.4</v>
+        <v>49.7</v>
       </c>
       <c r="F96" t="n">
-        <v>57.3</v>
+        <v>57.1</v>
       </c>
       <c r="G96" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="97">
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#XRPUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1482</v>
+        <v>1402</v>
       </c>
       <c r="D97" t="n">
-        <v>49.7</v>
+        <v>52.4</v>
       </c>
       <c r="E97" t="n">
-        <v>50.3</v>
+        <v>47.6</v>
       </c>
       <c r="F97" t="n">
-        <v>57.6</v>
+        <v>57.4</v>
       </c>
       <c r="G97" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
@@ -12338,19 +12338,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D98" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="E98" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="F98" t="n">
-        <v>58.3</v>
+        <v>57.7</v>
       </c>
       <c r="G98" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99">
@@ -12377,19 +12377,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D99" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="E99" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="F99" t="n">
-        <v>58.7</v>
+        <v>58.6</v>
       </c>
       <c r="G99" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100">
@@ -12416,13 +12416,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1498</v>
+        <v>1438</v>
       </c>
       <c r="D100" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E100" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F100" t="n">
         <v>59.1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="101">
@@ -12455,7 +12455,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1502</v>
+        <v>1442</v>
       </c>
       <c r="D101" t="n">
         <v>50.3</v>
@@ -12464,10 +12464,10 @@
         <v>49.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.3</v>
+        <v>59.2</v>
       </c>
       <c r="G101" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="102">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1481</v>
+        <v>1421</v>
       </c>
       <c r="D102" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="E102" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="F102" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="G102" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1450</v>
+        <v>1392</v>
       </c>
       <c r="D103" t="n">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="E103" t="n">
-        <v>48.7</v>
+        <v>48.2</v>
       </c>
       <c r="F103" t="n">
-        <v>60.3</v>
+        <v>60</v>
       </c>
       <c r="G103" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38484</v>
+        <v>38571</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38534</v>
+        <v>38619</v>
       </c>
       <c r="D3" t="n">
         <v>50.3</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38740</v>
+        <v>38826</v>
       </c>
       <c r="D4" t="n">
         <v>51.2</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38203</v>
+        <v>38230</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38678</v>
+        <v>38706</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38198</v>
+        <v>38225</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38016</v>
+        <v>38044</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,13 +12916,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38479</v>
+        <v>38507</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F9" t="n">
         <v>49.8</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38766</v>
+        <v>38794</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38821</v>
+        <v>38848</v>
       </c>
       <c r="D11" t="n">
         <v>50.7</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38828</v>
+        <v>38856</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38647</v>
+        <v>38675</v>
       </c>
       <c r="D13" t="n">
         <v>49.6</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38712</v>
+        <v>38739</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38613</v>
+        <v>38701</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,7 +13189,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38633</v>
+        <v>38720</v>
       </c>
       <c r="D16" t="n">
         <v>49.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36878</v>
+        <v>36904</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38888</v>
+        <v>38916</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38420</v>
+        <v>38448</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13315,10 +13315,10 @@
         <v>49.7</v>
       </c>
       <c r="F19" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35137</v>
+        <v>35157</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38958</v>
+        <v>38985</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38772</v>
+        <v>38800</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38817</v>
+        <v>38845</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39005</v>
+        <v>39093</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13536,23 +13536,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDHUF</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38960</v>
+        <v>39045</v>
       </c>
       <c r="D25" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="E25" t="n">
-        <v>50.1</v>
+        <v>50.8</v>
       </c>
       <c r="F25" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="G25" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -13575,17 +13575,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDHUF</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>39017</v>
+        <v>38988</v>
       </c>
       <c r="D26" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="E26" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="F26" t="n">
         <v>40.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35308</v>
+        <v>35327</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>39042</v>
+        <v>39070</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39050</v>
+        <v>39078</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38761</v>
+        <v>38788</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38795</v>
+        <v>38823</v>
       </c>
       <c r="D31" t="n">
         <v>49.4</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38800</v>
+        <v>38828</v>
       </c>
       <c r="D32" t="n">
         <v>49.2</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38822</v>
+        <v>38850</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,13 +13891,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38758</v>
+        <v>38786</v>
       </c>
       <c r="D34" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E34" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F34" t="n">
         <v>45.8</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38760</v>
+        <v>38788</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,13 +13969,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35193</v>
+        <v>35212</v>
       </c>
       <c r="D36" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E36" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F36" t="n">
         <v>47.6</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38597</v>
+        <v>38624</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37927</v>
+        <v>37955</v>
       </c>
       <c r="D38" t="n">
         <v>50.8</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38755</v>
+        <v>38783</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14112,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8189</v>
+        <v>8193</v>
       </c>
       <c r="D40" t="n">
         <v>51.2</v>
@@ -14134,10 +14134,10 @@
         <v>48.8</v>
       </c>
       <c r="F40" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38432</v>
+        <v>38460</v>
       </c>
       <c r="D41" t="n">
         <v>50.1</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38492</v>
+        <v>38520</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38532</v>
+        <v>38558</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38454</v>
+        <v>38481</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38101</v>
+        <v>38128</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38257</v>
+        <v>38285</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38636</v>
+        <v>38664</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38673</v>
+        <v>38700</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>36039</v>
+        <v>36066</v>
       </c>
       <c r="D49" t="n">
         <v>50.4</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38378</v>
+        <v>38405</v>
       </c>
       <c r="D50" t="n">
         <v>50.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38516</v>
+        <v>38543</v>
       </c>
       <c r="D51" t="n">
         <v>49.4</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38559</v>
+        <v>38587</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38430</v>
+        <v>38458</v>
       </c>
       <c r="D53" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="E53" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="F53" t="n">
         <v>61.5</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38464</v>
+        <v>38491</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38652</v>
+        <v>38679</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38353</v>
+        <v>38381</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38717</v>
+        <v>38744</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38800</v>
+        <v>38828</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39002</v>
+        <v>39030</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35407</v>
+        <v>35431</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37301</v>
+        <v>37386</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14953,10 +14953,10 @@
         <v>49.6</v>
       </c>
       <c r="F61" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -14970,7 +14970,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62">
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37808</v>
+        <v>37836</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24019</v>
+        <v>24020</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38704</v>
+        <v>38732</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38209</v>
+        <v>38237</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -15217,7 +15217,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21434</v>
+        <v>21435</v>
       </c>
       <c r="D68" t="n">
         <v>51.8</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36466</v>
+        <v>36488</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30828</v>
+        <v>30848</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37820</v>
+        <v>37908</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33298</v>
+        <v>33322</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26269</v>
+        <v>26284</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26884</v>
+        <v>26902</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36168</v>
+        <v>36192</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28880</v>
+        <v>28899</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28132</v>
+        <v>28147</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38232</v>
+        <v>38258</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38845</v>
+        <v>38873</v>
       </c>
       <c r="D95" t="n">
         <v>49.3</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36419</v>
+        <v>36447</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38961</v>
+        <v>38989</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38155</v>
+        <v>38182</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38749</v>
+        <v>38777</v>
       </c>
       <c r="D99" t="n">
         <v>49.1</v>
@@ -16435,10 +16435,10 @@
         <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.3</v>
+        <v>54.2</v>
       </c>
       <c r="G99" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -16465,13 +16465,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38355</v>
+        <v>38383</v>
       </c>
       <c r="D100" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="E100" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="F100" t="n">
         <v>54.4</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38608</v>
+        <v>38636</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39038</v>
+        <v>39066</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39059</v>
+        <v>39087</v>
       </c>
       <c r="D103" t="n">
         <v>49.8</v>
@@ -16591,10 +16591,10 @@
         <v>50.2</v>
       </c>
       <c r="F103" t="n">
-        <v>55</v>
+        <v>54.9</v>
       </c>
       <c r="G103" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1438</v>
+        <v>1527</v>
       </c>
       <c r="D2" t="n">
         <v>49.2</v>
@@ -505,10 +505,10 @@
         <v>50.8</v>
       </c>
       <c r="F2" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1431</v>
+        <v>1518</v>
       </c>
       <c r="D3" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E3" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F3" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -570,23 +570,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1431</v>
+        <v>1469</v>
       </c>
       <c r="D4" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E4" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F4" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -609,17 +609,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1382</v>
+        <v>1505</v>
       </c>
       <c r="D5" t="n">
-        <v>49.6</v>
+        <v>51.4</v>
       </c>
       <c r="E5" t="n">
-        <v>50.4</v>
+        <v>48.6</v>
       </c>
       <c r="F5" t="n">
         <v>47.2</v>
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1418</v>
+        <v>1519</v>
       </c>
       <c r="D6" t="n">
-        <v>51.5</v>
+        <v>49.5</v>
       </c>
       <c r="E6" t="n">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="F6" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1415</v>
+        <v>1502</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F7" t="n">
-        <v>54.9</v>
+        <v>55.3</v>
       </c>
       <c r="G7" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
@@ -730,19 +730,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1428</v>
+        <v>1516</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F8" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="G8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1431</v>
+        <v>1519</v>
       </c>
       <c r="D9" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E9" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F9" t="n">
-        <v>56</v>
+        <v>56.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -804,23 +804,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CADCHF</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1401</v>
+        <v>1496</v>
       </c>
       <c r="D10" t="n">
-        <v>51.9</v>
+        <v>50.4</v>
       </c>
       <c r="E10" t="n">
-        <v>48.1</v>
+        <v>49.6</v>
       </c>
       <c r="F10" t="n">
-        <v>42.9</v>
+        <v>42.4</v>
       </c>
       <c r="G10" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -843,23 +843,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EURCHF</t>
+          <t>CADCHF</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1408</v>
+        <v>1483</v>
       </c>
       <c r="D11" t="n">
-        <v>50.1</v>
+        <v>51.4</v>
       </c>
       <c r="E11" t="n">
-        <v>49.9</v>
+        <v>48.6</v>
       </c>
       <c r="F11" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1469</v>
+        <v>1555</v>
       </c>
       <c r="D12" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="E12" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1493</v>
+        <v>1579</v>
       </c>
       <c r="D13" t="n">
-        <v>50.2</v>
+        <v>50.9</v>
       </c>
       <c r="E13" t="n">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="F13" t="n">
-        <v>40.3</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1474</v>
+        <v>1561</v>
       </c>
       <c r="D14" t="n">
         <v>51.2</v>
@@ -973,10 +973,10 @@
         <v>48.8</v>
       </c>
       <c r="F14" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="G14" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1003,19 +1003,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1479</v>
+        <v>1566</v>
       </c>
       <c r="D15" t="n">
-        <v>48.4</v>
+        <v>47.5</v>
       </c>
       <c r="E15" t="n">
-        <v>51.6</v>
+        <v>52.5</v>
       </c>
       <c r="F15" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G15" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1042,13 +1042,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1477</v>
+        <v>1564</v>
       </c>
       <c r="D16" t="n">
-        <v>49.6</v>
+        <v>48.9</v>
       </c>
       <c r="E16" t="n">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="F16" t="n">
         <v>62.9</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -1077,23 +1077,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>EURNOK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1406</v>
+        <v>1366</v>
       </c>
       <c r="D17" t="n">
-        <v>50.7</v>
+        <v>48.7</v>
       </c>
       <c r="E17" t="n">
-        <v>49.3</v>
+        <v>51.3</v>
       </c>
       <c r="F17" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1116,23 +1116,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EURNOK</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1285</v>
+        <v>364</v>
       </c>
       <c r="D18" t="n">
-        <v>48.9</v>
+        <v>50.5</v>
       </c>
       <c r="E18" t="n">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
       <c r="F18" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1143,7 +1143,7 @@
         </is>
       </c>
       <c r="J18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1422</v>
+        <v>1495</v>
       </c>
       <c r="D19" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="E19" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="F19" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1185,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>341</v>
+        <v>1510</v>
       </c>
       <c r="D20" t="n">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="E20" t="n">
-        <v>50.1</v>
+        <v>48.5</v>
       </c>
       <c r="F20" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1434</v>
+        <v>1523</v>
       </c>
       <c r="D21" t="n">
         <v>45.2</v>
@@ -1246,10 +1246,10 @@
         <v>54.8</v>
       </c>
       <c r="F21" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -1276,13 +1276,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1409</v>
+        <v>1496</v>
       </c>
       <c r="D22" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="E22" t="n">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="F22" t="n">
         <v>52.1</v>
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1379</v>
+        <v>1464</v>
       </c>
       <c r="D23" t="n">
         <v>51.4</v>
@@ -1324,10 +1324,10 @@
         <v>48.6</v>
       </c>
       <c r="F23" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="G23" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1430</v>
+        <v>1518</v>
       </c>
       <c r="D24" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="E24" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="F24" t="n">
-        <v>53.1</v>
+        <v>53.5</v>
       </c>
       <c r="G24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1422</v>
+        <v>1509</v>
       </c>
       <c r="D25" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F25" t="n">
-        <v>46.3</v>
+        <v>45.7</v>
       </c>
       <c r="G25" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1432,19 +1432,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1424</v>
+        <v>1511</v>
       </c>
       <c r="D26" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="E26" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F26" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1419</v>
+        <v>1507</v>
       </c>
       <c r="D27" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="E27" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="F27" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="G27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1399</v>
+        <v>1484</v>
       </c>
       <c r="D28" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="E28" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="F28" t="n">
-        <v>55</v>
+        <v>55.2</v>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -1549,19 +1549,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1434</v>
+        <v>1521</v>
       </c>
       <c r="D29" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="E29" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="F29" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="G29" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1424</v>
+        <v>1517</v>
       </c>
       <c r="D30" t="n">
-        <v>50.8</v>
+        <v>47.7</v>
       </c>
       <c r="E30" t="n">
-        <v>49.2</v>
+        <v>52.3</v>
       </c>
       <c r="F30" t="n">
-        <v>44.8</v>
+        <v>55.6</v>
       </c>
       <c r="G30" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1428</v>
+        <v>1512</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>50.8</v>
       </c>
       <c r="E31" t="n">
-        <v>52</v>
+        <v>49.2</v>
       </c>
       <c r="F31" t="n">
-        <v>55.5</v>
+        <v>44.3</v>
       </c>
       <c r="G31" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1426</v>
+        <v>1513</v>
       </c>
       <c r="D32" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="E32" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="F32" t="n">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="G32" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33">
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1432</v>
+        <v>1520</v>
       </c>
       <c r="D33" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="E33" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="F33" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="G33" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1288</v>
+        <v>1369</v>
       </c>
       <c r="D34" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E34" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F34" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="G34" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1770,7 +1770,7 @@
         <v>1</v>
       </c>
       <c r="K34" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1319</v>
+        <v>1401</v>
       </c>
       <c r="D35" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E35" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="F35" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="G35" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1422</v>
+        <v>1507</v>
       </c>
       <c r="D36" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E36" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F36" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="G36" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1430</v>
+        <v>1497</v>
       </c>
       <c r="D37" t="n">
-        <v>49.9</v>
+        <v>48.9</v>
       </c>
       <c r="E37" t="n">
-        <v>50.1</v>
+        <v>51.1</v>
       </c>
       <c r="F37" t="n">
-        <v>41.5</v>
+        <v>58.8</v>
       </c>
       <c r="G37" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38">
@@ -1896,23 +1896,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1410</v>
+        <v>1516</v>
       </c>
       <c r="D38" t="n">
-        <v>49.2</v>
+        <v>50.3</v>
       </c>
       <c r="E38" t="n">
-        <v>50.8</v>
+        <v>49.7</v>
       </c>
       <c r="F38" t="n">
-        <v>58.6</v>
+        <v>41.1</v>
       </c>
       <c r="G38" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39">
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1417</v>
+        <v>1505</v>
       </c>
       <c r="D39" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>58.9</v>
+        <v>59.3</v>
       </c>
       <c r="G39" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1420</v>
+        <v>1509</v>
       </c>
       <c r="D40" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E40" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F40" t="n">
-        <v>59.6</v>
+        <v>59.8</v>
       </c>
       <c r="G40" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1436</v>
+        <v>1524</v>
       </c>
       <c r="D41" t="n">
         <v>50.1</v>
@@ -2026,10 +2026,10 @@
         <v>49.9</v>
       </c>
       <c r="F41" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
       <c r="G41" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1431</v>
+        <v>1518</v>
       </c>
       <c r="D42" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="E42" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="F42" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="G42" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D43" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="E43" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="F43" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="G43" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="44">
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1435</v>
+        <v>1524</v>
       </c>
       <c r="D44" t="n">
-        <v>49.8</v>
+        <v>50.1</v>
       </c>
       <c r="E44" t="n">
-        <v>50.2</v>
+        <v>49.9</v>
       </c>
       <c r="F44" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="G44" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45">
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1283</v>
+        <v>1364</v>
       </c>
       <c r="D45" t="n">
-        <v>50.6</v>
+        <v>51</v>
       </c>
       <c r="E45" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="G45" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
@@ -2212,13 +2212,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1500</v>
+        <v>1588</v>
       </c>
       <c r="D46" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E46" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F46" t="n">
         <v>37.1</v>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47">
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1416</v>
+        <v>1502</v>
       </c>
       <c r="D47" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="E47" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="F47" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="G47" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48">
@@ -2290,19 +2290,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1422</v>
+        <v>1510</v>
       </c>
       <c r="D48" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
       <c r="E48" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="F48" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="G48" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2316,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1439</v>
+        <v>1499</v>
       </c>
       <c r="D49" t="n">
-        <v>50</v>
+        <v>48.2</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>51.8</v>
       </c>
       <c r="F49" t="n">
-        <v>36.4</v>
+        <v>63.7</v>
       </c>
       <c r="G49" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="J49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1412</v>
+        <v>1528</v>
       </c>
       <c r="D50" t="n">
-        <v>48.5</v>
+        <v>50.2</v>
       </c>
       <c r="E50" t="n">
-        <v>51.5</v>
+        <v>49.8</v>
       </c>
       <c r="F50" t="n">
-        <v>63.7</v>
+        <v>36.2</v>
       </c>
       <c r="G50" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="51">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D51" t="n">
-        <v>51.4</v>
+        <v>51</v>
       </c>
       <c r="E51" t="n">
-        <v>48.6</v>
+        <v>49</v>
       </c>
       <c r="F51" t="n">
         <v>36.1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1407</v>
+        <v>1495</v>
       </c>
       <c r="D52" t="n">
-        <v>49.5</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
-        <v>50.5</v>
+        <v>50</v>
       </c>
       <c r="F52" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="G52" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2472,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53">
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D53" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="E53" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="F53" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="G53" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1344</v>
+        <v>1432</v>
       </c>
       <c r="D54" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E54" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F54" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="G54" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1429</v>
+        <v>1517</v>
       </c>
       <c r="D55" t="n">
         <v>48.5</v>
@@ -2572,10 +2572,10 @@
         <v>51.5</v>
       </c>
       <c r="F55" t="n">
-        <v>70.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="G55" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="56">
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1422</v>
+        <v>1511</v>
       </c>
       <c r="D56" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E56" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F56" t="n">
         <v>75.7</v>
@@ -2641,19 +2641,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1434</v>
+        <v>1523</v>
       </c>
       <c r="D57" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="E57" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="F57" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="G57" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1441</v>
+        <v>1530</v>
       </c>
       <c r="D58" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="E58" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="F58" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="G58" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1440</v>
+        <v>1529</v>
       </c>
       <c r="D59" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="E59" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="F59" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="G59" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1333</v>
+        <v>1549</v>
       </c>
       <c r="D60" t="n">
-        <v>52.7</v>
+        <v>51.5</v>
       </c>
       <c r="E60" t="n">
-        <v>47.3</v>
+        <v>48.5</v>
       </c>
       <c r="F60" t="n">
-        <v>40.1</v>
+        <v>39.8</v>
       </c>
       <c r="G60" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="D61" t="n">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
       <c r="E61" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="F61" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="G61" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>872</v>
+        <v>927</v>
       </c>
       <c r="D62" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E62" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F62" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="G62" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>859</v>
+        <v>914</v>
       </c>
       <c r="D63" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="E63" t="n">
-        <v>52.6</v>
+        <v>51.9</v>
       </c>
       <c r="F63" t="n">
-        <v>60.7</v>
+        <v>61.4</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -2910,17 +2910,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>860</v>
+        <v>1371</v>
       </c>
       <c r="D64" t="n">
-        <v>50.7</v>
+        <v>49.2</v>
       </c>
       <c r="E64" t="n">
-        <v>49.3</v>
+        <v>50.8</v>
       </c>
       <c r="F64" t="n">
         <v>62</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1284</v>
+        <v>915</v>
       </c>
       <c r="D65" t="n">
-        <v>49.1</v>
+        <v>51.6</v>
       </c>
       <c r="E65" t="n">
-        <v>50.9</v>
+        <v>48.4</v>
       </c>
       <c r="F65" t="n">
-        <v>62</v>
+        <v>62.3</v>
       </c>
       <c r="G65" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66">
@@ -2992,19 +2992,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1021</v>
+        <v>1085</v>
       </c>
       <c r="D66" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E66" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F66" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
       <c r="G66" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67">
@@ -3031,19 +3031,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>888</v>
+        <v>944</v>
       </c>
       <c r="D67" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="E67" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="F67" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="G67" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1407</v>
+        <v>1522</v>
       </c>
       <c r="D68" t="n">
-        <v>50.4</v>
+        <v>52.7</v>
       </c>
       <c r="E68" t="n">
-        <v>49.6</v>
+        <v>47.3</v>
       </c>
       <c r="F68" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G68" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1433</v>
+        <v>1495</v>
       </c>
       <c r="D69" t="n">
-        <v>52.8</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
         <v>64.3</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70">
@@ -3144,23 +3144,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1222</v>
+        <v>1506</v>
       </c>
       <c r="D70" t="n">
-        <v>47.5</v>
+        <v>50.3</v>
       </c>
       <c r="E70" t="n">
-        <v>52.5</v>
+        <v>49.7</v>
       </c>
       <c r="F70" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="G70" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1419</v>
+        <v>1299</v>
       </c>
       <c r="D71" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="E71" t="n">
-        <v>50</v>
+        <v>52.1</v>
       </c>
       <c r="F71" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72">
@@ -3226,19 +3226,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1463</v>
+        <v>1547</v>
       </c>
       <c r="D72" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E72" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F72" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1229</v>
+        <v>1307</v>
       </c>
       <c r="D73" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E73" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F73" t="n">
-        <v>65.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>15.4</v>
+        <v>15.9</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1040</v>
+        <v>1107</v>
       </c>
       <c r="D74" t="n">
         <v>49.9</v>
@@ -3313,10 +3313,10 @@
         <v>50.1</v>
       </c>
       <c r="F74" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="D75" t="n">
         <v>48.7</v>
@@ -3352,10 +3352,10 @@
         <v>51.3</v>
       </c>
       <c r="F75" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="D76" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="E76" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="F76" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="G76" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="D77" t="n">
-        <v>48.1</v>
+        <v>48.8</v>
       </c>
       <c r="E77" t="n">
-        <v>51.9</v>
+        <v>51.2</v>
       </c>
       <c r="F77" t="n">
-        <v>56.2</v>
+        <v>57.3</v>
       </c>
       <c r="G77" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1336</v>
+        <v>1421</v>
       </c>
       <c r="D78" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="F78" t="n">
-        <v>69.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>564</v>
+        <v>604</v>
       </c>
       <c r="D79" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="E79" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
       <c r="F79" t="n">
-        <v>62.6</v>
+        <v>63.1</v>
       </c>
       <c r="G79" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1114</v>
+        <v>1183</v>
       </c>
       <c r="D80" t="n">
-        <v>46.9</v>
+        <v>47.2</v>
       </c>
       <c r="E80" t="n">
-        <v>53.1</v>
+        <v>52.8</v>
       </c>
       <c r="F80" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
       <c r="G80" t="n">
-        <v>12.8</v>
+        <v>13.3</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1120</v>
+        <v>1191</v>
       </c>
       <c r="D81" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
       <c r="E81" t="n">
-        <v>52.6</v>
+        <v>52.3</v>
       </c>
       <c r="F81" t="n">
-        <v>64.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="G81" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82">
@@ -3612,11 +3612,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="D82" t="n">
         <v>47.5</v>
@@ -3625,10 +3625,10 @@
         <v>52.5</v>
       </c>
       <c r="F82" t="n">
-        <v>49.3</v>
+        <v>49.9</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -3651,23 +3651,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="D83" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="E83" t="n">
-        <v>52.9</v>
+        <v>52.3</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="D84" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="E84" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="F84" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="G84" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
@@ -3729,23 +3729,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="D85" t="n">
-        <v>45.2</v>
+        <v>50.2</v>
       </c>
       <c r="E85" t="n">
-        <v>54.8</v>
+        <v>49.8</v>
       </c>
       <c r="F85" t="n">
-        <v>55.8</v>
+        <v>55.6</v>
       </c>
       <c r="G85" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86">
@@ -3768,23 +3768,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="D86" t="n">
-        <v>49.7</v>
+        <v>45.3</v>
       </c>
       <c r="E86" t="n">
-        <v>50.3</v>
+        <v>54.7</v>
       </c>
       <c r="F86" t="n">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
       <c r="G86" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D87" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="E87" t="n">
-        <v>52.3</v>
+        <v>52.7</v>
       </c>
       <c r="F87" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="88">
@@ -3846,23 +3846,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="D88" t="n">
-        <v>47.8</v>
+        <v>51.1</v>
       </c>
       <c r="E88" t="n">
-        <v>52.2</v>
+        <v>48.9</v>
       </c>
       <c r="F88" t="n">
-        <v>61.4</v>
+        <v>62.3</v>
       </c>
       <c r="G88" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89">
@@ -3885,23 +3885,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="D89" t="n">
-        <v>50.1</v>
+        <v>48.7</v>
       </c>
       <c r="E89" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="F89" t="n">
-        <v>61.8</v>
+        <v>62.4</v>
       </c>
       <c r="G89" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="90">
@@ -3928,19 +3928,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E90" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F90" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
     <row r="91">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="D91" t="n">
-        <v>53.3</v>
+        <v>54.6</v>
       </c>
       <c r="E91" t="n">
-        <v>46.7</v>
+        <v>45.4</v>
       </c>
       <c r="F91" t="n">
-        <v>63.6</v>
+        <v>64.2</v>
       </c>
       <c r="G91" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92">
@@ -4006,19 +4006,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D92" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="E92" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="F92" t="n">
-        <v>63.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="D93" t="n">
-        <v>48.3</v>
+        <v>49.2</v>
       </c>
       <c r="E93" t="n">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
       <c r="F93" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="G93" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1298</v>
+        <v>1384</v>
       </c>
       <c r="D94" t="n">
         <v>50.8</v>
@@ -4093,10 +4093,10 @@
         <v>49.2</v>
       </c>
       <c r="F94" t="n">
-        <v>56</v>
+        <v>56.3</v>
       </c>
       <c r="G94" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="95">
@@ -4123,13 +4123,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D95" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E95" t="n">
         <v>49.8</v>
-      </c>
-      <c r="E95" t="n">
-        <v>50.2</v>
       </c>
       <c r="F95" t="n">
         <v>56.4</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96">
@@ -4162,19 +4162,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1426</v>
+        <v>1514</v>
       </c>
       <c r="D96" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="E96" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="F96" t="n">
-        <v>57.1</v>
+        <v>56.9</v>
       </c>
       <c r="G96" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4188,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="97">
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1402</v>
+        <v>1531</v>
       </c>
       <c r="D97" t="n">
-        <v>52.4</v>
+        <v>50.2</v>
       </c>
       <c r="E97" t="n">
-        <v>47.6</v>
+        <v>49.8</v>
       </c>
       <c r="F97" t="n">
-        <v>57.4</v>
+        <v>57.7</v>
       </c>
       <c r="G97" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1442</v>
+        <v>1489</v>
       </c>
       <c r="D98" t="n">
-        <v>49.9</v>
+        <v>52.2</v>
       </c>
       <c r="E98" t="n">
-        <v>50.1</v>
+        <v>47.8</v>
       </c>
       <c r="F98" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="G98" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4279,19 +4279,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D99" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="E99" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="F99" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="G99" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="100">
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1438</v>
+        <v>1527</v>
       </c>
       <c r="D100" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="E100" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="F100" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="G100" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101">
@@ -4357,13 +4357,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D101" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="E101" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="F101" t="n">
         <v>59.2</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="102">
@@ -4392,23 +4392,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1421</v>
+        <v>1481</v>
       </c>
       <c r="D102" t="n">
-        <v>50.6</v>
+        <v>51.9</v>
       </c>
       <c r="E102" t="n">
-        <v>49.4</v>
+        <v>48.1</v>
       </c>
       <c r="F102" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="G102" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="103">
@@ -4431,23 +4431,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1392</v>
+        <v>1510</v>
       </c>
       <c r="D103" t="n">
-        <v>51.8</v>
+        <v>50.9</v>
       </c>
       <c r="E103" t="n">
-        <v>48.2</v>
+        <v>49.1</v>
       </c>
       <c r="F103" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38507</v>
+        <v>38594</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38044</v>
+        <v>38131</v>
       </c>
       <c r="D3" t="n">
         <v>49</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38225</v>
+        <v>38313</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4632,10 +4632,10 @@
         <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38794</v>
+        <v>38882</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38848</v>
+        <v>38937</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38856</v>
+        <v>38943</v>
       </c>
       <c r="D7" t="n">
         <v>51.4</v>
@@ -4766,7 +4766,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38706</v>
+        <v>38794</v>
       </c>
       <c r="D8" t="n">
         <v>50.7</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38230</v>
+        <v>38312</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4844,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38675</v>
+        <v>38762</v>
       </c>
       <c r="D10" t="n">
         <v>49.6</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38739</v>
+        <v>38827</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,13 +4935,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38826</v>
+        <v>38912</v>
       </c>
       <c r="D12" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E12" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F12" t="n">
         <v>41.7</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38619</v>
+        <v>38705</v>
       </c>
       <c r="D13" t="n">
         <v>50.3</v>
@@ -5000,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14">
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38571</v>
+        <v>38658</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38701</v>
+        <v>38788</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -5091,13 +5091,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38720</v>
+        <v>38807</v>
       </c>
       <c r="D16" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E16" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F16" t="n">
         <v>60.8</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38783</v>
+        <v>38872</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8193</v>
+        <v>8216</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5178,10 +5178,10 @@
         <v>48.8</v>
       </c>
       <c r="F18" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -5195,7 +5195,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38460</v>
+        <v>38548</v>
       </c>
       <c r="D19" t="n">
         <v>50.1</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>37955</v>
+        <v>38040</v>
       </c>
       <c r="D20" t="n">
         <v>50.8</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38624</v>
+        <v>38711</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35212</v>
+        <v>35293</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38788</v>
+        <v>38876</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5373,10 +5373,10 @@
         <v>50.3</v>
       </c>
       <c r="F23" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="G23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38520</v>
+        <v>38607</v>
       </c>
       <c r="D24" t="n">
         <v>49.8</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38558</v>
+        <v>38647</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,19 +5481,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38786</v>
+        <v>38873</v>
       </c>
       <c r="D26" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E26" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F26" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38481</v>
+        <v>38568</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38128</v>
+        <v>38213</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38285</v>
+        <v>38374</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38664</v>
+        <v>38752</v>
       </c>
       <c r="D30" t="n">
         <v>50.6</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38700</v>
+        <v>38788</v>
       </c>
       <c r="D31" t="n">
         <v>51.1</v>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38850</v>
+        <v>38938</v>
       </c>
       <c r="D32" t="n">
         <v>49.5</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38823</v>
+        <v>38909</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38828</v>
+        <v>38915</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38788</v>
+        <v>38873</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39078</v>
+        <v>39167</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39070</v>
+        <v>39159</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36066</v>
+        <v>36148</v>
       </c>
       <c r="D38" t="n">
         <v>50.4</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35327</v>
+        <v>35408</v>
       </c>
       <c r="D39" t="n">
         <v>49.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38405</v>
+        <v>38492</v>
       </c>
       <c r="D40" t="n">
         <v>50.3</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38543</v>
+        <v>38631</v>
       </c>
       <c r="D41" t="n">
         <v>49.4</v>
@@ -6075,10 +6075,10 @@
         <v>50.6</v>
       </c>
       <c r="F41" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G41" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38587</v>
+        <v>38676</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38988</v>
+        <v>39076</v>
       </c>
       <c r="D43" t="n">
         <v>49.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>39045</v>
+        <v>39134</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39093</v>
+        <v>39181</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38845</v>
+        <v>38933</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38800</v>
+        <v>38887</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38985</v>
+        <v>39074</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,7 +6378,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35157</v>
+        <v>35238</v>
       </c>
       <c r="D49" t="n">
         <v>50.1</v>
@@ -6417,13 +6417,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38458</v>
+        <v>38544</v>
       </c>
       <c r="D50" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E50" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F50" t="n">
         <v>61.5</v>
@@ -6452,23 +6452,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38448</v>
+        <v>38578</v>
       </c>
       <c r="D51" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>49.7</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>38</v>
+        <v>62.1</v>
       </c>
       <c r="G51" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="J51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>92</v>
@@ -6491,20 +6491,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38491</v>
+        <v>38536</v>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F52" t="n">
-        <v>62.1</v>
+        <v>37.9</v>
       </c>
       <c r="G52" t="n">
         <v>12.1</v>
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="J52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
         <v>93</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38916</v>
+        <v>39005</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36904</v>
+        <v>36992</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38679</v>
+        <v>38767</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38381</v>
+        <v>38470</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38744</v>
+        <v>38833</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38828</v>
+        <v>38917</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -6738,10 +6738,10 @@
         <v>48.5</v>
       </c>
       <c r="F58" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="G58" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39030</v>
+        <v>39119</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37386</v>
+        <v>37471</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35431</v>
+        <v>35514</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37836</v>
+        <v>37924</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23600</v>
+        <v>23655</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24020</v>
+        <v>24075</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -6972,10 +6972,10 @@
         <v>49.2</v>
       </c>
       <c r="F64" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G64" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -6998,17 +6998,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>24044</v>
+        <v>38821</v>
       </c>
       <c r="D65" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E65" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="F65" t="n">
         <v>56</v>
@@ -7037,37 +7037,37 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38732</v>
+        <v>24099</v>
       </c>
       <c r="D66" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E66" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="G66" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H66" t="b">
+        <v>1</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Indices</t>
+        </is>
+      </c>
+      <c r="J66" t="b">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
         <v>56</v>
-      </c>
-      <c r="G66" t="n">
-        <v>6</v>
-      </c>
-      <c r="H66" t="b">
-        <v>1</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>Indices</t>
-        </is>
-      </c>
-      <c r="J66" t="b">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -7080,7 +7080,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38237</v>
+        <v>38324</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21435</v>
+        <v>21491</v>
       </c>
       <c r="D68" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="E68" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F68" t="n">
         <v>56.2</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69">
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36488</v>
+        <v>36575</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30848</v>
+        <v>30925</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37908</v>
+        <v>37992</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7245,10 +7245,10 @@
         <v>48.9</v>
       </c>
       <c r="F71" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="G71" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33322</v>
+        <v>33400</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26284</v>
+        <v>26348</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7340,7 +7340,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="74">
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14340</v>
+        <v>14374</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7362,10 +7362,10 @@
         <v>49.9</v>
       </c>
       <c r="F74" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14142</v>
+        <v>14176</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7431,7 +7431,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15280</v>
+        <v>15315</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26902</v>
+        <v>26969</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36192</v>
+        <v>36277</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7518,10 +7518,10 @@
         <v>49.4</v>
       </c>
       <c r="F78" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28899</v>
+        <v>28968</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7557,10 +7557,10 @@
         <v>50.7</v>
       </c>
       <c r="F79" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="G79" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15911</v>
+        <v>15951</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7596,10 +7596,10 @@
         <v>50.3</v>
       </c>
       <c r="F80" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G80" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="81">
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28147</v>
+        <v>28218</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7635,10 +7635,10 @@
         <v>50.6</v>
       </c>
       <c r="F81" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="G81" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -7652,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10519</v>
+        <v>10544</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -7674,10 +7674,10 @@
         <v>48.5</v>
       </c>
       <c r="F82" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -7691,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83">
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10525</v>
+        <v>10548</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10303</v>
+        <v>10325</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10821</v>
+        <v>10847</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7791,10 +7791,10 @@
         <v>49.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="G85" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10305</v>
+        <v>10331</v>
       </c>
       <c r="D86" t="n">
         <v>51.1</v>
@@ -7830,10 +7830,10 @@
         <v>48.9</v>
       </c>
       <c r="F86" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="G86" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="87">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10777</v>
+        <v>10803</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10881</v>
+        <v>10905</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11022</v>
+        <v>11048</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -7977,7 +7977,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11022</v>
+        <v>11048</v>
       </c>
       <c r="D90" t="n">
         <v>51.6</v>
@@ -7986,10 +7986,10 @@
         <v>48.4</v>
       </c>
       <c r="F90" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G90" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -8003,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91">
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10948</v>
+        <v>10974</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -8025,10 +8025,10 @@
         <v>48.3</v>
       </c>
       <c r="F91" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10364</v>
+        <v>10390</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10289</v>
+        <v>10311</v>
       </c>
       <c r="D93" t="n">
         <v>51.3</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38258</v>
+        <v>38345</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -8172,13 +8172,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38873</v>
+        <v>38962</v>
       </c>
       <c r="D95" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E95" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F95" t="n">
         <v>53.8</v>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36447</v>
+        <v>36533</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38989</v>
+        <v>39078</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38182</v>
+        <v>38271</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,13 +8328,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38777</v>
+        <v>38865</v>
       </c>
       <c r="D99" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E99" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F99" t="n">
         <v>54.2</v>
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100">
@@ -8367,13 +8367,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38383</v>
+        <v>38472</v>
       </c>
       <c r="D100" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E100" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F100" t="n">
         <v>54.4</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38636</v>
+        <v>38725</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39066</v>
+        <v>39155</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39087</v>
+        <v>39176</v>
       </c>
       <c r="D103" t="n">
         <v>49.8</v>
@@ -8493,10 +8493,10 @@
         <v>50.2</v>
       </c>
       <c r="F103" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G103" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1474</v>
+        <v>1561</v>
       </c>
       <c r="D2" t="n">
         <v>51.2</v>
@@ -8603,10 +8603,10 @@
         <v>48.8</v>
       </c>
       <c r="F2" t="n">
-        <v>37.9</v>
+        <v>37.7</v>
       </c>
       <c r="G2" t="n">
-        <v>12.1</v>
+        <v>12.3</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1493</v>
+        <v>1579</v>
       </c>
       <c r="D3" t="n">
-        <v>50.2</v>
+        <v>50.9</v>
       </c>
       <c r="E3" t="n">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="F3" t="n">
-        <v>40.3</v>
+        <v>40</v>
       </c>
       <c r="G3" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1469</v>
+        <v>1555</v>
       </c>
       <c r="D4" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="E4" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="F4" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8707,23 +8707,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EURCHF</t>
+          <t>CADCHF</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1408</v>
+        <v>1483</v>
       </c>
       <c r="D5" t="n">
-        <v>50.1</v>
+        <v>51.4</v>
       </c>
       <c r="E5" t="n">
-        <v>49.9</v>
+        <v>48.6</v>
       </c>
       <c r="F5" t="n">
-        <v>42.8</v>
+        <v>42.3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8746,23 +8746,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CADCHF</t>
+          <t>EURCHF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1401</v>
+        <v>1496</v>
       </c>
       <c r="D6" t="n">
-        <v>51.9</v>
+        <v>50.4</v>
       </c>
       <c r="E6" t="n">
-        <v>48.1</v>
+        <v>49.6</v>
       </c>
       <c r="F6" t="n">
-        <v>42.9</v>
+        <v>42.4</v>
       </c>
       <c r="G6" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8789,19 +8789,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1428</v>
+        <v>1516</v>
       </c>
       <c r="D7" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F7" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -8824,23 +8824,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURGBP</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1382</v>
+        <v>1519</v>
       </c>
       <c r="D8" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E8" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F8" t="n">
-        <v>47.2</v>
+        <v>47.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8863,17 +8863,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1418</v>
+        <v>1469</v>
       </c>
       <c r="D9" t="n">
-        <v>51.5</v>
+        <v>49.7</v>
       </c>
       <c r="E9" t="n">
-        <v>48.5</v>
+        <v>50.3</v>
       </c>
       <c r="F9" t="n">
         <v>47.2</v>
@@ -8902,23 +8902,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1431</v>
+        <v>1505</v>
       </c>
       <c r="D10" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
       <c r="E10" t="n">
-        <v>50.5</v>
+        <v>48.6</v>
       </c>
       <c r="F10" t="n">
-        <v>47.4</v>
+        <v>47.2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1431</v>
+        <v>1518</v>
       </c>
       <c r="D11" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="E11" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="F11" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8971,7 +8971,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1438</v>
+        <v>1527</v>
       </c>
       <c r="D12" t="n">
         <v>49.2</v>
@@ -8993,10 +8993,10 @@
         <v>50.8</v>
       </c>
       <c r="F12" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9010,7 +9010,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1415</v>
+        <v>1502</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F13" t="n">
-        <v>54.9</v>
+        <v>55.3</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -9062,33 +9062,33 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1431</v>
+        <v>1519</v>
       </c>
       <c r="D14" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E14" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F14" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Forex Major</t>
+        </is>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
         <v>56</v>
-      </c>
-      <c r="G14" t="n">
-        <v>6</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Forex Major</t>
-        </is>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -9101,19 +9101,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1479</v>
+        <v>1566</v>
       </c>
       <c r="D15" t="n">
-        <v>48.4</v>
+        <v>47.5</v>
       </c>
       <c r="E15" t="n">
-        <v>51.6</v>
+        <v>52.5</v>
       </c>
       <c r="F15" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G15" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9140,13 +9140,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1477</v>
+        <v>1564</v>
       </c>
       <c r="D16" t="n">
-        <v>49.6</v>
+        <v>48.9</v>
       </c>
       <c r="E16" t="n">
-        <v>50.4</v>
+        <v>51.1</v>
       </c>
       <c r="F16" t="n">
         <v>62.9</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -9179,19 +9179,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1344</v>
+        <v>1432</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="F17" t="n">
-        <v>29.8</v>
+        <v>29.6</v>
       </c>
       <c r="G17" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D18" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="E18" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="F18" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="G18" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9253,23 +9253,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDSGD</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1442</v>
+        <v>1495</v>
       </c>
       <c r="D19" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="G19" t="n">
-        <v>13.9</v>
+        <v>14.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -9292,17 +9292,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDSGD</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1407</v>
+        <v>1531</v>
       </c>
       <c r="D20" t="n">
-        <v>49.5</v>
+        <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
         <v>36.1</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1439</v>
+        <v>1528</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="F21" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="G21" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9374,19 +9374,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1422</v>
+        <v>1510</v>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>48.4</v>
       </c>
       <c r="E22" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="F22" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="G22" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9413,13 +9413,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1500</v>
+        <v>1588</v>
       </c>
       <c r="D23" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E23" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F23" t="n">
         <v>37.1</v>
@@ -9452,19 +9452,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1283</v>
+        <v>1364</v>
       </c>
       <c r="D24" t="n">
-        <v>50.6</v>
+        <v>51</v>
       </c>
       <c r="E24" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>37.8</v>
+        <v>37.5</v>
       </c>
       <c r="G24" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9487,23 +9487,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GBPZAR</t>
+          <t>USDPLN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1442</v>
+        <v>1524</v>
       </c>
       <c r="D25" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="E25" t="n">
-        <v>49.2</v>
+        <v>49.9</v>
       </c>
       <c r="F25" t="n">
-        <v>38.3</v>
+        <v>38</v>
       </c>
       <c r="G25" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="J25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>10</v>
@@ -9526,23 +9526,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDPLN</t>
+          <t>GBPZAR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1435</v>
+        <v>1531</v>
       </c>
       <c r="D26" t="n">
-        <v>49.8</v>
+        <v>50.3</v>
       </c>
       <c r="E26" t="n">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="F26" t="n">
-        <v>38.3</v>
+        <v>38.1</v>
       </c>
       <c r="G26" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9553,7 +9553,7 @@
         </is>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>11</v>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1431</v>
+        <v>1518</v>
       </c>
       <c r="D27" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="E27" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="F27" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1436</v>
+        <v>1524</v>
       </c>
       <c r="D28" t="n">
         <v>50.1</v>
@@ -9617,10 +9617,10 @@
         <v>49.9</v>
       </c>
       <c r="F28" t="n">
-        <v>39.9</v>
+        <v>39.6</v>
       </c>
       <c r="G28" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9647,19 +9647,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1430</v>
+        <v>1516</v>
       </c>
       <c r="D29" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="E29" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="F29" t="n">
-        <v>41.5</v>
+        <v>41.1</v>
       </c>
       <c r="G29" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1422</v>
+        <v>1507</v>
       </c>
       <c r="D30" t="n">
-        <v>49.6</v>
+        <v>49.3</v>
       </c>
       <c r="E30" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="F30" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="G30" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9725,19 +9725,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1288</v>
+        <v>1369</v>
       </c>
       <c r="D31" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E31" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F31" t="n">
-        <v>43.1</v>
+        <v>43.4</v>
       </c>
       <c r="G31" t="n">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -9764,19 +9764,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1432</v>
+        <v>1520</v>
       </c>
       <c r="D32" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="E32" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="F32" t="n">
-        <v>44.1</v>
+        <v>43.9</v>
       </c>
       <c r="G32" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1426</v>
+        <v>1513</v>
       </c>
       <c r="D33" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="E33" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="F33" t="n">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="G33" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1424</v>
+        <v>1512</v>
       </c>
       <c r="D34" t="n">
         <v>50.8</v>
@@ -9851,10 +9851,10 @@
         <v>49.2</v>
       </c>
       <c r="F34" t="n">
-        <v>44.8</v>
+        <v>44.3</v>
       </c>
       <c r="G34" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9868,7 +9868,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -9881,19 +9881,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1434</v>
+        <v>1521</v>
       </c>
       <c r="D35" t="n">
-        <v>48.1</v>
+        <v>47.9</v>
       </c>
       <c r="E35" t="n">
-        <v>51.9</v>
+        <v>52.1</v>
       </c>
       <c r="F35" t="n">
-        <v>44.9</v>
+        <v>44.7</v>
       </c>
       <c r="G35" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9920,19 +9920,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1419</v>
+        <v>1507</v>
       </c>
       <c r="D36" t="n">
-        <v>52.9</v>
+        <v>52.7</v>
       </c>
       <c r="E36" t="n">
-        <v>47.1</v>
+        <v>47.3</v>
       </c>
       <c r="F36" t="n">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="G36" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9959,19 +9959,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1422</v>
+        <v>1509</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F37" t="n">
-        <v>46.3</v>
+        <v>45.7</v>
       </c>
       <c r="G37" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9998,19 +9998,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1285</v>
+        <v>1366</v>
       </c>
       <c r="D38" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
       <c r="E38" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="F38" t="n">
-        <v>49.4</v>
+        <v>50.3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10033,23 +10033,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1406</v>
+        <v>364</v>
       </c>
       <c r="D39" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="E39" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="F39" t="n">
-        <v>50.6</v>
+        <v>50.3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="J39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -10072,23 +10072,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1422</v>
+        <v>1495</v>
       </c>
       <c r="D40" t="n">
-        <v>51.3</v>
+        <v>51.1</v>
       </c>
       <c r="E40" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="F40" t="n">
-        <v>51.1</v>
+        <v>50.6</v>
       </c>
       <c r="G40" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10111,23 +10111,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>341</v>
+        <v>1510</v>
       </c>
       <c r="D41" t="n">
-        <v>49.9</v>
+        <v>51.5</v>
       </c>
       <c r="E41" t="n">
-        <v>50.1</v>
+        <v>48.5</v>
       </c>
       <c r="F41" t="n">
-        <v>51.6</v>
+        <v>50.9</v>
       </c>
       <c r="G41" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="J41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>41</v>
@@ -10154,7 +10154,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1434</v>
+        <v>1523</v>
       </c>
       <c r="D42" t="n">
         <v>45.2</v>
@@ -10163,10 +10163,10 @@
         <v>54.8</v>
       </c>
       <c r="F42" t="n">
-        <v>51.6</v>
+        <v>51.4</v>
       </c>
       <c r="G42" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10193,13 +10193,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1409</v>
+        <v>1496</v>
       </c>
       <c r="D43" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="E43" t="n">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="F43" t="n">
         <v>52.1</v>
@@ -10232,7 +10232,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1379</v>
+        <v>1464</v>
       </c>
       <c r="D44" t="n">
         <v>51.4</v>
@@ -10241,10 +10241,10 @@
         <v>48.6</v>
       </c>
       <c r="F44" t="n">
-        <v>52.7</v>
+        <v>52.5</v>
       </c>
       <c r="G44" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1430</v>
+        <v>1518</v>
       </c>
       <c r="D45" t="n">
-        <v>48.5</v>
+        <v>48.3</v>
       </c>
       <c r="E45" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="F45" t="n">
-        <v>53.1</v>
+        <v>53.5</v>
       </c>
       <c r="G45" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1424</v>
+        <v>1511</v>
       </c>
       <c r="D46" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="E46" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F46" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="G46" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -10349,19 +10349,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1399</v>
+        <v>1484</v>
       </c>
       <c r="D47" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="E47" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="F47" t="n">
-        <v>55</v>
+        <v>55.2</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="48">
@@ -10388,19 +10388,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1428</v>
+        <v>1517</v>
       </c>
       <c r="D48" t="n">
-        <v>48</v>
+        <v>47.7</v>
       </c>
       <c r="E48" t="n">
-        <v>52</v>
+        <v>52.3</v>
       </c>
       <c r="F48" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G48" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1319</v>
+        <v>1401</v>
       </c>
       <c r="D49" t="n">
-        <v>47.8</v>
+        <v>48.3</v>
       </c>
       <c r="E49" t="n">
-        <v>52.2</v>
+        <v>51.7</v>
       </c>
       <c r="F49" t="n">
-        <v>57.5</v>
+        <v>57.7</v>
       </c>
       <c r="G49" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10466,19 +10466,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1410</v>
+        <v>1497</v>
       </c>
       <c r="D50" t="n">
-        <v>49.2</v>
+        <v>48.9</v>
       </c>
       <c r="E50" t="n">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="F50" t="n">
-        <v>58.6</v>
+        <v>58.8</v>
       </c>
       <c r="G50" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51">
@@ -10505,19 +10505,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1417</v>
+        <v>1505</v>
       </c>
       <c r="D51" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="E51" t="n">
-        <v>49.8</v>
+        <v>50</v>
       </c>
       <c r="F51" t="n">
-        <v>58.9</v>
+        <v>59.3</v>
       </c>
       <c r="G51" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1420</v>
+        <v>1509</v>
       </c>
       <c r="D52" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="E52" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="F52" t="n">
-        <v>59.6</v>
+        <v>59.8</v>
       </c>
       <c r="G52" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10583,19 +10583,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1416</v>
+        <v>1502</v>
       </c>
       <c r="D53" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="E53" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="F53" t="n">
-        <v>63.3</v>
+        <v>63.4</v>
       </c>
       <c r="G53" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54">
@@ -10622,13 +10622,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1412</v>
+        <v>1499</v>
       </c>
       <c r="D54" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="E54" t="n">
-        <v>51.5</v>
+        <v>51.8</v>
       </c>
       <c r="F54" t="n">
         <v>63.7</v>
@@ -10648,7 +10648,7 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55">
@@ -10661,7 +10661,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1429</v>
+        <v>1517</v>
       </c>
       <c r="D55" t="n">
         <v>48.5</v>
@@ -10670,10 +10670,10 @@
         <v>51.5</v>
       </c>
       <c r="F55" t="n">
-        <v>70.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="G55" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10687,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -10700,13 +10700,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1422</v>
+        <v>1511</v>
       </c>
       <c r="D56" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E56" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F56" t="n">
         <v>75.7</v>
@@ -10739,19 +10739,19 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1434</v>
+        <v>1523</v>
       </c>
       <c r="D57" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="E57" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="F57" t="n">
-        <v>81.7</v>
+        <v>81.8</v>
       </c>
       <c r="G57" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1441</v>
+        <v>1530</v>
       </c>
       <c r="D58" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="E58" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="F58" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="G58" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1440</v>
+        <v>1529</v>
       </c>
       <c r="D59" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="E59" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="F59" t="n">
-        <v>94.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="G59" t="n">
-        <v>44.1</v>
+        <v>44</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10852,23 +10852,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1464</v>
+        <v>1416</v>
       </c>
       <c r="D60" t="n">
-        <v>51.3</v>
+        <v>52.3</v>
       </c>
       <c r="E60" t="n">
-        <v>48.7</v>
+        <v>47.7</v>
       </c>
       <c r="F60" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="G60" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -10891,23 +10891,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1333</v>
+        <v>1549</v>
       </c>
       <c r="D61" t="n">
-        <v>52.7</v>
+        <v>51.5</v>
       </c>
       <c r="E61" t="n">
-        <v>47.3</v>
+        <v>48.5</v>
       </c>
       <c r="F61" t="n">
-        <v>40.1</v>
+        <v>39.8</v>
       </c>
       <c r="G61" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>872</v>
+        <v>927</v>
       </c>
       <c r="D62" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E62" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F62" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="G62" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>859</v>
+        <v>914</v>
       </c>
       <c r="D63" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="E63" t="n">
-        <v>52.6</v>
+        <v>51.9</v>
       </c>
       <c r="F63" t="n">
-        <v>60.7</v>
+        <v>61.4</v>
       </c>
       <c r="G63" t="n">
-        <v>10.7</v>
+        <v>11.4</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -11008,17 +11008,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>860</v>
+        <v>1371</v>
       </c>
       <c r="D64" t="n">
-        <v>50.7</v>
+        <v>49.2</v>
       </c>
       <c r="E64" t="n">
-        <v>49.3</v>
+        <v>50.8</v>
       </c>
       <c r="F64" t="n">
         <v>62</v>
@@ -11038,7 +11038,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65">
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1284</v>
+        <v>915</v>
       </c>
       <c r="D65" t="n">
-        <v>49.1</v>
+        <v>51.6</v>
       </c>
       <c r="E65" t="n">
-        <v>50.9</v>
+        <v>48.4</v>
       </c>
       <c r="F65" t="n">
-        <v>62</v>
+        <v>62.3</v>
       </c>
       <c r="G65" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11077,7 +11077,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66">
@@ -11090,19 +11090,19 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1021</v>
+        <v>1085</v>
       </c>
       <c r="D66" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="E66" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="F66" t="n">
-        <v>62.8</v>
+        <v>63.1</v>
       </c>
       <c r="G66" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -11129,19 +11129,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>888</v>
+        <v>944</v>
       </c>
       <c r="D67" t="n">
-        <v>51.4</v>
+        <v>51.7</v>
       </c>
       <c r="E67" t="n">
-        <v>48.6</v>
+        <v>48.3</v>
       </c>
       <c r="F67" t="n">
-        <v>63.2</v>
+        <v>63.3</v>
       </c>
       <c r="G67" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68">
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1407</v>
+        <v>1522</v>
       </c>
       <c r="D68" t="n">
-        <v>50.4</v>
+        <v>52.7</v>
       </c>
       <c r="E68" t="n">
-        <v>49.6</v>
+        <v>47.3</v>
       </c>
       <c r="F68" t="n">
-        <v>64.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="G68" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69">
@@ -11203,17 +11203,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1433</v>
+        <v>1495</v>
       </c>
       <c r="D69" t="n">
-        <v>52.8</v>
+        <v>50.4</v>
       </c>
       <c r="E69" t="n">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="F69" t="n">
         <v>64.3</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70">
@@ -11242,23 +11242,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1222</v>
+        <v>1506</v>
       </c>
       <c r="D70" t="n">
-        <v>47.5</v>
+        <v>50.3</v>
       </c>
       <c r="E70" t="n">
-        <v>52.5</v>
+        <v>49.7</v>
       </c>
       <c r="F70" t="n">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="G70" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71">
@@ -11281,23 +11281,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1419</v>
+        <v>1299</v>
       </c>
       <c r="D71" t="n">
-        <v>50</v>
+        <v>47.9</v>
       </c>
       <c r="E71" t="n">
-        <v>50</v>
+        <v>52.1</v>
       </c>
       <c r="F71" t="n">
-        <v>64.7</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72">
@@ -11324,19 +11324,19 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1463</v>
+        <v>1547</v>
       </c>
       <c r="D72" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E72" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F72" t="n">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1229</v>
+        <v>1307</v>
       </c>
       <c r="D73" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E73" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F73" t="n">
-        <v>65.40000000000001</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G73" t="n">
-        <v>15.4</v>
+        <v>15.9</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,7 +11402,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1040</v>
+        <v>1107</v>
       </c>
       <c r="D74" t="n">
         <v>49.9</v>
@@ -11411,10 +11411,10 @@
         <v>50.1</v>
       </c>
       <c r="F74" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="G74" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11441,7 +11441,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>526</v>
+        <v>561</v>
       </c>
       <c r="D75" t="n">
         <v>48.7</v>
@@ -11450,10 +11450,10 @@
         <v>51.3</v>
       </c>
       <c r="F75" t="n">
-        <v>53.4</v>
+        <v>53.5</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11480,19 +11480,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>442</v>
+        <v>476</v>
       </c>
       <c r="D76" t="n">
-        <v>51.8</v>
+        <v>51.7</v>
       </c>
       <c r="E76" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="F76" t="n">
-        <v>54.3</v>
+        <v>54</v>
       </c>
       <c r="G76" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>509</v>
+        <v>543</v>
       </c>
       <c r="D77" t="n">
-        <v>48.1</v>
+        <v>48.8</v>
       </c>
       <c r="E77" t="n">
-        <v>51.9</v>
+        <v>51.2</v>
       </c>
       <c r="F77" t="n">
-        <v>56.2</v>
+        <v>57.3</v>
       </c>
       <c r="G77" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="78">
@@ -11558,19 +11558,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1336</v>
+        <v>1421</v>
       </c>
       <c r="D78" t="n">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="E78" t="n">
-        <v>48</v>
+        <v>48.5</v>
       </c>
       <c r="F78" t="n">
-        <v>69.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G78" t="n">
-        <v>19.6</v>
+        <v>19.9</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -11597,19 +11597,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>564</v>
+        <v>604</v>
       </c>
       <c r="D79" t="n">
-        <v>49.8</v>
+        <v>49.5</v>
       </c>
       <c r="E79" t="n">
-        <v>50.2</v>
+        <v>50.5</v>
       </c>
       <c r="F79" t="n">
-        <v>62.6</v>
+        <v>63.1</v>
       </c>
       <c r="G79" t="n">
-        <v>12.6</v>
+        <v>13.1</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1114</v>
+        <v>1183</v>
       </c>
       <c r="D80" t="n">
-        <v>46.9</v>
+        <v>47.2</v>
       </c>
       <c r="E80" t="n">
-        <v>53.1</v>
+        <v>52.8</v>
       </c>
       <c r="F80" t="n">
-        <v>62.8</v>
+        <v>63.3</v>
       </c>
       <c r="G80" t="n">
-        <v>12.8</v>
+        <v>13.3</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="81">
@@ -11675,19 +11675,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1120</v>
+        <v>1191</v>
       </c>
       <c r="D81" t="n">
-        <v>47.4</v>
+        <v>47.7</v>
       </c>
       <c r="E81" t="n">
-        <v>52.6</v>
+        <v>52.3</v>
       </c>
       <c r="F81" t="n">
-        <v>64.59999999999999</v>
+        <v>65</v>
       </c>
       <c r="G81" t="n">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="82">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>371</v>
+        <v>396</v>
       </c>
       <c r="D82" t="n">
-        <v>49.9</v>
+        <v>49.5</v>
       </c>
       <c r="E82" t="n">
-        <v>50.1</v>
+        <v>50.5</v>
       </c>
       <c r="F82" t="n">
-        <v>48.8</v>
+        <v>48</v>
       </c>
       <c r="G82" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11749,11 +11749,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="D83" t="n">
         <v>47.5</v>
@@ -11762,10 +11762,10 @@
         <v>52.5</v>
       </c>
       <c r="F83" t="n">
-        <v>49.3</v>
+        <v>49.9</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84">
@@ -11788,23 +11788,23 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>365</v>
+        <v>398</v>
       </c>
       <c r="D84" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="E84" t="n">
-        <v>52.9</v>
+        <v>52.3</v>
       </c>
       <c r="F84" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
       <c r="G84" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="85">
@@ -11827,23 +11827,23 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>378</v>
+        <v>408</v>
       </c>
       <c r="D85" t="n">
-        <v>45.2</v>
+        <v>50.2</v>
       </c>
       <c r="E85" t="n">
-        <v>54.8</v>
+        <v>49.8</v>
       </c>
       <c r="F85" t="n">
-        <v>55.8</v>
+        <v>55.6</v>
       </c>
       <c r="G85" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11866,23 +11866,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLV</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="D86" t="n">
-        <v>49.7</v>
+        <v>45.3</v>
       </c>
       <c r="E86" t="n">
-        <v>50.3</v>
+        <v>54.7</v>
       </c>
       <c r="F86" t="n">
-        <v>56.5</v>
+        <v>56.7</v>
       </c>
       <c r="G86" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="87">
@@ -11909,19 +11909,19 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="D87" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="E87" t="n">
-        <v>52.3</v>
+        <v>52.7</v>
       </c>
       <c r="F87" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88">
@@ -11944,23 +11944,23 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XLB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>368</v>
+        <v>401</v>
       </c>
       <c r="D88" t="n">
-        <v>47.8</v>
+        <v>51.1</v>
       </c>
       <c r="E88" t="n">
-        <v>52.2</v>
+        <v>48.9</v>
       </c>
       <c r="F88" t="n">
-        <v>61.4</v>
+        <v>62.3</v>
       </c>
       <c r="G88" t="n">
-        <v>11.4</v>
+        <v>12.3</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89">
@@ -11983,23 +11983,23 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>XLB</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="D89" t="n">
-        <v>50.1</v>
+        <v>48.7</v>
       </c>
       <c r="E89" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="F89" t="n">
-        <v>61.8</v>
+        <v>62.4</v>
       </c>
       <c r="G89" t="n">
-        <v>11.8</v>
+        <v>12.4</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="90">
@@ -12026,19 +12026,19 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="D90" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E90" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F90" t="n">
-        <v>63.2</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G90" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91">
@@ -12065,19 +12065,19 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="D91" t="n">
-        <v>53.3</v>
+        <v>54.6</v>
       </c>
       <c r="E91" t="n">
-        <v>46.7</v>
+        <v>45.4</v>
       </c>
       <c r="F91" t="n">
-        <v>63.6</v>
+        <v>64.2</v>
       </c>
       <c r="G91" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="92">
@@ -12104,19 +12104,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="D92" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="E92" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="F92" t="n">
-        <v>63.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G92" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="D93" t="n">
-        <v>48.3</v>
+        <v>49.2</v>
       </c>
       <c r="E93" t="n">
-        <v>51.7</v>
+        <v>50.8</v>
       </c>
       <c r="F93" t="n">
-        <v>69.5</v>
+        <v>70.5</v>
       </c>
       <c r="G93" t="n">
-        <v>19.5</v>
+        <v>20.5</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12169,7 +12169,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94">
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1298</v>
+        <v>1384</v>
       </c>
       <c r="D94" t="n">
         <v>50.8</v>
@@ -12191,10 +12191,10 @@
         <v>49.2</v>
       </c>
       <c r="F94" t="n">
-        <v>56</v>
+        <v>56.3</v>
       </c>
       <c r="G94" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95">
@@ -12221,13 +12221,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D95" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="E95" t="n">
         <v>49.8</v>
-      </c>
-      <c r="E95" t="n">
-        <v>50.2</v>
       </c>
       <c r="F95" t="n">
         <v>56.4</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="96">
@@ -12260,19 +12260,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1426</v>
+        <v>1514</v>
       </c>
       <c r="D96" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="E96" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="F96" t="n">
-        <v>57.1</v>
+        <v>56.9</v>
       </c>
       <c r="G96" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="97">
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1402</v>
+        <v>1531</v>
       </c>
       <c r="D97" t="n">
-        <v>52.4</v>
+        <v>50.2</v>
       </c>
       <c r="E97" t="n">
-        <v>47.6</v>
+        <v>49.8</v>
       </c>
       <c r="F97" t="n">
-        <v>57.4</v>
+        <v>57.7</v>
       </c>
       <c r="G97" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1442</v>
+        <v>1489</v>
       </c>
       <c r="D98" t="n">
-        <v>49.9</v>
+        <v>52.2</v>
       </c>
       <c r="E98" t="n">
-        <v>50.1</v>
+        <v>47.8</v>
       </c>
       <c r="F98" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="G98" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99">
@@ -12377,19 +12377,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D99" t="n">
-        <v>50.4</v>
+        <v>50.8</v>
       </c>
       <c r="E99" t="n">
-        <v>49.6</v>
+        <v>49.2</v>
       </c>
       <c r="F99" t="n">
-        <v>58.6</v>
+        <v>58.7</v>
       </c>
       <c r="G99" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12403,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100">
@@ -12416,19 +12416,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1438</v>
+        <v>1527</v>
       </c>
       <c r="D100" t="n">
-        <v>51.3</v>
+        <v>50.9</v>
       </c>
       <c r="E100" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="F100" t="n">
-        <v>59.1</v>
+        <v>59</v>
       </c>
       <c r="G100" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="101">
@@ -12455,13 +12455,13 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1442</v>
+        <v>1531</v>
       </c>
       <c r="D101" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="E101" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="F101" t="n">
         <v>59.2</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="102">
@@ -12490,23 +12490,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#SOLUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1421</v>
+        <v>1481</v>
       </c>
       <c r="D102" t="n">
-        <v>50.6</v>
+        <v>51.9</v>
       </c>
       <c r="E102" t="n">
-        <v>49.4</v>
+        <v>48.1</v>
       </c>
       <c r="F102" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="G102" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12529,23 +12529,23 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#SOLUSD</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1392</v>
+        <v>1510</v>
       </c>
       <c r="D103" t="n">
-        <v>51.8</v>
+        <v>50.9</v>
       </c>
       <c r="E103" t="n">
-        <v>48.2</v>
+        <v>49.1</v>
       </c>
       <c r="F103" t="n">
-        <v>60</v>
+        <v>60.1</v>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38571</v>
+        <v>38658</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38619</v>
+        <v>38705</v>
       </c>
       <c r="D3" t="n">
         <v>50.3</v>
@@ -12721,13 +12721,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38826</v>
+        <v>38912</v>
       </c>
       <c r="D4" t="n">
-        <v>51.2</v>
+        <v>51.3</v>
       </c>
       <c r="E4" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="F4" t="n">
         <v>41.7</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38230</v>
+        <v>38312</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38706</v>
+        <v>38794</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38225</v>
+        <v>38313</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12847,10 +12847,10 @@
         <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -12877,7 +12877,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38044</v>
+        <v>38131</v>
       </c>
       <c r="D8" t="n">
         <v>49</v>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38507</v>
+        <v>38594</v>
       </c>
       <c r="D9" t="n">
         <v>50.1</v>
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38794</v>
+        <v>38882</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38848</v>
+        <v>38937</v>
       </c>
       <c r="D11" t="n">
         <v>50.7</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38856</v>
+        <v>38943</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13059,7 +13059,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
@@ -13072,7 +13072,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38675</v>
+        <v>38762</v>
       </c>
       <c r="D13" t="n">
         <v>49.6</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38739</v>
+        <v>38827</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13150,7 +13150,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38701</v>
+        <v>38788</v>
       </c>
       <c r="D15" t="n">
         <v>49.5</v>
@@ -13189,13 +13189,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38720</v>
+        <v>38807</v>
       </c>
       <c r="D16" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E16" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F16" t="n">
         <v>60.8</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36904</v>
+        <v>36992</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38916</v>
+        <v>39005</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38448</v>
+        <v>38536</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13315,10 +13315,10 @@
         <v>49.7</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="G19" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -13345,7 +13345,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35157</v>
+        <v>35238</v>
       </c>
       <c r="D20" t="n">
         <v>50.1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38985</v>
+        <v>39074</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38800</v>
+        <v>38887</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38845</v>
+        <v>38933</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39093</v>
+        <v>39181</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39045</v>
+        <v>39134</v>
       </c>
       <c r="D25" t="n">
         <v>49.2</v>
@@ -13579,7 +13579,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38988</v>
+        <v>39076</v>
       </c>
       <c r="D26" t="n">
         <v>49.9</v>
@@ -13618,7 +13618,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35327</v>
+        <v>35408</v>
       </c>
       <c r="D27" t="n">
         <v>49.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>39070</v>
+        <v>39159</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39078</v>
+        <v>39167</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38788</v>
+        <v>38873</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38823</v>
+        <v>38909</v>
       </c>
       <c r="D31" t="n">
         <v>49.4</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38828</v>
+        <v>38915</v>
       </c>
       <c r="D32" t="n">
         <v>49.2</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38850</v>
+        <v>38938</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,19 +13891,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38786</v>
+        <v>38873</v>
       </c>
       <c r="D34" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E34" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F34" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="G34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38788</v>
+        <v>38876</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13939,10 +13939,10 @@
         <v>50.3</v>
       </c>
       <c r="F35" t="n">
-        <v>46.4</v>
+        <v>46.3</v>
       </c>
       <c r="G35" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35212</v>
+        <v>35293</v>
       </c>
       <c r="D36" t="n">
         <v>49.8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38624</v>
+        <v>38711</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37955</v>
+        <v>38040</v>
       </c>
       <c r="D38" t="n">
         <v>50.8</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38783</v>
+        <v>38872</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8193</v>
+        <v>8216</v>
       </c>
       <c r="D40" t="n">
         <v>51.2</v>
@@ -14134,10 +14134,10 @@
         <v>48.8</v>
       </c>
       <c r="F40" t="n">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="G40" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -14164,7 +14164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38460</v>
+        <v>38548</v>
       </c>
       <c r="D41" t="n">
         <v>50.1</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38520</v>
+        <v>38607</v>
       </c>
       <c r="D42" t="n">
         <v>49.8</v>
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38558</v>
+        <v>38647</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38481</v>
+        <v>38568</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38128</v>
+        <v>38213</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38285</v>
+        <v>38374</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38664</v>
+        <v>38752</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38700</v>
+        <v>38788</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14476,7 +14476,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>36066</v>
+        <v>36148</v>
       </c>
       <c r="D49" t="n">
         <v>50.4</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38405</v>
+        <v>38492</v>
       </c>
       <c r="D50" t="n">
         <v>50.3</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38543</v>
+        <v>38631</v>
       </c>
       <c r="D51" t="n">
         <v>49.4</v>
@@ -14563,10 +14563,10 @@
         <v>50.6</v>
       </c>
       <c r="F51" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G51" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38587</v>
+        <v>38676</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,13 +14632,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38458</v>
+        <v>38544</v>
       </c>
       <c r="D53" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E53" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F53" t="n">
         <v>61.5</v>
@@ -14671,7 +14671,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38491</v>
+        <v>38578</v>
       </c>
       <c r="D54" t="n">
         <v>50</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38679</v>
+        <v>38767</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38381</v>
+        <v>38470</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38744</v>
+        <v>38833</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38828</v>
+        <v>38917</v>
       </c>
       <c r="D58" t="n">
         <v>51.5</v>
@@ -14836,10 +14836,10 @@
         <v>48.5</v>
       </c>
       <c r="F58" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="G58" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39030</v>
+        <v>39119</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35431</v>
+        <v>35514</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37386</v>
+        <v>37471</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14983,7 +14983,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37836</v>
+        <v>37924</v>
       </c>
       <c r="D62" t="n">
         <v>50.8</v>
@@ -15022,7 +15022,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23600</v>
+        <v>23655</v>
       </c>
       <c r="D63" t="n">
         <v>50.9</v>
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24020</v>
+        <v>24075</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15070,10 +15070,10 @@
         <v>49.2</v>
       </c>
       <c r="F64" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="G64" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -15096,17 +15096,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>24044</v>
+        <v>38821</v>
       </c>
       <c r="D65" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="E65" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="F65" t="n">
         <v>56</v>
@@ -15135,23 +15135,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38732</v>
+        <v>24099</v>
       </c>
       <c r="D66" t="n">
-        <v>51.2</v>
+        <v>51</v>
       </c>
       <c r="E66" t="n">
-        <v>48.8</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G66" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H66" t="b">
         <v>1</v>
@@ -15165,7 +15165,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
@@ -15178,7 +15178,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38237</v>
+        <v>38324</v>
       </c>
       <c r="D67" t="n">
         <v>50.6</v>
@@ -15204,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
@@ -15217,13 +15217,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21435</v>
+        <v>21491</v>
       </c>
       <c r="D68" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="E68" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="F68" t="n">
         <v>56.2</v>
@@ -15243,7 +15243,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69">
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36488</v>
+        <v>36575</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30848</v>
+        <v>30925</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37908</v>
+        <v>37992</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15343,10 +15343,10 @@
         <v>48.9</v>
       </c>
       <c r="F71" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="G71" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33322</v>
+        <v>33400</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26284</v>
+        <v>26348</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74">
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14340</v>
+        <v>14374</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15460,10 +15460,10 @@
         <v>49.9</v>
       </c>
       <c r="F74" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="G74" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14142</v>
+        <v>14176</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15529,7 +15529,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15280</v>
+        <v>15315</v>
       </c>
       <c r="D76" t="n">
         <v>50.5</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26902</v>
+        <v>26969</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36192</v>
+        <v>36277</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15616,10 +15616,10 @@
         <v>49.4</v>
       </c>
       <c r="F78" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79">
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28899</v>
+        <v>28968</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15655,10 +15655,10 @@
         <v>50.7</v>
       </c>
       <c r="F79" t="n">
-        <v>55.6</v>
+        <v>55.7</v>
       </c>
       <c r="G79" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15911</v>
+        <v>15951</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15694,10 +15694,10 @@
         <v>50.3</v>
       </c>
       <c r="F80" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G80" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81">
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28147</v>
+        <v>28218</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15733,10 +15733,10 @@
         <v>50.6</v>
       </c>
       <c r="F81" t="n">
-        <v>57</v>
+        <v>57.1</v>
       </c>
       <c r="G81" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10519</v>
+        <v>10544</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -15772,10 +15772,10 @@
         <v>48.5</v>
       </c>
       <c r="F82" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="G82" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -15789,7 +15789,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="83">
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10525</v>
+        <v>10548</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10303</v>
+        <v>10325</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10821</v>
+        <v>10847</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15889,10 +15889,10 @@
         <v>49.7</v>
       </c>
       <c r="F85" t="n">
-        <v>54.9</v>
+        <v>54.8</v>
       </c>
       <c r="G85" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10305</v>
+        <v>10331</v>
       </c>
       <c r="D86" t="n">
         <v>51.1</v>
@@ -15928,10 +15928,10 @@
         <v>48.9</v>
       </c>
       <c r="F86" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="G86" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87">
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10777</v>
+        <v>10803</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10881</v>
+        <v>10905</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11022</v>
+        <v>11048</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -16075,7 +16075,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11022</v>
+        <v>11048</v>
       </c>
       <c r="D90" t="n">
         <v>51.6</v>
@@ -16084,10 +16084,10 @@
         <v>48.4</v>
       </c>
       <c r="F90" t="n">
-        <v>59.2</v>
+        <v>59.3</v>
       </c>
       <c r="G90" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -16101,7 +16101,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
@@ -16114,7 +16114,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10948</v>
+        <v>10974</v>
       </c>
       <c r="D91" t="n">
         <v>51.7</v>
@@ -16123,10 +16123,10 @@
         <v>48.3</v>
       </c>
       <c r="F91" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
       <c r="G91" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10364</v>
+        <v>10390</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16192,7 +16192,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10289</v>
+        <v>10311</v>
       </c>
       <c r="D93" t="n">
         <v>51.3</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38258</v>
+        <v>38345</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -16270,13 +16270,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38873</v>
+        <v>38962</v>
       </c>
       <c r="D95" t="n">
-        <v>49.3</v>
+        <v>49.4</v>
       </c>
       <c r="E95" t="n">
-        <v>50.7</v>
+        <v>50.6</v>
       </c>
       <c r="F95" t="n">
         <v>53.8</v>
@@ -16309,7 +16309,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36447</v>
+        <v>36533</v>
       </c>
       <c r="D96" t="n">
         <v>48.9</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>38989</v>
+        <v>39078</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38182</v>
+        <v>38271</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,13 +16426,13 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38777</v>
+        <v>38865</v>
       </c>
       <c r="D99" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E99" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F99" t="n">
         <v>54.2</v>
@@ -16465,13 +16465,13 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38383</v>
+        <v>38472</v>
       </c>
       <c r="D100" t="n">
-        <v>49.2</v>
+        <v>49.3</v>
       </c>
       <c r="E100" t="n">
-        <v>50.8</v>
+        <v>50.7</v>
       </c>
       <c r="F100" t="n">
         <v>54.4</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38636</v>
+        <v>38725</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39066</v>
+        <v>39155</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39087</v>
+        <v>39176</v>
       </c>
       <c r="D103" t="n">
         <v>49.8</v>
@@ -16591,10 +16591,10 @@
         <v>50.2</v>
       </c>
       <c r="F103" t="n">
-        <v>54.9</v>
+        <v>55</v>
       </c>
       <c r="G103" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1527</v>
+        <v>1621</v>
       </c>
       <c r="D2" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E2" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1518</v>
+        <v>1612</v>
       </c>
       <c r="D3" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="E3" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="F3" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1469</v>
+        <v>1556</v>
       </c>
       <c r="D4" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="E4" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="F4" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -609,23 +609,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1505</v>
+        <v>1612</v>
       </c>
       <c r="D5" t="n">
-        <v>51.4</v>
+        <v>49.5</v>
       </c>
       <c r="E5" t="n">
-        <v>48.6</v>
+        <v>50.5</v>
       </c>
       <c r="F5" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -648,23 +648,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1519</v>
+        <v>1597</v>
       </c>
       <c r="D6" t="n">
-        <v>49.5</v>
+        <v>51</v>
       </c>
       <c r="E6" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -678,7 +678,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -687,23 +687,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EURCAD</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1502</v>
+        <v>1608</v>
       </c>
       <c r="D7" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E7" t="n">
         <v>49.9</v>
       </c>
-      <c r="E7" t="n">
-        <v>50.1</v>
-      </c>
       <c r="F7" t="n">
-        <v>55.3</v>
+        <v>44.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8">
@@ -726,20 +726,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>EURCAD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1516</v>
+        <v>1595</v>
       </c>
       <c r="D8" t="n">
-        <v>49.7</v>
+        <v>49.4</v>
       </c>
       <c r="E8" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="F8" t="n">
-        <v>44.5</v>
+        <v>55.5</v>
       </c>
       <c r="G8" t="n">
         <v>5.5</v>
@@ -769,13 +769,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1519</v>
+        <v>1612</v>
       </c>
       <c r="D9" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="E9" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="F9" t="n">
         <v>56.6</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1496</v>
+        <v>1588</v>
       </c>
       <c r="D10" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E10" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F10" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="G10" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1483</v>
+        <v>1577</v>
       </c>
       <c r="D11" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
       <c r="E11" t="n">
-        <v>48.6</v>
+        <v>48.1</v>
       </c>
       <c r="F11" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1555</v>
+        <v>1641</v>
       </c>
       <c r="D12" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="F12" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1579</v>
+        <v>1665</v>
       </c>
       <c r="D13" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E13" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>39.3</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -960,23 +960,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1561</v>
+        <v>1651</v>
       </c>
       <c r="D14" t="n">
-        <v>51.2</v>
+        <v>47.5</v>
       </c>
       <c r="E14" t="n">
-        <v>48.8</v>
+        <v>52.5</v>
       </c>
       <c r="F14" t="n">
-        <v>37.7</v>
+        <v>62.7</v>
       </c>
       <c r="G14" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -999,23 +999,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1566</v>
+        <v>1648</v>
       </c>
       <c r="D15" t="n">
-        <v>47.5</v>
+        <v>51.2</v>
       </c>
       <c r="E15" t="n">
-        <v>52.5</v>
+        <v>48.8</v>
       </c>
       <c r="F15" t="n">
-        <v>62.5</v>
+        <v>37.3</v>
       </c>
       <c r="G15" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="J15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16">
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1564</v>
+        <v>1652</v>
       </c>
       <c r="D16" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E16" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F16" t="n">
-        <v>62.9</v>
+        <v>63.4</v>
       </c>
       <c r="G16" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -1077,23 +1077,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EURNOK</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1366</v>
+        <v>395</v>
       </c>
       <c r="D17" t="n">
-        <v>48.7</v>
+        <v>51.1</v>
       </c>
       <c r="E17" t="n">
-        <v>51.3</v>
+        <v>48.9</v>
       </c>
       <c r="F17" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1104,10 +1104,10 @@
         </is>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1116,23 +1116,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>EURNOK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>364</v>
+        <v>1452</v>
       </c>
       <c r="D18" t="n">
-        <v>50.5</v>
+        <v>48.6</v>
       </c>
       <c r="E18" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
       <c r="F18" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1495</v>
+        <v>1617</v>
       </c>
       <c r="D19" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F19" t="n">
         <v>51.1</v>
       </c>
-      <c r="E19" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F19" t="n">
-        <v>50.6</v>
-      </c>
       <c r="G19" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1510</v>
+        <v>1587</v>
       </c>
       <c r="D20" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="E20" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="F20" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1523</v>
+        <v>1602</v>
       </c>
       <c r="D21" t="n">
-        <v>45.2</v>
+        <v>51.2</v>
       </c>
       <c r="E21" t="n">
-        <v>54.8</v>
+        <v>48.8</v>
       </c>
       <c r="F21" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>9</v>
@@ -1272,23 +1272,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1496</v>
+        <v>1556</v>
       </c>
       <c r="D22" t="n">
-        <v>47.5</v>
+        <v>51.5</v>
       </c>
       <c r="E22" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="F22" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1299,10 +1299,10 @@
         </is>
       </c>
       <c r="J22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -1311,23 +1311,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1464</v>
+        <v>1590</v>
       </c>
       <c r="D23" t="n">
-        <v>51.4</v>
+        <v>47.2</v>
       </c>
       <c r="E23" t="n">
-        <v>48.6</v>
+        <v>52.8</v>
       </c>
       <c r="F23" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1338,7 +1338,7 @@
         </is>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>13</v>
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1518</v>
+        <v>1612</v>
       </c>
       <c r="D24" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="E24" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F24" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="G24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1380,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -1389,23 +1389,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1509</v>
+        <v>1600</v>
       </c>
       <c r="D25" t="n">
-        <v>50.3</v>
+        <v>52.2</v>
       </c>
       <c r="E25" t="n">
-        <v>49.7</v>
+        <v>47.8</v>
       </c>
       <c r="F25" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="G25" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -1428,23 +1428,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GBPSGD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1511</v>
+        <v>1601</v>
       </c>
       <c r="D26" t="n">
-        <v>49.2</v>
+        <v>50.4</v>
       </c>
       <c r="E26" t="n">
-        <v>50.8</v>
+        <v>49.6</v>
       </c>
       <c r="F26" t="n">
-        <v>54.5</v>
+        <v>45.6</v>
       </c>
       <c r="G26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1467,20 +1467,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>GBPSGD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1507</v>
+        <v>1604</v>
       </c>
       <c r="D27" t="n">
-        <v>52.7</v>
+        <v>48.5</v>
       </c>
       <c r="E27" t="n">
-        <v>47.3</v>
+        <v>51.5</v>
       </c>
       <c r="F27" t="n">
-        <v>45.4</v>
+        <v>54.6</v>
       </c>
       <c r="G27" t="n">
         <v>4.6</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1484</v>
+        <v>1575</v>
       </c>
       <c r="D28" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E28" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F28" t="n">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
       <c r="G28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1536,7 +1536,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
@@ -1545,23 +1545,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GBPAUD</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1521</v>
+        <v>1611</v>
       </c>
       <c r="D29" t="n">
-        <v>47.9</v>
+        <v>47.8</v>
       </c>
       <c r="E29" t="n">
-        <v>52.1</v>
+        <v>52.2</v>
       </c>
       <c r="F29" t="n">
-        <v>44.7</v>
+        <v>55.9</v>
       </c>
       <c r="G29" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>GBPAUD</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1517</v>
+        <v>1615</v>
       </c>
       <c r="D30" t="n">
-        <v>47.7</v>
+        <v>47.9</v>
       </c>
       <c r="E30" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="F30" t="n">
-        <v>55.6</v>
+        <v>44</v>
       </c>
       <c r="G30" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -1623,23 +1623,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EURPLN</t>
+          <t>EURHUF</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1512</v>
+        <v>1607</v>
       </c>
       <c r="D31" t="n">
-        <v>50.8</v>
+        <v>48.2</v>
       </c>
       <c r="E31" t="n">
-        <v>49.2</v>
+        <v>51.8</v>
       </c>
       <c r="F31" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
       <c r="G31" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1662,23 +1662,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EURHUF</t>
+          <t>EURPLN</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1513</v>
+        <v>1605</v>
       </c>
       <c r="D32" t="n">
-        <v>48.1</v>
+        <v>50.9</v>
       </c>
       <c r="E32" t="n">
-        <v>51.9</v>
+        <v>49.1</v>
       </c>
       <c r="F32" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1701,23 +1701,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1520</v>
+        <v>1455</v>
       </c>
       <c r="D33" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E33" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F33" t="n">
-        <v>43.9</v>
+        <v>43.5</v>
       </c>
       <c r="G33" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="J33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1369</v>
+        <v>1614</v>
       </c>
       <c r="D34" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="E34" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="F34" t="n">
         <v>43.4</v>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35">
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1401</v>
+        <v>1490</v>
       </c>
       <c r="D35" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E35" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="F35" t="n">
-        <v>57.7</v>
+        <v>58.1</v>
       </c>
       <c r="G35" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36">
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1507</v>
+        <v>1601</v>
       </c>
       <c r="D36" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E36" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F36" t="n">
-        <v>41.9</v>
+        <v>41.5</v>
       </c>
       <c r="G36" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1857,23 +1857,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>EURNZD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1497</v>
+        <v>1610</v>
       </c>
       <c r="D37" t="n">
-        <v>48.9</v>
+        <v>49.9</v>
       </c>
       <c r="E37" t="n">
-        <v>51.1</v>
+        <v>50.1</v>
       </c>
       <c r="F37" t="n">
-        <v>58.8</v>
+        <v>41.1</v>
       </c>
       <c r="G37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38">
@@ -1896,23 +1896,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EURNZD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1516</v>
+        <v>1598</v>
       </c>
       <c r="D38" t="n">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="E38" t="n">
-        <v>49.7</v>
+        <v>50.2</v>
       </c>
       <c r="F38" t="n">
-        <v>41.1</v>
+        <v>59.2</v>
       </c>
       <c r="G38" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39">
@@ -1935,17 +1935,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1505</v>
+        <v>1591</v>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="F39" t="n">
         <v>59.3</v>
@@ -1965,7 +1965,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40">
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1509</v>
+        <v>1602</v>
       </c>
       <c r="D40" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="E40" t="n">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
       <c r="F40" t="n">
-        <v>59.8</v>
+        <v>60.3</v>
       </c>
       <c r="G40" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -2004,7 +2004,7 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41">
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1524</v>
+        <v>1618</v>
       </c>
       <c r="D41" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
       <c r="E41" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="F41" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
       <c r="G41" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
@@ -2056,19 +2056,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1518</v>
+        <v>1611</v>
       </c>
       <c r="D42" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="E42" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="F42" t="n">
-        <v>39</v>
+        <v>38.4</v>
       </c>
       <c r="G42" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2082,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43">
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D43" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="E43" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="F43" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="G43" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1524</v>
+        <v>1618</v>
       </c>
       <c r="D44" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="E44" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="F44" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="G44" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45">
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1364</v>
+        <v>1450</v>
       </c>
       <c r="D45" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E45" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F45" t="n">
-        <v>37.5</v>
+        <v>37.1</v>
       </c>
       <c r="G45" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDSEK</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1588</v>
+        <v>1595</v>
       </c>
       <c r="D46" t="n">
-        <v>51.1</v>
+        <v>47.6</v>
       </c>
       <c r="E46" t="n">
-        <v>48.9</v>
+        <v>52.4</v>
       </c>
       <c r="F46" t="n">
-        <v>37.1</v>
+        <v>63.4</v>
       </c>
       <c r="G46" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="J46" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="47">
@@ -2247,23 +2247,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>USDSEK</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1502</v>
+        <v>1676</v>
       </c>
       <c r="D47" t="n">
-        <v>47.8</v>
+        <v>51</v>
       </c>
       <c r="E47" t="n">
-        <v>52.2</v>
+        <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>63.4</v>
+        <v>36.5</v>
       </c>
       <c r="G47" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="J47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="48">
@@ -2290,19 +2290,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1510</v>
+        <v>1604</v>
       </c>
       <c r="D48" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E48" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F48" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="G48" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1499</v>
+        <v>1622</v>
       </c>
       <c r="D49" t="n">
-        <v>48.2</v>
+        <v>50.9</v>
       </c>
       <c r="E49" t="n">
-        <v>51.8</v>
+        <v>49.1</v>
       </c>
       <c r="F49" t="n">
-        <v>63.7</v>
+        <v>35.9</v>
       </c>
       <c r="G49" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="J49" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>80</v>
@@ -2364,23 +2364,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1528</v>
+        <v>1625</v>
       </c>
       <c r="D50" t="n">
-        <v>50.2</v>
+        <v>51.3</v>
       </c>
       <c r="E50" t="n">
-        <v>49.8</v>
+        <v>48.7</v>
       </c>
       <c r="F50" t="n">
-        <v>36.2</v>
+        <v>35.8</v>
       </c>
       <c r="G50" t="n">
-        <v>13.8</v>
+        <v>14.2</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="J50" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>81</v>
@@ -2403,23 +2403,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1531</v>
+        <v>1591</v>
       </c>
       <c r="D51" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E51" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F51" t="n">
-        <v>36.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G51" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1495</v>
+        <v>1589</v>
       </c>
       <c r="D52" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F52" t="n">
-        <v>35.9</v>
+        <v>35.2</v>
       </c>
       <c r="G52" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2472,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53">
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D53" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="E53" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="F53" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="G53" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1432</v>
+        <v>1519</v>
       </c>
       <c r="D54" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="E54" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="F54" t="n">
         <v>29.6</v>
@@ -2550,7 +2550,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55">
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1517</v>
+        <v>1611</v>
       </c>
       <c r="D55" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E55" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F55" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="G55" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="56">
@@ -2602,19 +2602,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1511</v>
+        <v>1603</v>
       </c>
       <c r="D56" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E56" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F56" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1523</v>
+        <v>1617</v>
       </c>
       <c r="D57" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
         <v>81.8</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1530</v>
+        <v>1623</v>
       </c>
       <c r="D58" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="E58" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="F58" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,19 +2719,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1529</v>
+        <v>1623</v>
       </c>
       <c r="D59" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E59" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F59" t="n">
-        <v>94</v>
+        <v>93.7</v>
       </c>
       <c r="G59" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1549</v>
+        <v>1506</v>
       </c>
       <c r="D60" t="n">
-        <v>51.5</v>
+        <v>52.7</v>
       </c>
       <c r="E60" t="n">
-        <v>48.5</v>
+        <v>47.3</v>
       </c>
       <c r="F60" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="G60" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="61">
@@ -2793,17 +2793,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1416</v>
+        <v>1636</v>
       </c>
       <c r="D61" t="n">
-        <v>52.3</v>
+        <v>51.3</v>
       </c>
       <c r="E61" t="n">
-        <v>47.7</v>
+        <v>48.7</v>
       </c>
       <c r="F61" t="n">
         <v>39.4</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62">
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>927</v>
+        <v>987</v>
       </c>
       <c r="D62" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="E62" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F62" t="n">
-        <v>60</v>
+        <v>59.6</v>
       </c>
       <c r="G62" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63">
@@ -2875,19 +2875,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>914</v>
+        <v>976</v>
       </c>
       <c r="D63" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="E63" t="n">
-        <v>51.9</v>
+        <v>52.5</v>
       </c>
       <c r="F63" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="G63" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64">
@@ -2910,23 +2910,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1371</v>
+        <v>974</v>
       </c>
       <c r="D64" t="n">
-        <v>49.2</v>
+        <v>51.2</v>
       </c>
       <c r="E64" t="n">
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="F64" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="G64" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65">
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>915</v>
+        <v>1463</v>
       </c>
       <c r="D65" t="n">
-        <v>51.6</v>
+        <v>48.7</v>
       </c>
       <c r="E65" t="n">
-        <v>48.4</v>
+        <v>51.3</v>
       </c>
       <c r="F65" t="n">
-        <v>62.3</v>
+        <v>62.1</v>
       </c>
       <c r="G65" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66">
@@ -2988,17 +2988,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1085</v>
+        <v>1006</v>
       </c>
       <c r="D66" t="n">
-        <v>49.7</v>
+        <v>51.1</v>
       </c>
       <c r="E66" t="n">
-        <v>50.3</v>
+        <v>48.9</v>
       </c>
       <c r="F66" t="n">
         <v>63.1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67">
@@ -3027,23 +3027,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>944</v>
+        <v>1155</v>
       </c>
       <c r="D67" t="n">
-        <v>51.7</v>
+        <v>49.2</v>
       </c>
       <c r="E67" t="n">
-        <v>48.3</v>
+        <v>50.8</v>
       </c>
       <c r="F67" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
       <c r="G67" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1522</v>
+        <v>1598</v>
       </c>
       <c r="D68" t="n">
-        <v>52.7</v>
+        <v>49.6</v>
       </c>
       <c r="E68" t="n">
-        <v>47.3</v>
+        <v>50.4</v>
       </c>
       <c r="F68" t="n">
-        <v>64.2</v>
+        <v>64.5</v>
       </c>
       <c r="G68" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69">
@@ -3109,19 +3109,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1495</v>
+        <v>1587</v>
       </c>
       <c r="D69" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="E69" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="F69" t="n">
-        <v>64.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70">
@@ -3144,23 +3144,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1506</v>
+        <v>1616</v>
       </c>
       <c r="D70" t="n">
-        <v>50.3</v>
+        <v>52.4</v>
       </c>
       <c r="E70" t="n">
-        <v>49.7</v>
+        <v>47.6</v>
       </c>
       <c r="F70" t="n">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
       <c r="G70" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71">
@@ -3187,19 +3187,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1299</v>
+        <v>1380</v>
       </c>
       <c r="D71" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="E71" t="n">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="F71" t="n">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="G71" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1547</v>
+        <v>1636</v>
       </c>
       <c r="D72" t="n">
         <v>50.9</v>
@@ -3235,10 +3235,10 @@
         <v>49.1</v>
       </c>
       <c r="F72" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -3265,19 +3265,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1307</v>
+        <v>1389</v>
       </c>
       <c r="D73" t="n">
-        <v>48.7</v>
+        <v>48.2</v>
       </c>
       <c r="E73" t="n">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="F73" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="G73" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1107</v>
+        <v>1180</v>
       </c>
       <c r="D74" t="n">
-        <v>49.9</v>
+        <v>50.4</v>
       </c>
       <c r="E74" t="n">
-        <v>50.1</v>
+        <v>49.6</v>
       </c>
       <c r="F74" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="G74" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>561</v>
+        <v>597</v>
       </c>
       <c r="D75" t="n">
-        <v>48.7</v>
+        <v>49.6</v>
       </c>
       <c r="E75" t="n">
-        <v>51.3</v>
+        <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76">
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="D76" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="E76" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="F76" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="G76" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="D77" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="E77" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="F77" t="n">
-        <v>57.3</v>
+        <v>56.5</v>
       </c>
       <c r="G77" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1421</v>
+        <v>1510</v>
       </c>
       <c r="D78" t="n">
         <v>51.5</v>
@@ -3469,10 +3469,10 @@
         <v>48.5</v>
       </c>
       <c r="F78" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,13 +3499,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="D79" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="E79" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="F79" t="n">
         <v>63.1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1183</v>
+        <v>1261</v>
       </c>
       <c r="D80" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="E80" t="n">
-        <v>52.8</v>
+        <v>53.1</v>
       </c>
       <c r="F80" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81">
@@ -3577,13 +3577,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1191</v>
+        <v>1269</v>
       </c>
       <c r="D81" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
       <c r="E81" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="F81" t="n">
         <v>65</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82">
@@ -3616,19 +3616,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="D82" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
       <c r="E82" t="n">
-        <v>52.5</v>
+        <v>52.9</v>
       </c>
       <c r="F82" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
       <c r="G82" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3642,7 +3642,7 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -3655,19 +3655,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="D83" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="E83" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="F83" t="n">
-        <v>50.3</v>
+        <v>51.5</v>
       </c>
       <c r="G83" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="D84" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="E84" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="F84" t="n">
-        <v>48</v>
+        <v>47.6</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
@@ -3733,19 +3733,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D85" t="n">
-        <v>50.2</v>
+        <v>49.1</v>
       </c>
       <c r="E85" t="n">
-        <v>49.8</v>
+        <v>50.9</v>
       </c>
       <c r="F85" t="n">
-        <v>55.6</v>
+        <v>54.6</v>
       </c>
       <c r="G85" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86">
@@ -3768,23 +3768,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D86" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
       <c r="E86" t="n">
-        <v>54.7</v>
+        <v>54.1</v>
       </c>
       <c r="F86" t="n">
-        <v>56.7</v>
+        <v>57.2</v>
       </c>
       <c r="G86" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="87">
@@ -3807,23 +3807,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="D87" t="n">
-        <v>47.3</v>
+        <v>44.4</v>
       </c>
       <c r="E87" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="F87" t="n">
-        <v>57</v>
+        <v>57.7</v>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="D88" t="n">
-        <v>51.1</v>
+        <v>50.4</v>
       </c>
       <c r="E88" t="n">
-        <v>48.9</v>
+        <v>49.6</v>
       </c>
       <c r="F88" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G88" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89">
@@ -3889,19 +3889,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="D89" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="E89" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="F89" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="G89" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="90">
@@ -3924,23 +3924,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="D90" t="n">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="E90" t="n">
-        <v>48.8</v>
+        <v>46.8</v>
       </c>
       <c r="F90" t="n">
-        <v>64.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G90" t="n">
-        <v>14.1</v>
+        <v>14.7</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="91">
@@ -3963,23 +3963,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="D91" t="n">
-        <v>54.6</v>
+        <v>49.9</v>
       </c>
       <c r="E91" t="n">
-        <v>45.4</v>
+        <v>50.1</v>
       </c>
       <c r="F91" t="n">
-        <v>64.2</v>
+        <v>65</v>
       </c>
       <c r="G91" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="92">
@@ -4006,19 +4006,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="D92" t="n">
-        <v>51.6</v>
+        <v>50.1</v>
       </c>
       <c r="E92" t="n">
-        <v>48.4</v>
+        <v>49.9</v>
       </c>
       <c r="F92" t="n">
-        <v>64.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="D93" t="n">
-        <v>49.2</v>
+        <v>47.5</v>
       </c>
       <c r="E93" t="n">
-        <v>50.8</v>
+        <v>52.5</v>
       </c>
       <c r="F93" t="n">
-        <v>70.5</v>
+        <v>70.8</v>
       </c>
       <c r="G93" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4080,17 +4080,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1384</v>
+        <v>1625</v>
       </c>
       <c r="D94" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>49.2</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
         <v>56.3</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="95">
@@ -4119,17 +4119,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1531</v>
+        <v>1464</v>
       </c>
       <c r="D95" t="n">
-        <v>50.2</v>
+        <v>50.9</v>
       </c>
       <c r="E95" t="n">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="F95" t="n">
         <v>56.4</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="96">
@@ -4162,19 +4162,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1514</v>
+        <v>1608</v>
       </c>
       <c r="D96" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="E96" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="F96" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
       <c r="G96" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -4197,23 +4197,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1531</v>
+        <v>1582</v>
       </c>
       <c r="D97" t="n">
-        <v>50.2</v>
+        <v>52.7</v>
       </c>
       <c r="E97" t="n">
-        <v>49.8</v>
+        <v>47.3</v>
       </c>
       <c r="F97" t="n">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
       <c r="G97" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98">
@@ -4236,23 +4236,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1489</v>
+        <v>1625</v>
       </c>
       <c r="D98" t="n">
-        <v>52.2</v>
+        <v>50.1</v>
       </c>
       <c r="E98" t="n">
-        <v>47.8</v>
+        <v>49.9</v>
       </c>
       <c r="F98" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="G98" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4279,19 +4279,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D99" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="E99" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="F99" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="G99" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100">
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1527</v>
+        <v>1621</v>
       </c>
       <c r="D100" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E100" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F100" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="G100" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101">
@@ -4357,19 +4357,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D101" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="E101" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.2</v>
+        <v>59.7</v>
       </c>
       <c r="G101" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="102">
@@ -4396,19 +4396,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1481</v>
+        <v>1572</v>
       </c>
       <c r="D102" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="E102" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="F102" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="G102" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4422,7 +4422,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="103">
@@ -4435,19 +4435,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1510</v>
+        <v>1602</v>
       </c>
       <c r="D103" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="E103" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
       <c r="G103" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4545,19 +4545,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38594</v>
+        <v>38686</v>
       </c>
       <c r="D2" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -4584,13 +4584,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38131</v>
+        <v>38218</v>
       </c>
       <c r="D3" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E3" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F3" t="n">
         <v>49.1</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38313</v>
+        <v>38405</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38882</v>
+        <v>38975</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38937</v>
+        <v>39031</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38943</v>
+        <v>39037</v>
       </c>
       <c r="D7" t="n">
         <v>51.4</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38794</v>
+        <v>38886</v>
       </c>
       <c r="D8" t="n">
         <v>50.7</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38312</v>
+        <v>38406</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4844,7 +4844,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
@@ -4857,13 +4857,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38762</v>
+        <v>38855</v>
       </c>
       <c r="D10" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E10" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F10" t="n">
         <v>54.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38827</v>
+        <v>38920</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38912</v>
+        <v>38998</v>
       </c>
       <c r="D12" t="n">
         <v>51.3</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38705</v>
+        <v>38791</v>
       </c>
       <c r="D13" t="n">
         <v>50.3</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38658</v>
+        <v>38745</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5048,17 +5048,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38788</v>
+        <v>38892</v>
       </c>
       <c r="D15" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E15" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F15" t="n">
         <v>60.8</v>
@@ -5087,23 +5087,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38807</v>
+        <v>38876</v>
       </c>
       <c r="D16" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E16" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F16" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G16" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38872</v>
+        <v>38966</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8216</v>
+        <v>8247</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38548</v>
+        <v>38641</v>
       </c>
       <c r="D19" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E19" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F19" t="n">
         <v>50.6</v>
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38040</v>
+        <v>38132</v>
       </c>
       <c r="D20" t="n">
         <v>50.8</v>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38711</v>
+        <v>38803</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35293</v>
+        <v>35379</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5351,7 +5351,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38876</v>
+        <v>38969</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,19 +5403,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38607</v>
+        <v>38701</v>
       </c>
       <c r="D24" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E24" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F24" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G24" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25">
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38647</v>
+        <v>38741</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38873</v>
+        <v>38967</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38568</v>
+        <v>38661</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38213</v>
+        <v>38304</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38374</v>
+        <v>38466</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38752</v>
+        <v>38846</v>
       </c>
       <c r="D30" t="n">
         <v>50.6</v>
@@ -5676,7 +5676,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38788</v>
+        <v>38880</v>
       </c>
       <c r="D31" t="n">
         <v>51.1</v>
@@ -5702,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="32">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38938</v>
+        <v>39032</v>
       </c>
       <c r="D32" t="n">
         <v>49.5</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38909</v>
+        <v>39003</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38915</v>
+        <v>39009</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38873</v>
+        <v>38967</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39167</v>
+        <v>39261</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5880,10 +5880,10 @@
         <v>50.9</v>
       </c>
       <c r="F36" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="G36" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -5897,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37">
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39159</v>
+        <v>39253</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5919,10 +5919,10 @@
         <v>50.9</v>
       </c>
       <c r="F37" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="G37" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -5936,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38">
@@ -5949,13 +5949,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36148</v>
+        <v>36237</v>
       </c>
       <c r="D38" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="E38" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F38" t="n">
         <v>57.3</v>
@@ -5988,13 +5988,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35408</v>
+        <v>35494</v>
       </c>
       <c r="D39" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
         <v>41.9</v>
@@ -6027,7 +6027,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38492</v>
+        <v>38586</v>
       </c>
       <c r="D40" t="n">
         <v>50.3</v>
@@ -6036,10 +6036,10 @@
         <v>49.7</v>
       </c>
       <c r="F40" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G40" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38631</v>
+        <v>38724</v>
       </c>
       <c r="D41" t="n">
         <v>49.4</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38676</v>
+        <v>38769</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,13 +6144,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39076</v>
+        <v>39170</v>
       </c>
       <c r="D43" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E43" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F43" t="n">
         <v>40.9</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>39134</v>
+        <v>39228</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39181</v>
+        <v>39269</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38933</v>
+        <v>39027</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38887</v>
+        <v>38980</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6309,10 +6309,10 @@
         <v>50.4</v>
       </c>
       <c r="F47" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="G47" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>39074</v>
+        <v>39168</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,19 +6378,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35238</v>
+        <v>35324</v>
       </c>
       <c r="D49" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E49" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F49" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="G49" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38544</v>
+        <v>38637</v>
       </c>
       <c r="D50" t="n">
         <v>49.5</v>
@@ -6456,13 +6456,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38578</v>
+        <v>38670</v>
       </c>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F51" t="n">
         <v>62.1</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38536</v>
+        <v>38630</v>
       </c>
       <c r="D52" t="n">
         <v>50.3</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>39005</v>
+        <v>39099</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>36992</v>
+        <v>37079</v>
       </c>
       <c r="D54" t="n">
         <v>49.1</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38767</v>
+        <v>38861</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38470</v>
+        <v>38562</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38833</v>
+        <v>38927</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6699,10 +6699,10 @@
         <v>49</v>
       </c>
       <c r="F57" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -6729,13 +6729,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38917</v>
+        <v>39010</v>
       </c>
       <c r="D58" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E58" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F58" t="n">
         <v>76.5</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39119</v>
+        <v>39213</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37471</v>
+        <v>37558</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35514</v>
+        <v>35604</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6881,17 +6881,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37924</v>
+        <v>23715</v>
       </c>
       <c r="D62" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E62" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F62" t="n">
         <v>55.1</v>
@@ -6920,23 +6920,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23655</v>
+        <v>38016</v>
       </c>
       <c r="D63" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E63" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F63" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="G63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24075</v>
+        <v>24134</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -6998,23 +6998,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>38821</v>
+        <v>24161</v>
       </c>
       <c r="D65" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E65" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F65" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G65" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66">
@@ -7037,17 +7037,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>24099</v>
+        <v>38915</v>
       </c>
       <c r="D66" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
         <v>56.1</v>
@@ -7076,23 +7076,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38324</v>
+        <v>21553</v>
       </c>
       <c r="D67" t="n">
-        <v>50.6</v>
+        <v>51.8</v>
       </c>
       <c r="E67" t="n">
-        <v>49.4</v>
+        <v>48.2</v>
       </c>
       <c r="F67" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G67" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -7115,17 +7115,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21491</v>
+        <v>38416</v>
       </c>
       <c r="D68" t="n">
-        <v>51.9</v>
+        <v>50.6</v>
       </c>
       <c r="E68" t="n">
-        <v>48.1</v>
+        <v>49.4</v>
       </c>
       <c r="F68" t="n">
         <v>56.2</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36575</v>
+        <v>36667</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -7184,7 +7184,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="70">
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30925</v>
+        <v>31006</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7206,10 +7206,10 @@
         <v>49.2</v>
       </c>
       <c r="F70" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="G70" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37992</v>
+        <v>38081</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33400</v>
+        <v>33482</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7284,10 +7284,10 @@
         <v>49.8</v>
       </c>
       <c r="F72" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="G72" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26348</v>
+        <v>26418</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14374</v>
+        <v>14408</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14176</v>
+        <v>14213</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7431,13 +7431,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15315</v>
+        <v>15351</v>
       </c>
       <c r="D76" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E76" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F76" t="n">
         <v>52.9</v>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26969</v>
+        <v>27042</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -7509,7 +7509,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36277</v>
+        <v>36366</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -7535,7 +7535,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79">
@@ -7548,7 +7548,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28968</v>
+        <v>29046</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -7587,7 +7587,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15951</v>
+        <v>15992</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -7626,7 +7626,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28218</v>
+        <v>28296</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -7652,7 +7652,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82">
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10544</v>
+        <v>10570</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -7704,7 +7704,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10548</v>
+        <v>10573</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -7713,10 +7713,10 @@
         <v>49.4</v>
       </c>
       <c r="F83" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="G83" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -7730,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84">
@@ -7743,7 +7743,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10325</v>
+        <v>10350</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -7752,10 +7752,10 @@
         <v>49.4</v>
       </c>
       <c r="F84" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="G84" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10847</v>
+        <v>10871</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -7821,7 +7821,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10331</v>
+        <v>10356</v>
       </c>
       <c r="D86" t="n">
         <v>51.1</v>
@@ -7847,7 +7847,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87">
@@ -7860,7 +7860,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10803</v>
+        <v>10829</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -7899,7 +7899,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10905</v>
+        <v>10931</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11048</v>
+        <v>11074</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -7947,10 +7947,10 @@
         <v>48.4</v>
       </c>
       <c r="F89" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="G89" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -7977,13 +7977,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11048</v>
+        <v>11073</v>
       </c>
       <c r="D90" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E90" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F90" t="n">
         <v>59.3</v>
@@ -8016,13 +8016,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10974</v>
+        <v>11000</v>
       </c>
       <c r="D91" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="E91" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="F91" t="n">
         <v>59.5</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10390</v>
+        <v>10414</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -8064,10 +8064,10 @@
         <v>49.3</v>
       </c>
       <c r="F92" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="G92" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -8094,19 +8094,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10311</v>
+        <v>10335</v>
       </c>
       <c r="D93" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E93" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -8120,7 +8120,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="94">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38345</v>
+        <v>38438</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -8159,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="95">
@@ -8172,7 +8172,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38962</v>
+        <v>39056</v>
       </c>
       <c r="D95" t="n">
         <v>49.4</v>
@@ -8211,13 +8211,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36533</v>
+        <v>36613</v>
       </c>
       <c r="D96" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E96" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F96" t="n">
         <v>53.8</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>39078</v>
+        <v>39172</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38271</v>
+        <v>38362</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -8328,19 +8328,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38865</v>
+        <v>38959</v>
       </c>
       <c r="D99" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E99" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="G99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -8354,7 +8354,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="100">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38472</v>
+        <v>38566</v>
       </c>
       <c r="D100" t="n">
         <v>49.3</v>
@@ -8406,7 +8406,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38725</v>
+        <v>38817</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -8445,7 +8445,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39155</v>
+        <v>39249</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -8484,7 +8484,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39176</v>
+        <v>39270</v>
       </c>
       <c r="D103" t="n">
         <v>49.8</v>
@@ -8594,7 +8594,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1561</v>
+        <v>1648</v>
       </c>
       <c r="D2" t="n">
         <v>51.2</v>
@@ -8603,10 +8603,10 @@
         <v>48.8</v>
       </c>
       <c r="F2" t="n">
-        <v>37.7</v>
+        <v>37.3</v>
       </c>
       <c r="G2" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -8633,19 +8633,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1579</v>
+        <v>1665</v>
       </c>
       <c r="D3" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E3" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>39.3</v>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -8659,7 +8659,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -8672,19 +8672,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1555</v>
+        <v>1641</v>
       </c>
       <c r="D4" t="n">
-        <v>52</v>
+        <v>52.1</v>
       </c>
       <c r="E4" t="n">
-        <v>48</v>
+        <v>47.9</v>
       </c>
       <c r="F4" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -8711,19 +8711,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1483</v>
+        <v>1577</v>
       </c>
       <c r="D5" t="n">
-        <v>51.4</v>
+        <v>51.9</v>
       </c>
       <c r="E5" t="n">
-        <v>48.6</v>
+        <v>48.1</v>
       </c>
       <c r="F5" t="n">
-        <v>42.3</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -8750,19 +8750,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1496</v>
+        <v>1588</v>
       </c>
       <c r="D6" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E6" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F6" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
@@ -8789,13 +8789,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1516</v>
+        <v>1608</v>
       </c>
       <c r="D7" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="E7" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="F7" t="n">
         <v>44.5</v>
@@ -8815,7 +8815,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -8824,23 +8824,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>GBPCHF</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1519</v>
+        <v>1597</v>
       </c>
       <c r="D8" t="n">
-        <v>49.5</v>
+        <v>51</v>
       </c>
       <c r="E8" t="n">
-        <v>50.5</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>47.1</v>
+        <v>46.4</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -8867,19 +8867,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1469</v>
+        <v>1556</v>
       </c>
       <c r="D9" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="E9" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="F9" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="G9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -8902,23 +8902,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GBPCHF</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1505</v>
+        <v>1612</v>
       </c>
       <c r="D10" t="n">
-        <v>51.4</v>
+        <v>49.5</v>
       </c>
       <c r="E10" t="n">
-        <v>48.6</v>
+        <v>50.5</v>
       </c>
       <c r="F10" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -8945,19 +8945,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1518</v>
+        <v>1612</v>
       </c>
       <c r="D11" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="E11" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="F11" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -8984,19 +8984,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1527</v>
+        <v>1621</v>
       </c>
       <c r="D12" t="n">
-        <v>49.2</v>
+        <v>49.4</v>
       </c>
       <c r="E12" t="n">
-        <v>50.8</v>
+        <v>50.6</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>50.6</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -9023,19 +9023,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1502</v>
+        <v>1595</v>
       </c>
       <c r="D13" t="n">
-        <v>49.9</v>
+        <v>49.4</v>
       </c>
       <c r="E13" t="n">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
       <c r="F13" t="n">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -9049,7 +9049,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -9062,13 +9062,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1519</v>
+        <v>1612</v>
       </c>
       <c r="D14" t="n">
-        <v>49.7</v>
+        <v>49.1</v>
       </c>
       <c r="E14" t="n">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="F14" t="n">
         <v>56.6</v>
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
@@ -9101,7 +9101,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1566</v>
+        <v>1651</v>
       </c>
       <c r="D15" t="n">
         <v>47.5</v>
@@ -9110,10 +9110,10 @@
         <v>52.5</v>
       </c>
       <c r="F15" t="n">
-        <v>62.5</v>
+        <v>62.7</v>
       </c>
       <c r="G15" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -9127,7 +9127,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16">
@@ -9140,19 +9140,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1564</v>
+        <v>1652</v>
       </c>
       <c r="D16" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="E16" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="F16" t="n">
-        <v>62.9</v>
+        <v>63.4</v>
       </c>
       <c r="G16" t="n">
-        <v>12.9</v>
+        <v>13.4</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -9179,13 +9179,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1432</v>
+        <v>1519</v>
       </c>
       <c r="D17" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="E17" t="n">
-        <v>48.9</v>
+        <v>48.5</v>
       </c>
       <c r="F17" t="n">
         <v>29.6</v>
@@ -9218,19 +9218,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D18" t="n">
-        <v>50.6</v>
+        <v>51.3</v>
       </c>
       <c r="E18" t="n">
-        <v>49.4</v>
+        <v>48.7</v>
       </c>
       <c r="F18" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="G18" t="n">
-        <v>17.4</v>
+        <v>17.7</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -9257,19 +9257,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1495</v>
+        <v>1589</v>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>50.3</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>49.7</v>
       </c>
       <c r="F19" t="n">
-        <v>35.9</v>
+        <v>35.2</v>
       </c>
       <c r="G19" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -9296,19 +9296,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D20" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F20" t="n">
-        <v>36.1</v>
+        <v>35.8</v>
       </c>
       <c r="G20" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -9335,19 +9335,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1528</v>
+        <v>1622</v>
       </c>
       <c r="D21" t="n">
-        <v>50.2</v>
+        <v>50.9</v>
       </c>
       <c r="E21" t="n">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="F21" t="n">
-        <v>36.2</v>
+        <v>35.9</v>
       </c>
       <c r="G21" t="n">
-        <v>13.8</v>
+        <v>14.1</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -9374,19 +9374,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1510</v>
+        <v>1604</v>
       </c>
       <c r="D22" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="E22" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="F22" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="G22" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -9413,19 +9413,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1588</v>
+        <v>1676</v>
       </c>
       <c r="D23" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="E23" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>37.1</v>
+        <v>36.5</v>
       </c>
       <c r="G23" t="n">
-        <v>12.9</v>
+        <v>13.5</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -9452,19 +9452,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1364</v>
+        <v>1450</v>
       </c>
       <c r="D24" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E24" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F24" t="n">
-        <v>37.5</v>
+        <v>37.1</v>
       </c>
       <c r="G24" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -9491,19 +9491,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1524</v>
+        <v>1618</v>
       </c>
       <c r="D25" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="E25" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="F25" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -9530,19 +9530,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D26" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="E26" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="F26" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
@@ -9569,19 +9569,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1518</v>
+        <v>1611</v>
       </c>
       <c r="D27" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="E27" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="F27" t="n">
-        <v>39</v>
+        <v>38.4</v>
       </c>
       <c r="G27" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
@@ -9608,19 +9608,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1524</v>
+        <v>1618</v>
       </c>
       <c r="D28" t="n">
-        <v>50.1</v>
+        <v>50.7</v>
       </c>
       <c r="E28" t="n">
-        <v>49.9</v>
+        <v>49.3</v>
       </c>
       <c r="F28" t="n">
-        <v>39.6</v>
+        <v>39.2</v>
       </c>
       <c r="G28" t="n">
-        <v>10.4</v>
+        <v>10.8</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
@@ -9647,13 +9647,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1516</v>
+        <v>1610</v>
       </c>
       <c r="D29" t="n">
-        <v>50.3</v>
+        <v>49.9</v>
       </c>
       <c r="E29" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="F29" t="n">
         <v>41.1</v>
@@ -9686,19 +9686,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1507</v>
+        <v>1601</v>
       </c>
       <c r="D30" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E30" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F30" t="n">
-        <v>41.9</v>
+        <v>41.5</v>
       </c>
       <c r="G30" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -9721,17 +9721,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USDNOK</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1369</v>
+        <v>1614</v>
       </c>
       <c r="D31" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="E31" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="F31" t="n">
         <v>43.4</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>22</v>
@@ -9760,23 +9760,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>USDNOK</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1520</v>
+        <v>1455</v>
       </c>
       <c r="D32" t="n">
-        <v>49.3</v>
+        <v>49.7</v>
       </c>
       <c r="E32" t="n">
-        <v>50.7</v>
+        <v>50.3</v>
       </c>
       <c r="F32" t="n">
-        <v>43.9</v>
+        <v>43.5</v>
       </c>
       <c r="G32" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -9787,7 +9787,7 @@
         </is>
       </c>
       <c r="J32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>23</v>
@@ -9803,19 +9803,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1513</v>
+        <v>1607</v>
       </c>
       <c r="D33" t="n">
-        <v>48.1</v>
+        <v>48.2</v>
       </c>
       <c r="E33" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="F33" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="G33" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -9842,19 +9842,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1512</v>
+        <v>1605</v>
       </c>
       <c r="D34" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E34" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F34" t="n">
-        <v>44.3</v>
+        <v>43.7</v>
       </c>
       <c r="G34" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -9881,7 +9881,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1521</v>
+        <v>1615</v>
       </c>
       <c r="D35" t="n">
         <v>47.9</v>
@@ -9890,10 +9890,10 @@
         <v>52.1</v>
       </c>
       <c r="F35" t="n">
-        <v>44.7</v>
+        <v>44</v>
       </c>
       <c r="G35" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
@@ -9916,23 +9916,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AUDNZD</t>
+          <t>SGDJPY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1507</v>
+        <v>1601</v>
       </c>
       <c r="D36" t="n">
-        <v>52.7</v>
+        <v>50.4</v>
       </c>
       <c r="E36" t="n">
-        <v>47.3</v>
+        <v>49.6</v>
       </c>
       <c r="F36" t="n">
-        <v>45.4</v>
+        <v>45.6</v>
       </c>
       <c r="G36" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -9955,23 +9955,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SGDJPY</t>
+          <t>AUDNZD</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1509</v>
+        <v>1600</v>
       </c>
       <c r="D37" t="n">
-        <v>50.3</v>
+        <v>52.2</v>
       </c>
       <c r="E37" t="n">
-        <v>49.7</v>
+        <v>47.8</v>
       </c>
       <c r="F37" t="n">
-        <v>45.7</v>
+        <v>45.9</v>
       </c>
       <c r="G37" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -9994,23 +9994,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EURNOK</t>
+          <t>USDRUB</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1366</v>
+        <v>395</v>
       </c>
       <c r="D38" t="n">
-        <v>48.7</v>
+        <v>51.1</v>
       </c>
       <c r="E38" t="n">
-        <v>51.3</v>
+        <v>48.9</v>
       </c>
       <c r="F38" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -10021,10 +10021,10 @@
         </is>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39">
@@ -10033,23 +10033,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>USDRUB</t>
+          <t>EURNOK</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>364</v>
+        <v>1452</v>
       </c>
       <c r="D39" t="n">
-        <v>50.5</v>
+        <v>48.6</v>
       </c>
       <c r="E39" t="n">
-        <v>49.5</v>
+        <v>51.4</v>
       </c>
       <c r="F39" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="G39" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -10060,10 +10060,10 @@
         </is>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40">
@@ -10072,23 +10072,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1495</v>
+        <v>1617</v>
       </c>
       <c r="D40" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="F40" t="n">
         <v>51.1</v>
       </c>
-      <c r="E40" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="F40" t="n">
-        <v>50.6</v>
-      </c>
       <c r="G40" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
@@ -10099,10 +10099,10 @@
         </is>
       </c>
       <c r="J40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
@@ -10111,23 +10111,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1510</v>
+        <v>1587</v>
       </c>
       <c r="D41" t="n">
-        <v>51.5</v>
+        <v>50.8</v>
       </c>
       <c r="E41" t="n">
-        <v>48.5</v>
+        <v>49.2</v>
       </c>
       <c r="F41" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -10141,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -10150,23 +10150,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1523</v>
+        <v>1602</v>
       </c>
       <c r="D42" t="n">
-        <v>45.2</v>
+        <v>51.2</v>
       </c>
       <c r="E42" t="n">
-        <v>54.8</v>
+        <v>48.8</v>
       </c>
       <c r="F42" t="n">
-        <v>51.4</v>
+        <v>51.6</v>
       </c>
       <c r="G42" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="J42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>42</v>
@@ -10189,23 +10189,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EURSGD</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1496</v>
+        <v>1556</v>
       </c>
       <c r="D43" t="n">
-        <v>47.5</v>
+        <v>51.5</v>
       </c>
       <c r="E43" t="n">
-        <v>52.5</v>
+        <v>48.5</v>
       </c>
       <c r="F43" t="n">
-        <v>52.1</v>
+        <v>52.3</v>
       </c>
       <c r="G43" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -10216,7 +10216,7 @@
         </is>
       </c>
       <c r="J43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>44</v>
@@ -10228,23 +10228,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>EURSGD</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1464</v>
+        <v>1590</v>
       </c>
       <c r="D44" t="n">
-        <v>51.4</v>
+        <v>47.2</v>
       </c>
       <c r="E44" t="n">
-        <v>48.6</v>
+        <v>52.8</v>
       </c>
       <c r="F44" t="n">
-        <v>52.5</v>
+        <v>52.6</v>
       </c>
       <c r="G44" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="J44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>45</v>
@@ -10271,19 +10271,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1518</v>
+        <v>1612</v>
       </c>
       <c r="D45" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="E45" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F45" t="n">
-        <v>53.5</v>
+        <v>53.6</v>
       </c>
       <c r="G45" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -10297,7 +10297,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="46">
@@ -10310,19 +10310,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1511</v>
+        <v>1604</v>
       </c>
       <c r="D46" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="E46" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="F46" t="n">
-        <v>54.5</v>
+        <v>54.6</v>
       </c>
       <c r="G46" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
@@ -10349,19 +10349,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1484</v>
+        <v>1575</v>
       </c>
       <c r="D47" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="E47" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="F47" t="n">
-        <v>55.2</v>
+        <v>55.3</v>
       </c>
       <c r="G47" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48">
@@ -10388,19 +10388,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1517</v>
+        <v>1611</v>
       </c>
       <c r="D48" t="n">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="E48" t="n">
-        <v>52.3</v>
+        <v>52.2</v>
       </c>
       <c r="F48" t="n">
-        <v>55.6</v>
+        <v>55.9</v>
       </c>
       <c r="G48" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="49">
@@ -10427,19 +10427,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1401</v>
+        <v>1490</v>
       </c>
       <c r="D49" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E49" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="F49" t="n">
-        <v>57.7</v>
+        <v>58.1</v>
       </c>
       <c r="G49" t="n">
-        <v>7.7</v>
+        <v>8.1</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -10453,7 +10453,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="50">
@@ -10462,23 +10462,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1497</v>
+        <v>1598</v>
       </c>
       <c r="D50" t="n">
-        <v>48.9</v>
+        <v>49.8</v>
       </c>
       <c r="E50" t="n">
-        <v>51.1</v>
+        <v>50.2</v>
       </c>
       <c r="F50" t="n">
-        <v>58.8</v>
+        <v>59.2</v>
       </c>
       <c r="G50" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51">
@@ -10501,17 +10501,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1505</v>
+        <v>1591</v>
       </c>
       <c r="D51" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>51.4</v>
       </c>
       <c r="F51" t="n">
         <v>59.3</v>
@@ -10531,7 +10531,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52">
@@ -10544,19 +10544,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1509</v>
+        <v>1602</v>
       </c>
       <c r="D52" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="E52" t="n">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
       <c r="F52" t="n">
-        <v>59.8</v>
+        <v>60.3</v>
       </c>
       <c r="G52" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53">
@@ -10583,13 +10583,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1502</v>
+        <v>1595</v>
       </c>
       <c r="D53" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="E53" t="n">
-        <v>52.2</v>
+        <v>52.4</v>
       </c>
       <c r="F53" t="n">
         <v>63.4</v>
@@ -10609,7 +10609,7 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54">
@@ -10622,19 +10622,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1499</v>
+        <v>1591</v>
       </c>
       <c r="D54" t="n">
-        <v>48.2</v>
+        <v>48</v>
       </c>
       <c r="E54" t="n">
-        <v>51.8</v>
+        <v>52</v>
       </c>
       <c r="F54" t="n">
-        <v>63.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G54" t="n">
-        <v>13.7</v>
+        <v>14.4</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -10661,19 +10661,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1517</v>
+        <v>1611</v>
       </c>
       <c r="D55" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="E55" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="F55" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="G55" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -10700,19 +10700,19 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1511</v>
+        <v>1603</v>
       </c>
       <c r="D56" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="E56" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="F56" t="n">
-        <v>75.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -10739,13 +10739,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1523</v>
+        <v>1617</v>
       </c>
       <c r="D57" t="n">
-        <v>50.6</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="F57" t="n">
         <v>81.8</v>
@@ -10778,19 +10778,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1530</v>
+        <v>1623</v>
       </c>
       <c r="D58" t="n">
-        <v>50.5</v>
+        <v>49.9</v>
       </c>
       <c r="E58" t="n">
-        <v>49.5</v>
+        <v>50.1</v>
       </c>
       <c r="F58" t="n">
-        <v>82.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -10817,19 +10817,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1529</v>
+        <v>1623</v>
       </c>
       <c r="D59" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E59" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F59" t="n">
-        <v>94</v>
+        <v>93.7</v>
       </c>
       <c r="G59" t="n">
-        <v>44</v>
+        <v>43.7</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -10856,13 +10856,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1416</v>
+        <v>1506</v>
       </c>
       <c r="D60" t="n">
-        <v>52.3</v>
+        <v>52.7</v>
       </c>
       <c r="E60" t="n">
-        <v>47.7</v>
+        <v>47.3</v>
       </c>
       <c r="F60" t="n">
         <v>39.4</v>
@@ -10882,7 +10882,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61">
@@ -10895,19 +10895,19 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1549</v>
+        <v>1636</v>
       </c>
       <c r="D61" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="E61" t="n">
-        <v>48.5</v>
+        <v>48.7</v>
       </c>
       <c r="F61" t="n">
-        <v>39.8</v>
+        <v>39.4</v>
       </c>
       <c r="G61" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -10921,7 +10921,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62">
@@ -10934,19 +10934,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>927</v>
+        <v>987</v>
       </c>
       <c r="D62" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="E62" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F62" t="n">
-        <v>60</v>
+        <v>59.6</v>
       </c>
       <c r="G62" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
@@ -10973,19 +10973,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>914</v>
+        <v>976</v>
       </c>
       <c r="D63" t="n">
-        <v>48.1</v>
+        <v>47.5</v>
       </c>
       <c r="E63" t="n">
-        <v>51.9</v>
+        <v>52.5</v>
       </c>
       <c r="F63" t="n">
-        <v>61.4</v>
+        <v>61.3</v>
       </c>
       <c r="G63" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -11008,23 +11008,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1371</v>
+        <v>974</v>
       </c>
       <c r="D64" t="n">
-        <v>49.2</v>
+        <v>51.2</v>
       </c>
       <c r="E64" t="n">
-        <v>50.8</v>
+        <v>48.8</v>
       </c>
       <c r="F64" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
       <c r="G64" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -11047,23 +11047,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>915</v>
+        <v>1463</v>
       </c>
       <c r="D65" t="n">
-        <v>51.6</v>
+        <v>48.7</v>
       </c>
       <c r="E65" t="n">
-        <v>48.4</v>
+        <v>51.3</v>
       </c>
       <c r="F65" t="n">
-        <v>62.3</v>
+        <v>62.1</v>
       </c>
       <c r="G65" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -11086,17 +11086,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HK50</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1085</v>
+        <v>1006</v>
       </c>
       <c r="D66" t="n">
-        <v>49.7</v>
+        <v>51.1</v>
       </c>
       <c r="E66" t="n">
-        <v>50.3</v>
+        <v>48.9</v>
       </c>
       <c r="F66" t="n">
         <v>63.1</v>
@@ -11116,7 +11116,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67">
@@ -11125,23 +11125,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>HK50</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>944</v>
+        <v>1155</v>
       </c>
       <c r="D67" t="n">
-        <v>51.7</v>
+        <v>49.2</v>
       </c>
       <c r="E67" t="n">
-        <v>48.3</v>
+        <v>50.8</v>
       </c>
       <c r="F67" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
       <c r="G67" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -11155,7 +11155,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68">
@@ -11164,23 +11164,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1522</v>
+        <v>1598</v>
       </c>
       <c r="D68" t="n">
-        <v>52.7</v>
+        <v>49.6</v>
       </c>
       <c r="E68" t="n">
-        <v>47.3</v>
+        <v>50.4</v>
       </c>
       <c r="F68" t="n">
-        <v>64.2</v>
+        <v>64.5</v>
       </c>
       <c r="G68" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69">
@@ -11207,19 +11207,19 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1495</v>
+        <v>1587</v>
       </c>
       <c r="D69" t="n">
-        <v>50.4</v>
+        <v>49.8</v>
       </c>
       <c r="E69" t="n">
-        <v>49.6</v>
+        <v>50.2</v>
       </c>
       <c r="F69" t="n">
-        <v>64.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -11233,7 +11233,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70">
@@ -11242,23 +11242,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1506</v>
+        <v>1616</v>
       </c>
       <c r="D70" t="n">
-        <v>50.3</v>
+        <v>52.4</v>
       </c>
       <c r="E70" t="n">
-        <v>49.7</v>
+        <v>47.6</v>
       </c>
       <c r="F70" t="n">
-        <v>64.3</v>
+        <v>64.7</v>
       </c>
       <c r="G70" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71">
@@ -11285,19 +11285,19 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1299</v>
+        <v>1380</v>
       </c>
       <c r="D71" t="n">
-        <v>47.9</v>
+        <v>47.5</v>
       </c>
       <c r="E71" t="n">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="F71" t="n">
-        <v>64.59999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="G71" t="n">
-        <v>14.6</v>
+        <v>14.8</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -11311,7 +11311,7 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72">
@@ -11324,7 +11324,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1547</v>
+        <v>1636</v>
       </c>
       <c r="D72" t="n">
         <v>50.9</v>
@@ -11333,10 +11333,10 @@
         <v>49.1</v>
       </c>
       <c r="F72" t="n">
-        <v>65.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -11363,19 +11363,19 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1307</v>
+        <v>1389</v>
       </c>
       <c r="D73" t="n">
-        <v>48.7</v>
+        <v>48.2</v>
       </c>
       <c r="E73" t="n">
-        <v>51.3</v>
+        <v>51.8</v>
       </c>
       <c r="F73" t="n">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="G73" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -11402,19 +11402,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1107</v>
+        <v>1180</v>
       </c>
       <c r="D74" t="n">
-        <v>49.9</v>
+        <v>50.4</v>
       </c>
       <c r="E74" t="n">
-        <v>50.1</v>
+        <v>49.6</v>
       </c>
       <c r="F74" t="n">
-        <v>51.5</v>
+        <v>51.7</v>
       </c>
       <c r="G74" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -11441,19 +11441,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>561</v>
+        <v>597</v>
       </c>
       <c r="D75" t="n">
-        <v>48.7</v>
+        <v>49.6</v>
       </c>
       <c r="E75" t="n">
-        <v>51.3</v>
+        <v>50.4</v>
       </c>
       <c r="F75" t="n">
-        <v>53.5</v>
+        <v>53.1</v>
       </c>
       <c r="G75" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -11467,7 +11467,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76">
@@ -11480,19 +11480,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="D76" t="n">
-        <v>51.7</v>
+        <v>52</v>
       </c>
       <c r="E76" t="n">
-        <v>48.3</v>
+        <v>48</v>
       </c>
       <c r="F76" t="n">
-        <v>54</v>
+        <v>54.6</v>
       </c>
       <c r="G76" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77">
@@ -11519,19 +11519,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="D77" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="E77" t="n">
-        <v>51.2</v>
+        <v>50.8</v>
       </c>
       <c r="F77" t="n">
-        <v>57.3</v>
+        <v>56.5</v>
       </c>
       <c r="G77" t="n">
-        <v>7.3</v>
+        <v>6.5</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -11545,7 +11545,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="78">
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1421</v>
+        <v>1510</v>
       </c>
       <c r="D78" t="n">
         <v>51.5</v>
@@ -11567,10 +11567,10 @@
         <v>48.5</v>
       </c>
       <c r="F78" t="n">
-        <v>69.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -11597,13 +11597,13 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="D79" t="n">
-        <v>49.5</v>
+        <v>48.5</v>
       </c>
       <c r="E79" t="n">
-        <v>50.5</v>
+        <v>51.5</v>
       </c>
       <c r="F79" t="n">
         <v>63.1</v>
@@ -11623,7 +11623,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80">
@@ -11636,19 +11636,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1183</v>
+        <v>1261</v>
       </c>
       <c r="D80" t="n">
-        <v>47.2</v>
+        <v>46.9</v>
       </c>
       <c r="E80" t="n">
-        <v>52.8</v>
+        <v>53.1</v>
       </c>
       <c r="F80" t="n">
-        <v>63.3</v>
+        <v>63.6</v>
       </c>
       <c r="G80" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="81">
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1191</v>
+        <v>1269</v>
       </c>
       <c r="D81" t="n">
-        <v>47.7</v>
+        <v>47.1</v>
       </c>
       <c r="E81" t="n">
-        <v>52.3</v>
+        <v>52.9</v>
       </c>
       <c r="F81" t="n">
         <v>65</v>
@@ -11701,7 +11701,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82">
@@ -11714,19 +11714,19 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="D82" t="n">
-        <v>49.5</v>
+        <v>49.8</v>
       </c>
       <c r="E82" t="n">
-        <v>50.5</v>
+        <v>50.2</v>
       </c>
       <c r="F82" t="n">
-        <v>48</v>
+        <v>47.6</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -11753,19 +11753,19 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>387</v>
+        <v>412</v>
       </c>
       <c r="D83" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
       <c r="E83" t="n">
-        <v>52.5</v>
+        <v>52.9</v>
       </c>
       <c r="F83" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
       <c r="G83" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -11779,7 +11779,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84">
@@ -11792,19 +11792,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>398</v>
+        <v>423</v>
       </c>
       <c r="D84" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="E84" t="n">
-        <v>52.3</v>
+        <v>52.5</v>
       </c>
       <c r="F84" t="n">
-        <v>50.3</v>
+        <v>51.5</v>
       </c>
       <c r="G84" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="85">
@@ -11831,19 +11831,19 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D85" t="n">
-        <v>50.2</v>
+        <v>49.1</v>
       </c>
       <c r="E85" t="n">
-        <v>49.8</v>
+        <v>50.9</v>
       </c>
       <c r="F85" t="n">
-        <v>55.6</v>
+        <v>54.6</v>
       </c>
       <c r="G85" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="H85" t="b">
         <v>1</v>
@@ -11857,7 +11857,7 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86">
@@ -11866,23 +11866,23 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XLY</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D86" t="n">
-        <v>45.3</v>
+        <v>45.9</v>
       </c>
       <c r="E86" t="n">
-        <v>54.7</v>
+        <v>54.1</v>
       </c>
       <c r="F86" t="n">
-        <v>56.7</v>
+        <v>57.2</v>
       </c>
       <c r="G86" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87">
@@ -11905,23 +11905,23 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLY</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>393</v>
+        <v>430</v>
       </c>
       <c r="D87" t="n">
-        <v>47.3</v>
+        <v>44.4</v>
       </c>
       <c r="E87" t="n">
-        <v>52.7</v>
+        <v>55.6</v>
       </c>
       <c r="F87" t="n">
-        <v>57</v>
+        <v>57.7</v>
       </c>
       <c r="G87" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -11935,7 +11935,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="88">
@@ -11948,19 +11948,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="D88" t="n">
-        <v>51.1</v>
+        <v>50.4</v>
       </c>
       <c r="E88" t="n">
-        <v>48.9</v>
+        <v>49.6</v>
       </c>
       <c r="F88" t="n">
-        <v>62.3</v>
+        <v>62.5</v>
       </c>
       <c r="G88" t="n">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -11987,19 +11987,19 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="D89" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="E89" t="n">
-        <v>51.3</v>
+        <v>50.7</v>
       </c>
       <c r="F89" t="n">
-        <v>62.4</v>
+        <v>62.9</v>
       </c>
       <c r="G89" t="n">
-        <v>12.4</v>
+        <v>12.9</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -12013,7 +12013,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90">
@@ -12022,23 +12022,23 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SPY</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>412</v>
+        <v>442</v>
       </c>
       <c r="D90" t="n">
-        <v>51.2</v>
+        <v>53.2</v>
       </c>
       <c r="E90" t="n">
-        <v>48.8</v>
+        <v>46.8</v>
       </c>
       <c r="F90" t="n">
-        <v>64.09999999999999</v>
+        <v>64.7</v>
       </c>
       <c r="G90" t="n">
-        <v>14.1</v>
+        <v>14.7</v>
       </c>
       <c r="H90" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="91">
@@ -12061,23 +12061,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="D91" t="n">
-        <v>54.6</v>
+        <v>49.9</v>
       </c>
       <c r="E91" t="n">
-        <v>45.4</v>
+        <v>50.1</v>
       </c>
       <c r="F91" t="n">
-        <v>64.2</v>
+        <v>65</v>
       </c>
       <c r="G91" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -12091,7 +12091,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
     </row>
     <row r="92">
@@ -12104,19 +12104,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="D92" t="n">
-        <v>51.6</v>
+        <v>50.1</v>
       </c>
       <c r="E92" t="n">
-        <v>48.4</v>
+        <v>49.9</v>
       </c>
       <c r="F92" t="n">
-        <v>64.59999999999999</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G92" t="n">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
@@ -12143,19 +12143,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="D93" t="n">
-        <v>49.2</v>
+        <v>47.5</v>
       </c>
       <c r="E93" t="n">
-        <v>50.8</v>
+        <v>52.5</v>
       </c>
       <c r="F93" t="n">
-        <v>70.5</v>
+        <v>70.8</v>
       </c>
       <c r="G93" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -12178,17 +12178,17 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>#DOTUSD</t>
+          <t>#BCHUSD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1384</v>
+        <v>1625</v>
       </c>
       <c r="D94" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="E94" t="n">
-        <v>49.2</v>
+        <v>50</v>
       </c>
       <c r="F94" t="n">
         <v>56.3</v>
@@ -12217,17 +12217,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>#BCHUSD</t>
+          <t>#DOTUSD</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1531</v>
+        <v>1464</v>
       </c>
       <c r="D95" t="n">
-        <v>50.2</v>
+        <v>50.9</v>
       </c>
       <c r="E95" t="n">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="F95" t="n">
         <v>56.4</v>
@@ -12260,19 +12260,19 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1514</v>
+        <v>1608</v>
       </c>
       <c r="D96" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="E96" t="n">
-        <v>49.2</v>
+        <v>49.8</v>
       </c>
       <c r="F96" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
       <c r="G96" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="H96" t="b">
         <v>1</v>
@@ -12295,23 +12295,23 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#LINKUSD</t>
+          <t>#LTCUSD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1531</v>
+        <v>1582</v>
       </c>
       <c r="D97" t="n">
-        <v>50.2</v>
+        <v>52.7</v>
       </c>
       <c r="E97" t="n">
-        <v>49.8</v>
+        <v>47.3</v>
       </c>
       <c r="F97" t="n">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
       <c r="G97" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -12325,7 +12325,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98">
@@ -12334,23 +12334,23 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#LTCUSD</t>
+          <t>#LINKUSD</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1489</v>
+        <v>1625</v>
       </c>
       <c r="D98" t="n">
-        <v>52.2</v>
+        <v>50.1</v>
       </c>
       <c r="E98" t="n">
-        <v>47.8</v>
+        <v>49.9</v>
       </c>
       <c r="F98" t="n">
-        <v>57.8</v>
+        <v>58.2</v>
       </c>
       <c r="G98" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -12377,19 +12377,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D99" t="n">
-        <v>50.8</v>
+        <v>50.3</v>
       </c>
       <c r="E99" t="n">
-        <v>49.2</v>
+        <v>49.7</v>
       </c>
       <c r="F99" t="n">
-        <v>58.7</v>
+        <v>58.9</v>
       </c>
       <c r="G99" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -12416,19 +12416,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1527</v>
+        <v>1621</v>
       </c>
       <c r="D100" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E100" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F100" t="n">
-        <v>59</v>
+        <v>59.1</v>
       </c>
       <c r="G100" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101">
@@ -12455,19 +12455,19 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1531</v>
+        <v>1625</v>
       </c>
       <c r="D101" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="E101" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.2</v>
+        <v>59.7</v>
       </c>
       <c r="G101" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -12481,7 +12481,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="102">
@@ -12494,19 +12494,19 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1481</v>
+        <v>1572</v>
       </c>
       <c r="D102" t="n">
-        <v>51.9</v>
+        <v>51.7</v>
       </c>
       <c r="E102" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="F102" t="n">
-        <v>60</v>
+        <v>59.9</v>
       </c>
       <c r="G102" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -12520,7 +12520,7 @@
         <v>0</v>
       </c>
       <c r="K102" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="103">
@@ -12533,19 +12533,19 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1510</v>
+        <v>1602</v>
       </c>
       <c r="D103" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="E103" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60.1</v>
+        <v>60.4</v>
       </c>
       <c r="G103" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -12643,7 +12643,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38658</v>
+        <v>38745</v>
       </c>
       <c r="D2" t="n">
         <v>50.1</v>
@@ -12669,7 +12669,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -12682,7 +12682,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38705</v>
+        <v>38791</v>
       </c>
       <c r="D3" t="n">
         <v>50.3</v>
@@ -12721,7 +12721,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38912</v>
+        <v>38998</v>
       </c>
       <c r="D4" t="n">
         <v>51.3</v>
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38312</v>
+        <v>38406</v>
       </c>
       <c r="D5" t="n">
         <v>49.7</v>
@@ -12799,7 +12799,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>38794</v>
+        <v>38886</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>38313</v>
+        <v>38405</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -12877,13 +12877,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38131</v>
+        <v>38218</v>
       </c>
       <c r="D8" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="F8" t="n">
         <v>49.1</v>
@@ -12916,19 +12916,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38594</v>
+        <v>38686</v>
       </c>
       <c r="D9" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E9" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -12942,7 +12942,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -12955,7 +12955,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38882</v>
+        <v>38975</v>
       </c>
       <c r="D10" t="n">
         <v>51.1</v>
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38937</v>
+        <v>39031</v>
       </c>
       <c r="D11" t="n">
         <v>50.7</v>
@@ -13033,7 +13033,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38943</v>
+        <v>39037</v>
       </c>
       <c r="D12" t="n">
         <v>51.4</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38762</v>
+        <v>38855</v>
       </c>
       <c r="D13" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="E13" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="F13" t="n">
         <v>54.5</v>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38827</v>
+        <v>38920</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -13146,17 +13146,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38788</v>
+        <v>38892</v>
       </c>
       <c r="D15" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E15" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F15" t="n">
         <v>60.8</v>
@@ -13185,23 +13185,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38807</v>
+        <v>38876</v>
       </c>
       <c r="D16" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E16" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F16" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G16" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -13228,7 +13228,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36992</v>
+        <v>37079</v>
       </c>
       <c r="D17" t="n">
         <v>49.1</v>
@@ -13267,7 +13267,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>39005</v>
+        <v>39099</v>
       </c>
       <c r="D18" t="n">
         <v>49.1</v>
@@ -13306,7 +13306,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38536</v>
+        <v>38630</v>
       </c>
       <c r="D19" t="n">
         <v>50.3</v>
@@ -13345,19 +13345,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>35238</v>
+        <v>35324</v>
       </c>
       <c r="D20" t="n">
-        <v>50.1</v>
+        <v>50.2</v>
       </c>
       <c r="E20" t="n">
-        <v>49.9</v>
+        <v>49.8</v>
       </c>
       <c r="F20" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="G20" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -13384,7 +13384,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>39074</v>
+        <v>39168</v>
       </c>
       <c r="D21" t="n">
         <v>49.9</v>
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38887</v>
+        <v>38980</v>
       </c>
       <c r="D22" t="n">
         <v>49.6</v>
@@ -13432,10 +13432,10 @@
         <v>50.4</v>
       </c>
       <c r="F22" t="n">
-        <v>40.2</v>
+        <v>40.1</v>
       </c>
       <c r="G22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -13449,7 +13449,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -13462,7 +13462,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38933</v>
+        <v>39027</v>
       </c>
       <c r="D23" t="n">
         <v>49.6</v>
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>39181</v>
+        <v>39269</v>
       </c>
       <c r="D24" t="n">
         <v>49.5</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>39134</v>
+        <v>39228</v>
       </c>
       <c r="D25" t="n">
         <v>49.2</v>
@@ -13579,13 +13579,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>39076</v>
+        <v>39170</v>
       </c>
       <c r="D26" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E26" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F26" t="n">
         <v>40.9</v>
@@ -13618,13 +13618,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35408</v>
+        <v>35494</v>
       </c>
       <c r="D27" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F27" t="n">
         <v>41.9</v>
@@ -13657,7 +13657,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>39159</v>
+        <v>39253</v>
       </c>
       <c r="D28" t="n">
         <v>49.1</v>
@@ -13666,10 +13666,10 @@
         <v>50.9</v>
       </c>
       <c r="F28" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -13696,7 +13696,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39167</v>
+        <v>39261</v>
       </c>
       <c r="D29" t="n">
         <v>49.1</v>
@@ -13705,10 +13705,10 @@
         <v>50.9</v>
       </c>
       <c r="F29" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="G29" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -13735,7 +13735,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38873</v>
+        <v>38967</v>
       </c>
       <c r="D30" t="n">
         <v>48.9</v>
@@ -13774,7 +13774,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38909</v>
+        <v>39003</v>
       </c>
       <c r="D31" t="n">
         <v>49.4</v>
@@ -13813,7 +13813,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38915</v>
+        <v>39009</v>
       </c>
       <c r="D32" t="n">
         <v>49.2</v>
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>38938</v>
+        <v>39032</v>
       </c>
       <c r="D33" t="n">
         <v>49.5</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>38873</v>
+        <v>38967</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -13930,7 +13930,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38876</v>
+        <v>38969</v>
       </c>
       <c r="D35" t="n">
         <v>49.7</v>
@@ -13969,7 +13969,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>35293</v>
+        <v>35379</v>
       </c>
       <c r="D36" t="n">
         <v>49.8</v>
@@ -14008,7 +14008,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>38711</v>
+        <v>38803</v>
       </c>
       <c r="D37" t="n">
         <v>51.7</v>
@@ -14047,7 +14047,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38040</v>
+        <v>38132</v>
       </c>
       <c r="D38" t="n">
         <v>50.8</v>
@@ -14086,7 +14086,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>38872</v>
+        <v>38966</v>
       </c>
       <c r="D39" t="n">
         <v>47.2</v>
@@ -14112,7 +14112,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40">
@@ -14125,7 +14125,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>8216</v>
+        <v>8247</v>
       </c>
       <c r="D40" t="n">
         <v>51.2</v>
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38548</v>
+        <v>38641</v>
       </c>
       <c r="D41" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E41" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F41" t="n">
         <v>50.6</v>
@@ -14203,19 +14203,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38607</v>
+        <v>38701</v>
       </c>
       <c r="D42" t="n">
-        <v>49.8</v>
+        <v>49.7</v>
       </c>
       <c r="E42" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="F42" t="n">
-        <v>53.7</v>
+        <v>53.8</v>
       </c>
       <c r="G42" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -14229,7 +14229,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
@@ -14242,7 +14242,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>38647</v>
+        <v>38741</v>
       </c>
       <c r="D43" t="n">
         <v>49</v>
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>38568</v>
+        <v>38661</v>
       </c>
       <c r="D44" t="n">
         <v>50.4</v>
@@ -14320,7 +14320,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38213</v>
+        <v>38304</v>
       </c>
       <c r="D45" t="n">
         <v>49.4</v>
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>38374</v>
+        <v>38466</v>
       </c>
       <c r="D46" t="n">
         <v>50.1</v>
@@ -14398,7 +14398,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38752</v>
+        <v>38846</v>
       </c>
       <c r="D47" t="n">
         <v>50.6</v>
@@ -14437,7 +14437,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>38788</v>
+        <v>38880</v>
       </c>
       <c r="D48" t="n">
         <v>51.1</v>
@@ -14463,7 +14463,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="49">
@@ -14476,13 +14476,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>36148</v>
+        <v>36237</v>
       </c>
       <c r="D49" t="n">
-        <v>50.4</v>
+        <v>50.3</v>
       </c>
       <c r="E49" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="F49" t="n">
         <v>57.3</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38492</v>
+        <v>38586</v>
       </c>
       <c r="D50" t="n">
         <v>50.3</v>
@@ -14524,10 +14524,10 @@
         <v>49.7</v>
       </c>
       <c r="F50" t="n">
-        <v>58.3</v>
+        <v>58.4</v>
       </c>
       <c r="G50" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -14554,7 +14554,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38631</v>
+        <v>38724</v>
       </c>
       <c r="D51" t="n">
         <v>49.4</v>
@@ -14593,7 +14593,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38676</v>
+        <v>38769</v>
       </c>
       <c r="D52" t="n">
         <v>50</v>
@@ -14632,7 +14632,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>38544</v>
+        <v>38637</v>
       </c>
       <c r="D53" t="n">
         <v>49.5</v>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>38578</v>
+        <v>38670</v>
       </c>
       <c r="D54" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="F54" t="n">
         <v>62.1</v>
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38767</v>
+        <v>38861</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -14749,7 +14749,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38470</v>
+        <v>38562</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -14788,7 +14788,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38833</v>
+        <v>38927</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -14797,10 +14797,10 @@
         <v>49</v>
       </c>
       <c r="F57" t="n">
-        <v>74</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -14827,13 +14827,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>38917</v>
+        <v>39010</v>
       </c>
       <c r="D58" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E58" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F58" t="n">
         <v>76.5</v>
@@ -14866,7 +14866,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39119</v>
+        <v>39213</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -14905,7 +14905,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>35514</v>
+        <v>35604</v>
       </c>
       <c r="D60" t="n">
         <v>50.8</v>
@@ -14944,7 +14944,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37471</v>
+        <v>37558</v>
       </c>
       <c r="D61" t="n">
         <v>50.4</v>
@@ -14979,17 +14979,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>SUI20</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>37924</v>
+        <v>23715</v>
       </c>
       <c r="D62" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="E62" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="F62" t="n">
         <v>55.1</v>
@@ -15018,23 +15018,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SUI20</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>23655</v>
+        <v>38016</v>
       </c>
       <c r="D63" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="E63" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="F63" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="G63" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H63" t="b">
         <v>1</v>
@@ -15048,7 +15048,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64">
@@ -15061,7 +15061,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24075</v>
+        <v>24134</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -15096,23 +15096,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>FRA40</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>38821</v>
+        <v>24161</v>
       </c>
       <c r="D65" t="n">
-        <v>51.2</v>
+        <v>50.9</v>
       </c>
       <c r="E65" t="n">
-        <v>48.8</v>
+        <v>49.1</v>
       </c>
       <c r="F65" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="G65" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -15126,7 +15126,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66">
@@ -15135,17 +15135,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRA40</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>24099</v>
+        <v>38915</v>
       </c>
       <c r="D66" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E66" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F66" t="n">
         <v>56.1</v>
@@ -15174,23 +15174,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>38324</v>
+        <v>21553</v>
       </c>
       <c r="D67" t="n">
-        <v>50.6</v>
+        <v>51.8</v>
       </c>
       <c r="E67" t="n">
-        <v>49.4</v>
+        <v>48.2</v>
       </c>
       <c r="F67" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="G67" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -15213,17 +15213,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>21491</v>
+        <v>38416</v>
       </c>
       <c r="D68" t="n">
-        <v>51.9</v>
+        <v>50.6</v>
       </c>
       <c r="E68" t="n">
-        <v>48.1</v>
+        <v>49.4</v>
       </c>
       <c r="F68" t="n">
         <v>56.2</v>
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36575</v>
+        <v>36667</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -15295,7 +15295,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>30925</v>
+        <v>31006</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -15304,10 +15304,10 @@
         <v>49.2</v>
       </c>
       <c r="F70" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="G70" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -15334,7 +15334,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>37992</v>
+        <v>38081</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33400</v>
+        <v>33482</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -15382,10 +15382,10 @@
         <v>49.8</v>
       </c>
       <c r="F72" t="n">
-        <v>58.5</v>
+        <v>58.6</v>
       </c>
       <c r="G72" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H72" t="b">
         <v>1</v>
@@ -15412,7 +15412,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26348</v>
+        <v>26418</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -15451,7 +15451,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14374</v>
+        <v>14408</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -15490,7 +15490,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14176</v>
+        <v>14213</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -15529,13 +15529,13 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>15315</v>
+        <v>15351</v>
       </c>
       <c r="D76" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E76" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F76" t="n">
         <v>52.9</v>
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26969</v>
+        <v>27042</v>
       </c>
       <c r="D77" t="n">
         <v>49.9</v>
@@ -15607,7 +15607,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>36277</v>
+        <v>36366</v>
       </c>
       <c r="D78" t="n">
         <v>50.6</v>
@@ -15633,7 +15633,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79">
@@ -15646,7 +15646,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>28968</v>
+        <v>29046</v>
       </c>
       <c r="D79" t="n">
         <v>49.3</v>
@@ -15685,7 +15685,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>15951</v>
+        <v>15992</v>
       </c>
       <c r="D80" t="n">
         <v>49.7</v>
@@ -15724,7 +15724,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>28218</v>
+        <v>28296</v>
       </c>
       <c r="D81" t="n">
         <v>49.4</v>
@@ -15763,7 +15763,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10544</v>
+        <v>10570</v>
       </c>
       <c r="D82" t="n">
         <v>51.5</v>
@@ -15802,7 +15802,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>10548</v>
+        <v>10573</v>
       </c>
       <c r="D83" t="n">
         <v>50.6</v>
@@ -15811,10 +15811,10 @@
         <v>49.4</v>
       </c>
       <c r="F83" t="n">
-        <v>52.3</v>
+        <v>52.4</v>
       </c>
       <c r="G83" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -15841,7 +15841,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>10325</v>
+        <v>10350</v>
       </c>
       <c r="D84" t="n">
         <v>50.6</v>
@@ -15850,10 +15850,10 @@
         <v>49.4</v>
       </c>
       <c r="F84" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="G84" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10847</v>
+        <v>10871</v>
       </c>
       <c r="D85" t="n">
         <v>50.3</v>
@@ -15919,7 +15919,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>10331</v>
+        <v>10356</v>
       </c>
       <c r="D86" t="n">
         <v>51.1</v>
@@ -15945,7 +15945,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87">
@@ -15958,7 +15958,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>10803</v>
+        <v>10829</v>
       </c>
       <c r="D87" t="n">
         <v>50.7</v>
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10905</v>
+        <v>10931</v>
       </c>
       <c r="D88" t="n">
         <v>51.6</v>
@@ -16036,7 +16036,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>11048</v>
+        <v>11074</v>
       </c>
       <c r="D89" t="n">
         <v>51.6</v>
@@ -16045,10 +16045,10 @@
         <v>48.4</v>
       </c>
       <c r="F89" t="n">
-        <v>58.4</v>
+        <v>58.5</v>
       </c>
       <c r="G89" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -16075,13 +16075,13 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>11048</v>
+        <v>11073</v>
       </c>
       <c r="D90" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="E90" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="F90" t="n">
         <v>59.3</v>
@@ -16114,13 +16114,13 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10974</v>
+        <v>11000</v>
       </c>
       <c r="D91" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="E91" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="F91" t="n">
         <v>59.5</v>
@@ -16153,7 +16153,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10390</v>
+        <v>10414</v>
       </c>
       <c r="D92" t="n">
         <v>50.7</v>
@@ -16162,10 +16162,10 @@
         <v>49.3</v>
       </c>
       <c r="F92" t="n">
-        <v>59.8</v>
+        <v>59.9</v>
       </c>
       <c r="G92" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -16192,19 +16192,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10311</v>
+        <v>10335</v>
       </c>
       <c r="D93" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E93" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F93" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -16218,7 +16218,7 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="94">
@@ -16231,7 +16231,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>38345</v>
+        <v>38438</v>
       </c>
       <c r="D94" t="n">
         <v>50</v>
@@ -16257,7 +16257,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="95">
@@ -16270,7 +16270,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>38962</v>
+        <v>39056</v>
       </c>
       <c r="D95" t="n">
         <v>49.4</v>
@@ -16309,13 +16309,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36533</v>
+        <v>36613</v>
       </c>
       <c r="D96" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="E96" t="n">
-        <v>51.1</v>
+        <v>51</v>
       </c>
       <c r="F96" t="n">
         <v>53.8</v>
@@ -16348,7 +16348,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>39078</v>
+        <v>39172</v>
       </c>
       <c r="D97" t="n">
         <v>50.3</v>
@@ -16387,7 +16387,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38271</v>
+        <v>38362</v>
       </c>
       <c r="D98" t="n">
         <v>49.3</v>
@@ -16426,19 +16426,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>38865</v>
+        <v>38959</v>
       </c>
       <c r="D99" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="E99" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="F99" t="n">
-        <v>54.2</v>
+        <v>54.3</v>
       </c>
       <c r="G99" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -16465,7 +16465,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>38472</v>
+        <v>38566</v>
       </c>
       <c r="D100" t="n">
         <v>49.3</v>
@@ -16504,7 +16504,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>38725</v>
+        <v>38817</v>
       </c>
       <c r="D101" t="n">
         <v>49.7</v>
@@ -16543,7 +16543,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>39155</v>
+        <v>39249</v>
       </c>
       <c r="D102" t="n">
         <v>50.1</v>
@@ -16582,7 +16582,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>39176</v>
+        <v>39270</v>
       </c>
       <c r="D103" t="n">
         <v>49.8</v>

--- a/output/Multi_Asset_Correlation.xlsx
+++ b/output/Multi_Asset_Correlation.xlsx
@@ -496,19 +496,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1621</v>
+        <v>1614</v>
       </c>
       <c r="D2" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="E2" t="n">
-        <v>50.6</v>
+        <v>50.9</v>
       </c>
       <c r="F2" t="n">
-        <v>50.6</v>
+        <v>50.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="b">
         <v>1</v>
@@ -522,7 +522,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="D3" t="n">
         <v>50.5</v>
@@ -544,10 +544,10 @@
         <v>49.5</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="b">
         <v>1</v>
@@ -561,7 +561,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +574,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1556</v>
+        <v>1549</v>
       </c>
       <c r="D4" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="E4" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="F4" t="n">
-        <v>47.3</v>
+        <v>47.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="b">
         <v>1</v>
@@ -600,7 +600,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -613,19 +613,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="D5" t="n">
-        <v>49.5</v>
+        <v>49.3</v>
       </c>
       <c r="E5" t="n">
-        <v>50.5</v>
+        <v>50.7</v>
       </c>
       <c r="F5" t="n">
-        <v>47.3</v>
+        <v>46.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1597</v>
+        <v>1587</v>
       </c>
       <c r="D6" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>48.8</v>
       </c>
       <c r="F6" t="n">
         <v>46.4</v>
@@ -687,23 +687,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CADJPY</t>
+          <t>EURCAD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1608</v>
+        <v>1590</v>
       </c>
       <c r="D7" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="E7" t="n">
-        <v>49.9</v>
+        <v>50.6</v>
       </c>
       <c r="F7" t="n">
-        <v>44.5</v>
+        <v>55.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -726,23 +726,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EURCAD</t>
+          <t>CADJPY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1595</v>
+        <v>1602</v>
       </c>
       <c r="D8" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="E8" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="F8" t="n">
-        <v>55.5</v>
+        <v>43.9</v>
       </c>
       <c r="G8" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -769,19 +769,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1612</v>
+        <v>1606</v>
       </c>
       <c r="D9" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="E9" t="n">
-        <v>50.9</v>
+        <v>50.4</v>
       </c>
       <c r="F9" t="n">
-        <v>56.6</v>
+        <v>56.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1588</v>
+        <v>1582</v>
       </c>
       <c r="D10" t="n">
-        <v>50.5</v>
+        <v>50.9</v>
       </c>
       <c r="E10" t="n">
-        <v>49.5</v>
+        <v>49.1</v>
       </c>
       <c r="F10" t="n">
-        <v>42.3</v>
+        <v>42.7</v>
       </c>
       <c r="G10" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -847,19 +847,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="D11" t="n">
-        <v>51.9</v>
+        <v>51.5</v>
       </c>
       <c r="E11" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="F11" t="n">
-        <v>42</v>
+        <v>41.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -873,7 +873,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
@@ -886,19 +886,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="D12" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="E12" t="n">
-        <v>47.9</v>
+        <v>47.3</v>
       </c>
       <c r="F12" t="n">
-        <v>41.6</v>
+        <v>40.7</v>
       </c>
       <c r="G12" t="n">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
@@ -925,19 +925,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1665</v>
+        <v>1662</v>
       </c>
       <c r="D13" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="E13" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="G13" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
@@ -951,7 +951,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14">
@@ -960,23 +960,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>USDCHF</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="D14" t="n">
-        <v>47.5</v>
+        <v>51.6</v>
       </c>
       <c r="E14" t="n">
-        <v>52.5</v>
+        <v>48.4</v>
       </c>
       <c r="F14" t="n">
-        <v>62.7</v>
+        <v>37.2</v>
       </c>
       <c r="G14" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
@@ -987,10 +987,10 @@
         </is>
       </c>
       <c r="J14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -999,23 +999,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>USDCHF</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1648</v>
+        <v>1644</v>
       </c>
       <c r="D15" t="n">
-        <v>51.2</v>
+        <v>47.3</v>
       </c>
       <c r="E15" t="n">
-        <v>48.8</v>
+        <v>52.7</v>
       </c>
       <c r="F15" t="n">
-        <v>37.3</v>
+        <v>63.1</v>
       </c>
       <c r="G15" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -1026,7 +1026,7 @@
         </is>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>69</v>
@@ -1042,19 +1042,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1652</v>
+        <v>1644</v>
       </c>
       <c r="D16" t="n">
-        <v>49.1</v>
+        <v>48.4</v>
       </c>
       <c r="E16" t="n">
-        <v>50.9</v>
+        <v>51.6</v>
       </c>
       <c r="F16" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
       <c r="G16" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
@@ -1068,7 +1068,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -1081,19 +1081,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D17" t="n">
-        <v>51.1</v>
+        <v>51.4</v>
       </c>
       <c r="E17" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="F17" t="n">
-        <v>50.1</v>
+        <v>49.6</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
@@ -1107,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1452</v>
+        <v>1450</v>
       </c>
       <c r="D18" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="E18" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="F18" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>USDTRY</t>
+          <t>AUDCHF</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1617</v>
+        <v>1582</v>
       </c>
       <c r="D19" t="n">
-        <v>45.3</v>
+        <v>50.8</v>
       </c>
       <c r="E19" t="n">
-        <v>54.7</v>
+        <v>49.2</v>
       </c>
       <c r="F19" t="n">
-        <v>51.1</v>
+        <v>51.3</v>
       </c>
       <c r="G19" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1194,23 +1194,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AUDCHF</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="D20" t="n">
-        <v>50.8</v>
+        <v>51.2</v>
       </c>
       <c r="E20" t="n">
-        <v>49.2</v>
+        <v>48.8</v>
       </c>
       <c r="F20" t="n">
-        <v>51.2</v>
+        <v>51.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -1233,23 +1233,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>USDTRY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1602</v>
+        <v>1611</v>
       </c>
       <c r="D21" t="n">
-        <v>51.2</v>
+        <v>44.9</v>
       </c>
       <c r="E21" t="n">
-        <v>48.8</v>
+        <v>55.1</v>
       </c>
       <c r="F21" t="n">
-        <v>51.6</v>
+        <v>51.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
@@ -1260,10 +1260,10 @@
         </is>
       </c>
       <c r="J21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -1276,19 +1276,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1556</v>
+        <v>1544</v>
       </c>
       <c r="D22" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E22" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F22" t="n">
-        <v>52.3</v>
+        <v>51.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -1302,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1315,19 +1315,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1590</v>
+        <v>1583</v>
       </c>
       <c r="D23" t="n">
-        <v>47.2</v>
+        <v>47.3</v>
       </c>
       <c r="E23" t="n">
-        <v>52.8</v>
+        <v>52.7</v>
       </c>
       <c r="F23" t="n">
-        <v>52.6</v>
+        <v>52.4</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1612</v>
+        <v>1605</v>
       </c>
       <c r="D24" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="E24" t="n">
-        <v>51.6</v>
+        <v>52</v>
       </c>
       <c r="F24" t="n">
-        <v>53.6</v>
+        <v>53.7</v>
       </c>
       <c r="G24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
@@ -1393,19 +1393,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1600</v>
+        <v>1594</v>
       </c>
       <c r="D25" t="n">
-        <v>52.2</v>
+        <v>51.9</v>
       </c>
       <c r="E25" t="n">
-        <v>47.8</v>
+        <v>48.1</v>
       </c>
       <c r="F25" t="n">
-        <v>45.9</v>
+        <v>45.8</v>
       </c>
       <c r="G25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
@@ -1419,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1601</v>
+        <v>1595</v>
       </c>
       <c r="D26" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="E26" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="F26" t="n">
         <v>45.6</v>
@@ -1458,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27">
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1604</v>
+        <v>1595</v>
       </c>
       <c r="D27" t="n">
         <v>48.5</v>
@@ -1497,7 +1497,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1506,23 +1506,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NZDCHF</t>
+          <t>CHFSGD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1575</v>
+        <v>1603</v>
       </c>
       <c r="D28" t="n">
-        <v>49.8</v>
+        <v>47.8</v>
       </c>
       <c r="E28" t="n">
-        <v>50.2</v>
+        <v>52.2</v>
       </c>
       <c r="F28" t="n">
-        <v>55.3</v>
+        <v>55.7</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
@@ -1545,23 +1545,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHFSGD</t>
+          <t>NZDCHF</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1611</v>
+        <v>1563</v>
       </c>
       <c r="D29" t="n">
-        <v>47.8</v>
+        <v>49.5</v>
       </c>
       <c r="E29" t="n">
-        <v>52.2</v>
+        <v>50.5</v>
       </c>
       <c r="F29" t="n">
-        <v>55.9</v>
+        <v>55.7</v>
       </c>
       <c r="G29" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
@@ -1575,7 +1575,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -1588,19 +1588,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1615</v>
+        <v>1608</v>
       </c>
       <c r="D30" t="n">
-        <v>47.9</v>
+        <v>48.1</v>
       </c>
       <c r="E30" t="n">
-        <v>52.1</v>
+        <v>51.9</v>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="G30" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
@@ -1614,7 +1614,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31">
@@ -1627,19 +1627,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1607</v>
+        <v>1601</v>
       </c>
       <c r="D31" t="n">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="E31" t="n">
-        <v>51.8</v>
+        <v>51.6</v>
       </c>
       <c r="F31" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="G31" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
@@ -1653,7 +1653,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -1666,19 +1666,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1605</v>
+        <v>1598</v>
       </c>
       <c r="D32" t="n">
-        <v>50.9</v>
+        <v>50.6</v>
       </c>
       <c r="E32" t="n">
-        <v>49.1</v>
+        <v>49.4</v>
       </c>
       <c r="F32" t="n">
-        <v>43.7</v>
+        <v>43.2</v>
       </c>
       <c r="G32" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -1692,7 +1692,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -1705,19 +1705,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1455</v>
+        <v>1452</v>
       </c>
       <c r="D33" t="n">
-        <v>49.7</v>
+        <v>49.9</v>
       </c>
       <c r="E33" t="n">
-        <v>50.3</v>
+        <v>50.1</v>
       </c>
       <c r="F33" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="G33" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
@@ -1731,7 +1731,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
@@ -1744,19 +1744,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1614</v>
+        <v>1608</v>
       </c>
       <c r="D34" t="n">
-        <v>49.1</v>
+        <v>49.5</v>
       </c>
       <c r="E34" t="n">
-        <v>50.9</v>
+        <v>50.5</v>
       </c>
       <c r="F34" t="n">
-        <v>43.4</v>
+        <v>43</v>
       </c>
       <c r="G34" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
@@ -1783,19 +1783,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="D35" t="n">
-        <v>47.8</v>
+        <v>47.9</v>
       </c>
       <c r="E35" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="F35" t="n">
-        <v>58.1</v>
+        <v>58</v>
       </c>
       <c r="G35" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
@@ -1822,19 +1822,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1601</v>
+        <v>1597</v>
       </c>
       <c r="D36" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="E36" t="n">
-        <v>50.5</v>
+        <v>50.8</v>
       </c>
       <c r="F36" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="G36" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -1861,19 +1861,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1610</v>
+        <v>1603</v>
       </c>
       <c r="D37" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="F37" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="G37" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
@@ -1896,23 +1896,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NZDCAD</t>
+          <t>AUDSGD</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1598</v>
+        <v>1585</v>
       </c>
       <c r="D38" t="n">
-        <v>49.8</v>
+        <v>49.3</v>
       </c>
       <c r="E38" t="n">
-        <v>50.2</v>
+        <v>50.7</v>
       </c>
       <c r="F38" t="n">
-        <v>59.2</v>
+        <v>59.4</v>
       </c>
       <c r="G38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
@@ -1935,23 +1935,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AUDSGD</t>
+          <t>NZDCAD</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="D39" t="n">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="E39" t="n">
-        <v>51.4</v>
+        <v>50</v>
       </c>
       <c r="F39" t="n">
-        <v>59.3</v>
+        <v>59.6</v>
       </c>
       <c r="G39" t="n">
-        <v>9.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="D40" t="n">
-        <v>48.6</v>
+        <v>49.4</v>
       </c>
       <c r="E40" t="n">
-        <v>51.4</v>
+        <v>50.6</v>
       </c>
       <c r="F40" t="n">
         <v>60.3</v>
@@ -2017,19 +2017,19 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="D41" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="E41" t="n">
-        <v>49.3</v>
+        <v>49.2</v>
       </c>
       <c r="F41" t="n">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="G41" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
@@ -2043,7 +2043,7 @@
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42">
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1611</v>
+        <v>1607</v>
       </c>
       <c r="D42" t="n">
         <v>52.1</v>
@@ -2065,10 +2065,10 @@
         <v>47.9</v>
       </c>
       <c r="F42" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="G42" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
@@ -2095,19 +2095,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="D43" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="E43" t="n">
-        <v>49.5</v>
+        <v>49.4</v>
       </c>
       <c r="F43" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="G43" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
@@ -2134,19 +2134,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1618</v>
+        <v>1611</v>
       </c>
       <c r="D44" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="E44" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="F44" t="n">
-        <v>37.5</v>
+        <v>37.1</v>
       </c>
       <c r="G44" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
@@ -2160,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45">
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1450</v>
+        <v>1447</v>
       </c>
       <c r="D45" t="n">
-        <v>51.3</v>
+        <v>51.5</v>
       </c>
       <c r="E45" t="n">
-        <v>48.7</v>
+        <v>48.5</v>
       </c>
       <c r="F45" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="G45" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46">
@@ -2208,23 +2208,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NZDUSD</t>
+          <t>EURZAR</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1595</v>
+        <v>1618</v>
       </c>
       <c r="D46" t="n">
-        <v>47.6</v>
+        <v>51.2</v>
       </c>
       <c r="E46" t="n">
-        <v>52.4</v>
+        <v>48.8</v>
       </c>
       <c r="F46" t="n">
-        <v>63.4</v>
+        <v>36.5</v>
       </c>
       <c r="G46" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47">
@@ -2251,19 +2251,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="D47" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="E47" t="n">
-        <v>49</v>
+        <v>48.7</v>
       </c>
       <c r="F47" t="n">
-        <v>36.5</v>
+        <v>36.2</v>
       </c>
       <c r="G47" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
@@ -2286,23 +2286,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>NZDUSD</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1604</v>
+        <v>1589</v>
       </c>
       <c r="D48" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="E48" t="n">
-        <v>51.7</v>
+        <v>52.2</v>
       </c>
       <c r="F48" t="n">
-        <v>36.2</v>
+        <v>64</v>
       </c>
       <c r="G48" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="J48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
@@ -2325,23 +2325,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDMXN</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1622</v>
+        <v>1597</v>
       </c>
       <c r="D49" t="n">
-        <v>50.9</v>
+        <v>48.9</v>
       </c>
       <c r="E49" t="n">
-        <v>49.1</v>
+        <v>51.1</v>
       </c>
       <c r="F49" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="G49" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
@@ -2355,7 +2355,7 @@
         <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
@@ -2364,11 +2364,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EURZAR</t>
+          <t>USDMXN</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1625</v>
+        <v>1615</v>
       </c>
       <c r="D50" t="n">
         <v>51.3</v>
@@ -2377,10 +2377,10 @@
         <v>48.7</v>
       </c>
       <c r="F50" t="n">
-        <v>35.8</v>
+        <v>35.5</v>
       </c>
       <c r="G50" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="J50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
         <v>81</v>
@@ -2407,19 +2407,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1591</v>
+        <v>1585</v>
       </c>
       <c r="D51" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="E51" t="n">
-        <v>52</v>
+        <v>51.7</v>
       </c>
       <c r="F51" t="n">
-        <v>64.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="G51" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52">
@@ -2446,19 +2446,19 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1589</v>
+        <v>1583</v>
       </c>
       <c r="D52" t="n">
-        <v>50.3</v>
+        <v>50.8</v>
       </c>
       <c r="E52" t="n">
-        <v>49.7</v>
+        <v>49.2</v>
       </c>
       <c r="F52" t="n">
-        <v>35.2</v>
+        <v>34.3</v>
       </c>
       <c r="G52" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="H52" t="b">
         <v>1</v>
@@ -2472,7 +2472,7 @@
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
@@ -2485,19 +2485,19 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="D53" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E53" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F53" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="G53" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="H53" t="b">
         <v>1</v>
@@ -2524,19 +2524,19 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1519</v>
+        <v>1514</v>
       </c>
       <c r="D54" t="n">
-        <v>51.5</v>
+        <v>51.4</v>
       </c>
       <c r="E54" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="F54" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="G54" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="H54" t="b">
         <v>1</v>
@@ -2563,19 +2563,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="D55" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="E55" t="n">
-        <v>51.3</v>
+        <v>51.4</v>
       </c>
       <c r="F55" t="n">
-        <v>70.5</v>
+        <v>71</v>
       </c>
       <c r="G55" t="n">
-        <v>20.5</v>
+        <v>21</v>
       </c>
       <c r="H55" t="b">
         <v>1</v>
@@ -2602,13 +2602,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="D56" t="n">
-        <v>49.3</v>
+        <v>49.6</v>
       </c>
       <c r="E56" t="n">
-        <v>50.7</v>
+        <v>50.4</v>
       </c>
       <c r="F56" t="n">
         <v>75.59999999999999</v>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1617</v>
+        <v>1611</v>
       </c>
       <c r="D57" t="n">
         <v>50</v>
@@ -2650,10 +2650,10 @@
         <v>50</v>
       </c>
       <c r="F57" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="H57" t="b">
         <v>1</v>
@@ -2680,19 +2680,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1623</v>
+        <v>1616</v>
       </c>
       <c r="D58" t="n">
-        <v>49.9</v>
+        <v>49.6</v>
       </c>
       <c r="E58" t="n">
-        <v>50.1</v>
+        <v>50.4</v>
       </c>
       <c r="F58" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="G58" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="H58" t="b">
         <v>1</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1623</v>
+        <v>1616</v>
       </c>
       <c r="D59" t="n">
         <v>49.2</v>
@@ -2728,10 +2728,10 @@
         <v>50.8</v>
       </c>
       <c r="F59" t="n">
-        <v>93.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G59" t="n">
-        <v>43.7</v>
+        <v>43.4</v>
       </c>
       <c r="H59" t="b">
         <v>1</v>
@@ -2754,23 +2754,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UKOIL.S</t>
+          <t>USOIL.S</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1506</v>
+        <v>1631</v>
       </c>
       <c r="D60" t="n">
-        <v>52.7</v>
+        <v>50.6</v>
       </c>
       <c r="E60" t="n">
-        <v>47.3</v>
+        <v>49.4</v>
       </c>
       <c r="F60" t="n">
-        <v>39.4</v>
+        <v>38.8</v>
       </c>
       <c r="G60" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
@@ -2793,23 +2793,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>USOIL.S</t>
+          <t>UKOIL.S</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1636</v>
+        <v>1503</v>
       </c>
       <c r="D61" t="n">
-        <v>51.3</v>
+        <v>52.5</v>
       </c>
       <c r="E61" t="n">
-        <v>48.7</v>
+        <v>47.5</v>
       </c>
       <c r="F61" t="n">
-        <v>39.4</v>
+        <v>38.7</v>
       </c>
       <c r="G61" t="n">
-        <v>10.6</v>
+        <v>11.3</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
@@ -2836,19 +2836,19 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="D62" t="n">
-        <v>49.2</v>
+        <v>50.2</v>
       </c>
       <c r="E62" t="n">
-        <v>50.8</v>
+        <v>49.8</v>
       </c>
       <c r="F62" t="n">
-        <v>59.6</v>
+        <v>59.8</v>
       </c>
       <c r="G62" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H62" t="b">
         <v>1</v>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>976</v>
+        <v>973</v>
       </c>
       <c r="D63" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="E63" t="n">
-        <v>52.5</v>
+        <v>52.2</v>
       </c>
       <c r="F63" t="n">
         <v>61.3</v>
@@ -2910,23 +2910,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NETH25</t>
+          <t>UK100</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>974</v>
+        <v>1547</v>
       </c>
       <c r="D64" t="n">
-        <v>51.2</v>
+        <v>48.7</v>
       </c>
       <c r="E64" t="n">
-        <v>48.8</v>
+        <v>51.3</v>
       </c>
       <c r="F64" t="n">
-        <v>62.1</v>
+        <v>62.4</v>
       </c>
       <c r="G64" t="n">
-        <v>12.1</v>
+        <v>12.4</v>
       </c>
       <c r="H64" t="b">
         <v>1</v>
@@ -2949,23 +2949,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UK100</t>
+          <t>NETH25</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1463</v>
+        <v>972</v>
       </c>
       <c r="D65" t="n">
-        <v>48.7</v>
+        <v>51.1</v>
       </c>
       <c r="E65" t="n">
-        <v>51.3</v>
+        <v>48.9</v>
       </c>
       <c r="F65" t="n">
-        <v>62.1</v>
+        <v>62.7</v>
       </c>
       <c r="G65" t="n">
-        <v>12.1</v>
+        <v>12.7</v>
       </c>
       <c r="H65" t="b">
         <v>1</v>
@@ -2992,13 +2992,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="D66" t="n">
-        <v>51.1</v>
+        <v>50.9</v>
       </c>
       <c r="E66" t="n">
-        <v>48.9</v>
+        <v>49.1</v>
       </c>
       <c r="F66" t="n">
         <v>63.1</v>
@@ -3018,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
@@ -3031,19 +3031,19 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="D67" t="n">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="E67" t="n">
-        <v>50.8</v>
+        <v>51</v>
       </c>
       <c r="F67" t="n">
-        <v>63.6</v>
+        <v>63.3</v>
       </c>
       <c r="G67" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="H67" t="b">
         <v>1</v>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68">
@@ -3066,23 +3066,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>USA100</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>1598</v>
+        <v>1608</v>
       </c>
       <c r="D68" t="n">
-        <v>49.6</v>
+        <v>52.4</v>
       </c>
       <c r="E68" t="n">
-        <v>50.4</v>
+        <v>47.6</v>
       </c>
       <c r="F68" t="n">
-        <v>64.5</v>
+        <v>64.8</v>
       </c>
       <c r="G68" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69">
@@ -3105,23 +3105,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPN225</t>
+          <t>GER40</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>1587</v>
+        <v>1380</v>
       </c>
       <c r="D69" t="n">
-        <v>49.8</v>
+        <v>48.3</v>
       </c>
       <c r="E69" t="n">
-        <v>50.2</v>
+        <v>51.7</v>
       </c>
       <c r="F69" t="n">
-        <v>64.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G69" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="H69" t="b">
         <v>1</v>
@@ -3135,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70">
@@ -3144,23 +3144,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USA100</t>
+          <t>JPN225</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1616</v>
+        <v>1579</v>
       </c>
       <c r="D70" t="n">
-        <v>52.4</v>
+        <v>50.1</v>
       </c>
       <c r="E70" t="n">
-        <v>47.6</v>
+        <v>49.9</v>
       </c>
       <c r="F70" t="n">
-        <v>64.7</v>
+        <v>65</v>
       </c>
       <c r="G70" t="n">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="H70" t="b">
         <v>1</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71">
@@ -3183,23 +3183,23 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GER40</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1380</v>
+        <v>1592</v>
       </c>
       <c r="D71" t="n">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="E71" t="n">
-        <v>52.5</v>
+        <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>64.8</v>
+        <v>65.2</v>
       </c>
       <c r="G71" t="n">
-        <v>14.8</v>
+        <v>15.2</v>
       </c>
       <c r="H71" t="b">
         <v>1</v>
@@ -3222,17 +3222,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>USA500</t>
+          <t>AUS200</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1636</v>
+        <v>1391</v>
       </c>
       <c r="D72" t="n">
-        <v>50.9</v>
+        <v>48.2</v>
       </c>
       <c r="E72" t="n">
-        <v>49.1</v>
+        <v>51.8</v>
       </c>
       <c r="F72" t="n">
         <v>65.59999999999999</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73">
@@ -3261,23 +3261,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AUS200</t>
+          <t>USA500</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>1389</v>
+        <v>1630</v>
       </c>
       <c r="D73" t="n">
-        <v>48.2</v>
+        <v>51.1</v>
       </c>
       <c r="E73" t="n">
-        <v>51.8</v>
+        <v>48.9</v>
       </c>
       <c r="F73" t="n">
-        <v>65.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>15.8</v>
+        <v>15.6</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -3291,7 +3291,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74">
@@ -3304,19 +3304,19 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="D74" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="E74" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="F74" t="n">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="G74" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="H74" t="b">
         <v>1</v>
@@ -3343,19 +3343,19 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="D75" t="n">
-        <v>49.6</v>
+        <v>50.1</v>
       </c>
       <c r="E75" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="F75" t="n">
-        <v>53.1</v>
+        <v>52.7</v>
       </c>
       <c r="G75" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="H75" t="b">
         <v>1</v>
@@ -3369,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
@@ -3382,19 +3382,19 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="D76" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E76" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>54.6</v>
+        <v>53.8</v>
       </c>
       <c r="G76" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="H76" t="b">
         <v>1</v>
@@ -3408,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
@@ -3421,19 +3421,19 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="D77" t="n">
-        <v>49.2</v>
+        <v>48.5</v>
       </c>
       <c r="E77" t="n">
-        <v>50.8</v>
+        <v>51.5</v>
       </c>
       <c r="F77" t="n">
-        <v>56.5</v>
+        <v>55.8</v>
       </c>
       <c r="G77" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="H77" t="b">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -3460,19 +3460,19 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="D78" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E78" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="F78" t="n">
-        <v>70.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="G78" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="H78" t="b">
         <v>1</v>
@@ -3499,19 +3499,19 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>645</v>
+        <v>680</v>
       </c>
       <c r="D79" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="E79" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="F79" t="n">
-        <v>63.1</v>
+        <v>63.5</v>
       </c>
       <c r="G79" t="n">
-        <v>13.1</v>
+        <v>13.5</v>
       </c>
       <c r="H79" t="b">
         <v>1</v>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="80">
@@ -3538,19 +3538,19 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="D80" t="n">
-        <v>46.9</v>
+        <v>47.1</v>
       </c>
       <c r="E80" t="n">
-        <v>53.1</v>
+        <v>52.9</v>
       </c>
       <c r="F80" t="n">
-        <v>63.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>13.6</v>
+        <v>14.1</v>
       </c>
       <c r="H80" t="b">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="81">
@@ -3577,19 +3577,19 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1269</v>
+        <v>1288</v>
       </c>
       <c r="D81" t="n">
-        <v>47.1</v>
+        <v>47.2</v>
       </c>
       <c r="E81" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="F81" t="n">
-        <v>65</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="H81" t="b">
         <v>1</v>
@@ -3603,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82">
@@ -3612,23 +3612,23 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="D82" t="n">
-        <v>47.1</v>
+        <v>46.8</v>
       </c>
       <c r="E82" t="n">
-        <v>52.9</v>
+        <v>53.2</v>
       </c>
       <c r="F82" t="n">
-        <v>51</v>
+        <v>51.3</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H82" t="b">
         <v>1</v>
@@ -3651,23 +3651,23 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D83" t="n">
-        <v>47.5</v>
+        <v>46.2</v>
       </c>
       <c r="E83" t="n">
-        <v>52.5</v>
+        <v>53.8</v>
       </c>
       <c r="F83" t="n">
-        <v>51.5</v>
+        <v>53</v>
       </c>
       <c r="G83" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H83" t="b">
         <v>1</v>
@@ -3681,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="84">
@@ -3694,19 +3694,19 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D84" t="n">
-        <v>49.8</v>
+        <v>49.4</v>
       </c>
       <c r="E84" t="n">
-        <v>50.2</v>
+        <v>50.6</v>
       </c>
       <c r="F84" t="n">
-        <v>47.6</v>
+        <v>46.8</v>
       </c>
       <c r="G84" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="H84" t="b">
         <v>1</v>
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85">
@@ -3736,10 +3736,10 @@
         <v>432</v>
       </c>
       <c r="D85" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="E85" t="n">
-        <v>50.9</v>
+        <v>51.2</v>
       </c>
       <c r="F85" t="n">
         <v>54.6</v>
@@ -3775,16 +3775,16 @@
         <v>418</v>
       </c>
       <c r="D86" t="n">
-        <v>45.9</v>
+        <v>46.2</v>
       </c>
       <c r="E86" t="n">
-        <v>54.1</v>
+        <v>53.8</v>
       </c>
       <c r="F86" t="n">
-        <v>57.2</v>
+        <v>57.9</v>
       </c>
       <c r="G86" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="H86" t="b">
         <v>1</v>
@@ -3798,7 +3798,7 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
@@ -3814,16 +3814,16 @@
         <v>430</v>
       </c>
       <c r="D87" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="E87" t="n">
-        <v>55.6</v>
+        <v>56</v>
       </c>
       <c r="F87" t="n">
-        <v>57.7</v>
+        <v>57.9</v>
       </c>
       <c r="G87" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="H87" t="b">
         <v>1</v>
@@ -3837,7 +3837,7 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88">
@@ -3850,19 +3850,19 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D88" t="n">
-        <v>50.4</v>
+        <v>50.2</v>
       </c>
       <c r="E88" t="n">
-        <v>49.6</v>
+        <v>49.8</v>
       </c>
       <c r="F88" t="n">
-        <v>62.5</v>
+        <v>62.9</v>
       </c>
       <c r="G88" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="H88" t="b">
         <v>1</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="89">
@@ -3892,16 +3892,16 @@
         <v>418</v>
       </c>
       <c r="D89" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="E89" t="n">
-        <v>50.7</v>
+        <v>50.5</v>
       </c>
       <c r="F89" t="n">
-        <v>62.9</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="G89" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="H89" t="b">
         <v>1</v>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90">
@@ -3931,10 +3931,10 @@
         <v>442</v>
       </c>
       <c r="D90" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="E90" t="n">
-        <v>46.8</v>
+        <v>47.1</v>
       </c>
       <c r="F90" t="n">
         <v>64.7</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="91">
@@ -3970,16 +3970,16 @@
         <v>437</v>
       </c>
       <c r="D91" t="n">
-        <v>49.9</v>
+        <v>50.3</v>
       </c>
       <c r="E91" t="n">
-        <v>50.1</v>
+        <v>49.7</v>
       </c>
       <c r="F91" t="n">
-        <v>65</v>
+        <v>65.2</v>
       </c>
       <c r="G91" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="H91" t="b">
         <v>1</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92">
@@ -4006,19 +4006,19 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D92" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="E92" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="F92" t="n">
-        <v>65.40000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="G92" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="H92" t="b">
         <v>1</v>
@@ -4032,7 +4032,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
@@ -4045,19 +4045,19 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D93" t="n">
-        <v>47.5</v>
+        <v>47.9</v>
       </c>
       <c r="E93" t="n">
-        <v>52.5</v>
+        <v>52.1</v>
       </c>
       <c r="F93" t="n">
-        <v>70.8</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="G93" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="H93" t="b">
         <v>1</v>
@@ -4084,19 +4084,19 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="D94" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>49.8</v>
       </c>
       <c r="F94" t="n">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
       <c r="G94" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H94" t="b">
         <v>1</v>
@@ -4110,7 +4110,7 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="95">
@@ -4123,19 +4123,19 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="D95" t="n">
-        <v>50.9</v>
+        <v>51.1</v>
       </c>
       <c r="E95" t="n">
-        <v>49.1</v>
+        <v>48.9</v>
       </c>
       <c r="F95" t="n">
-        <v>56.4</v>
+        <v>56.7</v>
       </c>
       <c r="G95" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H95" t="b">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="96">
@@ -4162,13 +4162,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>1608</v>
+        <v>1602</v>
       </c>
       <c r="D96" t="n">
-        <v>50.2</v>
+        <v>50.4</v>
       </c>
       <c r="E96" t="n">
-        <v>49.8</v>
+        <v>49.6</v>
       </c>
       <c r="F96" t="n">
         <v>57</v>
@@ -4201,19 +4201,19 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="D97" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="E97" t="n">
-        <v>47.3</v>
+        <v>47.4</v>
       </c>
       <c r="F97" t="n">
-        <v>57.9</v>
+        <v>57.3</v>
       </c>
       <c r="G97" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="H97" t="b">
         <v>1</v>
@@ -4227,7 +4227,7 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98">
@@ -4240,19 +4240,19 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="D98" t="n">
-        <v>50.1</v>
+        <v>50.3</v>
       </c>
       <c r="E98" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="F98" t="n">
-        <v>58.2</v>
+        <v>58.5</v>
       </c>
       <c r="G98" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="H98" t="b">
         <v>1</v>
@@ -4279,19 +4279,19 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>1625</v>
+        <v>1618</v>
       </c>
       <c r="D99" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="E99" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="F99" t="n">
-        <v>58.9</v>
+        <v>59</v>
       </c>
       <c r="G99" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="H99" t="b">
         <v>1</v>
@@ -4305,7 +4305,7 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="100">
@@ -4318,19 +4318,19 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1621</v>
+        <v>1615</v>
       </c>
       <c r="D100" t="n">
-        <v>50.8</v>
+        <v>50.5</v>
       </c>
       <c r="E100" t="n">
-        <v>49.2</v>
+        <v>49.5</v>
       </c>
       <c r="F100" t="n">
-        <v>59.1</v>
+        <v>59.2</v>
       </c>
       <c r="G100" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H100" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101">
@@ -4353,23 +4353,23 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#ETHUSD</t>
+          <t>#ADAUSD</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1625</v>
+        <v>1568</v>
       </c>
       <c r="D101" t="n">
-        <v>50.3</v>
+        <v>51.3</v>
       </c>
       <c r="E101" t="n">
-        <v>49.7</v>
+        <v>48.7</v>
       </c>
       <c r="F101" t="n">
-        <v>59.7</v>
+        <v>60</v>
       </c>
       <c r="G101" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="H101" t="b">
         <v>1</v>
@@ -4392,23 +4392,23 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#ADAUSD</t>
+          <t>#ETHUSD</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1572</v>
+        <v>1618</v>
       </c>
       <c r="D102" t="n">
-        <v>51.7</v>
+        <v>50.4</v>
       </c>
       <c r="E102" t="n">
-        <v>48.3</v>
+        <v>49.6</v>
       </c>
       <c r="F102" t="n">
-        <v>59.9</v>
+        <v>60.1</v>
       </c>
       <c r="G102" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="H102" t="b">
         <v>1</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1602</v>
+        <v>1595</v>
       </c>
       <c r="D103" t="n">
         <v>50.6</v>
@@ -4444,10 +4444,10 @@
         <v>49.4</v>
       </c>
       <c r="F103" t="n">
-        <v>60.4</v>
+        <v>60.9</v>
       </c>
       <c r="G103" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="H103" t="b">
         <v>1</v>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4545,13 +4545,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>38686</v>
+        <v>38767</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>50.1</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F2" t="n">
         <v>49.7</v>
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38218</v>
+        <v>38299</v>
       </c>
       <c r="D3" t="n">
         <v>49.1</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38405</v>
+        <v>38490</v>
       </c>
       <c r="D4" t="n">
         <v>50</v>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38975</v>
+        <v>39060</v>
       </c>
       <c r="D5" t="n">
         <v>51.1</v>
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>39031</v>
+        <v>39116</v>
       </c>
       <c r="D6" t="n">
         <v>50.7</v>
@@ -4740,7 +4740,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39037</v>
+        <v>39122</v>
       </c>
       <c r="D7" t="n">
         <v>51.4</v>
@@ -4779,7 +4779,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38886</v>
+        <v>38971</v>
       </c>
       <c r="D8" t="n">
         <v>50.7</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>38406</v>
+        <v>38490</v>
       </c>
       <c r="D9" t="n">
         <v>49.7</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>38855</v>
+        <v>38939</v>
       </c>
       <c r="D10" t="n">
         <v>49.5</v>
@@ -4896,7 +4896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38920</v>
+        <v>39005</v>
       </c>
       <c r="D11" t="n">
         <v>50.1</v>
@@ -4905,10 +4905,10 @@
         <v>49.9</v>
       </c>
       <c r="F11" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="G11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
@@ -4922,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -4935,13 +4935,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>38998</v>
+        <v>39086</v>
       </c>
       <c r="D12" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E12" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="F12" t="n">
         <v>41.7</v>
@@ -4974,7 +4974,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>38791</v>
+        <v>38878</v>
       </c>
       <c r="D13" t="n">
         <v>50.3</v>
@@ -5013,7 +5013,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>38745</v>
+        <v>38832</v>
       </c>
       <c r="D14" t="n">
         <v>50.1</v>
@@ -5039,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -5048,23 +5048,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GBPUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38892</v>
+        <v>38958</v>
       </c>
       <c r="D15" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="E15" t="n">
-        <v>50.3</v>
+        <v>50.5</v>
       </c>
       <c r="F15" t="n">
-        <v>60.8</v>
+        <v>60.9</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
@@ -5087,17 +5087,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>GBPUSD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>38876</v>
+        <v>38974</v>
       </c>
       <c r="D16" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="E16" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="F16" t="n">
         <v>60.9</v>
@@ -5130,7 +5130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>38966</v>
+        <v>39050</v>
       </c>
       <c r="D17" t="n">
         <v>47.2</v>
@@ -5169,7 +5169,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8247</v>
+        <v>8264</v>
       </c>
       <c r="D18" t="n">
         <v>51.2</v>
@@ -5208,7 +5208,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38641</v>
+        <v>38725</v>
       </c>
       <c r="D19" t="n">
         <v>50</v>
@@ -5217,10 +5217,10 @@
         <v>50</v>
       </c>
       <c r="F19" t="n">
-        <v>50.6</v>
+        <v>50.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
@@ -5234,7 +5234,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -5247,7 +5247,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>38132</v>
+        <v>38211</v>
       </c>
       <c r="D20" t="n">
         <v>50.8</v>
@@ -5273,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>38803</v>
+        <v>38887</v>
       </c>
       <c r="D21" t="n">
         <v>51.7</v>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>35379</v>
+        <v>35456</v>
       </c>
       <c r="D22" t="n">
         <v>49.8</v>
@@ -5334,10 +5334,10 @@
         <v>50.2</v>
       </c>
       <c r="F22" t="n">
-        <v>47.6</v>
+        <v>47.7</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
@@ -5364,7 +5364,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>38969</v>
+        <v>39054</v>
       </c>
       <c r="D23" t="n">
         <v>49.7</v>
@@ -5403,7 +5403,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>38701</v>
+        <v>38783</v>
       </c>
       <c r="D24" t="n">
         <v>49.7</v>
@@ -5442,7 +5442,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38741</v>
+        <v>38824</v>
       </c>
       <c r="D25" t="n">
         <v>49</v>
@@ -5481,7 +5481,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38967</v>
+        <v>39052</v>
       </c>
       <c r="D26" t="n">
         <v>49.2</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>38661</v>
+        <v>38743</v>
       </c>
       <c r="D27" t="n">
         <v>50.4</v>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>38304</v>
+        <v>38382</v>
       </c>
       <c r="D28" t="n">
         <v>49.4</v>
@@ -5598,7 +5598,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>38466</v>
+        <v>38551</v>
       </c>
       <c r="D29" t="n">
         <v>50.1</v>
@@ -5624,7 +5624,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
@@ -5637,7 +5637,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>38846</v>
+        <v>38930</v>
       </c>
       <c r="D30" t="n">
         <v>50.6</v>
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31">
@@ -5672,20 +5672,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>GBPNZD</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>38880</v>
+        <v>39117</v>
       </c>
       <c r="D31" t="n">
-        <v>51.1</v>
+        <v>49.5</v>
       </c>
       <c r="E31" t="n">
-        <v>48.9</v>
+        <v>50.5</v>
       </c>
       <c r="F31" t="n">
-        <v>55.2</v>
+        <v>44.8</v>
       </c>
       <c r="G31" t="n">
         <v>5.2</v>
@@ -5711,23 +5711,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GBPNZD</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>39032</v>
+        <v>38965</v>
       </c>
       <c r="D32" t="n">
-        <v>49.5</v>
+        <v>51.1</v>
       </c>
       <c r="E32" t="n">
-        <v>50.5</v>
+        <v>48.9</v>
       </c>
       <c r="F32" t="n">
-        <v>44.8</v>
+        <v>55.3</v>
       </c>
       <c r="G32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>39003</v>
+        <v>39088</v>
       </c>
       <c r="D33" t="n">
         <v>49.4</v>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>39009</v>
+        <v>39093</v>
       </c>
       <c r="D34" t="n">
         <v>49.2</v>
@@ -5832,7 +5832,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>38967</v>
+        <v>39051</v>
       </c>
       <c r="D35" t="n">
         <v>48.9</v>
@@ -5841,10 +5841,10 @@
         <v>51.1</v>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>43.9</v>
       </c>
       <c r="G35" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
@@ -5871,7 +5871,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>39261</v>
+        <v>39346</v>
       </c>
       <c r="D36" t="n">
         <v>49.1</v>
@@ -5910,7 +5910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39253</v>
+        <v>39338</v>
       </c>
       <c r="D37" t="n">
         <v>49.1</v>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>36237</v>
+        <v>36317</v>
       </c>
       <c r="D38" t="n">
         <v>50.3</v>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>35494</v>
+        <v>35571</v>
       </c>
       <c r="D39" t="n">
         <v>50</v>
@@ -6027,13 +6027,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>38586</v>
+        <v>38669</v>
       </c>
       <c r="D40" t="n">
-        <v>50.3</v>
+        <v>50.2</v>
       </c>
       <c r="E40" t="n">
-        <v>49.7</v>
+        <v>49.8</v>
       </c>
       <c r="F40" t="n">
         <v>58.4</v>
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>38724</v>
+        <v>38808</v>
       </c>
       <c r="D41" t="n">
         <v>49.4</v>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38769</v>
+        <v>38853</v>
       </c>
       <c r="D42" t="n">
         <v>50</v>
@@ -6144,7 +6144,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>39170</v>
+        <v>39255</v>
       </c>
       <c r="D43" t="n">
         <v>50</v>
@@ -6183,7 +6183,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>39228</v>
+        <v>39313</v>
       </c>
       <c r="D44" t="n">
         <v>49.2</v>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>39269</v>
+        <v>39357</v>
       </c>
       <c r="D45" t="n">
         <v>49.5</v>
@@ -6248,7 +6248,7 @@
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46">
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>39027</v>
+        <v>39111</v>
       </c>
       <c r="D46" t="n">
         <v>49.6</v>
@@ -6270,10 +6270,10 @@
         <v>50.4</v>
       </c>
       <c r="F46" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="G46" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
@@ -6287,7 +6287,7 @@
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47">
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>38980</v>
+        <v>39065</v>
       </c>
       <c r="D47" t="n">
         <v>49.6</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>39168</v>
+        <v>39252</v>
       </c>
       <c r="D48" t="n">
         <v>49.9</v>
@@ -6378,13 +6378,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>35324</v>
+        <v>35401</v>
       </c>
       <c r="D49" t="n">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="E49" t="n">
-        <v>49.8</v>
+        <v>49.9</v>
       </c>
       <c r="F49" t="n">
         <v>39.4</v>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>38637</v>
+        <v>38721</v>
       </c>
       <c r="D50" t="n">
         <v>49.5</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>38670</v>
+        <v>38755</v>
       </c>
       <c r="D51" t="n">
         <v>49.9</v>
@@ -6495,7 +6495,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38630</v>
+        <v>38712</v>
       </c>
       <c r="D52" t="n">
         <v>50.3</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>39099</v>
+        <v>39184</v>
       </c>
       <c r="D53" t="n">
         <v>49.1</v>
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>37079</v>
+        <v>37161</v>
       </c>
       <c r="D54" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="E54" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="F54" t="n">
         <v>32.6</v>
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38861</v>
+        <v>38946</v>
       </c>
       <c r="D55" t="n">
         <v>50.1</v>
@@ -6651,7 +6651,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>38562</v>
+        <v>38647</v>
       </c>
       <c r="D56" t="n">
         <v>50.9</v>
@@ -6660,10 +6660,10 @@
         <v>49.1</v>
       </c>
       <c r="F56" t="n">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="H56" t="b">
         <v>1</v>
@@ -6690,7 +6690,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>38927</v>
+        <v>39012</v>
       </c>
       <c r="D57" t="n">
         <v>51</v>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>39010</v>
+        <v>39095</v>
       </c>
       <c r="D58" t="n">
         <v>51.4</v>
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>39213</v>
+        <v>39298</v>
       </c>
       <c r="D59" t="n">
         <v>51.3</v>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>37558</v>
+        <v>37642</v>
       </c>
       <c r="D60" t="n">
         <v>50.4</v>
@@ -6816,10 +6816,10 @@
         <v>49.6</v>
       </c>
       <c r="F60" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="G60" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H60" t="b">
         <v>1</v>
@@ -6833,7 +6833,7 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>35604</v>
+        <v>35685</v>
       </c>
       <c r="D61" t="n">
         <v>50.8</v>
@@ -6855,10 +6855,10 @@
         <v>49.2</v>
       </c>
       <c r="F61" t="n">
-        <v>49.4</v>
+        <v>49.3</v>
       </c>
       <c r="G61" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H61" t="b">
         <v>1</v>
@@ -6872,7 +6872,7 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>23715</v>
+        <v>23768</v>
       </c>
       <c r="D62" t="n">
         <v>50.9</v>
@@ -6911,7 +6911,7 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63">
@@ -6924,7 +6924,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>38016</v>
+        <v>38099</v>
       </c>
       <c r="D63" t="n">
         <v>50.8</v>
@@ -6950,7 +6950,7 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64">
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24134</v>
+        <v>24185</v>
       </c>
       <c r="D64" t="n">
         <v>50.8</v>
@@ -7002,7 +7002,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>24161</v>
+        <v>24213</v>
       </c>
       <c r="D65" t="n">
         <v>50.9</v>
@@ -7028,7 +7028,7 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66">
@@ -7041,7 +7041,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>38915</v>
+        <v>38999</v>
       </c>
       <c r="D66" t="n">
         <v>51.2</v>
@@ -7067,7 +7067,7 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -7076,17 +7076,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SPA35</t>
+          <t>USA30</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>21553</v>
+        <v>38501</v>
       </c>
       <c r="D67" t="n">
-        <v>51.8</v>
+        <v>50.6</v>
       </c>
       <c r="E67" t="n">
-        <v>48.2</v>
+        <v>49.4</v>
       </c>
       <c r="F67" t="n">
         <v>56.2</v>
@@ -7115,23 +7115,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USA30</t>
+          <t>SPA35</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>38416</v>
+        <v>21606</v>
       </c>
       <c r="D68" t="n">
-        <v>50.6</v>
+        <v>51.8</v>
       </c>
       <c r="E68" t="n">
-        <v>49.4</v>
+        <v>48.2</v>
       </c>
       <c r="F68" t="n">
-        <v>56.2</v>
+        <v>56.3</v>
       </c>
       <c r="G68" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H68" t="b">
         <v>1</v>
@@ -7145,7 +7145,7 @@
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69">
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>36667</v>
+        <v>36751</v>
       </c>
       <c r="D69" t="n">
         <v>50.4</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>31006</v>
+        <v>31079</v>
       </c>
       <c r="D70" t="n">
         <v>50.8</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>38081</v>
+        <v>38164</v>
       </c>
       <c r="D71" t="n">
         <v>51.1</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33482</v>
+        <v>33558</v>
       </c>
       <c r="D72" t="n">
         <v>50.2</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>26418</v>
+        <v>26479</v>
       </c>
       <c r="D73" t="n">
         <v>50.1</v>
@@ -7323,10 +7323,10 @@
         <v>49.9</v>
       </c>
       <c r="F73" t="n">
-        <v>59.3</v>
+        <v>59.4</v>
       </c>
       <c r="G73" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H73" t="b">
         <v>1</v>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>14408</v>
+        <v>14443</v>
       </c>
       <c r="D74" t="n">
         <v>50.1</v>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>14213</v>
+        <v>14247</v>
       </c>
       <c r="D75" t="n">
         <v>49.6</v>
@@ -7431,7 +7431,7 @@
         </is>
       <